--- a/Formatos/Visita 3 GFPI-F023.xlsx
+++ b/Formatos/Visita 3 GFPI-F023.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SEANT\OneDrive\Documents\Seto 2026\sena\Manual SENA Etapa Productiva\manual-general-aprendiz\Formatos\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SEANT\OneDrive\Documents\Seto 2026\sena\Manual SENA Etapa Productiva\manual-aprendiz-sena\Formatos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61CA67F1-A72B-4316-AEFD-42E7FDD3D7E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{156D0CC8-6B14-4058-B52B-497D59C7198D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{BC3553EE-4E49-4F2A-B03E-CFAC4EB3009B}"/>
   </bookViews>
@@ -16,7 +16,8 @@
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_Hlk197527663" localSheetId="0">Hoja1!$B$72</definedName>
+    <definedName name="_Hlk197527663" localSheetId="0">Hoja1!$B$71</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Hoja1!$A$1:$M$81</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="80">
   <si>
     <t>Información general</t>
   </si>
@@ -120,6 +121,12 @@
   </si>
   <si>
     <t>Nombre:</t>
+  </si>
+  <si>
+    <t>Sergio Andrés Torres Martínez</t>
+  </si>
+  <si>
+    <t>satorres@sena.edu.co</t>
   </si>
   <si>
     <t xml:space="preserve">Datos del ente co-formador </t>
@@ -372,9 +379,6 @@
     </r>
   </si>
   <si>
-    <t>El momento 3 – Evaluación se llevó a cabo en la Ciudad____________ y fecha de diligenciamiento: ___/___/____ de forma presencial ___ o virtual ___</t>
-  </si>
-  <si>
     <t>Fecha inicio etapa productiva: (DD/MM/AA)</t>
   </si>
   <si>
@@ -391,7 +395,10 @@
     <t>Número de visitas realizadas en toda la etapa productiva:</t>
   </si>
   <si>
-    <t>Nombre instructor</t>
+    <t>.</t>
+  </si>
+  <si>
+    <t>El momento 5 – Evaluación se llevó a cabo en la Ciudad____________ y fecha de diligenciamiento: ___/___/____ de forma presencial ___ o virtual ___</t>
   </si>
 </sst>
 </file>
@@ -549,7 +556,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="25">
+  <borders count="24">
     <border>
       <left/>
       <right/>
@@ -814,15 +821,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="slantDashDot">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
@@ -841,7 +839,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="157">
+  <cellXfs count="152">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
@@ -879,7 +877,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -900,7 +897,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -908,7 +905,7 @@
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -957,15 +954,15 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -975,15 +972,15 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="justify" vertical="center"/>
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="justify" vertical="center"/>
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="justify" vertical="center"/>
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1001,15 +998,15 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="justify" vertical="center"/>
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="justify" vertical="center"/>
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="justify" vertical="center"/>
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1058,15 +1055,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1119,15 +1116,15 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1274,24 +1271,15 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
@@ -1359,16 +1347,12 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="7">
+  <dxfs count="9">
     <dxf>
       <fill>
         <patternFill>
@@ -1380,6 +1364,20 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFEEEC9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1435,61 +1433,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>205468</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>93378</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>202482</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>835478</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Imagen 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{90A089CB-121C-48D4-83D4-E6331B0FBE74}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="4777468" y="93378"/>
-          <a:ext cx="759014" cy="742100"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1812,7 +1755,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O108"/>
+  <dimension ref="A1:O141"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="15" zeroHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.5703125" customWidth="1"/>
@@ -1824,570 +1767,575 @@
     <col min="11" max="11" width="7.5703125" customWidth="1"/>
     <col min="12" max="12" width="3.7109375" customWidth="1"/>
     <col min="13" max="13" width="13.28515625" customWidth="1"/>
+    <col min="14" max="15" width="0" hidden="1" customWidth="1"/>
     <col min="16" max="16384" width="11.42578125" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="68.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="13"/>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
-      <c r="I1" s="13"/>
-      <c r="J1" s="13"/>
-      <c r="K1" s="13"/>
-      <c r="L1" s="13"/>
-      <c r="M1" s="13"/>
-    </row>
-    <row r="2" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="116" t="s">
+    <row r="1" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="115" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="117"/>
-      <c r="C2" s="117"/>
-      <c r="D2" s="117"/>
-      <c r="E2" s="117"/>
-      <c r="F2" s="117"/>
-      <c r="G2" s="117"/>
-      <c r="H2" s="117"/>
-      <c r="I2" s="117"/>
-      <c r="J2" s="117"/>
-      <c r="K2" s="117"/>
-      <c r="L2" s="117"/>
-      <c r="M2" s="117"/>
-    </row>
-    <row r="3" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="26" t="s">
+      <c r="B1" s="116"/>
+      <c r="C1" s="116"/>
+      <c r="D1" s="116"/>
+      <c r="E1" s="116"/>
+      <c r="F1" s="116"/>
+      <c r="G1" s="116"/>
+      <c r="H1" s="116"/>
+      <c r="I1" s="116"/>
+      <c r="J1" s="116"/>
+      <c r="K1" s="116"/>
+      <c r="L1" s="116"/>
+      <c r="M1" s="116"/>
+    </row>
+    <row r="2" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="27"/>
-      <c r="C3" s="103" t="s">
+      <c r="B2" s="26"/>
+      <c r="C2" s="102" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="115"/>
-      <c r="E3" s="115"/>
-      <c r="F3" s="115"/>
-      <c r="G3" s="115"/>
-      <c r="H3" s="115"/>
-      <c r="I3" s="115"/>
-      <c r="J3" s="115"/>
-      <c r="K3" s="115"/>
-      <c r="L3" s="115"/>
-      <c r="M3" s="104"/>
-    </row>
-    <row r="4" spans="1:13" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="26" t="s">
+      <c r="D2" s="114"/>
+      <c r="E2" s="114"/>
+      <c r="F2" s="114"/>
+      <c r="G2" s="114"/>
+      <c r="H2" s="114"/>
+      <c r="I2" s="114"/>
+      <c r="J2" s="114"/>
+      <c r="K2" s="114"/>
+      <c r="L2" s="114"/>
+      <c r="M2" s="103"/>
+    </row>
+    <row r="3" spans="1:13" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="27"/>
-      <c r="C4" s="87" t="s">
+      <c r="B3" s="26"/>
+      <c r="C3" s="86" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="88"/>
-      <c r="E4" s="88"/>
-      <c r="F4" s="88"/>
-      <c r="G4" s="89"/>
-      <c r="H4" s="1" t="s">
+      <c r="D3" s="87"/>
+      <c r="E3" s="87"/>
+      <c r="F3" s="87"/>
+      <c r="G3" s="88"/>
+      <c r="H3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="I4" s="132"/>
-      <c r="J4" s="133"/>
-      <c r="K4" s="133"/>
-      <c r="L4" s="133"/>
-      <c r="M4" s="134"/>
+      <c r="I3" s="83"/>
+      <c r="J3" s="84"/>
+      <c r="K3" s="84"/>
+      <c r="L3" s="84"/>
+      <c r="M3" s="85"/>
+    </row>
+    <row r="4" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="26"/>
+      <c r="C4" s="99"/>
+      <c r="D4" s="100"/>
+      <c r="E4" s="100"/>
+      <c r="F4" s="100"/>
+      <c r="G4" s="100"/>
+      <c r="H4" s="101"/>
+      <c r="I4" s="52" t="s">
+        <v>7</v>
+      </c>
+      <c r="J4" s="53"/>
+      <c r="K4" s="117"/>
+      <c r="L4" s="118"/>
+      <c r="M4" s="119"/>
     </row>
     <row r="5" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="26" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="27"/>
-      <c r="C5" s="100"/>
-      <c r="D5" s="101"/>
-      <c r="E5" s="101"/>
-      <c r="F5" s="101"/>
-      <c r="G5" s="101"/>
-      <c r="H5" s="102"/>
-      <c r="I5" s="53" t="s">
-        <v>7</v>
-      </c>
-      <c r="J5" s="54"/>
-      <c r="K5" s="118"/>
-      <c r="L5" s="119"/>
-      <c r="M5" s="120"/>
+      <c r="A5" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="26"/>
+      <c r="C5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="102" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="103"/>
+      <c r="F5" s="54" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5" s="56"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="54" t="s">
+        <v>12</v>
+      </c>
+      <c r="J5" s="56"/>
+      <c r="K5" s="120"/>
+      <c r="L5" s="121"/>
+      <c r="M5" s="122"/>
     </row>
     <row r="6" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="26" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="27"/>
-      <c r="C6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6" s="103" t="s">
-        <v>10</v>
-      </c>
-      <c r="E6" s="104"/>
-      <c r="F6" s="55" t="s">
-        <v>11</v>
-      </c>
-      <c r="G6" s="57"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="55" t="s">
-        <v>12</v>
-      </c>
-      <c r="J6" s="57"/>
-      <c r="K6" s="121"/>
-      <c r="L6" s="122"/>
-      <c r="M6" s="123"/>
+      <c r="A6" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="26"/>
+      <c r="C6" s="89"/>
+      <c r="D6" s="90"/>
+      <c r="E6" s="90"/>
+      <c r="F6" s="91"/>
+      <c r="G6" s="89" t="s">
+        <v>14</v>
+      </c>
+      <c r="H6" s="90"/>
+      <c r="I6" s="91"/>
+      <c r="J6" s="117"/>
+      <c r="K6" s="118"/>
+      <c r="L6" s="118"/>
+      <c r="M6" s="119"/>
     </row>
     <row r="7" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="26" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" s="27"/>
-      <c r="C7" s="90"/>
-      <c r="D7" s="91"/>
-      <c r="E7" s="91"/>
-      <c r="F7" s="92"/>
-      <c r="G7" s="90" t="s">
-        <v>14</v>
-      </c>
-      <c r="H7" s="91"/>
-      <c r="I7" s="92"/>
-      <c r="J7" s="118"/>
-      <c r="K7" s="119"/>
-      <c r="L7" s="119"/>
-      <c r="M7" s="120"/>
+      <c r="A7" s="92" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="25" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="95"/>
+      <c r="D7" s="26"/>
+      <c r="E7" s="107"/>
+      <c r="F7" s="108"/>
+      <c r="G7" s="108"/>
+      <c r="H7" s="108"/>
+      <c r="I7" s="108"/>
+      <c r="J7" s="108"/>
+      <c r="K7" s="108"/>
+      <c r="L7" s="108"/>
+      <c r="M7" s="109"/>
     </row>
     <row r="8" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="93" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" s="96"/>
-      <c r="D8" s="27"/>
-      <c r="E8" s="108"/>
-      <c r="F8" s="109"/>
-      <c r="G8" s="109"/>
-      <c r="H8" s="109"/>
-      <c r="I8" s="109"/>
-      <c r="J8" s="109"/>
-      <c r="K8" s="109"/>
-      <c r="L8" s="109"/>
-      <c r="M8" s="110"/>
+      <c r="A8" s="93"/>
+      <c r="B8" s="96" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="97"/>
+      <c r="D8" s="98"/>
+      <c r="E8" s="123"/>
+      <c r="F8" s="124"/>
+      <c r="G8" s="124"/>
+      <c r="H8" s="124"/>
+      <c r="I8" s="124"/>
+      <c r="J8" s="124"/>
+      <c r="K8" s="124"/>
+      <c r="L8" s="124"/>
+      <c r="M8" s="125"/>
     </row>
     <row r="9" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="94"/>
-      <c r="B9" s="97" t="s">
-        <v>17</v>
-      </c>
-      <c r="C9" s="98"/>
-      <c r="D9" s="99"/>
-      <c r="E9" s="124"/>
-      <c r="F9" s="125"/>
-      <c r="G9" s="125"/>
-      <c r="H9" s="125"/>
-      <c r="I9" s="125"/>
-      <c r="J9" s="125"/>
-      <c r="K9" s="125"/>
-      <c r="L9" s="125"/>
-      <c r="M9" s="126"/>
+      <c r="A9" s="93"/>
+      <c r="B9" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="95"/>
+      <c r="D9" s="26"/>
+      <c r="E9" s="107"/>
+      <c r="F9" s="108"/>
+      <c r="G9" s="108"/>
+      <c r="H9" s="108"/>
+      <c r="I9" s="108"/>
+      <c r="J9" s="108"/>
+      <c r="K9" s="108"/>
+      <c r="L9" s="108"/>
+      <c r="M9" s="109"/>
     </row>
     <row r="10" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="94"/>
-      <c r="B10" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="C10" s="96"/>
-      <c r="D10" s="27"/>
-      <c r="E10" s="108"/>
-      <c r="F10" s="109"/>
-      <c r="G10" s="109"/>
-      <c r="H10" s="109"/>
-      <c r="I10" s="109"/>
-      <c r="J10" s="109"/>
-      <c r="K10" s="109"/>
-      <c r="L10" s="109"/>
-      <c r="M10" s="110"/>
+      <c r="A10" s="93"/>
+      <c r="B10" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" s="95"/>
+      <c r="D10" s="26"/>
+      <c r="E10" s="107"/>
+      <c r="F10" s="108"/>
+      <c r="G10" s="108"/>
+      <c r="H10" s="108"/>
+      <c r="I10" s="108"/>
+      <c r="J10" s="108"/>
+      <c r="K10" s="108"/>
+      <c r="L10" s="108"/>
+      <c r="M10" s="109"/>
     </row>
     <row r="11" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="94"/>
-      <c r="B11" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="C11" s="96"/>
-      <c r="D11" s="27"/>
-      <c r="E11" s="108"/>
-      <c r="F11" s="109"/>
-      <c r="G11" s="109"/>
-      <c r="H11" s="109"/>
-      <c r="I11" s="109"/>
-      <c r="J11" s="109"/>
-      <c r="K11" s="109"/>
-      <c r="L11" s="109"/>
-      <c r="M11" s="110"/>
+      <c r="A11" s="93"/>
+      <c r="B11" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11" s="95"/>
+      <c r="D11" s="26"/>
+      <c r="E11" s="107"/>
+      <c r="F11" s="108"/>
+      <c r="G11" s="108"/>
+      <c r="H11" s="108"/>
+      <c r="I11" s="108"/>
+      <c r="J11" s="108"/>
+      <c r="K11" s="108"/>
+      <c r="L11" s="108"/>
+      <c r="M11" s="109"/>
     </row>
     <row r="12" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="94"/>
-      <c r="B12" s="26" t="s">
-        <v>20</v>
-      </c>
-      <c r="C12" s="96"/>
-      <c r="D12" s="27"/>
-      <c r="E12" s="108"/>
-      <c r="F12" s="109"/>
-      <c r="G12" s="109"/>
-      <c r="H12" s="109"/>
-      <c r="I12" s="109"/>
-      <c r="J12" s="109"/>
-      <c r="K12" s="109"/>
-      <c r="L12" s="109"/>
-      <c r="M12" s="110"/>
+      <c r="A12" s="93"/>
+      <c r="B12" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="C12" s="95"/>
+      <c r="D12" s="26"/>
+      <c r="E12" s="107"/>
+      <c r="F12" s="108"/>
+      <c r="G12" s="108"/>
+      <c r="H12" s="108"/>
+      <c r="I12" s="108"/>
+      <c r="J12" s="108"/>
+      <c r="K12" s="108"/>
+      <c r="L12" s="108"/>
+      <c r="M12" s="109"/>
     </row>
     <row r="13" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="94"/>
-      <c r="B13" s="26" t="s">
-        <v>21</v>
-      </c>
-      <c r="C13" s="96"/>
-      <c r="D13" s="27"/>
-      <c r="E13" s="108"/>
-      <c r="F13" s="109"/>
-      <c r="G13" s="109"/>
-      <c r="H13" s="109"/>
-      <c r="I13" s="109"/>
-      <c r="J13" s="109"/>
-      <c r="K13" s="109"/>
-      <c r="L13" s="109"/>
-      <c r="M13" s="110"/>
+      <c r="A13" s="93"/>
+      <c r="B13" s="25" t="s">
+        <v>22</v>
+      </c>
+      <c r="C13" s="95"/>
+      <c r="D13" s="26"/>
+      <c r="E13" s="104"/>
+      <c r="F13" s="105"/>
+      <c r="G13" s="105"/>
+      <c r="H13" s="105"/>
+      <c r="I13" s="105"/>
+      <c r="J13" s="105"/>
+      <c r="K13" s="105"/>
+      <c r="L13" s="105"/>
+      <c r="M13" s="106"/>
     </row>
     <row r="14" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="94"/>
-      <c r="B14" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="C14" s="96"/>
-      <c r="D14" s="27"/>
-      <c r="E14" s="105"/>
-      <c r="F14" s="106"/>
-      <c r="G14" s="106"/>
-      <c r="H14" s="106"/>
-      <c r="I14" s="106"/>
-      <c r="J14" s="106"/>
-      <c r="K14" s="106"/>
-      <c r="L14" s="106"/>
-      <c r="M14" s="107"/>
+      <c r="A14" s="93"/>
+      <c r="B14" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="C14" s="95"/>
+      <c r="D14" s="26"/>
+      <c r="E14" s="104"/>
+      <c r="F14" s="105"/>
+      <c r="G14" s="105"/>
+      <c r="H14" s="105"/>
+      <c r="I14" s="105"/>
+      <c r="J14" s="105"/>
+      <c r="K14" s="105"/>
+      <c r="L14" s="105"/>
+      <c r="M14" s="106"/>
     </row>
     <row r="15" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="94"/>
-      <c r="B15" s="26" t="s">
-        <v>23</v>
-      </c>
-      <c r="C15" s="96"/>
-      <c r="D15" s="27"/>
-      <c r="E15" s="105"/>
-      <c r="F15" s="106"/>
-      <c r="G15" s="106"/>
-      <c r="H15" s="106"/>
-      <c r="I15" s="106"/>
-      <c r="J15" s="106"/>
-      <c r="K15" s="106"/>
-      <c r="L15" s="106"/>
-      <c r="M15" s="107"/>
-    </row>
-    <row r="16" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="95"/>
-      <c r="B16" s="26" t="s">
+      <c r="B15" s="25" t="s">
         <v>24</v>
       </c>
-      <c r="C16" s="96"/>
-      <c r="D16" s="27"/>
-      <c r="E16" s="105"/>
-      <c r="F16" s="106"/>
-      <c r="G16" s="106"/>
-      <c r="H16" s="106"/>
-      <c r="I16" s="106"/>
-      <c r="J16" s="106"/>
-      <c r="K16" s="106"/>
-      <c r="L16" s="106"/>
-      <c r="M16" s="107"/>
-    </row>
-    <row r="17" spans="1:13" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="111" t="s">
+      <c r="C15" s="95"/>
+      <c r="D15" s="26"/>
+      <c r="E15" s="104"/>
+      <c r="F15" s="105"/>
+      <c r="G15" s="105"/>
+      <c r="H15" s="105"/>
+      <c r="I15" s="105"/>
+      <c r="J15" s="105"/>
+      <c r="K15" s="105"/>
+      <c r="L15" s="105"/>
+      <c r="M15" s="106"/>
+    </row>
+    <row r="16" spans="1:13" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="110" t="s">
         <v>25</v>
       </c>
-      <c r="B17" s="26" t="s">
+      <c r="B16" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="C17" s="96"/>
-      <c r="D17" s="27"/>
-      <c r="E17" s="112"/>
-      <c r="F17" s="113"/>
-      <c r="G17" s="113"/>
-      <c r="H17" s="113"/>
-      <c r="I17" s="113"/>
-      <c r="J17" s="113"/>
-      <c r="K17" s="113"/>
-      <c r="L17" s="113"/>
-      <c r="M17" s="114"/>
-    </row>
-    <row r="18" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C16" s="95"/>
+      <c r="D16" s="26"/>
+      <c r="E16" s="111" t="s">
+        <v>27</v>
+      </c>
+      <c r="F16" s="112"/>
+      <c r="G16" s="112"/>
+      <c r="H16" s="112"/>
+      <c r="I16" s="112"/>
+      <c r="J16" s="112"/>
+      <c r="K16" s="112"/>
+      <c r="L16" s="112"/>
+      <c r="M16" s="113"/>
+    </row>
+    <row r="17" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="93"/>
+      <c r="B17" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="C17" s="95"/>
+      <c r="D17" s="26"/>
+      <c r="E17" s="22"/>
+      <c r="F17" s="23"/>
+      <c r="G17" s="23"/>
+      <c r="H17" s="23"/>
+      <c r="I17" s="23"/>
+      <c r="J17" s="23"/>
+      <c r="K17" s="23"/>
+      <c r="L17" s="23"/>
+      <c r="M17" s="24"/>
+    </row>
+    <row r="18" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="94"/>
-      <c r="B18" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="C18" s="96"/>
-      <c r="D18" s="27"/>
-      <c r="E18" s="23"/>
-      <c r="F18" s="24"/>
-      <c r="G18" s="24"/>
-      <c r="H18" s="24"/>
-      <c r="I18" s="24"/>
-      <c r="J18" s="24"/>
-      <c r="K18" s="24"/>
-      <c r="L18" s="24"/>
-      <c r="M18" s="25"/>
-    </row>
-    <row r="19" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="95"/>
-      <c r="B19" s="26" t="s">
+      <c r="B18" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="C19" s="96"/>
-      <c r="D19" s="27"/>
-      <c r="E19" s="112"/>
-      <c r="F19" s="113"/>
-      <c r="G19" s="113"/>
-      <c r="H19" s="113"/>
-      <c r="I19" s="113"/>
-      <c r="J19" s="113"/>
-      <c r="K19" s="113"/>
-      <c r="L19" s="113"/>
-      <c r="M19" s="114"/>
-    </row>
-    <row r="20" spans="1:13" ht="25.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B20" s="26" t="s">
+      <c r="C18" s="95"/>
+      <c r="D18" s="26"/>
+      <c r="E18" s="111" t="s">
+        <v>28</v>
+      </c>
+      <c r="F18" s="112"/>
+      <c r="G18" s="112"/>
+      <c r="H18" s="112"/>
+      <c r="I18" s="112"/>
+      <c r="J18" s="112"/>
+      <c r="K18" s="112"/>
+      <c r="L18" s="112"/>
+      <c r="M18" s="113"/>
+    </row>
+    <row r="19" spans="1:13" ht="25.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B19" s="25" t="s">
+        <v>32</v>
+      </c>
+      <c r="C19" s="95"/>
+      <c r="D19" s="26"/>
+      <c r="E19" s="107"/>
+      <c r="F19" s="108"/>
+      <c r="G19" s="108"/>
+      <c r="H19" s="108"/>
+      <c r="I19" s="108"/>
+      <c r="J19" s="108"/>
+      <c r="K19" s="108"/>
+      <c r="L19" s="108"/>
+      <c r="M19" s="109"/>
+    </row>
+    <row r="20" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="C20" s="96"/>
-      <c r="D20" s="27"/>
-      <c r="E20" s="108"/>
-      <c r="F20" s="109"/>
-      <c r="G20" s="109"/>
-      <c r="H20" s="109"/>
-      <c r="I20" s="109"/>
-      <c r="J20" s="109"/>
-      <c r="K20" s="109"/>
-      <c r="L20" s="109"/>
-      <c r="M20" s="110"/>
-    </row>
-    <row r="21" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="B21" s="26" t="s">
+      <c r="B20" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="C21" s="96"/>
-      <c r="D21" s="27"/>
-      <c r="E21" s="108"/>
-      <c r="F21" s="109"/>
-      <c r="G21" s="109"/>
-      <c r="H21" s="109"/>
-      <c r="I21" s="109"/>
-      <c r="J21" s="109"/>
-      <c r="K21" s="109"/>
-      <c r="L21" s="109"/>
-      <c r="M21" s="110"/>
+      <c r="C20" s="95"/>
+      <c r="D20" s="26"/>
+      <c r="E20" s="107"/>
+      <c r="F20" s="108"/>
+      <c r="G20" s="108"/>
+      <c r="H20" s="108"/>
+      <c r="I20" s="108"/>
+      <c r="J20" s="108"/>
+      <c r="K20" s="108"/>
+      <c r="L20" s="108"/>
+      <c r="M20" s="109"/>
+    </row>
+    <row r="21" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="3"/>
+      <c r="B21" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="C21" s="95"/>
+      <c r="D21" s="26"/>
+      <c r="E21" s="107"/>
+      <c r="F21" s="108"/>
+      <c r="G21" s="108"/>
+      <c r="H21" s="108"/>
+      <c r="I21" s="108"/>
+      <c r="J21" s="108"/>
+      <c r="K21" s="108"/>
+      <c r="L21" s="108"/>
+      <c r="M21" s="109"/>
     </row>
     <row r="22" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="3"/>
-      <c r="B22" s="26" t="s">
+      <c r="B22" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="C22" s="95"/>
+      <c r="D22" s="26"/>
+      <c r="E22" s="107"/>
+      <c r="F22" s="108"/>
+      <c r="G22" s="108"/>
+      <c r="H22" s="108"/>
+      <c r="I22" s="108"/>
+      <c r="J22" s="108"/>
+      <c r="K22" s="108"/>
+      <c r="L22" s="108"/>
+      <c r="M22" s="109"/>
+    </row>
+    <row r="23" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C22" s="96"/>
-      <c r="D22" s="27"/>
-      <c r="E22" s="108"/>
-      <c r="F22" s="109"/>
-      <c r="G22" s="109"/>
-      <c r="H22" s="109"/>
-      <c r="I22" s="109"/>
-      <c r="J22" s="109"/>
-      <c r="K22" s="109"/>
-      <c r="L22" s="109"/>
-      <c r="M22" s="110"/>
-    </row>
-    <row r="23" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="3"/>
-      <c r="B23" s="26" t="s">
-        <v>32</v>
-      </c>
-      <c r="C23" s="96"/>
-      <c r="D23" s="27"/>
-      <c r="E23" s="108"/>
-      <c r="F23" s="109"/>
-      <c r="G23" s="109"/>
-      <c r="H23" s="109"/>
-      <c r="I23" s="109"/>
-      <c r="J23" s="109"/>
-      <c r="K23" s="109"/>
-      <c r="L23" s="109"/>
-      <c r="M23" s="110"/>
-    </row>
-    <row r="24" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="B24" s="26" t="s">
-        <v>33</v>
-      </c>
-      <c r="C24" s="96"/>
-      <c r="D24" s="27"/>
-      <c r="E24" s="108"/>
-      <c r="F24" s="109"/>
-      <c r="G24" s="109"/>
-      <c r="H24" s="109"/>
-      <c r="I24" s="109"/>
-      <c r="J24" s="109"/>
-      <c r="K24" s="109"/>
-      <c r="L24" s="109"/>
-      <c r="M24" s="110"/>
+      <c r="B23" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="C23" s="95"/>
+      <c r="D23" s="26"/>
+      <c r="E23" s="107"/>
+      <c r="F23" s="108"/>
+      <c r="G23" s="108"/>
+      <c r="H23" s="108"/>
+      <c r="I23" s="108"/>
+      <c r="J23" s="108"/>
+      <c r="K23" s="108"/>
+      <c r="L23" s="108"/>
+      <c r="M23" s="109"/>
+    </row>
+    <row r="24" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="6"/>
+      <c r="B24" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="C24" s="95"/>
+      <c r="D24" s="26"/>
+      <c r="E24" s="107"/>
+      <c r="F24" s="108"/>
+      <c r="G24" s="108"/>
+      <c r="H24" s="108"/>
+      <c r="I24" s="108"/>
+      <c r="J24" s="108"/>
+      <c r="K24" s="108"/>
+      <c r="L24" s="108"/>
+      <c r="M24" s="109"/>
     </row>
     <row r="25" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="6"/>
-      <c r="B25" s="26" t="s">
-        <v>34</v>
-      </c>
-      <c r="C25" s="96"/>
-      <c r="D25" s="27"/>
-      <c r="E25" s="108"/>
-      <c r="F25" s="109"/>
-      <c r="G25" s="109"/>
-      <c r="H25" s="109"/>
-      <c r="I25" s="109"/>
-      <c r="J25" s="109"/>
-      <c r="K25" s="109"/>
-      <c r="L25" s="109"/>
-      <c r="M25" s="110"/>
+      <c r="B25" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="C25" s="95"/>
+      <c r="D25" s="26"/>
+      <c r="E25" s="104"/>
+      <c r="F25" s="105"/>
+      <c r="G25" s="105"/>
+      <c r="H25" s="105"/>
+      <c r="I25" s="105"/>
+      <c r="J25" s="105"/>
+      <c r="K25" s="105"/>
+      <c r="L25" s="105"/>
+      <c r="M25" s="106"/>
     </row>
     <row r="26" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="6"/>
-      <c r="B26" s="26" t="s">
+      <c r="B26" s="25" t="s">
+        <v>37</v>
+      </c>
+      <c r="C26" s="95"/>
+      <c r="D26" s="26"/>
+      <c r="E26" s="107"/>
+      <c r="F26" s="108"/>
+      <c r="G26" s="108"/>
+      <c r="H26" s="108"/>
+      <c r="I26" s="108"/>
+      <c r="J26" s="108"/>
+      <c r="K26" s="108"/>
+      <c r="L26" s="108"/>
+      <c r="M26" s="109"/>
+    </row>
+    <row r="27" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="7"/>
+      <c r="B27" s="126" t="s">
+        <v>38</v>
+      </c>
+      <c r="C27" s="127"/>
+      <c r="D27" s="128"/>
+      <c r="E27" s="104"/>
+      <c r="F27" s="105"/>
+      <c r="G27" s="105"/>
+      <c r="H27" s="105"/>
+      <c r="I27" s="105"/>
+      <c r="J27" s="105"/>
+      <c r="K27" s="105"/>
+      <c r="L27" s="105"/>
+      <c r="M27" s="106"/>
+    </row>
+    <row r="28" spans="1:13" ht="25.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="B28" s="149" t="s">
+        <v>41</v>
+      </c>
+      <c r="C28" s="150"/>
+      <c r="D28" s="151"/>
+      <c r="E28" s="104"/>
+      <c r="F28" s="105"/>
+      <c r="G28" s="105"/>
+      <c r="H28" s="105"/>
+      <c r="I28" s="105"/>
+      <c r="J28" s="105"/>
+      <c r="K28" s="105"/>
+      <c r="L28" s="105"/>
+      <c r="M28" s="106"/>
+    </row>
+    <row r="29" spans="1:13" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="B29" s="25" t="s">
+        <v>42</v>
+      </c>
+      <c r="C29" s="95"/>
+      <c r="D29" s="26"/>
+      <c r="E29" s="104"/>
+      <c r="F29" s="105"/>
+      <c r="G29" s="105"/>
+      <c r="H29" s="105"/>
+      <c r="I29" s="105"/>
+      <c r="J29" s="105"/>
+      <c r="K29" s="105"/>
+      <c r="L29" s="105"/>
+      <c r="M29" s="106"/>
+    </row>
+    <row r="30" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="10"/>
+      <c r="B30" s="25" t="s">
         <v>19</v>
       </c>
-      <c r="C26" s="96"/>
-      <c r="D26" s="27"/>
-      <c r="E26" s="105"/>
-      <c r="F26" s="106"/>
-      <c r="G26" s="106"/>
-      <c r="H26" s="106"/>
-      <c r="I26" s="106"/>
-      <c r="J26" s="106"/>
-      <c r="K26" s="106"/>
-      <c r="L26" s="106"/>
-      <c r="M26" s="107"/>
-    </row>
-    <row r="27" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="6"/>
-      <c r="B27" s="26" t="s">
-        <v>35</v>
-      </c>
-      <c r="C27" s="96"/>
-      <c r="D27" s="27"/>
-      <c r="E27" s="108"/>
-      <c r="F27" s="109"/>
-      <c r="G27" s="109"/>
-      <c r="H27" s="109"/>
-      <c r="I27" s="109"/>
-      <c r="J27" s="109"/>
-      <c r="K27" s="109"/>
-      <c r="L27" s="109"/>
-      <c r="M27" s="110"/>
-    </row>
-    <row r="28" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="7"/>
-      <c r="B28" s="127" t="s">
-        <v>36</v>
-      </c>
-      <c r="C28" s="128"/>
-      <c r="D28" s="129"/>
-      <c r="E28" s="105"/>
-      <c r="F28" s="106"/>
-      <c r="G28" s="106"/>
-      <c r="H28" s="106"/>
-      <c r="I28" s="106"/>
-      <c r="J28" s="106"/>
-      <c r="K28" s="106"/>
-      <c r="L28" s="106"/>
-      <c r="M28" s="107"/>
-    </row>
-    <row r="29" spans="1:13" ht="25.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="B29" s="152" t="s">
-        <v>39</v>
-      </c>
-      <c r="C29" s="153"/>
-      <c r="D29" s="154"/>
-      <c r="E29" s="105"/>
-      <c r="F29" s="106"/>
-      <c r="G29" s="106"/>
-      <c r="H29" s="106"/>
-      <c r="I29" s="106"/>
-      <c r="J29" s="106"/>
-      <c r="K29" s="106"/>
-      <c r="L29" s="106"/>
-      <c r="M29" s="107"/>
-    </row>
-    <row r="30" spans="1:13" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="B30" s="26" t="s">
-        <v>40</v>
-      </c>
-      <c r="C30" s="96"/>
-      <c r="D30" s="27"/>
-      <c r="E30" s="105"/>
-      <c r="F30" s="106"/>
-      <c r="G30" s="106"/>
-      <c r="H30" s="106"/>
-      <c r="I30" s="106"/>
-      <c r="J30" s="106"/>
-      <c r="K30" s="106"/>
-      <c r="L30" s="106"/>
-      <c r="M30" s="107"/>
-    </row>
-    <row r="31" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="10"/>
-      <c r="B31" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="C31" s="96"/>
-      <c r="D31" s="27"/>
-      <c r="E31" s="105"/>
-      <c r="F31" s="106"/>
-      <c r="G31" s="106"/>
-      <c r="H31" s="106"/>
-      <c r="I31" s="106"/>
-      <c r="J31" s="106"/>
-      <c r="K31" s="106"/>
-      <c r="L31" s="106"/>
-      <c r="M31" s="107"/>
+      <c r="C30" s="95"/>
+      <c r="D30" s="26"/>
+      <c r="E30" s="104"/>
+      <c r="F30" s="105"/>
+      <c r="G30" s="105"/>
+      <c r="H30" s="105"/>
+      <c r="I30" s="105"/>
+      <c r="J30" s="105"/>
+      <c r="K30" s="105"/>
+      <c r="L30" s="105"/>
+      <c r="M30" s="106"/>
+    </row>
+    <row r="31" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="130" t="s">
+        <v>43</v>
+      </c>
+      <c r="B31" s="130"/>
+      <c r="C31" s="130"/>
+      <c r="D31" s="130"/>
+      <c r="E31" s="130"/>
+      <c r="F31" s="130"/>
+      <c r="G31" s="130"/>
+      <c r="H31" s="130"/>
+      <c r="I31" s="130"/>
+      <c r="J31" s="130"/>
+      <c r="K31" s="130"/>
+      <c r="L31" s="130"/>
+      <c r="M31" s="130"/>
     </row>
     <row r="32" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="130" t="s">
-        <v>41</v>
-      </c>
+      <c r="A32" s="130"/>
       <c r="B32" s="130"/>
       <c r="C32" s="130"/>
       <c r="D32" s="130"/>
@@ -2401,7 +2349,7 @@
       <c r="L32" s="130"/>
       <c r="M32" s="130"/>
     </row>
-    <row r="33" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:13" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="130"/>
       <c r="B33" s="130"/>
       <c r="C33" s="130"/>
@@ -2416,1071 +2364,1051 @@
       <c r="L33" s="130"/>
       <c r="M33" s="130"/>
     </row>
-    <row r="34" spans="1:13" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="130"/>
-      <c r="B34" s="130"/>
-      <c r="C34" s="130"/>
-      <c r="D34" s="130"/>
-      <c r="E34" s="130"/>
-      <c r="F34" s="130"/>
-      <c r="G34" s="130"/>
-      <c r="H34" s="130"/>
-      <c r="I34" s="130"/>
-      <c r="J34" s="130"/>
-      <c r="K34" s="130"/>
-      <c r="L34" s="130"/>
-      <c r="M34" s="130"/>
-    </row>
-    <row r="35" spans="1:13" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="11"/>
-      <c r="B35" s="69" t="s">
-        <v>63</v>
-      </c>
-      <c r="C35" s="69"/>
-      <c r="D35" s="69"/>
-      <c r="E35" s="69"/>
-      <c r="F35" s="69"/>
-      <c r="G35" s="69"/>
-      <c r="H35" s="69"/>
-      <c r="I35" s="69"/>
-      <c r="J35" s="69"/>
-      <c r="K35" s="11"/>
-      <c r="L35" s="11"/>
-      <c r="M35" s="11"/>
-    </row>
-    <row r="36" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B36" s="69" t="s">
-        <v>64</v>
-      </c>
-      <c r="C36" s="69"/>
-      <c r="D36" s="69"/>
-      <c r="E36" s="69"/>
-      <c r="F36" s="69"/>
-      <c r="G36" s="69"/>
-      <c r="H36" s="69"/>
-      <c r="I36" s="69"/>
-      <c r="J36" s="69"/>
-      <c r="L36" s="19"/>
-    </row>
-    <row r="37" spans="1:13" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B37" s="142" t="s">
-        <v>72</v>
-      </c>
-      <c r="C37" s="143"/>
+    <row r="34" spans="1:13" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="11"/>
+      <c r="B34" s="68" t="s">
+        <v>65</v>
+      </c>
+      <c r="C34" s="68"/>
+      <c r="D34" s="68"/>
+      <c r="E34" s="68"/>
+      <c r="F34" s="68"/>
+      <c r="G34" s="68"/>
+      <c r="H34" s="68"/>
+      <c r="I34" s="68"/>
+      <c r="J34" s="68"/>
+      <c r="K34" s="11"/>
+      <c r="L34" s="11"/>
+      <c r="M34" s="11"/>
+    </row>
+    <row r="35" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B35" s="68" t="s">
+        <v>66</v>
+      </c>
+      <c r="C35" s="68"/>
+      <c r="D35" s="68"/>
+      <c r="E35" s="68"/>
+      <c r="F35" s="68"/>
+      <c r="G35" s="68"/>
+      <c r="H35" s="68"/>
+      <c r="I35" s="68"/>
+      <c r="J35" s="68"/>
+      <c r="L35" s="18"/>
+    </row>
+    <row r="36" spans="1:13" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B36" s="139" t="s">
+        <v>73</v>
+      </c>
+      <c r="C36" s="140"/>
+      <c r="D36" s="20"/>
+      <c r="E36" s="72" t="s">
+        <v>76</v>
+      </c>
+      <c r="F36" s="73"/>
+      <c r="G36" s="74"/>
+      <c r="H36" s="75"/>
+      <c r="I36" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="J36" s="19"/>
+    </row>
+    <row r="37" spans="1:13" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B37" s="141" t="s">
+        <v>74</v>
+      </c>
+      <c r="C37" s="142"/>
       <c r="D37" s="21"/>
-      <c r="E37" s="73" t="s">
+      <c r="E37" s="143" t="s">
         <v>75</v>
       </c>
-      <c r="F37" s="74"/>
-      <c r="G37" s="75"/>
-      <c r="H37" s="76"/>
-      <c r="I37" s="18" t="s">
-        <v>76</v>
-      </c>
-      <c r="J37" s="20"/>
-    </row>
-    <row r="38" spans="1:13" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B38" s="144" t="s">
-        <v>73</v>
-      </c>
-      <c r="C38" s="145"/>
-      <c r="D38" s="22"/>
-      <c r="E38" s="146" t="s">
-        <v>74</v>
-      </c>
-      <c r="F38" s="147"/>
-      <c r="G38" s="148"/>
-      <c r="H38" s="149"/>
-      <c r="I38" s="150"/>
-      <c r="J38" s="151"/>
-    </row>
-    <row r="39" spans="1:13" ht="2.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="40" spans="1:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F37" s="144"/>
+      <c r="G37" s="145"/>
+      <c r="H37" s="146" t="s">
+        <v>78</v>
+      </c>
+      <c r="I37" s="147"/>
+      <c r="J37" s="148"/>
+    </row>
+    <row r="38" spans="1:13" ht="2.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="39" spans="1:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="11"/>
+      <c r="B39" s="69" t="s">
+        <v>45</v>
+      </c>
+      <c r="C39" s="70"/>
+      <c r="D39" s="70"/>
+      <c r="E39" s="70"/>
+      <c r="F39" s="70"/>
+      <c r="G39" s="70"/>
+      <c r="H39" s="70"/>
+      <c r="I39" s="70"/>
+      <c r="J39" s="71"/>
+      <c r="K39" s="11"/>
+      <c r="L39" s="11"/>
+      <c r="M39" s="11"/>
+    </row>
+    <row r="40" spans="1:13" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="11"/>
-      <c r="B40" s="70" t="s">
-        <v>43</v>
-      </c>
-      <c r="C40" s="71"/>
-      <c r="D40" s="71"/>
-      <c r="E40" s="71"/>
-      <c r="F40" s="71"/>
-      <c r="G40" s="71"/>
-      <c r="H40" s="71"/>
-      <c r="I40" s="71"/>
-      <c r="J40" s="72"/>
+      <c r="B40" s="50" t="s">
+        <v>46</v>
+      </c>
+      <c r="C40" s="51"/>
+      <c r="D40" s="54" t="s">
+        <v>47</v>
+      </c>
+      <c r="E40" s="55"/>
+      <c r="F40" s="55"/>
+      <c r="G40" s="56"/>
+      <c r="H40" s="57" t="s">
+        <v>48</v>
+      </c>
+      <c r="I40" s="58"/>
+      <c r="J40" s="59"/>
       <c r="K40" s="11"/>
       <c r="L40" s="11"/>
       <c r="M40" s="11"/>
     </row>
     <row r="41" spans="1:13" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="11"/>
-      <c r="B41" s="51" t="s">
-        <v>44</v>
-      </c>
-      <c r="C41" s="52"/>
-      <c r="D41" s="55" t="s">
-        <v>45</v>
-      </c>
-      <c r="E41" s="56"/>
-      <c r="F41" s="56"/>
-      <c r="G41" s="57"/>
-      <c r="H41" s="58" t="s">
-        <v>46</v>
-      </c>
-      <c r="I41" s="59"/>
-      <c r="J41" s="60"/>
+      <c r="B41" s="52"/>
+      <c r="C41" s="53"/>
+      <c r="D41" s="63" t="s">
+        <v>49</v>
+      </c>
+      <c r="E41" s="64"/>
+      <c r="F41" s="63" t="s">
+        <v>50</v>
+      </c>
+      <c r="G41" s="64"/>
+      <c r="H41" s="60"/>
+      <c r="I41" s="61"/>
+      <c r="J41" s="62"/>
       <c r="K41" s="11"/>
       <c r="L41" s="11"/>
       <c r="M41" s="11"/>
     </row>
-    <row r="42" spans="1:13" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="11"/>
-      <c r="B42" s="53"/>
-      <c r="C42" s="54"/>
-      <c r="D42" s="64" t="s">
+    <row r="42" spans="1:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="13"/>
+      <c r="B42" s="31" t="s">
+        <v>51</v>
+      </c>
+      <c r="C42" s="32"/>
+      <c r="D42" s="33"/>
+      <c r="E42" s="34"/>
+      <c r="F42" s="33"/>
+      <c r="G42" s="34"/>
+      <c r="H42" s="65"/>
+      <c r="I42" s="66"/>
+      <c r="J42" s="67"/>
+      <c r="K42" s="13"/>
+      <c r="L42" s="13"/>
+      <c r="M42" s="13"/>
+    </row>
+    <row r="43" spans="1:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="13"/>
+      <c r="B43" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="C43" s="32"/>
+      <c r="D43" s="33"/>
+      <c r="E43" s="34"/>
+      <c r="F43" s="132"/>
+      <c r="G43" s="133"/>
+      <c r="H43" s="40"/>
+      <c r="I43" s="41"/>
+      <c r="J43" s="42"/>
+      <c r="K43" s="13"/>
+      <c r="L43" s="13"/>
+      <c r="M43" s="13"/>
+    </row>
+    <row r="44" spans="1:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="13"/>
+      <c r="B44" s="31" t="s">
+        <v>53</v>
+      </c>
+      <c r="C44" s="32"/>
+      <c r="D44" s="33"/>
+      <c r="E44" s="34"/>
+      <c r="F44" s="33"/>
+      <c r="G44" s="34"/>
+      <c r="H44" s="40"/>
+      <c r="I44" s="41"/>
+      <c r="J44" s="42"/>
+      <c r="K44" s="13"/>
+      <c r="L44" s="13"/>
+      <c r="M44" s="13"/>
+    </row>
+    <row r="45" spans="1:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="13"/>
+      <c r="B45" s="38" t="s">
+        <v>64</v>
+      </c>
+      <c r="C45" s="39"/>
+      <c r="D45" s="81"/>
+      <c r="E45" s="82"/>
+      <c r="F45" s="81"/>
+      <c r="G45" s="82"/>
+      <c r="H45" s="83"/>
+      <c r="I45" s="84"/>
+      <c r="J45" s="85"/>
+      <c r="K45" s="13"/>
+      <c r="L45" s="13"/>
+      <c r="M45" s="13"/>
+    </row>
+    <row r="46" spans="1:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="13"/>
+      <c r="B46" s="31" t="s">
+        <v>54</v>
+      </c>
+      <c r="C46" s="32"/>
+      <c r="D46" s="33"/>
+      <c r="E46" s="34"/>
+      <c r="F46" s="33"/>
+      <c r="G46" s="34"/>
+      <c r="H46" s="35"/>
+      <c r="I46" s="36"/>
+      <c r="J46" s="37"/>
+      <c r="K46" s="13"/>
+      <c r="L46" s="13"/>
+      <c r="M46" s="13"/>
+    </row>
+    <row r="47" spans="1:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="13"/>
+      <c r="B47" s="31" t="s">
+        <v>55</v>
+      </c>
+      <c r="C47" s="32"/>
+      <c r="D47" s="33"/>
+      <c r="E47" s="34"/>
+      <c r="F47" s="33"/>
+      <c r="G47" s="34"/>
+      <c r="H47" s="40"/>
+      <c r="I47" s="41"/>
+      <c r="J47" s="42"/>
+      <c r="K47" s="13"/>
+      <c r="L47" s="13"/>
+      <c r="M47" s="13"/>
+    </row>
+    <row r="48" spans="1:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="13"/>
+      <c r="B48" s="31" t="s">
+        <v>56</v>
+      </c>
+      <c r="C48" s="32"/>
+      <c r="D48" s="33"/>
+      <c r="E48" s="34"/>
+      <c r="F48" s="33"/>
+      <c r="G48" s="34"/>
+      <c r="H48" s="40"/>
+      <c r="I48" s="41"/>
+      <c r="J48" s="42"/>
+      <c r="K48" s="13"/>
+      <c r="L48" s="13"/>
+      <c r="M48" s="13"/>
+    </row>
+    <row r="49" spans="1:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="13"/>
+      <c r="B49" s="43" t="s">
+        <v>57</v>
+      </c>
+      <c r="C49" s="44"/>
+      <c r="D49" s="45"/>
+      <c r="E49" s="46"/>
+      <c r="F49" s="45"/>
+      <c r="G49" s="46"/>
+      <c r="H49" s="47"/>
+      <c r="I49" s="48"/>
+      <c r="J49" s="49"/>
+      <c r="K49" s="13"/>
+      <c r="L49" s="13"/>
+      <c r="M49" s="13"/>
+    </row>
+    <row r="50" spans="1:13" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="13"/>
+      <c r="B50" s="78" t="s">
+        <v>58</v>
+      </c>
+      <c r="C50" s="79"/>
+      <c r="D50" s="79"/>
+      <c r="E50" s="79"/>
+      <c r="F50" s="79"/>
+      <c r="G50" s="79"/>
+      <c r="H50" s="79"/>
+      <c r="I50" s="79"/>
+      <c r="J50" s="80"/>
+      <c r="K50" s="13"/>
+      <c r="L50" s="13"/>
+      <c r="M50" s="13"/>
+    </row>
+    <row r="51" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="13"/>
+      <c r="B51" s="57" t="s">
+        <v>46</v>
+      </c>
+      <c r="C51" s="59"/>
+      <c r="D51" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="E42" s="65"/>
-      <c r="F42" s="64" t="s">
+      <c r="E51" s="23"/>
+      <c r="F51" s="23"/>
+      <c r="G51" s="24"/>
+      <c r="H51" s="57" t="s">
         <v>48</v>
       </c>
-      <c r="G42" s="65"/>
-      <c r="H42" s="61"/>
-      <c r="I42" s="62"/>
-      <c r="J42" s="63"/>
-      <c r="K42" s="11"/>
-      <c r="L42" s="11"/>
-      <c r="M42" s="11"/>
-    </row>
-    <row r="43" spans="1:13" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="14"/>
-      <c r="B43" s="32" t="s">
+      <c r="I51" s="58"/>
+      <c r="J51" s="59"/>
+      <c r="K51" s="13"/>
+      <c r="L51" s="13"/>
+      <c r="M51" s="13"/>
+    </row>
+    <row r="52" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="13"/>
+      <c r="B52" s="60"/>
+      <c r="C52" s="62"/>
+      <c r="D52" s="76" t="s">
         <v>49</v>
       </c>
-      <c r="C43" s="33"/>
-      <c r="D43" s="34"/>
-      <c r="E43" s="35"/>
-      <c r="F43" s="34"/>
-      <c r="G43" s="35"/>
-      <c r="H43" s="66"/>
-      <c r="I43" s="67"/>
-      <c r="J43" s="68"/>
-      <c r="K43" s="14"/>
-      <c r="L43" s="14"/>
-      <c r="M43" s="14"/>
-    </row>
-    <row r="44" spans="1:13" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="14"/>
-      <c r="B44" s="32" t="s">
+      <c r="E52" s="77"/>
+      <c r="F52" s="76" t="s">
         <v>50</v>
       </c>
-      <c r="C44" s="33"/>
-      <c r="D44" s="34"/>
-      <c r="E44" s="35"/>
-      <c r="F44" s="135"/>
-      <c r="G44" s="136"/>
-      <c r="H44" s="41"/>
-      <c r="I44" s="42"/>
-      <c r="J44" s="43"/>
-      <c r="K44" s="14"/>
-      <c r="L44" s="14"/>
-      <c r="M44" s="14"/>
-    </row>
-    <row r="45" spans="1:13" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="14"/>
-      <c r="B45" s="32" t="s">
-        <v>51</v>
-      </c>
-      <c r="C45" s="33"/>
-      <c r="D45" s="34"/>
-      <c r="E45" s="35"/>
-      <c r="F45" s="34"/>
-      <c r="G45" s="35"/>
-      <c r="H45" s="41"/>
-      <c r="I45" s="42"/>
-      <c r="J45" s="43"/>
-      <c r="K45" s="14"/>
-      <c r="L45" s="14"/>
-      <c r="M45" s="14"/>
-    </row>
-    <row r="46" spans="1:13" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="14"/>
-      <c r="B46" s="39" t="s">
+      <c r="G52" s="77"/>
+      <c r="H52" s="60"/>
+      <c r="I52" s="61"/>
+      <c r="J52" s="62"/>
+      <c r="K52" s="13"/>
+      <c r="L52" s="13"/>
+      <c r="M52" s="13"/>
+    </row>
+    <row r="53" spans="1:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="13"/>
+      <c r="B53" s="31" t="s">
+        <v>59</v>
+      </c>
+      <c r="C53" s="32"/>
+      <c r="D53" s="33"/>
+      <c r="E53" s="34"/>
+      <c r="F53" s="33"/>
+      <c r="G53" s="34"/>
+      <c r="H53" s="35"/>
+      <c r="I53" s="36"/>
+      <c r="J53" s="37"/>
+      <c r="K53" s="13"/>
+      <c r="L53" s="13"/>
+      <c r="M53" s="13"/>
+    </row>
+    <row r="54" spans="1:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="13"/>
+      <c r="B54" s="31" t="s">
+        <v>60</v>
+      </c>
+      <c r="C54" s="32"/>
+      <c r="D54" s="33"/>
+      <c r="E54" s="34"/>
+      <c r="F54" s="33"/>
+      <c r="G54" s="34"/>
+      <c r="H54" s="35"/>
+      <c r="I54" s="36"/>
+      <c r="J54" s="37"/>
+      <c r="K54" s="13"/>
+      <c r="L54" s="13"/>
+      <c r="M54" s="13"/>
+    </row>
+    <row r="55" spans="1:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="13"/>
+      <c r="B55" s="31" t="s">
+        <v>61</v>
+      </c>
+      <c r="C55" s="32"/>
+      <c r="D55" s="33"/>
+      <c r="E55" s="34"/>
+      <c r="F55" s="33"/>
+      <c r="G55" s="34"/>
+      <c r="H55" s="35"/>
+      <c r="I55" s="36"/>
+      <c r="J55" s="37"/>
+      <c r="K55" s="13"/>
+      <c r="L55" s="13"/>
+      <c r="M55" s="13"/>
+    </row>
+    <row r="56" spans="1:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="13"/>
+      <c r="B56" s="31" t="s">
         <v>62</v>
       </c>
-      <c r="C46" s="40"/>
-      <c r="D46" s="82"/>
-      <c r="E46" s="83"/>
-      <c r="F46" s="82"/>
-      <c r="G46" s="83"/>
-      <c r="H46" s="84"/>
-      <c r="I46" s="85"/>
-      <c r="J46" s="86"/>
-      <c r="K46" s="14"/>
-      <c r="L46" s="14"/>
-      <c r="M46" s="14"/>
-    </row>
-    <row r="47" spans="1:13" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="14"/>
-      <c r="B47" s="32" t="s">
-        <v>52</v>
-      </c>
-      <c r="C47" s="33"/>
-      <c r="D47" s="34"/>
-      <c r="E47" s="35"/>
-      <c r="F47" s="34"/>
-      <c r="G47" s="35"/>
-      <c r="H47" s="36"/>
-      <c r="I47" s="37"/>
-      <c r="J47" s="38"/>
-      <c r="K47" s="14"/>
-      <c r="L47" s="14"/>
-      <c r="M47" s="14"/>
-    </row>
-    <row r="48" spans="1:13" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="14"/>
-      <c r="B48" s="32" t="s">
-        <v>53</v>
-      </c>
-      <c r="C48" s="33"/>
-      <c r="D48" s="34"/>
-      <c r="E48" s="35"/>
-      <c r="F48" s="34"/>
-      <c r="G48" s="35"/>
-      <c r="H48" s="41"/>
-      <c r="I48" s="42"/>
-      <c r="J48" s="43"/>
-      <c r="K48" s="14"/>
-      <c r="L48" s="14"/>
-      <c r="M48" s="14"/>
-    </row>
-    <row r="49" spans="1:13" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="14"/>
-      <c r="B49" s="32" t="s">
-        <v>54</v>
-      </c>
-      <c r="C49" s="33"/>
-      <c r="D49" s="34"/>
-      <c r="E49" s="35"/>
-      <c r="F49" s="34"/>
-      <c r="G49" s="35"/>
-      <c r="H49" s="41"/>
-      <c r="I49" s="42"/>
-      <c r="J49" s="43"/>
-      <c r="K49" s="14"/>
-      <c r="L49" s="14"/>
-      <c r="M49" s="14"/>
-    </row>
-    <row r="50" spans="1:13" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="14"/>
-      <c r="B50" s="44" t="s">
-        <v>55</v>
-      </c>
-      <c r="C50" s="45"/>
-      <c r="D50" s="46"/>
-      <c r="E50" s="47"/>
-      <c r="F50" s="46"/>
-      <c r="G50" s="47"/>
-      <c r="H50" s="48"/>
-      <c r="I50" s="49"/>
-      <c r="J50" s="50"/>
-      <c r="K50" s="14"/>
-      <c r="L50" s="14"/>
-      <c r="M50" s="14"/>
-    </row>
-    <row r="51" spans="1:13" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="14"/>
-      <c r="B51" s="79" t="s">
-        <v>56</v>
-      </c>
-      <c r="C51" s="80"/>
-      <c r="D51" s="80"/>
-      <c r="E51" s="80"/>
-      <c r="F51" s="80"/>
-      <c r="G51" s="80"/>
-      <c r="H51" s="80"/>
-      <c r="I51" s="80"/>
-      <c r="J51" s="81"/>
-      <c r="K51" s="14"/>
-      <c r="L51" s="14"/>
-      <c r="M51" s="14"/>
-    </row>
-    <row r="52" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="14"/>
-      <c r="B52" s="58" t="s">
+      <c r="C56" s="32"/>
+      <c r="D56" s="33"/>
+      <c r="E56" s="34"/>
+      <c r="F56" s="33"/>
+      <c r="G56" s="34"/>
+      <c r="H56" s="35"/>
+      <c r="I56" s="36"/>
+      <c r="J56" s="37"/>
+      <c r="K56" s="13"/>
+      <c r="L56" s="13"/>
+      <c r="M56" s="13"/>
+    </row>
+    <row r="57" spans="1:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="13"/>
+      <c r="B57" s="31" t="s">
+        <v>63</v>
+      </c>
+      <c r="C57" s="32"/>
+      <c r="D57" s="33"/>
+      <c r="E57" s="34"/>
+      <c r="F57" s="33"/>
+      <c r="G57" s="34"/>
+      <c r="H57" s="35"/>
+      <c r="I57" s="36"/>
+      <c r="J57" s="37"/>
+      <c r="K57" s="13"/>
+      <c r="L57" s="13"/>
+      <c r="M57" s="13"/>
+    </row>
+    <row r="58" spans="1:13" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="13"/>
+      <c r="B58" s="14"/>
+      <c r="C58" s="14"/>
+      <c r="D58" s="15"/>
+      <c r="E58" s="15"/>
+      <c r="F58" s="15"/>
+      <c r="G58" s="15"/>
+      <c r="H58" s="16"/>
+      <c r="I58" s="16"/>
+      <c r="J58" s="16"/>
+      <c r="K58" s="13"/>
+      <c r="L58" s="13"/>
+      <c r="M58" s="13"/>
+    </row>
+    <row r="59" spans="1:13" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="13"/>
+      <c r="B59" s="22" t="s">
+        <v>67</v>
+      </c>
+      <c r="C59" s="23"/>
+      <c r="D59" s="23"/>
+      <c r="E59" s="23"/>
+      <c r="F59" s="23"/>
+      <c r="G59" s="23"/>
+      <c r="H59" s="23"/>
+      <c r="I59" s="23"/>
+      <c r="J59" s="24"/>
+      <c r="K59" s="13"/>
+      <c r="L59" s="13"/>
+      <c r="M59" s="13"/>
+    </row>
+    <row r="60" spans="1:13" ht="72" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="13"/>
+      <c r="B60" s="25" t="s">
+        <v>68</v>
+      </c>
+      <c r="C60" s="26"/>
+      <c r="D60" s="27"/>
+      <c r="E60" s="28"/>
+      <c r="F60" s="28"/>
+      <c r="G60" s="28"/>
+      <c r="H60" s="28"/>
+      <c r="I60" s="28"/>
+      <c r="J60" s="29"/>
+      <c r="K60" s="13"/>
+      <c r="L60" s="13"/>
+      <c r="M60" s="13"/>
+    </row>
+    <row r="61" spans="1:13" ht="72" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="13"/>
+      <c r="B61" s="25" t="s">
+        <v>69</v>
+      </c>
+      <c r="C61" s="26"/>
+      <c r="D61" s="27"/>
+      <c r="E61" s="28"/>
+      <c r="F61" s="28"/>
+      <c r="G61" s="28"/>
+      <c r="H61" s="28"/>
+      <c r="I61" s="28"/>
+      <c r="J61" s="29"/>
+      <c r="K61" s="13"/>
+      <c r="L61" s="13"/>
+      <c r="M61" s="13"/>
+    </row>
+    <row r="62" spans="1:13" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="13"/>
+      <c r="B62" s="14"/>
+      <c r="C62" s="14"/>
+      <c r="D62" s="15"/>
+      <c r="E62" s="15"/>
+      <c r="F62" s="15"/>
+      <c r="G62" s="15"/>
+      <c r="H62" s="16"/>
+      <c r="I62" s="16"/>
+      <c r="J62" s="16"/>
+      <c r="K62" s="13"/>
+      <c r="L62" s="13"/>
+      <c r="M62" s="13"/>
+    </row>
+    <row r="63" spans="1:13" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="13"/>
+      <c r="B63" s="22" t="s">
+        <v>70</v>
+      </c>
+      <c r="C63" s="23"/>
+      <c r="D63" s="23"/>
+      <c r="E63" s="23"/>
+      <c r="F63" s="23"/>
+      <c r="G63" s="23"/>
+      <c r="H63" s="23"/>
+      <c r="I63" s="23"/>
+      <c r="J63" s="24"/>
+      <c r="K63" s="13"/>
+      <c r="L63" s="13"/>
+      <c r="M63" s="13"/>
+    </row>
+    <row r="64" spans="1:13" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="13"/>
+      <c r="B64" s="25" t="s">
+        <v>68</v>
+      </c>
+      <c r="C64" s="26"/>
+      <c r="D64" s="27"/>
+      <c r="E64" s="28"/>
+      <c r="F64" s="28"/>
+      <c r="G64" s="28"/>
+      <c r="H64" s="28"/>
+      <c r="I64" s="28"/>
+      <c r="J64" s="29"/>
+      <c r="K64" s="13"/>
+      <c r="L64" s="13"/>
+      <c r="M64" s="13"/>
+    </row>
+    <row r="65" spans="1:13" ht="72" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="13"/>
+      <c r="B65" s="25" t="s">
+        <v>69</v>
+      </c>
+      <c r="C65" s="26"/>
+      <c r="D65" s="27"/>
+      <c r="E65" s="28"/>
+      <c r="F65" s="28"/>
+      <c r="G65" s="28"/>
+      <c r="H65" s="28"/>
+      <c r="I65" s="28"/>
+      <c r="J65" s="29"/>
+      <c r="K65" s="13"/>
+      <c r="L65" s="13"/>
+      <c r="M65" s="13"/>
+    </row>
+    <row r="66" spans="1:13" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="13"/>
+      <c r="B66" s="14"/>
+      <c r="C66" s="14"/>
+      <c r="D66" s="15"/>
+      <c r="E66" s="15"/>
+      <c r="F66" s="15"/>
+      <c r="G66" s="15"/>
+      <c r="H66" s="16"/>
+      <c r="I66" s="16"/>
+      <c r="J66" s="16"/>
+      <c r="K66" s="13"/>
+      <c r="L66" s="13"/>
+      <c r="M66" s="13"/>
+    </row>
+    <row r="67" spans="1:13" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="13"/>
+      <c r="B67" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="C67" s="23"/>
+      <c r="D67" s="23"/>
+      <c r="E67" s="23"/>
+      <c r="F67" s="23"/>
+      <c r="G67" s="23"/>
+      <c r="H67" s="23"/>
+      <c r="I67" s="23"/>
+      <c r="J67" s="24"/>
+      <c r="K67" s="13"/>
+      <c r="L67" s="13"/>
+      <c r="M67" s="13"/>
+    </row>
+    <row r="68" spans="1:13" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="13"/>
+      <c r="B68" s="25" t="s">
+        <v>68</v>
+      </c>
+      <c r="C68" s="26"/>
+      <c r="D68" s="27"/>
+      <c r="E68" s="28"/>
+      <c r="F68" s="28"/>
+      <c r="G68" s="28"/>
+      <c r="H68" s="28"/>
+      <c r="I68" s="28"/>
+      <c r="J68" s="29"/>
+      <c r="K68" s="13"/>
+      <c r="L68" s="13"/>
+      <c r="M68" s="13"/>
+    </row>
+    <row r="69" spans="1:13" ht="71.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="13"/>
+      <c r="B69" s="25" t="s">
+        <v>69</v>
+      </c>
+      <c r="C69" s="26"/>
+      <c r="D69" s="27"/>
+      <c r="E69" s="28"/>
+      <c r="F69" s="28"/>
+      <c r="G69" s="28"/>
+      <c r="H69" s="28"/>
+      <c r="I69" s="28"/>
+      <c r="J69" s="29"/>
+      <c r="K69" s="13"/>
+      <c r="L69" s="13"/>
+      <c r="M69" s="13"/>
+    </row>
+    <row r="70" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="13"/>
+      <c r="B70" s="14"/>
+      <c r="C70" s="14"/>
+      <c r="D70" s="15"/>
+      <c r="E70" s="15"/>
+      <c r="F70" s="15"/>
+      <c r="G70" s="15"/>
+      <c r="H70" s="16"/>
+      <c r="I70" s="16"/>
+      <c r="J70" s="16"/>
+      <c r="K70" s="13"/>
+      <c r="L70" s="13"/>
+      <c r="M70" s="13"/>
+    </row>
+    <row r="71" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="13"/>
+      <c r="B71" s="30" t="s">
+        <v>72</v>
+      </c>
+      <c r="C71" s="30"/>
+      <c r="D71" s="30"/>
+      <c r="E71" s="30"/>
+      <c r="F71" s="30"/>
+      <c r="G71" s="30"/>
+      <c r="H71" s="30"/>
+      <c r="I71" s="30"/>
+      <c r="J71" s="30"/>
+      <c r="K71" s="13"/>
+      <c r="L71" s="13"/>
+      <c r="M71" s="13"/>
+    </row>
+    <row r="72" spans="1:13" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="11"/>
+      <c r="B72" s="12"/>
+      <c r="C72" s="12"/>
+      <c r="D72" s="12"/>
+      <c r="E72" s="12"/>
+      <c r="F72" s="12"/>
+      <c r="G72" s="12"/>
+      <c r="H72" s="12"/>
+      <c r="I72" s="12"/>
+      <c r="J72" s="12"/>
+      <c r="K72" s="11"/>
+      <c r="L72" s="11"/>
+      <c r="M72" s="11"/>
+    </row>
+    <row r="73" spans="1:13" ht="48.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A73" s="137"/>
+      <c r="B73" s="137"/>
+      <c r="C73" s="137"/>
+      <c r="D73" s="137"/>
+      <c r="E73" s="135"/>
+      <c r="F73" s="135"/>
+      <c r="G73" s="137"/>
+      <c r="H73" s="137"/>
+      <c r="I73" s="135"/>
+      <c r="J73" s="135"/>
+      <c r="K73" s="137"/>
+      <c r="L73" s="137"/>
+      <c r="M73" s="137"/>
+    </row>
+    <row r="74" spans="1:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A74" s="137"/>
+      <c r="B74" s="137"/>
+      <c r="C74" s="137"/>
+      <c r="D74" s="137"/>
+      <c r="E74" s="135"/>
+      <c r="F74" s="135"/>
+      <c r="G74" s="137"/>
+      <c r="H74" s="137"/>
+      <c r="I74" s="135"/>
+      <c r="J74" s="135"/>
+      <c r="K74" s="137"/>
+      <c r="L74" s="137"/>
+      <c r="M74" s="137"/>
+    </row>
+    <row r="75" spans="1:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="137"/>
+      <c r="B75" s="137"/>
+      <c r="C75" s="137"/>
+      <c r="D75" s="137"/>
+      <c r="E75" s="135"/>
+      <c r="F75" s="135"/>
+      <c r="G75" s="137"/>
+      <c r="H75" s="137"/>
+      <c r="I75" s="135"/>
+      <c r="J75" s="135"/>
+      <c r="K75" s="137"/>
+      <c r="L75" s="137"/>
+      <c r="M75" s="137"/>
+    </row>
+    <row r="76" spans="1:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A76" s="137"/>
+      <c r="B76" s="137"/>
+      <c r="C76" s="137"/>
+      <c r="D76" s="137"/>
+      <c r="E76" s="135"/>
+      <c r="F76" s="135"/>
+      <c r="G76" s="137"/>
+      <c r="H76" s="137"/>
+      <c r="I76" s="135"/>
+      <c r="J76" s="135"/>
+      <c r="K76" s="137"/>
+      <c r="L76" s="137"/>
+      <c r="M76" s="137"/>
+    </row>
+    <row r="77" spans="1:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A77" s="138"/>
+      <c r="B77" s="138"/>
+      <c r="C77" s="138"/>
+      <c r="D77" s="138"/>
+      <c r="E77" s="135"/>
+      <c r="F77" s="135"/>
+      <c r="G77" s="138"/>
+      <c r="H77" s="138"/>
+      <c r="I77" s="135"/>
+      <c r="J77" s="135"/>
+      <c r="K77" s="138"/>
+      <c r="L77" s="138"/>
+      <c r="M77" s="138"/>
+    </row>
+    <row r="78" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="134"/>
+      <c r="B78" s="134"/>
+      <c r="C78" s="134"/>
+      <c r="D78" s="134"/>
+      <c r="E78" s="135"/>
+      <c r="F78" s="135"/>
+      <c r="G78" s="136" t="s">
+        <v>27</v>
+      </c>
+      <c r="H78" s="136"/>
+      <c r="I78" s="135"/>
+      <c r="J78" s="135"/>
+      <c r="K78" s="134"/>
+      <c r="L78" s="134"/>
+      <c r="M78" s="134"/>
+    </row>
+    <row r="79" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A79" s="12"/>
+      <c r="B79" s="12"/>
+      <c r="C79" s="12"/>
+      <c r="D79" s="12"/>
+      <c r="E79" s="12"/>
+      <c r="F79" s="12"/>
+      <c r="G79" s="12"/>
+      <c r="H79" s="12"/>
+      <c r="I79" s="12"/>
+      <c r="J79" s="12"/>
+      <c r="K79" s="12"/>
+      <c r="L79" s="12"/>
+      <c r="M79" s="12"/>
+    </row>
+    <row r="80" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A80" s="131" t="s">
+        <v>79</v>
+      </c>
+      <c r="B80" s="131"/>
+      <c r="C80" s="131"/>
+      <c r="D80" s="131"/>
+      <c r="E80" s="131"/>
+      <c r="F80" s="131"/>
+      <c r="G80" s="131"/>
+      <c r="H80" s="131"/>
+      <c r="I80" s="131"/>
+      <c r="J80" s="131"/>
+      <c r="K80" s="131"/>
+      <c r="L80" s="131"/>
+      <c r="M80" s="131"/>
+    </row>
+    <row r="81" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F81" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="C52" s="60"/>
-      <c r="D52" s="23" t="s">
-        <v>45</v>
-      </c>
-      <c r="E52" s="24"/>
-      <c r="F52" s="24"/>
-      <c r="G52" s="25"/>
-      <c r="H52" s="58" t="s">
-        <v>46</v>
-      </c>
-      <c r="I52" s="59"/>
-      <c r="J52" s="60"/>
-      <c r="K52" s="14"/>
-      <c r="L52" s="14"/>
-      <c r="M52" s="14"/>
-    </row>
-    <row r="53" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="14"/>
-      <c r="B53" s="61"/>
-      <c r="C53" s="63"/>
-      <c r="D53" s="77" t="s">
-        <v>47</v>
-      </c>
-      <c r="E53" s="78"/>
-      <c r="F53" s="77" t="s">
-        <v>48</v>
-      </c>
-      <c r="G53" s="78"/>
-      <c r="H53" s="61"/>
-      <c r="I53" s="62"/>
-      <c r="J53" s="63"/>
-      <c r="K53" s="14"/>
-      <c r="L53" s="14"/>
-      <c r="M53" s="14"/>
-    </row>
-    <row r="54" spans="1:13" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="14"/>
-      <c r="B54" s="32" t="s">
-        <v>57</v>
-      </c>
-      <c r="C54" s="33"/>
-      <c r="D54" s="34"/>
-      <c r="E54" s="35"/>
-      <c r="F54" s="34"/>
-      <c r="G54" s="35"/>
-      <c r="H54" s="36"/>
-      <c r="I54" s="37"/>
-      <c r="J54" s="38"/>
-      <c r="K54" s="14"/>
-      <c r="L54" s="14"/>
-      <c r="M54" s="14"/>
-    </row>
-    <row r="55" spans="1:13" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="14"/>
-      <c r="B55" s="32" t="s">
-        <v>58</v>
-      </c>
-      <c r="C55" s="33"/>
-      <c r="D55" s="34"/>
-      <c r="E55" s="35"/>
-      <c r="F55" s="34"/>
-      <c r="G55" s="35"/>
-      <c r="H55" s="36"/>
-      <c r="I55" s="37"/>
-      <c r="J55" s="38"/>
-      <c r="K55" s="14"/>
-      <c r="L55" s="14"/>
-      <c r="M55" s="14"/>
-    </row>
-    <row r="56" spans="1:13" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="14"/>
-      <c r="B56" s="32" t="s">
-        <v>59</v>
-      </c>
-      <c r="C56" s="33"/>
-      <c r="D56" s="34"/>
-      <c r="E56" s="35"/>
-      <c r="F56" s="34"/>
-      <c r="G56" s="35"/>
-      <c r="H56" s="36"/>
-      <c r="I56" s="37"/>
-      <c r="J56" s="38"/>
-      <c r="K56" s="14"/>
-      <c r="L56" s="14"/>
-      <c r="M56" s="14"/>
-    </row>
-    <row r="57" spans="1:13" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="14"/>
-      <c r="B57" s="32" t="s">
-        <v>60</v>
-      </c>
-      <c r="C57" s="33"/>
-      <c r="D57" s="34"/>
-      <c r="E57" s="35"/>
-      <c r="F57" s="34"/>
-      <c r="G57" s="35"/>
-      <c r="H57" s="36"/>
-      <c r="I57" s="37"/>
-      <c r="J57" s="38"/>
-      <c r="K57" s="14"/>
-      <c r="L57" s="14"/>
-      <c r="M57" s="14"/>
-    </row>
-    <row r="58" spans="1:13" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="14"/>
-      <c r="B58" s="32" t="s">
-        <v>61</v>
-      </c>
-      <c r="C58" s="33"/>
-      <c r="D58" s="34"/>
-      <c r="E58" s="35"/>
-      <c r="F58" s="34"/>
-      <c r="G58" s="35"/>
-      <c r="H58" s="36"/>
-      <c r="I58" s="37"/>
-      <c r="J58" s="38"/>
-      <c r="K58" s="14"/>
-      <c r="L58" s="14"/>
-      <c r="M58" s="14"/>
-    </row>
-    <row r="59" spans="1:13" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="14"/>
-      <c r="B59" s="15"/>
-      <c r="C59" s="15"/>
-      <c r="D59" s="16"/>
-      <c r="E59" s="16"/>
-      <c r="F59" s="16"/>
-      <c r="G59" s="16"/>
-      <c r="H59" s="17"/>
-      <c r="I59" s="17"/>
-      <c r="J59" s="17"/>
-      <c r="K59" s="14"/>
-      <c r="L59" s="14"/>
-      <c r="M59" s="14"/>
-    </row>
-    <row r="60" spans="1:13" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="14"/>
-      <c r="B60" s="23" t="s">
-        <v>65</v>
-      </c>
-      <c r="C60" s="24"/>
-      <c r="D60" s="24"/>
-      <c r="E60" s="24"/>
-      <c r="F60" s="24"/>
-      <c r="G60" s="24"/>
-      <c r="H60" s="24"/>
-      <c r="I60" s="24"/>
-      <c r="J60" s="25"/>
-      <c r="K60" s="14"/>
-      <c r="L60" s="14"/>
-      <c r="M60" s="14"/>
-    </row>
-    <row r="61" spans="1:13" ht="72" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="14"/>
-      <c r="B61" s="26" t="s">
-        <v>66</v>
-      </c>
-      <c r="C61" s="27"/>
-      <c r="D61" s="28"/>
-      <c r="E61" s="29"/>
-      <c r="F61" s="29"/>
-      <c r="G61" s="29"/>
-      <c r="H61" s="29"/>
-      <c r="I61" s="29"/>
-      <c r="J61" s="30"/>
-      <c r="K61" s="14"/>
-      <c r="L61" s="14"/>
-      <c r="M61" s="14"/>
-    </row>
-    <row r="62" spans="1:13" ht="72" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="14"/>
-      <c r="B62" s="26" t="s">
-        <v>67</v>
-      </c>
-      <c r="C62" s="27"/>
-      <c r="D62" s="28"/>
-      <c r="E62" s="29"/>
-      <c r="F62" s="29"/>
-      <c r="G62" s="29"/>
-      <c r="H62" s="29"/>
-      <c r="I62" s="29"/>
-      <c r="J62" s="30"/>
-      <c r="K62" s="14"/>
-      <c r="L62" s="14"/>
-      <c r="M62" s="14"/>
-    </row>
-    <row r="63" spans="1:13" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="14"/>
-      <c r="B63" s="15"/>
-      <c r="C63" s="15"/>
-      <c r="D63" s="16"/>
-      <c r="E63" s="16"/>
-      <c r="F63" s="16"/>
-      <c r="G63" s="16"/>
-      <c r="H63" s="17"/>
-      <c r="I63" s="17"/>
-      <c r="J63" s="17"/>
-      <c r="K63" s="14"/>
-      <c r="L63" s="14"/>
-      <c r="M63" s="14"/>
-    </row>
-    <row r="64" spans="1:13" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="14"/>
-      <c r="B64" s="23" t="s">
-        <v>68</v>
-      </c>
-      <c r="C64" s="24"/>
-      <c r="D64" s="24"/>
-      <c r="E64" s="24"/>
-      <c r="F64" s="24"/>
-      <c r="G64" s="24"/>
-      <c r="H64" s="24"/>
-      <c r="I64" s="24"/>
-      <c r="J64" s="25"/>
-      <c r="K64" s="14"/>
-      <c r="L64" s="14"/>
-      <c r="M64" s="14"/>
-    </row>
-    <row r="65" spans="1:13" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="14"/>
-      <c r="B65" s="26" t="s">
-        <v>66</v>
-      </c>
-      <c r="C65" s="27"/>
-      <c r="D65" s="28"/>
-      <c r="E65" s="29"/>
-      <c r="F65" s="29"/>
-      <c r="G65" s="29"/>
-      <c r="H65" s="29"/>
-      <c r="I65" s="29"/>
-      <c r="J65" s="30"/>
-      <c r="K65" s="14"/>
-      <c r="L65" s="14"/>
-      <c r="M65" s="14"/>
-    </row>
-    <row r="66" spans="1:13" ht="72" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="14"/>
-      <c r="B66" s="26" t="s">
-        <v>67</v>
-      </c>
-      <c r="C66" s="27"/>
-      <c r="D66" s="28"/>
-      <c r="E66" s="29"/>
-      <c r="F66" s="29"/>
-      <c r="G66" s="29"/>
-      <c r="H66" s="29"/>
-      <c r="I66" s="29"/>
-      <c r="J66" s="30"/>
-      <c r="K66" s="14"/>
-      <c r="L66" s="14"/>
-      <c r="M66" s="14"/>
-    </row>
-    <row r="67" spans="1:13" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="14"/>
-      <c r="B67" s="15"/>
-      <c r="C67" s="15"/>
-      <c r="D67" s="16"/>
-      <c r="E67" s="16"/>
-      <c r="F67" s="16"/>
-      <c r="G67" s="16"/>
-      <c r="H67" s="17"/>
-      <c r="I67" s="17"/>
-      <c r="J67" s="17"/>
-      <c r="K67" s="14"/>
-      <c r="L67" s="14"/>
-      <c r="M67" s="14"/>
-    </row>
-    <row r="68" spans="1:13" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="14"/>
-      <c r="B68" s="23" t="s">
-        <v>69</v>
-      </c>
-      <c r="C68" s="24"/>
-      <c r="D68" s="24"/>
-      <c r="E68" s="24"/>
-      <c r="F68" s="24"/>
-      <c r="G68" s="24"/>
-      <c r="H68" s="24"/>
-      <c r="I68" s="24"/>
-      <c r="J68" s="25"/>
-      <c r="K68" s="14"/>
-      <c r="L68" s="14"/>
-      <c r="M68" s="14"/>
-    </row>
-    <row r="69" spans="1:13" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="14"/>
-      <c r="B69" s="26" t="s">
-        <v>66</v>
-      </c>
-      <c r="C69" s="27"/>
-      <c r="D69" s="28"/>
-      <c r="E69" s="29"/>
-      <c r="F69" s="29"/>
-      <c r="G69" s="29"/>
-      <c r="H69" s="29"/>
-      <c r="I69" s="29"/>
-      <c r="J69" s="30"/>
-      <c r="K69" s="14"/>
-      <c r="L69" s="14"/>
-      <c r="M69" s="14"/>
-    </row>
-    <row r="70" spans="1:13" ht="71.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="14"/>
-      <c r="B70" s="26" t="s">
-        <v>67</v>
-      </c>
-      <c r="C70" s="27"/>
-      <c r="D70" s="28"/>
-      <c r="E70" s="29"/>
-      <c r="F70" s="29"/>
-      <c r="G70" s="29"/>
-      <c r="H70" s="29"/>
-      <c r="I70" s="29"/>
-      <c r="J70" s="30"/>
-      <c r="K70" s="14"/>
-      <c r="L70" s="14"/>
-      <c r="M70" s="14"/>
-    </row>
-    <row r="71" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="14"/>
-      <c r="B71" s="15"/>
-      <c r="C71" s="15"/>
-      <c r="D71" s="16"/>
-      <c r="E71" s="16"/>
-      <c r="F71" s="16"/>
-      <c r="G71" s="16"/>
-      <c r="H71" s="17"/>
-      <c r="I71" s="17"/>
-      <c r="J71" s="17"/>
-      <c r="K71" s="14"/>
-      <c r="L71" s="14"/>
-      <c r="M71" s="14"/>
-    </row>
-    <row r="72" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="14"/>
-      <c r="B72" s="31" t="s">
-        <v>70</v>
-      </c>
-      <c r="C72" s="31"/>
-      <c r="D72" s="31"/>
-      <c r="E72" s="31"/>
-      <c r="F72" s="31"/>
-      <c r="G72" s="31"/>
-      <c r="H72" s="31"/>
-      <c r="I72" s="31"/>
-      <c r="J72" s="31"/>
-      <c r="K72" s="14"/>
-      <c r="L72" s="14"/>
-      <c r="M72" s="14"/>
-    </row>
-    <row r="73" spans="1:13" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="11"/>
-      <c r="B73" s="12"/>
-      <c r="C73" s="12"/>
-      <c r="D73" s="12"/>
-      <c r="E73" s="12"/>
-      <c r="F73" s="12"/>
-      <c r="G73" s="12"/>
-      <c r="H73" s="12"/>
-      <c r="I73" s="12"/>
-      <c r="J73" s="12"/>
-      <c r="K73" s="11"/>
-      <c r="L73" s="11"/>
-      <c r="M73" s="11"/>
-    </row>
-    <row r="74" spans="1:13" ht="48.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="140"/>
-      <c r="B74" s="140"/>
-      <c r="C74" s="140"/>
-      <c r="D74" s="140"/>
-      <c r="E74" s="138"/>
-      <c r="F74" s="138"/>
-      <c r="G74" s="140"/>
-      <c r="H74" s="140"/>
-      <c r="I74" s="138"/>
-      <c r="J74" s="138"/>
-      <c r="K74" s="140"/>
-      <c r="L74" s="140"/>
-      <c r="M74" s="140"/>
-    </row>
-    <row r="75" spans="1:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="140"/>
-      <c r="B75" s="140"/>
-      <c r="C75" s="140"/>
-      <c r="D75" s="140"/>
-      <c r="E75" s="138"/>
-      <c r="F75" s="138"/>
-      <c r="G75" s="140"/>
-      <c r="H75" s="140"/>
-      <c r="I75" s="138"/>
-      <c r="J75" s="138"/>
-      <c r="K75" s="140"/>
-      <c r="L75" s="140"/>
-      <c r="M75" s="140"/>
-    </row>
-    <row r="76" spans="1:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="140"/>
-      <c r="B76" s="140"/>
-      <c r="C76" s="140"/>
-      <c r="D76" s="140"/>
-      <c r="E76" s="138"/>
-      <c r="F76" s="138"/>
-      <c r="G76" s="140"/>
-      <c r="H76" s="140"/>
-      <c r="I76" s="138"/>
-      <c r="J76" s="138"/>
-      <c r="K76" s="140"/>
-      <c r="L76" s="140"/>
-      <c r="M76" s="140"/>
-    </row>
-    <row r="77" spans="1:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="140"/>
-      <c r="B77" s="140"/>
-      <c r="C77" s="140"/>
-      <c r="D77" s="140"/>
-      <c r="E77" s="138"/>
-      <c r="F77" s="138"/>
-      <c r="G77" s="140"/>
-      <c r="H77" s="140"/>
-      <c r="I77" s="138"/>
-      <c r="J77" s="138"/>
-      <c r="K77" s="140"/>
-      <c r="L77" s="140"/>
-      <c r="M77" s="140"/>
-    </row>
-    <row r="78" spans="1:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="141"/>
-      <c r="B78" s="141"/>
-      <c r="C78" s="141"/>
-      <c r="D78" s="141"/>
-      <c r="E78" s="138"/>
-      <c r="F78" s="138"/>
-      <c r="G78" s="141"/>
-      <c r="H78" s="141"/>
-      <c r="I78" s="138"/>
-      <c r="J78" s="138"/>
-      <c r="K78" s="141"/>
-      <c r="L78" s="141"/>
-      <c r="M78" s="141"/>
-    </row>
-    <row r="79" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="137"/>
-      <c r="B79" s="137"/>
-      <c r="C79" s="137"/>
-      <c r="D79" s="137"/>
-      <c r="E79" s="138"/>
-      <c r="F79" s="138"/>
-      <c r="G79" s="139" t="s">
-        <v>77</v>
-      </c>
-      <c r="H79" s="139"/>
-      <c r="I79" s="138"/>
-      <c r="J79" s="138"/>
-      <c r="K79" s="137"/>
-      <c r="L79" s="137"/>
-      <c r="M79" s="137"/>
-    </row>
-    <row r="80" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A80" s="12"/>
-      <c r="B80" s="12"/>
-      <c r="C80" s="12"/>
-      <c r="D80" s="12"/>
-      <c r="E80" s="12"/>
-      <c r="F80" s="12"/>
-      <c r="G80" s="12"/>
-      <c r="H80" s="12"/>
-      <c r="I80" s="12"/>
-      <c r="J80" s="12"/>
-      <c r="K80" s="12"/>
-      <c r="L80" s="12"/>
-      <c r="M80" s="12"/>
-    </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A81" s="131" t="s">
-        <v>71</v>
-      </c>
-      <c r="B81" s="131"/>
-      <c r="C81" s="131"/>
-      <c r="D81" s="131"/>
-      <c r="E81" s="131"/>
-      <c r="F81" s="131"/>
-      <c r="G81" s="131"/>
-      <c r="H81" s="131"/>
-      <c r="I81" s="131"/>
-      <c r="J81" s="131"/>
-      <c r="K81" s="131"/>
-      <c r="L81" s="131"/>
-      <c r="M81" s="131"/>
-    </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A82" s="155"/>
-      <c r="B82" s="155"/>
-      <c r="C82" s="155"/>
-      <c r="D82" s="155"/>
-      <c r="E82" s="155"/>
-      <c r="F82" s="156" t="s">
-        <v>42</v>
-      </c>
-      <c r="G82" s="156"/>
-      <c r="H82" s="155"/>
-      <c r="I82" s="155"/>
-      <c r="J82" s="155"/>
-      <c r="K82" s="155"/>
-      <c r="L82" s="155"/>
-      <c r="M82" s="155"/>
-    </row>
-    <row r="91" spans="1:13" ht="24" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="95" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="96" spans="1:13" ht="24" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="97" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="98" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="108" ht="24" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="G81" s="129"/>
+    </row>
+    <row r="141" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="170">
-    <mergeCell ref="F82:G82"/>
-    <mergeCell ref="A32:M34"/>
-    <mergeCell ref="A81:M81"/>
-    <mergeCell ref="I4:M4"/>
-    <mergeCell ref="B64:J64"/>
-    <mergeCell ref="F44:G44"/>
-    <mergeCell ref="A79:D79"/>
-    <mergeCell ref="E79:F79"/>
-    <mergeCell ref="G79:H79"/>
-    <mergeCell ref="I79:J79"/>
-    <mergeCell ref="K79:M79"/>
-    <mergeCell ref="A74:D78"/>
-    <mergeCell ref="E74:F78"/>
-    <mergeCell ref="G74:H78"/>
-    <mergeCell ref="I74:J78"/>
-    <mergeCell ref="K74:M78"/>
+    <mergeCell ref="F81:G81"/>
+    <mergeCell ref="A31:M33"/>
+    <mergeCell ref="A80:M80"/>
+    <mergeCell ref="I3:M3"/>
+    <mergeCell ref="B63:J63"/>
+    <mergeCell ref="F43:G43"/>
+    <mergeCell ref="A78:D78"/>
+    <mergeCell ref="E78:F78"/>
+    <mergeCell ref="G78:H78"/>
+    <mergeCell ref="I78:J78"/>
+    <mergeCell ref="K78:M78"/>
+    <mergeCell ref="A73:D77"/>
+    <mergeCell ref="E73:F77"/>
+    <mergeCell ref="G73:H77"/>
+    <mergeCell ref="I73:J77"/>
+    <mergeCell ref="K73:M77"/>
+    <mergeCell ref="B36:C36"/>
     <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="E38:G38"/>
-    <mergeCell ref="H38:J38"/>
+    <mergeCell ref="E37:G37"/>
+    <mergeCell ref="H37:J37"/>
+    <mergeCell ref="B28:D28"/>
     <mergeCell ref="B29:D29"/>
     <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="E28:M28"/>
     <mergeCell ref="E29:M29"/>
     <mergeCell ref="E30:M30"/>
-    <mergeCell ref="E31:M31"/>
-    <mergeCell ref="C3:M3"/>
-    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="C2:M2"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="E7:M7"/>
+    <mergeCell ref="K4:M4"/>
+    <mergeCell ref="K5:M5"/>
+    <mergeCell ref="J6:M6"/>
     <mergeCell ref="E8:M8"/>
-    <mergeCell ref="K5:M5"/>
-    <mergeCell ref="K6:M6"/>
-    <mergeCell ref="J7:M7"/>
     <mergeCell ref="E9:M9"/>
-    <mergeCell ref="E10:M10"/>
+    <mergeCell ref="B25:D25"/>
     <mergeCell ref="B26:D26"/>
     <mergeCell ref="B27:D27"/>
-    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="E25:M25"/>
     <mergeCell ref="E26:M26"/>
     <mergeCell ref="E27:M27"/>
-    <mergeCell ref="E28:M28"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="B23:D23"/>
     <mergeCell ref="B24:D24"/>
-    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="E22:M22"/>
     <mergeCell ref="E23:M23"/>
     <mergeCell ref="E24:M24"/>
-    <mergeCell ref="E25:M25"/>
+    <mergeCell ref="B19:D19"/>
     <mergeCell ref="B20:D20"/>
     <mergeCell ref="B21:D21"/>
-    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="E19:M19"/>
     <mergeCell ref="E20:M20"/>
     <mergeCell ref="E21:M21"/>
-    <mergeCell ref="E22:M22"/>
-    <mergeCell ref="A17:A19"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="B16:D16"/>
     <mergeCell ref="B17:D17"/>
     <mergeCell ref="B18:D18"/>
-    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="E16:M16"/>
     <mergeCell ref="E17:M17"/>
     <mergeCell ref="E18:M18"/>
-    <mergeCell ref="E19:M19"/>
-    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="E13:M13"/>
     <mergeCell ref="E14:M14"/>
     <mergeCell ref="E15:M15"/>
-    <mergeCell ref="E16:M16"/>
+    <mergeCell ref="B10:D10"/>
     <mergeCell ref="B11:D11"/>
     <mergeCell ref="B12:D12"/>
-    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="E10:M10"/>
     <mergeCell ref="E11:M11"/>
     <mergeCell ref="E12:M12"/>
-    <mergeCell ref="E13:M13"/>
+    <mergeCell ref="H43:J43"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="D44:E44"/>
+    <mergeCell ref="F44:G44"/>
     <mergeCell ref="H44:J44"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="D45:E45"/>
-    <mergeCell ref="F45:G45"/>
-    <mergeCell ref="H45:J45"/>
+    <mergeCell ref="A2:B2"/>
     <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C4:G4"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:F7"/>
-    <mergeCell ref="G7:I7"/>
-    <mergeCell ref="A8:A16"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:F6"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="A7:A15"/>
+    <mergeCell ref="B7:D7"/>
     <mergeCell ref="B8:D8"/>
     <mergeCell ref="B9:D9"/>
-    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:H4"/>
+    <mergeCell ref="I4:J4"/>
     <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C5:H5"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="F5:G5"/>
     <mergeCell ref="I5:J5"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="B13:D13"/>
     <mergeCell ref="B14:D14"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="D44:E44"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="D43:E43"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="D54:E54"/>
+    <mergeCell ref="F54:G54"/>
+    <mergeCell ref="H54:J54"/>
     <mergeCell ref="B55:C55"/>
     <mergeCell ref="D55:E55"/>
     <mergeCell ref="F55:G55"/>
     <mergeCell ref="H55:J55"/>
+    <mergeCell ref="B51:C52"/>
+    <mergeCell ref="D51:G51"/>
+    <mergeCell ref="H51:J52"/>
+    <mergeCell ref="D52:E52"/>
+    <mergeCell ref="F52:G52"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="D53:E53"/>
+    <mergeCell ref="F53:G53"/>
+    <mergeCell ref="H53:J53"/>
+    <mergeCell ref="B50:J50"/>
+    <mergeCell ref="D45:E45"/>
+    <mergeCell ref="F45:G45"/>
+    <mergeCell ref="H45:J45"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B40:C41"/>
+    <mergeCell ref="D40:G40"/>
+    <mergeCell ref="H40:J41"/>
+    <mergeCell ref="D41:E41"/>
+    <mergeCell ref="F41:G41"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="D42:E42"/>
+    <mergeCell ref="H42:J42"/>
+    <mergeCell ref="B34:J34"/>
+    <mergeCell ref="B39:J39"/>
+    <mergeCell ref="B35:J35"/>
+    <mergeCell ref="F42:G42"/>
+    <mergeCell ref="E36:F36"/>
+    <mergeCell ref="G36:H36"/>
     <mergeCell ref="B56:C56"/>
     <mergeCell ref="D56:E56"/>
     <mergeCell ref="F56:G56"/>
     <mergeCell ref="H56:J56"/>
-    <mergeCell ref="B52:C53"/>
-    <mergeCell ref="D52:G52"/>
-    <mergeCell ref="H52:J53"/>
-    <mergeCell ref="D53:E53"/>
-    <mergeCell ref="F53:G53"/>
-    <mergeCell ref="B54:C54"/>
-    <mergeCell ref="D54:E54"/>
-    <mergeCell ref="F54:G54"/>
-    <mergeCell ref="H54:J54"/>
-    <mergeCell ref="B51:J51"/>
     <mergeCell ref="D46:E46"/>
     <mergeCell ref="F46:G46"/>
     <mergeCell ref="H46:J46"/>
     <mergeCell ref="B47:C47"/>
-    <mergeCell ref="B41:C42"/>
-    <mergeCell ref="D41:G41"/>
-    <mergeCell ref="H41:J42"/>
-    <mergeCell ref="D42:E42"/>
-    <mergeCell ref="F42:G42"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="D43:E43"/>
-    <mergeCell ref="H43:J43"/>
-    <mergeCell ref="B35:J35"/>
-    <mergeCell ref="B40:J40"/>
-    <mergeCell ref="B36:J36"/>
-    <mergeCell ref="F43:G43"/>
-    <mergeCell ref="E37:F37"/>
-    <mergeCell ref="G37:H37"/>
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="D57:E57"/>
-    <mergeCell ref="F57:G57"/>
-    <mergeCell ref="H57:J57"/>
     <mergeCell ref="D47:E47"/>
     <mergeCell ref="F47:G47"/>
+    <mergeCell ref="B45:C45"/>
     <mergeCell ref="H47:J47"/>
     <mergeCell ref="B48:C48"/>
     <mergeCell ref="D48:E48"/>
     <mergeCell ref="F48:G48"/>
-    <mergeCell ref="B46:C46"/>
     <mergeCell ref="H48:J48"/>
     <mergeCell ref="B49:C49"/>
     <mergeCell ref="D49:E49"/>
     <mergeCell ref="F49:G49"/>
     <mergeCell ref="H49:J49"/>
-    <mergeCell ref="B50:C50"/>
-    <mergeCell ref="D50:E50"/>
-    <mergeCell ref="F50:G50"/>
-    <mergeCell ref="H50:J50"/>
-    <mergeCell ref="B68:J68"/>
+    <mergeCell ref="B67:J67"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="D68:J68"/>
     <mergeCell ref="B69:C69"/>
     <mergeCell ref="D69:J69"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="D70:J70"/>
-    <mergeCell ref="B72:J72"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="D58:E58"/>
-    <mergeCell ref="F58:G58"/>
-    <mergeCell ref="H58:J58"/>
-    <mergeCell ref="B60:J60"/>
+    <mergeCell ref="B71:J71"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="D57:E57"/>
+    <mergeCell ref="F57:G57"/>
+    <mergeCell ref="H57:J57"/>
+    <mergeCell ref="B59:J59"/>
+    <mergeCell ref="B60:C60"/>
     <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="D60:J60"/>
     <mergeCell ref="D61:J61"/>
-    <mergeCell ref="D62:J62"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="D64:J64"/>
     <mergeCell ref="B65:C65"/>
     <mergeCell ref="D65:J65"/>
-    <mergeCell ref="B66:C66"/>
-    <mergeCell ref="D66:J66"/>
   </mergeCells>
-  <conditionalFormatting sqref="A79:D79 K79:M79">
-    <cfRule type="containsBlanks" dxfId="6" priority="11" stopIfTrue="1">
-      <formula>LEN(TRIM(A79))=0</formula>
+  <conditionalFormatting sqref="A78:D78 K78:M78">
+    <cfRule type="containsBlanks" dxfId="8" priority="13" stopIfTrue="1">
+      <formula>LEN(TRIM(A78))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A79:D79">
-    <cfRule type="containsBlanks" dxfId="5" priority="6">
-      <formula>LEN(TRIM(A79))=0</formula>
+  <conditionalFormatting sqref="A78:D78">
+    <cfRule type="containsBlanks" dxfId="7" priority="8">
+      <formula>LEN(TRIM(A78))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D37:D38 H38:J38">
-    <cfRule type="containsBlanks" dxfId="4" priority="2">
-      <formula>LEN(TRIM(D37))=0</formula>
+  <conditionalFormatting sqref="D36:D37 H37:J37">
+    <cfRule type="containsBlanks" dxfId="6" priority="4">
+      <formula>LEN(TRIM(D36))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G37:H37 J37">
-    <cfRule type="containsBlanks" dxfId="3" priority="1">
-      <formula>LEN(TRIM(G37))=0</formula>
+  <conditionalFormatting sqref="D42:J49 D53:J57">
+    <cfRule type="containsBlanks" dxfId="5" priority="2">
+      <formula>LEN(TRIM(D42))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I4:M4 C5:H5 K5:M5 J7:M7 E8:M16 E20:M31 H43:J50 H54:J58 D69:J70 A79:D79 K79:M79">
-    <cfRule type="containsBlanks" dxfId="2" priority="3">
-      <formula>LEN(TRIM(A4))=0</formula>
+  <conditionalFormatting sqref="D60:J61">
+    <cfRule type="containsBlanks" dxfId="4" priority="1">
+      <formula>LEN(TRIM(D60))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I4:M4 C5:H5 K5:M5 J7:M7 E8:M16 E20:M31">
-    <cfRule type="containsBlanks" dxfId="1" priority="10" stopIfTrue="1">
-      <formula>LEN(TRIM(C4))=0</formula>
+  <conditionalFormatting sqref="G36:H36 J36">
+    <cfRule type="containsBlanks" dxfId="3" priority="3">
+      <formula>LEN(TRIM(G36))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K79:M79">
-    <cfRule type="containsBlanks" dxfId="0" priority="5">
-      <formula>LEN(TRIM(K79))=0</formula>
+  <conditionalFormatting sqref="I3:M3 C4:H4 K4:M4 J6:M6 E7:M15 E19:M30 D68:J69 A78:D78 K78:M78">
+    <cfRule type="containsBlanks" dxfId="2" priority="5">
+      <formula>LEN(TRIM(A3))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I3:M3 C4:H4 K4:M4 J6:M6 E7:M15 E19:M30">
+    <cfRule type="containsBlanks" dxfId="1" priority="12" stopIfTrue="1">
+      <formula>LEN(TRIM(C3))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K78:M78">
+    <cfRule type="containsBlanks" dxfId="0" priority="7">
+      <formula>LEN(TRIM(K78))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations xWindow="756" yWindow="874" count="47">
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Indicar el nivel formativo en el cual se encuentra el aprendiz. Técnio o Tecnólogo" sqref="I4:M4" xr:uid="{FDFD4240-B4E4-40FA-8880-3E4E045C5084}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Registrar el nombre del programa" prompt="Registrar el nombre del programa" sqref="C5:H5" xr:uid="{34EF5BAD-650F-4FA7-AB25-B4A5694BB4C0}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Número Ficha" prompt="Registre el número de ficha en el que se encuentra matriculado según el programa de formación." sqref="K5:M5" xr:uid="{C295E52F-E427-4103-89DB-18FF195E95C6}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Fin Etapa Lectiva" prompt="Registrar la fecha de culminación de la etapa lectiva del aprendiz." sqref="J7:M7" xr:uid="{5EB3E1EF-1E32-4E95-8D18-C01EA7CF4F61}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Registrar nombre del aprendiz como aparece en su documento de identificación." sqref="E8:M8" xr:uid="{9B40B093-9C34-4E63-9F64-4BFF88393B31}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Tipo Documento Identificación" prompt="Este tipo de documento debe coincidir con las opciones de identificación descritas en el aplicativo Sofia Plus (NUIP, TI, CC, CE, PEP). " sqref="E9:M9" xr:uid="{DA947DA3-FB5C-4D1A-942B-8548E48311E3}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Registrar el número de identificación del aprendiz SIN puntos, comas o espacios" sqref="E10:M10" xr:uid="{26796309-EF62-4852-B260-C64A329B6E61}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Registrar teléfonos fijo y celular del aprendiz u otro número de contacto." sqref="E11:M11" xr:uid="{227D64D5-7E2E-48B5-834F-26D52CA83B47}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Ingrese la dirección residencial actual de correspondencia del aprendiz." sqref="E12:M12" xr:uid="{EC33A478-21D0-417A-960A-07B663B862B0}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Registrar el correo electrónico personal del aprendiz" sqref="E13:M13" xr:uid="{CEDF05F3-A498-464C-AF78-C83490E95D67}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Registrar el correo electrónico institucional del aprendiz @sena.edu.co , @soysena.edu.co" sqref="E14:M14" xr:uid="{8AC0CC91-D06D-4D82-A06B-CEDFF66185FC}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Registrar el nombre de la alternativa de etapa productiva, de acuerdo con las alternativas descritas en el reglamento del aprendiz vigente" sqref="E15:M15" xr:uid="{48CA359C-CBBE-4B45-B681-EA4693D12177}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Indicar la fecha en que quedó registrada la alternativa en el aplicativo SofiaPlus.  Gestione con la coordinación académica el reporte del SVP para obtener la información requerida en este apartado" sqref="E16:M16" xr:uid="{A4B53DE5-4CEE-4C8C-A08B-9C6344C18954}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Registrar el nombre completo de la empresa o entidad co-formadora (empresa, entidad o institución gubernamental o no gubernamental)." sqref="E20:M20" xr:uid="{35AC5BC6-659F-4E4C-B567-3C3F16C509BD}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Registrar la dirección de la empresa, entidad o institución gubernamental o no gubernamental." sqref="E21:M21" xr:uid="{18FD205E-10DD-4EB5-8E57-F8B0C00BF5BC}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Registrar el numero NIT de la empresa, entidad o institución gubernamental o no gubernamental." sqref="E22:M22" xr:uid="{0E9499EA-A21D-4209-94F0-6561C0BEA458}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Registrar el correo organizacional o institucional del jefe inmediato." sqref="E23:M23" xr:uid="{F7B09C4A-6282-4561-9C6E-128034419E72}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Registrar el nombre del jefe inmediato o quien va a supervisar las actividades del aprendiz en la empresa. En caso de estar participando en una convocatoria de proyecto productivo, aquí se registran los datos del instructor de proyecto productivo." sqref="E24:M24" xr:uid="{3F1EE247-C76F-4BD4-A0A3-6B6F02F83B03}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Registrar el cargo del jefe inmediato dentro de la empresa" sqref="E25:M25" xr:uid="{44C4A18A-BD9D-4153-94CA-F617EBC7DCBA}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Registrar el número del celular del jefe inmediato o supervisor y el número fijo de la empresa con extensión" sqref="E26:M26" xr:uid="{D17896B5-5299-404D-BF06-0A7409E6BB11}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="En caso de que aplique, registrar el nombre de otro contacto en la empresa. De no tener digitar N/A" sqref="E27:M27" xr:uid="{A6F4976B-257F-4E38-96A4-122163F2BCDA}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Registrar el teléfono institucional al cual contactarse en caso que el ente coformador no responda" sqref="E28:M28" xr:uid="{A593241B-15E7-4EA6-B9DE-E0DF01ED6DB9}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="En caso de que el aprendiz sea una persona en situación de discapacidad, diligencie este espacio con el nombre de la persona que le asiste." sqref="E29:M29" xr:uid="{C19946D2-B571-4104-A1EA-FEF5A7253596}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Aquí se especifica el tipo de asistencia brindada al aprendiz para que desempeñe la totalidad de sus tareas asegurando un ambiente laboral inclusivo adecuado a sus necesidades. Puede incluir asistencias como lenguaje de señas, soporte visual etc" sqref="E30:M30" xr:uid="{B635F5F5-108B-409C-BCAD-0AA5A654CF02}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Registrar el número del celular de la persona que asiste al aprendiz " sqref="E31:M31" xr:uid="{77AEF51E-4966-4ADA-B94D-7E72C6BE4FFA}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Registrar el nombre completo del aprendiz y en la parte superior la Firma manuscrita o digital." sqref="A79:D79" xr:uid="{A7FEFB2B-7370-4FA2-8820-7EB89B730FD1}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Registrar el nombre completo del co-formador y en la parte superior de esta la Firma manuscrita o digital." sqref="K79:M79" xr:uid="{DAE2A968-2309-42D5-952C-BC599D7BE50F}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Indique las razones por las que se brinda dicha valoración (indispensable en las valoradas por mejorar)." sqref="H43:J43" xr:uid="{2775CE5B-7882-46E3-9B64-A1DCACE5C767}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Aporta activamente al mejoramiento de sus habilidades técnicas y métodos de trabajo." sqref="D44:F44" xr:uid="{A8FCB973-8FC0-4BDD-BF0E-CC9BB61BE366}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Marcar con una X según correspon" prompt="Demuestra las competencias específicas del programa de formación en situaciones reales de trabajo. " sqref="D43:G43" xr:uid="{948FA747-4CF8-48C4-8768-F9CADBC3F362}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Realiza acciones que fortalezcan su perfil ocupacional potenciando sus competencias en el marco de su proyecto de vida." sqref="D45:G45" xr:uid="{379961D4-6BD4-47A0-B009-E49C8B35A883}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Presenta con oportunidad y calidad los productos generados en el desarrollo de sus actividades." sqref="D46:G46" xr:uid="{19539D16-ED2B-4BF9-A64A-1332E00D8693}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Administra los recursos para el desarrollo de sus actividades con criterios de responsabilidad ambiental." sqref="D47:G47" xr:uid="{2B7AA1E4-5959-4E7A-871B-23982F85D610}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Utiliza de manera racional los materiales, equipos y herramientas suministrados para el desempeño de sus actividades." sqref="D48:G48" xr:uid="{3DAD6ADF-7EDC-428E-A36E-3CB7EE1A10E7}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Utiliza los elementos de seguridad y salud en el trabajo de acuerdo con la normatividad vigente establecida para sus actividades." sqref="D49:G49" xr:uid="{85CDCD1C-AA51-4ED1-B43A-B475BA4D68ED}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Cumple con la documentación exigida por el instructor de seguimiento dentro de los tiempos establecidos y según la alternativa seleccionada por el aprendiz." sqref="D50:G50" xr:uid="{A49ACC1F-E494-4AD4-8D8D-890B446B1CFA}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Marcar con X segun corresponda" prompt="Desarrolla relaciones interpersonales en las diferentes áreas de la empresa en forma armoniosa, respetuosa y enmarcada en la comunicación asertiva demostrando un sentido de pertenencia con la organización." sqref="D54:G54" xr:uid="{2A8EA381-A4F1-4FE3-B713-8EF2613D8E6B}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Participa en forma activa y propositiva en equipos de trabajo asumiendo los roles, de acuerdo con sus fortalezas." sqref="D55:G55" xr:uid="{93A504BB-63A5-4D20-AB75-17DB32BC8DA7}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Propone alternativas de solución a situaciones problemáticas, en el contexto del desarrollo de su etapa productiva. " sqref="D56:G56" xr:uid="{8CFCA47A-7FFB-4C81-B160-32FC56FE753D}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Es comprometido con las actividades asignadas y con la empresa, demostrando puntualidad, proactividad y buena presentación personal en el desarrollo de su etapa productiva" sqref="D57:G57" xr:uid="{C5D9BB00-F014-4DE5-B59C-090440CDA5FD}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Demuestra capacidad para ordenar y disponer los elementos necesarios e información que facilite la ejecución del trabajo y el logro de los objetivos." sqref="D58:G59" xr:uid="{B8588CD4-9B9C-4123-8FA4-B0191CFB9CEA}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Registrar la retroalimentación sobre el proceso de formación realizado por parte del aprendiz, así como las recomendaciones u oportunidades de mejora." sqref="D69:J69" xr:uid="{BB60E4B5-FB76-4B94-9BA7-36C763570B67}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Registrar observaciones finales del procesos por parte del aprendiz" sqref="D70:J70" xr:uid="{979A95D0-1B6C-4B96-AED2-E0EA9955374B}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Registrar la retroalimentación sobre el proceso de formación realizado por parte del ente co-formador, así como las recomendaciones u oportunidades de mejora. De la misma manera, si el aprendiz tiene o no reconocimientos especiales frente a su desempeño." sqref="D65:J65 D61:J61" xr:uid="{F2874302-4049-43C8-A0B5-AB713683C70D}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Registrar si el aprendiz tiene o no reconocimientos especiales frente a su desempeño. registrar otras observaciones , recomendaciones u oportunidades de mejora sobre las competencias del programa desarrolladas por el aprendiz" sqref="D66:J66 D62:J62" xr:uid="{31FFF10E-CBCB-44E0-A79A-920B54E65B68}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Ingresar el Link de la Grabacion del teams" sqref="H38:J38" xr:uid="{F2C9EF6C-D3FF-4587-A8E6-606880F942C2}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Virtual o Presencial?" sqref="D38" xr:uid="{5D446980-EFCB-4F87-AF79-7C40D04D4175}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Indicar el nivel formativo en el cual se encuentra el aprendiz. Técnio o Tecnólogo" sqref="I3:M3" xr:uid="{FDFD4240-B4E4-40FA-8880-3E4E045C5084}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Registrar el nombre del programa" prompt="Registrar el nombre del programa" sqref="C4:H4" xr:uid="{34EF5BAD-650F-4FA7-AB25-B4A5694BB4C0}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Número Ficha" prompt="Registre el número de ficha en el que se encuentra matriculado según el programa de formación." sqref="K4:M4" xr:uid="{C295E52F-E427-4103-89DB-18FF195E95C6}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Fin Etapa Lectiva" prompt="Registrar la fecha de culminación de la etapa lectiva del aprendiz." sqref="J6:M6" xr:uid="{5EB3E1EF-1E32-4E95-8D18-C01EA7CF4F61}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Registrar nombre del aprendiz como aparece en su documento de identificación." sqref="E7:M7" xr:uid="{9B40B093-9C34-4E63-9F64-4BFF88393B31}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Tipo Documento Identificación" prompt="Este tipo de documento debe coincidir con las opciones de identificación descritas en el aplicativo Sofia Plus (NUIP, TI, CC, CE, PEP). " sqref="E8:M8" xr:uid="{DA947DA3-FB5C-4D1A-942B-8548E48311E3}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Registrar el número de identificación del aprendiz SIN puntos, comas o espacios" sqref="E9:M9" xr:uid="{26796309-EF62-4852-B260-C64A329B6E61}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Registrar teléfonos fijo y celular del aprendiz u otro número de contacto." sqref="E10:M10" xr:uid="{227D64D5-7E2E-48B5-834F-26D52CA83B47}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Ingrese la dirección residencial actual de correspondencia del aprendiz." sqref="E11:M11" xr:uid="{EC33A478-21D0-417A-960A-07B663B862B0}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Registrar el correo electrónico personal del aprendiz" sqref="E12:M12" xr:uid="{CEDF05F3-A498-464C-AF78-C83490E95D67}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Registrar el correo electrónico institucional del aprendiz @sena.edu.co , @soysena.edu.co" sqref="E13:M13" xr:uid="{8AC0CC91-D06D-4D82-A06B-CEDFF66185FC}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Registrar el nombre de la alternativa de etapa productiva, de acuerdo con las alternativas descritas en el reglamento del aprendiz vigente" sqref="E14:M14" xr:uid="{48CA359C-CBBE-4B45-B681-EA4693D12177}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Indicar la fecha en que quedó registrada la alternativa en el aplicativo SofiaPlus.  Gestione con la coordinación académica el reporte del SVP para obtener la información requerida en este apartado" sqref="E15:M15" xr:uid="{A4B53DE5-4CEE-4C8C-A08B-9C6344C18954}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Registrar el nombre completo de la empresa o entidad co-formadora (empresa, entidad o institución gubernamental o no gubernamental)." sqref="E19:M19" xr:uid="{35AC5BC6-659F-4E4C-B567-3C3F16C509BD}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Registrar la dirección de la empresa, entidad o institución gubernamental o no gubernamental." sqref="E20:M20" xr:uid="{18FD205E-10DD-4EB5-8E57-F8B0C00BF5BC}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Registrar el numero NIT de la empresa, entidad o institución gubernamental o no gubernamental." sqref="E21:M21" xr:uid="{0E9499EA-A21D-4209-94F0-6561C0BEA458}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Registrar el correo organizacional o institucional del jefe inmediato." sqref="E22:M22" xr:uid="{F7B09C4A-6282-4561-9C6E-128034419E72}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Registrar el nombre del jefe inmediato o quien va a supervisar las actividades del aprendiz en la empresa. En caso de estar participando en una convocatoria de proyecto productivo, aquí se registran los datos del instructor de proyecto productivo." sqref="E23:M23" xr:uid="{3F1EE247-C76F-4BD4-A0A3-6B6F02F83B03}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Registrar el cargo del jefe inmediato dentro de la empresa" sqref="E24:M24" xr:uid="{44C4A18A-BD9D-4153-94CA-F617EBC7DCBA}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Registrar el número del celular del jefe inmediato o supervisor y el número fijo de la empresa con extensión" sqref="E25:M25" xr:uid="{D17896B5-5299-404D-BF06-0A7409E6BB11}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="En caso de que aplique, registrar el nombre de otro contacto en la empresa. De no tener digitar N/A" sqref="E26:M26" xr:uid="{A6F4976B-257F-4E38-96A4-122163F2BCDA}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Registrar el teléfono institucional al cual contactarse en caso que el ente coformador no responda" sqref="E27:M27" xr:uid="{A593241B-15E7-4EA6-B9DE-E0DF01ED6DB9}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="En caso de que el aprendiz sea una persona en situación de discapacidad, diligencie este espacio con el nombre de la persona que le asiste." sqref="E28:M28" xr:uid="{C19946D2-B571-4104-A1EA-FEF5A7253596}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Aquí se especifica el tipo de asistencia brindada al aprendiz para que desempeñe la totalidad de sus tareas asegurando un ambiente laboral inclusivo adecuado a sus necesidades. Puede incluir asistencias como lenguaje de señas, soporte visual etc" sqref="E29:M29" xr:uid="{B635F5F5-108B-409C-BCAD-0AA5A654CF02}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Registrar el número del celular de la persona que asiste al aprendiz " sqref="E30:M30" xr:uid="{77AEF51E-4966-4ADA-B94D-7E72C6BE4FFA}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Registrar el nombre completo del aprendiz y en la parte superior la Firma manuscrita o digital." sqref="A78:D78" xr:uid="{A7FEFB2B-7370-4FA2-8820-7EB89B730FD1}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Registrar el nombre completo del co-formador y en la parte superior de esta la Firma manuscrita o digital." sqref="K78:M78" xr:uid="{DAE2A968-2309-42D5-952C-BC599D7BE50F}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Indique las razones por las que se brinda dicha valoración (indispensable en las valoradas por mejorar)." sqref="H42:J42" xr:uid="{2775CE5B-7882-46E3-9B64-A1DCACE5C767}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Aporta activamente al mejoramiento de sus habilidades técnicas y métodos de trabajo." sqref="D43:F43" xr:uid="{A8FCB973-8FC0-4BDD-BF0E-CC9BB61BE366}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Marcar con una X según correspon" prompt="Demuestra las competencias específicas del programa de formación en situaciones reales de trabajo. " sqref="D42:G42" xr:uid="{948FA747-4CF8-48C4-8768-F9CADBC3F362}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Realiza acciones que fortalezcan su perfil ocupacional potenciando sus competencias en el marco de su proyecto de vida." sqref="D44:G44" xr:uid="{379961D4-6BD4-47A0-B009-E49C8B35A883}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Presenta con oportunidad y calidad los productos generados en el desarrollo de sus actividades." sqref="D45:G45" xr:uid="{19539D16-ED2B-4BF9-A64A-1332E00D8693}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Administra los recursos para el desarrollo de sus actividades con criterios de responsabilidad ambiental." sqref="D46:G46" xr:uid="{2B7AA1E4-5959-4E7A-871B-23982F85D610}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Utiliza de manera racional los materiales, equipos y herramientas suministrados para el desempeño de sus actividades." sqref="D47:G47" xr:uid="{3DAD6ADF-7EDC-428E-A36E-3CB7EE1A10E7}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Utiliza los elementos de seguridad y salud en el trabajo de acuerdo con la normatividad vigente establecida para sus actividades." sqref="D48:G48" xr:uid="{85CDCD1C-AA51-4ED1-B43A-B475BA4D68ED}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Cumple con la documentación exigida por el instructor de seguimiento dentro de los tiempos establecidos y según la alternativa seleccionada por el aprendiz." sqref="D49:G49" xr:uid="{A49ACC1F-E494-4AD4-8D8D-890B446B1CFA}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Marcar con X segun corresponda" prompt="Desarrolla relaciones interpersonales en las diferentes áreas de la empresa en forma armoniosa, respetuosa y enmarcada en la comunicación asertiva demostrando un sentido de pertenencia con la organización." sqref="D53:G53" xr:uid="{2A8EA381-A4F1-4FE3-B713-8EF2613D8E6B}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Participa en forma activa y propositiva en equipos de trabajo asumiendo los roles, de acuerdo con sus fortalezas." sqref="D54:G54" xr:uid="{93A504BB-63A5-4D20-AB75-17DB32BC8DA7}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Propone alternativas de solución a situaciones problemáticas, en el contexto del desarrollo de su etapa productiva. " sqref="D55:G55" xr:uid="{8CFCA47A-7FFB-4C81-B160-32FC56FE753D}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Es comprometido con las actividades asignadas y con la empresa, demostrando puntualidad, proactividad y buena presentación personal en el desarrollo de su etapa productiva" sqref="D56:G56" xr:uid="{C5D9BB00-F014-4DE5-B59C-090440CDA5FD}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Demuestra capacidad para ordenar y disponer los elementos necesarios e información que facilite la ejecución del trabajo y el logro de los objetivos." sqref="D57:G58" xr:uid="{B8588CD4-9B9C-4123-8FA4-B0191CFB9CEA}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Registrar la retroalimentación sobre el proceso de formación realizado por parte del aprendiz, así como las recomendaciones u oportunidades de mejora." sqref="D68:J68" xr:uid="{BB60E4B5-FB76-4B94-9BA7-36C763570B67}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Registrar observaciones finales del procesos por parte del aprendiz" sqref="D69:J69" xr:uid="{979A95D0-1B6C-4B96-AED2-E0EA9955374B}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Registrar la retroalimentación sobre el proceso de formación realizado por parte del ente co-formador, así como las recomendaciones u oportunidades de mejora. De la misma manera, si el aprendiz tiene o no reconocimientos especiales frente a su desempeño." sqref="D64:J64 D60:J60" xr:uid="{F2874302-4049-43C8-A0B5-AB713683C70D}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Registrar si el aprendiz tiene o no reconocimientos especiales frente a su desempeño. registrar otras observaciones , recomendaciones u oportunidades de mejora sobre las competencias del programa desarrolladas por el aprendiz" sqref="D65:J65 D61:J61" xr:uid="{31FFF10E-CBCB-44E0-A79A-920B54E65B68}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Ingresar el Link de la Grabacion del teams" sqref="H37:J37" xr:uid="{F2C9EF6C-D3FF-4587-A8E6-606880F942C2}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Virtual o Presencial?" sqref="D37" xr:uid="{5D446980-EFCB-4F87-AF79-7C40D04D4175}"/>
   </dataValidations>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="65" fitToHeight="0" orientation="portrait" r:id="rId1"/>
-  <drawing r:id="rId2"/>
+  <pageSetup paperSize="5" scale="68" fitToHeight="0" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Formatos/Visita 3 GFPI-F023.xlsx
+++ b/Formatos/Visita 3 GFPI-F023.xlsx
@@ -1,23 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SEANT\OneDrive\Documents\Seto 2026\sena\Manual SENA Etapa Productiva\manual-aprendiz-sena\Formatos\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SEANT\3D Objects\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3898366A-72DD-4E6B-8E8D-ECA46D8806A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAB61486-BA46-46E5-9645-FAD2FBFB33E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{BC3553EE-4E49-4F2A-B03E-CFAC4EB3009B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{BC3553EE-4E49-4F2A-B03E-CFAC4EB3009B}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
+    <sheet name="Hoja2" sheetId="2" state="hidden" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_Hlk197527663" localSheetId="0">Hoja1!$B$78</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Hoja1!$A$8:$M$88</definedName>
+    <definedName name="_Hlk197527663" localSheetId="0">Hoja1!#REF!</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Hoja1!$A$8:$M$87</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="100">
   <si>
     <t>Información general</t>
   </si>
@@ -316,69 +317,6 @@
     <t>Retroalimentación del aprendiz</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <u/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Juicio de evaluación de la etapa productiva (seleccione): </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">    Aprobado </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">□    </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">    No aprobado </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">□  </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">       </t>
-    </r>
-  </si>
-  <si>
     <t>Fecha inicio etapa productiva: (DD/MM/AA)</t>
   </si>
   <si>
@@ -417,13 +355,58 @@
   </si>
   <si>
     <t>Pública Reservada</t>
+  </si>
+  <si>
+    <t>Observaciones positivas del proceso general de formación</t>
+  </si>
+  <si>
+    <t>Observaciones positivas sobre competencias técnicas y actitudinales del sector software</t>
+  </si>
+  <si>
+    <t>Se destaca por su participación activa en las actividades de formación, así como por su disposición para fortalecer sus competencias personales y profesionales. Mantiene una actitud receptiva frente a las orientaciones recibidas y demuestra interés por aplicar lo aprendido en los diferentes espacios de práctica.</t>
+  </si>
+  <si>
+    <t>El aprendiz evidencia un proceso de formación satisfactorio, mostrando compromiso, responsabilidad y una actitud constante de mejora continua. Su participación en las actividades propuestas refleja interés por fortalecer sus conocimientos y consolidar su crecimiento personal y profesional dentro del proceso formativo.</t>
+  </si>
+  <si>
+    <t>El aprendiz ha desarrollado de manera favorable su proceso formativo, demostrando interés, disciplina y apropiación progresiva de los conocimientos adquiridos. Su desempeño general permite evidenciar avances significativos en su construcción como futuro profesional.</t>
+  </si>
+  <si>
+    <t>Presenta un avance positivo en su formación integral, reflejado en su cumplimiento, sentido de pertenencia y disposición para aprender. Su actitud frente a los retos formativos contribuye de manera favorable al desarrollo de las actividades y al logro de los objetivos propuestos.</t>
+  </si>
+  <si>
+    <t>El proceso de formación del aprendiz se caracterizó por un desempeño estable y favorable, con buena receptividad frente a las orientaciones recibidas. Su compromiso con el aprendizaje y su disposición para mejorar permanentemente fortalecen su evolución dentro de la etapa productiva</t>
+  </si>
+  <si>
+    <t>El aprendiz aplica adecuadamente los conocimientos adquiridos en el área de software, evidenciando responsabilidad, trabajo en equipo y buena disposición frente a los retos del entorno. Su desempeño técnico refleja avances acordes con el proceso de formación y una actitud favorable frente a la práctica.</t>
+  </si>
+  <si>
+    <t>El aprendiz demuestra competencias técnicas acordes con su proceso de formación, así como habilidades actitudinales que favorecen su integración al equipo de trabajo. Su comunicación, respeto y disposición para recibir retroalimentación fortalecen su desempeño en el entorno laboral.</t>
+  </si>
+  <si>
+    <t>Su desempeño en actividades técnicas y actitudinales refleja avances positivos, con capacidad de adaptación, responsabilidad y buen relacionamiento en el entorno laboral. Asimismo, evidencia interés por seguir fortaleciendo sus competencias para desempeñarse de forma cada vez más autónoma y eficiente.</t>
+  </si>
+  <si>
+    <t>Presenta un manejo adecuado de las tareas asignadas en el área de software, resaltando su compromiso, comunicación asertiva y disposición para el aprendizaje continuo. Su actitud frente a las responsabilidades encomendadas contribuye de manera positiva al desarrollo de las actividades.</t>
+  </si>
+  <si>
+    <t>Se observa un desempeño favorable en la ejecución de actividades técnicas relacionadas con el sector software, acompañado de una actitud proactiva y colaborativa. Su participación en los procesos asignados demuestra interés por dar solución a las tareas con compromiso y oportunidad.</t>
+  </si>
+  <si>
+    <t>No aprobado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Aprobado</t>
+  </si>
+  <si>
+    <t>Juicio de evaluación de la etapa productiva (seleccione):</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="22" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -524,21 +507,6 @@
       <family val="2"/>
     </font>
     <font>
-      <b/>
-      <sz val="14"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <u/>
-      <sz val="9"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="9"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
@@ -565,6 +533,35 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF27251E"/>
+      <name val="Georgia"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF27251E"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF27251E"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Aptos"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -942,7 +939,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="169">
+  <cellXfs count="177">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
@@ -994,7 +991,7 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
@@ -1003,467 +1000,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1">
       <extLst>
@@ -1472,9 +1008,6 @@
         </ext>
       </extLst>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1">
       <extLst>
         <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -1482,49 +1015,535 @@
         </ext>
       </extLst>
     </xf>
-    <xf numFmtId="15" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="15" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="15" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="15" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="15" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="15" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement i="0"/>
+        </ext>
+      </extLst>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="15" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="15" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="15" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="19">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="10">
     <dxf>
       <fill>
         <patternFill>
@@ -1543,62 +1562,6 @@
       <fill>
         <patternFill>
           <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFE4EE5C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFEEEC9C"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2012,7 +1975,7 @@
   <cols>
     <col min="1" max="1" width="18.5703125" customWidth="1"/>
     <col min="2" max="6" width="11.42578125" customWidth="1"/>
-    <col min="7" max="7" width="9" customWidth="1"/>
+    <col min="7" max="7" width="9.7109375" customWidth="1"/>
     <col min="8" max="8" width="11.42578125" customWidth="1"/>
     <col min="9" max="9" width="11.85546875" customWidth="1"/>
     <col min="10" max="10" width="16.85546875" customWidth="1"/>
@@ -2024,1090 +1987,1090 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B1" s="148" t="s">
+      <c r="B1" s="165" t="s">
+        <v>77</v>
+      </c>
+      <c r="C1" s="166"/>
+      <c r="D1" s="166"/>
+      <c r="E1" s="166"/>
+      <c r="F1" s="166"/>
+      <c r="G1" s="166"/>
+      <c r="H1" s="166"/>
+      <c r="I1" s="166"/>
+      <c r="J1" s="166"/>
+      <c r="K1" s="167"/>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B2" s="168" t="s">
         <v>78</v>
       </c>
-      <c r="C1" s="149"/>
-      <c r="D1" s="149"/>
-      <c r="E1" s="149"/>
-      <c r="F1" s="149"/>
-      <c r="G1" s="149"/>
-      <c r="H1" s="149"/>
-      <c r="I1" s="149"/>
-      <c r="J1" s="149"/>
-      <c r="K1" s="150"/>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B2" s="151" t="s">
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="32"/>
+      <c r="H2" s="32"/>
+      <c r="I2" s="32"/>
+      <c r="J2" s="32"/>
+      <c r="K2" s="169"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B3" s="170" t="s">
         <v>79</v>
       </c>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="20"/>
-      <c r="I2" s="20"/>
-      <c r="J2" s="20"/>
-      <c r="K2" s="152"/>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B3" s="153" t="s">
+      <c r="C3" s="171"/>
+      <c r="D3" s="171"/>
+      <c r="E3" s="171"/>
+      <c r="F3" s="171"/>
+      <c r="G3" s="171"/>
+      <c r="H3" s="171"/>
+      <c r="I3" s="171"/>
+      <c r="J3" s="171"/>
+      <c r="K3" s="172"/>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B4" s="168" t="s">
         <v>80</v>
       </c>
-      <c r="C3" s="154"/>
-      <c r="D3" s="154"/>
-      <c r="E3" s="154"/>
-      <c r="F3" s="154"/>
-      <c r="G3" s="154"/>
-      <c r="H3" s="154"/>
-      <c r="I3" s="154"/>
-      <c r="J3" s="154"/>
-      <c r="K3" s="155"/>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B4" s="151" t="s">
+      <c r="C4" s="32"/>
+      <c r="D4" s="32"/>
+      <c r="E4" s="32"/>
+      <c r="F4" s="32"/>
+      <c r="G4" s="32"/>
+      <c r="H4" s="32"/>
+      <c r="I4" s="32"/>
+      <c r="J4" s="32"/>
+      <c r="K4" s="169"/>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B5" s="170" t="s">
         <v>81</v>
       </c>
-      <c r="C4" s="20"/>
-      <c r="D4" s="20"/>
-      <c r="E4" s="20"/>
-      <c r="F4" s="20"/>
-      <c r="G4" s="20"/>
-      <c r="H4" s="20"/>
-      <c r="I4" s="20"/>
-      <c r="J4" s="20"/>
-      <c r="K4" s="152"/>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B5" s="153" t="s">
+      <c r="C5" s="171"/>
+      <c r="D5" s="171"/>
+      <c r="E5" s="171"/>
+      <c r="F5" s="171"/>
+      <c r="G5" s="171"/>
+      <c r="H5" s="171"/>
+      <c r="I5" s="171"/>
+      <c r="J5" s="171"/>
+      <c r="K5" s="172"/>
+    </row>
+    <row r="6" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="173" t="s">
         <v>82</v>
       </c>
-      <c r="C5" s="154"/>
-      <c r="D5" s="154"/>
-      <c r="E5" s="154"/>
-      <c r="F5" s="154"/>
-      <c r="G5" s="154"/>
-      <c r="H5" s="154"/>
-      <c r="I5" s="154"/>
-      <c r="J5" s="154"/>
-      <c r="K5" s="155"/>
-    </row>
-    <row r="6" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="156" t="s">
+      <c r="C6" s="174"/>
+      <c r="D6" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="E6" s="175" t="s">
         <v>83</v>
       </c>
-      <c r="C6" s="157"/>
-      <c r="D6" s="158" t="b">
+      <c r="F6" s="174"/>
+      <c r="G6" s="174"/>
+      <c r="H6" s="20" t="b">
         <v>0</v>
       </c>
-      <c r="E6" s="159" t="s">
+      <c r="I6" s="175" t="s">
         <v>84</v>
       </c>
-      <c r="F6" s="157"/>
-      <c r="G6" s="157"/>
-      <c r="H6" s="158" t="b">
-        <v>0</v>
-      </c>
-      <c r="I6" s="159" t="s">
-        <v>85</v>
-      </c>
-      <c r="J6" s="157"/>
-      <c r="K6" s="160" t="b">
+      <c r="J6" s="174"/>
+      <c r="K6" s="21" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25"/>
     <row r="8" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="58" t="s">
+      <c r="A8" s="71" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="59"/>
-      <c r="C8" s="59"/>
-      <c r="D8" s="59"/>
-      <c r="E8" s="59"/>
-      <c r="F8" s="59"/>
-      <c r="G8" s="59"/>
-      <c r="H8" s="59"/>
-      <c r="I8" s="59"/>
-      <c r="J8" s="59"/>
-      <c r="K8" s="59"/>
-      <c r="L8" s="59"/>
-      <c r="M8" s="59"/>
+      <c r="B8" s="72"/>
+      <c r="C8" s="72"/>
+      <c r="D8" s="72"/>
+      <c r="E8" s="72"/>
+      <c r="F8" s="72"/>
+      <c r="G8" s="72"/>
+      <c r="H8" s="72"/>
+      <c r="I8" s="72"/>
+      <c r="J8" s="72"/>
+      <c r="K8" s="72"/>
+      <c r="L8" s="72"/>
+      <c r="M8" s="72"/>
     </row>
     <row r="9" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="49" t="s">
+      <c r="A9" s="60" t="s">
         <v>1</v>
       </c>
-      <c r="B9" s="51"/>
-      <c r="C9" s="55" t="s">
+      <c r="B9" s="62"/>
+      <c r="C9" s="68" t="s">
         <v>2</v>
       </c>
-      <c r="D9" s="56"/>
-      <c r="E9" s="56"/>
-      <c r="F9" s="56"/>
-      <c r="G9" s="56"/>
-      <c r="H9" s="56"/>
-      <c r="I9" s="56"/>
-      <c r="J9" s="56"/>
-      <c r="K9" s="56"/>
-      <c r="L9" s="56"/>
-      <c r="M9" s="57"/>
+      <c r="D9" s="69"/>
+      <c r="E9" s="69"/>
+      <c r="F9" s="69"/>
+      <c r="G9" s="69"/>
+      <c r="H9" s="69"/>
+      <c r="I9" s="69"/>
+      <c r="J9" s="69"/>
+      <c r="K9" s="69"/>
+      <c r="L9" s="69"/>
+      <c r="M9" s="70"/>
     </row>
     <row r="10" spans="1:13" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="49" t="s">
+      <c r="A10" s="60" t="s">
         <v>3</v>
       </c>
-      <c r="B10" s="51"/>
-      <c r="C10" s="88" t="s">
+      <c r="B10" s="62"/>
+      <c r="C10" s="104" t="s">
         <v>4</v>
       </c>
-      <c r="D10" s="89"/>
-      <c r="E10" s="89"/>
-      <c r="F10" s="89"/>
-      <c r="G10" s="90"/>
+      <c r="D10" s="105"/>
+      <c r="E10" s="105"/>
+      <c r="F10" s="105"/>
+      <c r="G10" s="106"/>
       <c r="H10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="I10" s="23"/>
-      <c r="J10" s="24"/>
-      <c r="K10" s="24"/>
-      <c r="L10" s="24"/>
-      <c r="M10" s="25"/>
+      <c r="I10" s="34"/>
+      <c r="J10" s="35"/>
+      <c r="K10" s="35"/>
+      <c r="L10" s="35"/>
+      <c r="M10" s="36"/>
     </row>
     <row r="11" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="49" t="s">
+      <c r="A11" s="60" t="s">
         <v>6</v>
       </c>
-      <c r="B11" s="51"/>
-      <c r="C11" s="98"/>
-      <c r="D11" s="99"/>
-      <c r="E11" s="99"/>
-      <c r="F11" s="99"/>
-      <c r="G11" s="99"/>
-      <c r="H11" s="100"/>
-      <c r="I11" s="101" t="s">
+      <c r="B11" s="62"/>
+      <c r="C11" s="114"/>
+      <c r="D11" s="115"/>
+      <c r="E11" s="115"/>
+      <c r="F11" s="115"/>
+      <c r="G11" s="115"/>
+      <c r="H11" s="116"/>
+      <c r="I11" s="117" t="s">
         <v>7</v>
       </c>
-      <c r="J11" s="102"/>
-      <c r="K11" s="63"/>
-      <c r="L11" s="64"/>
-      <c r="M11" s="65"/>
+      <c r="J11" s="118"/>
+      <c r="K11" s="76"/>
+      <c r="L11" s="77"/>
+      <c r="M11" s="78"/>
     </row>
     <row r="12" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="49" t="s">
+      <c r="A12" s="60" t="s">
         <v>8</v>
       </c>
-      <c r="B12" s="51"/>
+      <c r="B12" s="62"/>
       <c r="C12" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D12" s="55" t="s">
+      <c r="D12" s="68" t="s">
         <v>10</v>
       </c>
-      <c r="E12" s="57"/>
-      <c r="F12" s="103" t="s">
+      <c r="E12" s="70"/>
+      <c r="F12" s="119" t="s">
         <v>11</v>
       </c>
-      <c r="G12" s="104"/>
+      <c r="G12" s="120"/>
       <c r="H12" s="1"/>
-      <c r="I12" s="103" t="s">
+      <c r="I12" s="119" t="s">
         <v>12</v>
       </c>
-      <c r="J12" s="104"/>
-      <c r="K12" s="66"/>
-      <c r="L12" s="67"/>
-      <c r="M12" s="68"/>
+      <c r="J12" s="120"/>
+      <c r="K12" s="79"/>
+      <c r="L12" s="80"/>
+      <c r="M12" s="81"/>
     </row>
     <row r="13" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="49" t="s">
+      <c r="A13" s="60" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="51"/>
-      <c r="C13" s="91"/>
-      <c r="D13" s="92"/>
-      <c r="E13" s="92"/>
-      <c r="F13" s="93"/>
-      <c r="G13" s="91" t="s">
+      <c r="B13" s="62"/>
+      <c r="C13" s="107"/>
+      <c r="D13" s="108"/>
+      <c r="E13" s="108"/>
+      <c r="F13" s="109"/>
+      <c r="G13" s="107" t="s">
         <v>14</v>
       </c>
-      <c r="H13" s="92"/>
-      <c r="I13" s="93"/>
-      <c r="J13" s="161"/>
-      <c r="K13" s="162"/>
-      <c r="L13" s="162"/>
-      <c r="M13" s="163"/>
+      <c r="H13" s="108"/>
+      <c r="I13" s="109"/>
+      <c r="J13" s="82"/>
+      <c r="K13" s="83"/>
+      <c r="L13" s="83"/>
+      <c r="M13" s="84"/>
     </row>
     <row r="14" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="94" t="s">
+      <c r="A14" s="110" t="s">
         <v>15</v>
       </c>
-      <c r="B14" s="49" t="s">
+      <c r="B14" s="60" t="s">
         <v>16</v>
       </c>
-      <c r="C14" s="50"/>
-      <c r="D14" s="51"/>
-      <c r="E14" s="60"/>
-      <c r="F14" s="61"/>
-      <c r="G14" s="61"/>
-      <c r="H14" s="61"/>
-      <c r="I14" s="61"/>
-      <c r="J14" s="61"/>
-      <c r="K14" s="61"/>
-      <c r="L14" s="61"/>
-      <c r="M14" s="62"/>
+      <c r="C14" s="61"/>
+      <c r="D14" s="62"/>
+      <c r="E14" s="73"/>
+      <c r="F14" s="74"/>
+      <c r="G14" s="74"/>
+      <c r="H14" s="74"/>
+      <c r="I14" s="74"/>
+      <c r="J14" s="74"/>
+      <c r="K14" s="74"/>
+      <c r="L14" s="74"/>
+      <c r="M14" s="75"/>
     </row>
     <row r="15" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="76"/>
-      <c r="B15" s="95" t="s">
+      <c r="A15" s="92"/>
+      <c r="B15" s="111" t="s">
         <v>17</v>
       </c>
-      <c r="C15" s="96"/>
-      <c r="D15" s="97"/>
-      <c r="E15" s="69"/>
-      <c r="F15" s="70"/>
-      <c r="G15" s="70"/>
-      <c r="H15" s="70"/>
-      <c r="I15" s="70"/>
-      <c r="J15" s="70"/>
-      <c r="K15" s="70"/>
-      <c r="L15" s="70"/>
-      <c r="M15" s="71"/>
+      <c r="C15" s="112"/>
+      <c r="D15" s="113"/>
+      <c r="E15" s="85"/>
+      <c r="F15" s="86"/>
+      <c r="G15" s="86"/>
+      <c r="H15" s="86"/>
+      <c r="I15" s="86"/>
+      <c r="J15" s="86"/>
+      <c r="K15" s="86"/>
+      <c r="L15" s="86"/>
+      <c r="M15" s="87"/>
     </row>
     <row r="16" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="76"/>
-      <c r="B16" s="49" t="s">
+      <c r="A16" s="92"/>
+      <c r="B16" s="60" t="s">
         <v>18</v>
       </c>
-      <c r="C16" s="50"/>
-      <c r="D16" s="51"/>
-      <c r="E16" s="60"/>
-      <c r="F16" s="61"/>
-      <c r="G16" s="61"/>
-      <c r="H16" s="61"/>
-      <c r="I16" s="61"/>
-      <c r="J16" s="61"/>
-      <c r="K16" s="61"/>
-      <c r="L16" s="61"/>
-      <c r="M16" s="62"/>
+      <c r="C16" s="61"/>
+      <c r="D16" s="62"/>
+      <c r="E16" s="73"/>
+      <c r="F16" s="74"/>
+      <c r="G16" s="74"/>
+      <c r="H16" s="74"/>
+      <c r="I16" s="74"/>
+      <c r="J16" s="74"/>
+      <c r="K16" s="74"/>
+      <c r="L16" s="74"/>
+      <c r="M16" s="75"/>
     </row>
     <row r="17" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="76"/>
-      <c r="B17" s="49" t="s">
+      <c r="A17" s="92"/>
+      <c r="B17" s="60" t="s">
         <v>19</v>
       </c>
-      <c r="C17" s="50"/>
-      <c r="D17" s="51"/>
-      <c r="E17" s="60"/>
-      <c r="F17" s="61"/>
-      <c r="G17" s="61"/>
-      <c r="H17" s="61"/>
-      <c r="I17" s="61"/>
-      <c r="J17" s="61"/>
-      <c r="K17" s="61"/>
-      <c r="L17" s="61"/>
-      <c r="M17" s="62"/>
+      <c r="C17" s="61"/>
+      <c r="D17" s="62"/>
+      <c r="E17" s="73"/>
+      <c r="F17" s="74"/>
+      <c r="G17" s="74"/>
+      <c r="H17" s="74"/>
+      <c r="I17" s="74"/>
+      <c r="J17" s="74"/>
+      <c r="K17" s="74"/>
+      <c r="L17" s="74"/>
+      <c r="M17" s="75"/>
     </row>
     <row r="18" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="76"/>
-      <c r="B18" s="49" t="s">
+      <c r="A18" s="92"/>
+      <c r="B18" s="60" t="s">
         <v>20</v>
       </c>
-      <c r="C18" s="50"/>
-      <c r="D18" s="51"/>
-      <c r="E18" s="60"/>
-      <c r="F18" s="61"/>
-      <c r="G18" s="61"/>
-      <c r="H18" s="61"/>
-      <c r="I18" s="61"/>
-      <c r="J18" s="61"/>
-      <c r="K18" s="61"/>
-      <c r="L18" s="61"/>
-      <c r="M18" s="62"/>
+      <c r="C18" s="61"/>
+      <c r="D18" s="62"/>
+      <c r="E18" s="73"/>
+      <c r="F18" s="74"/>
+      <c r="G18" s="74"/>
+      <c r="H18" s="74"/>
+      <c r="I18" s="74"/>
+      <c r="J18" s="74"/>
+      <c r="K18" s="74"/>
+      <c r="L18" s="74"/>
+      <c r="M18" s="75"/>
     </row>
     <row r="19" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="76"/>
-      <c r="B19" s="49" t="s">
+      <c r="A19" s="92"/>
+      <c r="B19" s="60" t="s">
         <v>21</v>
       </c>
-      <c r="C19" s="50"/>
-      <c r="D19" s="51"/>
-      <c r="E19" s="60"/>
-      <c r="F19" s="61"/>
-      <c r="G19" s="61"/>
-      <c r="H19" s="61"/>
-      <c r="I19" s="61"/>
-      <c r="J19" s="61"/>
-      <c r="K19" s="61"/>
-      <c r="L19" s="61"/>
-      <c r="M19" s="62"/>
+      <c r="C19" s="61"/>
+      <c r="D19" s="62"/>
+      <c r="E19" s="73"/>
+      <c r="F19" s="74"/>
+      <c r="G19" s="74"/>
+      <c r="H19" s="74"/>
+      <c r="I19" s="74"/>
+      <c r="J19" s="74"/>
+      <c r="K19" s="74"/>
+      <c r="L19" s="74"/>
+      <c r="M19" s="75"/>
     </row>
     <row r="20" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="76"/>
-      <c r="B20" s="49" t="s">
+      <c r="A20" s="92"/>
+      <c r="B20" s="60" t="s">
         <v>22</v>
       </c>
-      <c r="C20" s="50"/>
-      <c r="D20" s="51"/>
-      <c r="E20" s="52"/>
-      <c r="F20" s="53"/>
-      <c r="G20" s="53"/>
-      <c r="H20" s="53"/>
-      <c r="I20" s="53"/>
-      <c r="J20" s="53"/>
-      <c r="K20" s="53"/>
-      <c r="L20" s="53"/>
-      <c r="M20" s="54"/>
+      <c r="C20" s="61"/>
+      <c r="D20" s="62"/>
+      <c r="E20" s="63"/>
+      <c r="F20" s="64"/>
+      <c r="G20" s="64"/>
+      <c r="H20" s="64"/>
+      <c r="I20" s="64"/>
+      <c r="J20" s="64"/>
+      <c r="K20" s="64"/>
+      <c r="L20" s="64"/>
+      <c r="M20" s="65"/>
     </row>
     <row r="21" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="76"/>
-      <c r="B21" s="49" t="s">
+      <c r="A21" s="92"/>
+      <c r="B21" s="60" t="s">
         <v>23</v>
       </c>
-      <c r="C21" s="50"/>
-      <c r="D21" s="51"/>
-      <c r="E21" s="52"/>
-      <c r="F21" s="53"/>
-      <c r="G21" s="53"/>
-      <c r="H21" s="53"/>
-      <c r="I21" s="53"/>
-      <c r="J21" s="53"/>
-      <c r="K21" s="53"/>
-      <c r="L21" s="53"/>
-      <c r="M21" s="54"/>
+      <c r="C21" s="61"/>
+      <c r="D21" s="62"/>
+      <c r="E21" s="63"/>
+      <c r="F21" s="64"/>
+      <c r="G21" s="64"/>
+      <c r="H21" s="64"/>
+      <c r="I21" s="64"/>
+      <c r="J21" s="64"/>
+      <c r="K21" s="64"/>
+      <c r="L21" s="64"/>
+      <c r="M21" s="65"/>
     </row>
     <row r="22" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="77"/>
-      <c r="B22" s="49" t="s">
+      <c r="A22" s="93"/>
+      <c r="B22" s="60" t="s">
         <v>24</v>
       </c>
-      <c r="C22" s="50"/>
-      <c r="D22" s="51"/>
-      <c r="E22" s="52"/>
-      <c r="F22" s="53"/>
-      <c r="G22" s="53"/>
-      <c r="H22" s="53"/>
-      <c r="I22" s="53"/>
-      <c r="J22" s="53"/>
-      <c r="K22" s="53"/>
-      <c r="L22" s="53"/>
-      <c r="M22" s="54"/>
+      <c r="C22" s="61"/>
+      <c r="D22" s="62"/>
+      <c r="E22" s="63"/>
+      <c r="F22" s="64"/>
+      <c r="G22" s="64"/>
+      <c r="H22" s="64"/>
+      <c r="I22" s="64"/>
+      <c r="J22" s="64"/>
+      <c r="K22" s="64"/>
+      <c r="L22" s="64"/>
+      <c r="M22" s="65"/>
     </row>
     <row r="23" spans="1:13" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="75" t="s">
+      <c r="A23" s="91" t="s">
         <v>25</v>
       </c>
-      <c r="B23" s="49" t="s">
+      <c r="B23" s="60" t="s">
         <v>26</v>
       </c>
-      <c r="C23" s="50"/>
-      <c r="D23" s="51"/>
-      <c r="E23" s="78" t="s">
+      <c r="C23" s="61"/>
+      <c r="D23" s="62"/>
+      <c r="E23" s="94" t="s">
         <v>27</v>
       </c>
-      <c r="F23" s="79"/>
-      <c r="G23" s="79"/>
-      <c r="H23" s="79"/>
-      <c r="I23" s="79"/>
-      <c r="J23" s="79"/>
-      <c r="K23" s="79"/>
-      <c r="L23" s="79"/>
-      <c r="M23" s="80"/>
+      <c r="F23" s="95"/>
+      <c r="G23" s="95"/>
+      <c r="H23" s="95"/>
+      <c r="I23" s="95"/>
+      <c r="J23" s="95"/>
+      <c r="K23" s="95"/>
+      <c r="L23" s="95"/>
+      <c r="M23" s="96"/>
     </row>
     <row r="24" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="76"/>
-      <c r="B24" s="49" t="s">
+      <c r="A24" s="92"/>
+      <c r="B24" s="60" t="s">
         <v>19</v>
       </c>
-      <c r="C24" s="50"/>
-      <c r="D24" s="51"/>
-      <c r="E24" s="26"/>
-      <c r="F24" s="27"/>
-      <c r="G24" s="27"/>
-      <c r="H24" s="27"/>
-      <c r="I24" s="27"/>
-      <c r="J24" s="27"/>
-      <c r="K24" s="27"/>
-      <c r="L24" s="27"/>
-      <c r="M24" s="28"/>
+      <c r="C24" s="61"/>
+      <c r="D24" s="62"/>
+      <c r="E24" s="37"/>
+      <c r="F24" s="38"/>
+      <c r="G24" s="38"/>
+      <c r="H24" s="38"/>
+      <c r="I24" s="38"/>
+      <c r="J24" s="38"/>
+      <c r="K24" s="38"/>
+      <c r="L24" s="38"/>
+      <c r="M24" s="39"/>
     </row>
     <row r="25" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="77"/>
-      <c r="B25" s="49" t="s">
+      <c r="A25" s="93"/>
+      <c r="B25" s="60" t="s">
         <v>22</v>
       </c>
-      <c r="C25" s="50"/>
-      <c r="D25" s="51"/>
-      <c r="E25" s="78" t="s">
+      <c r="C25" s="61"/>
+      <c r="D25" s="62"/>
+      <c r="E25" s="94" t="s">
         <v>28</v>
       </c>
-      <c r="F25" s="79"/>
-      <c r="G25" s="79"/>
-      <c r="H25" s="79"/>
-      <c r="I25" s="79"/>
-      <c r="J25" s="79"/>
-      <c r="K25" s="79"/>
-      <c r="L25" s="79"/>
-      <c r="M25" s="80"/>
+      <c r="F25" s="95"/>
+      <c r="G25" s="95"/>
+      <c r="H25" s="95"/>
+      <c r="I25" s="95"/>
+      <c r="J25" s="95"/>
+      <c r="K25" s="95"/>
+      <c r="L25" s="95"/>
+      <c r="M25" s="96"/>
     </row>
     <row r="26" spans="1:13" ht="25.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B26" s="49" t="s">
+      <c r="B26" s="60" t="s">
         <v>32</v>
       </c>
-      <c r="C26" s="50"/>
-      <c r="D26" s="51"/>
-      <c r="E26" s="60"/>
-      <c r="F26" s="61"/>
-      <c r="G26" s="61"/>
-      <c r="H26" s="61"/>
-      <c r="I26" s="61"/>
-      <c r="J26" s="61"/>
-      <c r="K26" s="61"/>
-      <c r="L26" s="61"/>
-      <c r="M26" s="62"/>
+      <c r="C26" s="61"/>
+      <c r="D26" s="62"/>
+      <c r="E26" s="73"/>
+      <c r="F26" s="74"/>
+      <c r="G26" s="74"/>
+      <c r="H26" s="74"/>
+      <c r="I26" s="74"/>
+      <c r="J26" s="74"/>
+      <c r="K26" s="74"/>
+      <c r="L26" s="74"/>
+      <c r="M26" s="75"/>
     </row>
     <row r="27" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="B27" s="49" t="s">
+      <c r="B27" s="60" t="s">
         <v>20</v>
       </c>
-      <c r="C27" s="50"/>
-      <c r="D27" s="51"/>
-      <c r="E27" s="60"/>
-      <c r="F27" s="61"/>
-      <c r="G27" s="61"/>
-      <c r="H27" s="61"/>
-      <c r="I27" s="61"/>
-      <c r="J27" s="61"/>
-      <c r="K27" s="61"/>
-      <c r="L27" s="61"/>
-      <c r="M27" s="62"/>
+      <c r="C27" s="61"/>
+      <c r="D27" s="62"/>
+      <c r="E27" s="73"/>
+      <c r="F27" s="74"/>
+      <c r="G27" s="74"/>
+      <c r="H27" s="74"/>
+      <c r="I27" s="74"/>
+      <c r="J27" s="74"/>
+      <c r="K27" s="74"/>
+      <c r="L27" s="74"/>
+      <c r="M27" s="75"/>
     </row>
     <row r="28" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="3"/>
-      <c r="B28" s="49" t="s">
+      <c r="B28" s="60" t="s">
         <v>33</v>
       </c>
-      <c r="C28" s="50"/>
-      <c r="D28" s="51"/>
-      <c r="E28" s="60"/>
-      <c r="F28" s="61"/>
-      <c r="G28" s="61"/>
-      <c r="H28" s="61"/>
-      <c r="I28" s="61"/>
-      <c r="J28" s="61"/>
-      <c r="K28" s="61"/>
-      <c r="L28" s="61"/>
-      <c r="M28" s="62"/>
+      <c r="C28" s="61"/>
+      <c r="D28" s="62"/>
+      <c r="E28" s="73"/>
+      <c r="F28" s="74"/>
+      <c r="G28" s="74"/>
+      <c r="H28" s="74"/>
+      <c r="I28" s="74"/>
+      <c r="J28" s="74"/>
+      <c r="K28" s="74"/>
+      <c r="L28" s="74"/>
+      <c r="M28" s="75"/>
     </row>
     <row r="29" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="3"/>
-      <c r="B29" s="49" t="s">
+      <c r="B29" s="60" t="s">
         <v>34</v>
       </c>
-      <c r="C29" s="50"/>
-      <c r="D29" s="51"/>
-      <c r="E29" s="60"/>
-      <c r="F29" s="61"/>
-      <c r="G29" s="61"/>
-      <c r="H29" s="61"/>
-      <c r="I29" s="61"/>
-      <c r="J29" s="61"/>
-      <c r="K29" s="61"/>
-      <c r="L29" s="61"/>
-      <c r="M29" s="62"/>
+      <c r="C29" s="61"/>
+      <c r="D29" s="62"/>
+      <c r="E29" s="73"/>
+      <c r="F29" s="74"/>
+      <c r="G29" s="74"/>
+      <c r="H29" s="74"/>
+      <c r="I29" s="74"/>
+      <c r="J29" s="74"/>
+      <c r="K29" s="74"/>
+      <c r="L29" s="74"/>
+      <c r="M29" s="75"/>
     </row>
     <row r="30" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="B30" s="49" t="s">
+      <c r="B30" s="60" t="s">
         <v>35</v>
       </c>
-      <c r="C30" s="50"/>
-      <c r="D30" s="51"/>
-      <c r="E30" s="60"/>
-      <c r="F30" s="61"/>
-      <c r="G30" s="61"/>
-      <c r="H30" s="61"/>
-      <c r="I30" s="61"/>
-      <c r="J30" s="61"/>
-      <c r="K30" s="61"/>
-      <c r="L30" s="61"/>
-      <c r="M30" s="62"/>
+      <c r="C30" s="61"/>
+      <c r="D30" s="62"/>
+      <c r="E30" s="73"/>
+      <c r="F30" s="74"/>
+      <c r="G30" s="74"/>
+      <c r="H30" s="74"/>
+      <c r="I30" s="74"/>
+      <c r="J30" s="74"/>
+      <c r="K30" s="74"/>
+      <c r="L30" s="74"/>
+      <c r="M30" s="75"/>
     </row>
     <row r="31" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="6"/>
-      <c r="B31" s="49" t="s">
+      <c r="B31" s="60" t="s">
         <v>36</v>
       </c>
-      <c r="C31" s="50"/>
-      <c r="D31" s="51"/>
-      <c r="E31" s="60"/>
-      <c r="F31" s="61"/>
-      <c r="G31" s="61"/>
-      <c r="H31" s="61"/>
-      <c r="I31" s="61"/>
-      <c r="J31" s="61"/>
-      <c r="K31" s="61"/>
-      <c r="L31" s="61"/>
-      <c r="M31" s="62"/>
+      <c r="C31" s="61"/>
+      <c r="D31" s="62"/>
+      <c r="E31" s="73"/>
+      <c r="F31" s="74"/>
+      <c r="G31" s="74"/>
+      <c r="H31" s="74"/>
+      <c r="I31" s="74"/>
+      <c r="J31" s="74"/>
+      <c r="K31" s="74"/>
+      <c r="L31" s="74"/>
+      <c r="M31" s="75"/>
     </row>
     <row r="32" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="6"/>
-      <c r="B32" s="49" t="s">
+      <c r="B32" s="60" t="s">
         <v>19</v>
       </c>
-      <c r="C32" s="50"/>
-      <c r="D32" s="51"/>
-      <c r="E32" s="52"/>
-      <c r="F32" s="53"/>
-      <c r="G32" s="53"/>
-      <c r="H32" s="53"/>
-      <c r="I32" s="53"/>
-      <c r="J32" s="53"/>
-      <c r="K32" s="53"/>
-      <c r="L32" s="53"/>
-      <c r="M32" s="54"/>
+      <c r="C32" s="61"/>
+      <c r="D32" s="62"/>
+      <c r="E32" s="63"/>
+      <c r="F32" s="64"/>
+      <c r="G32" s="64"/>
+      <c r="H32" s="64"/>
+      <c r="I32" s="64"/>
+      <c r="J32" s="64"/>
+      <c r="K32" s="64"/>
+      <c r="L32" s="64"/>
+      <c r="M32" s="65"/>
     </row>
     <row r="33" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="6"/>
-      <c r="B33" s="49" t="s">
+      <c r="B33" s="60" t="s">
         <v>37</v>
       </c>
-      <c r="C33" s="50"/>
-      <c r="D33" s="51"/>
-      <c r="E33" s="60"/>
-      <c r="F33" s="61"/>
-      <c r="G33" s="61"/>
-      <c r="H33" s="61"/>
-      <c r="I33" s="61"/>
-      <c r="J33" s="61"/>
-      <c r="K33" s="61"/>
-      <c r="L33" s="61"/>
-      <c r="M33" s="62"/>
+      <c r="C33" s="61"/>
+      <c r="D33" s="62"/>
+      <c r="E33" s="73"/>
+      <c r="F33" s="74"/>
+      <c r="G33" s="74"/>
+      <c r="H33" s="74"/>
+      <c r="I33" s="74"/>
+      <c r="J33" s="74"/>
+      <c r="K33" s="74"/>
+      <c r="L33" s="74"/>
+      <c r="M33" s="75"/>
     </row>
     <row r="34" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="7"/>
-      <c r="B34" s="72" t="s">
+      <c r="B34" s="88" t="s">
         <v>38</v>
       </c>
-      <c r="C34" s="73"/>
-      <c r="D34" s="74"/>
-      <c r="E34" s="52"/>
-      <c r="F34" s="53"/>
-      <c r="G34" s="53"/>
-      <c r="H34" s="53"/>
-      <c r="I34" s="53"/>
-      <c r="J34" s="53"/>
-      <c r="K34" s="53"/>
-      <c r="L34" s="53"/>
-      <c r="M34" s="54"/>
+      <c r="C34" s="89"/>
+      <c r="D34" s="90"/>
+      <c r="E34" s="63"/>
+      <c r="F34" s="64"/>
+      <c r="G34" s="64"/>
+      <c r="H34" s="64"/>
+      <c r="I34" s="64"/>
+      <c r="J34" s="64"/>
+      <c r="K34" s="64"/>
+      <c r="L34" s="64"/>
+      <c r="M34" s="65"/>
     </row>
     <row r="35" spans="1:13" ht="25.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="B35" s="46" t="s">
+      <c r="B35" s="57" t="s">
         <v>41</v>
       </c>
-      <c r="C35" s="47"/>
-      <c r="D35" s="48"/>
-      <c r="E35" s="52"/>
-      <c r="F35" s="53"/>
-      <c r="G35" s="53"/>
-      <c r="H35" s="53"/>
-      <c r="I35" s="53"/>
-      <c r="J35" s="53"/>
-      <c r="K35" s="53"/>
-      <c r="L35" s="53"/>
-      <c r="M35" s="54"/>
+      <c r="C35" s="58"/>
+      <c r="D35" s="59"/>
+      <c r="E35" s="63"/>
+      <c r="F35" s="64"/>
+      <c r="G35" s="64"/>
+      <c r="H35" s="64"/>
+      <c r="I35" s="64"/>
+      <c r="J35" s="64"/>
+      <c r="K35" s="64"/>
+      <c r="L35" s="64"/>
+      <c r="M35" s="65"/>
     </row>
     <row r="36" spans="1:13" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="B36" s="49" t="s">
+      <c r="B36" s="60" t="s">
         <v>42</v>
       </c>
-      <c r="C36" s="50"/>
-      <c r="D36" s="51"/>
-      <c r="E36" s="52"/>
-      <c r="F36" s="53"/>
-      <c r="G36" s="53"/>
-      <c r="H36" s="53"/>
-      <c r="I36" s="53"/>
-      <c r="J36" s="53"/>
-      <c r="K36" s="53"/>
-      <c r="L36" s="53"/>
-      <c r="M36" s="54"/>
+      <c r="C36" s="61"/>
+      <c r="D36" s="62"/>
+      <c r="E36" s="63"/>
+      <c r="F36" s="64"/>
+      <c r="G36" s="64"/>
+      <c r="H36" s="64"/>
+      <c r="I36" s="64"/>
+      <c r="J36" s="64"/>
+      <c r="K36" s="64"/>
+      <c r="L36" s="64"/>
+      <c r="M36" s="65"/>
     </row>
     <row r="37" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="10"/>
-      <c r="B37" s="49" t="s">
+      <c r="B37" s="60" t="s">
         <v>19</v>
       </c>
-      <c r="C37" s="50"/>
-      <c r="D37" s="51"/>
-      <c r="E37" s="52"/>
-      <c r="F37" s="53"/>
-      <c r="G37" s="53"/>
-      <c r="H37" s="53"/>
-      <c r="I37" s="53"/>
-      <c r="J37" s="53"/>
-      <c r="K37" s="53"/>
-      <c r="L37" s="53"/>
-      <c r="M37" s="54"/>
+      <c r="C37" s="61"/>
+      <c r="D37" s="62"/>
+      <c r="E37" s="63"/>
+      <c r="F37" s="64"/>
+      <c r="G37" s="64"/>
+      <c r="H37" s="64"/>
+      <c r="I37" s="64"/>
+      <c r="J37" s="64"/>
+      <c r="K37" s="64"/>
+      <c r="L37" s="64"/>
+      <c r="M37" s="65"/>
     </row>
     <row r="38" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="21" t="s">
+      <c r="A38" s="33" t="s">
         <v>43</v>
       </c>
-      <c r="B38" s="21"/>
-      <c r="C38" s="21"/>
-      <c r="D38" s="21"/>
-      <c r="E38" s="21"/>
-      <c r="F38" s="21"/>
-      <c r="G38" s="21"/>
-      <c r="H38" s="21"/>
-      <c r="I38" s="21"/>
-      <c r="J38" s="21"/>
-      <c r="K38" s="21"/>
-      <c r="L38" s="21"/>
-      <c r="M38" s="21"/>
+      <c r="B38" s="33"/>
+      <c r="C38" s="33"/>
+      <c r="D38" s="33"/>
+      <c r="E38" s="33"/>
+      <c r="F38" s="33"/>
+      <c r="G38" s="33"/>
+      <c r="H38" s="33"/>
+      <c r="I38" s="33"/>
+      <c r="J38" s="33"/>
+      <c r="K38" s="33"/>
+      <c r="L38" s="33"/>
+      <c r="M38" s="33"/>
     </row>
     <row r="39" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="21"/>
-      <c r="B39" s="21"/>
-      <c r="C39" s="21"/>
-      <c r="D39" s="21"/>
-      <c r="E39" s="21"/>
-      <c r="F39" s="21"/>
-      <c r="G39" s="21"/>
-      <c r="H39" s="21"/>
-      <c r="I39" s="21"/>
-      <c r="J39" s="21"/>
-      <c r="K39" s="21"/>
-      <c r="L39" s="21"/>
-      <c r="M39" s="21"/>
+      <c r="A39" s="33"/>
+      <c r="B39" s="33"/>
+      <c r="C39" s="33"/>
+      <c r="D39" s="33"/>
+      <c r="E39" s="33"/>
+      <c r="F39" s="33"/>
+      <c r="G39" s="33"/>
+      <c r="H39" s="33"/>
+      <c r="I39" s="33"/>
+      <c r="J39" s="33"/>
+      <c r="K39" s="33"/>
+      <c r="L39" s="33"/>
+      <c r="M39" s="33"/>
     </row>
     <row r="40" spans="1:13" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="21"/>
-      <c r="B40" s="21"/>
-      <c r="C40" s="21"/>
-      <c r="D40" s="21"/>
-      <c r="E40" s="21"/>
-      <c r="F40" s="21"/>
-      <c r="G40" s="21"/>
-      <c r="H40" s="21"/>
-      <c r="I40" s="21"/>
-      <c r="J40" s="21"/>
-      <c r="K40" s="21"/>
-      <c r="L40" s="21"/>
-      <c r="M40" s="21"/>
+      <c r="A40" s="33"/>
+      <c r="B40" s="33"/>
+      <c r="C40" s="33"/>
+      <c r="D40" s="33"/>
+      <c r="E40" s="33"/>
+      <c r="F40" s="33"/>
+      <c r="G40" s="33"/>
+      <c r="H40" s="33"/>
+      <c r="I40" s="33"/>
+      <c r="J40" s="33"/>
+      <c r="K40" s="33"/>
+      <c r="L40" s="33"/>
+      <c r="M40" s="33"/>
     </row>
     <row r="41" spans="1:13" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="11"/>
-      <c r="B41" s="129" t="s">
+      <c r="B41" s="145" t="s">
         <v>65</v>
       </c>
-      <c r="C41" s="129"/>
-      <c r="D41" s="129"/>
-      <c r="E41" s="129"/>
-      <c r="F41" s="129"/>
-      <c r="G41" s="129"/>
-      <c r="H41" s="129"/>
-      <c r="I41" s="129"/>
-      <c r="J41" s="129"/>
+      <c r="C41" s="145"/>
+      <c r="D41" s="145"/>
+      <c r="E41" s="145"/>
+      <c r="F41" s="145"/>
+      <c r="G41" s="145"/>
+      <c r="H41" s="145"/>
+      <c r="I41" s="145"/>
+      <c r="J41" s="145"/>
       <c r="K41" s="11"/>
       <c r="L41" s="11"/>
       <c r="M41" s="11"/>
     </row>
     <row r="42" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B42" s="129" t="s">
+      <c r="B42" s="145" t="s">
         <v>66</v>
       </c>
-      <c r="C42" s="129"/>
-      <c r="D42" s="129"/>
-      <c r="E42" s="129"/>
-      <c r="F42" s="129"/>
-      <c r="G42" s="129"/>
-      <c r="H42" s="129"/>
-      <c r="I42" s="129"/>
-      <c r="J42" s="129"/>
+      <c r="C42" s="145"/>
+      <c r="D42" s="145"/>
+      <c r="E42" s="145"/>
+      <c r="F42" s="145"/>
+      <c r="G42" s="145"/>
+      <c r="H42" s="145"/>
+      <c r="I42" s="145"/>
+      <c r="J42" s="145"/>
       <c r="L42" s="18"/>
     </row>
     <row r="43" spans="1:13" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B43" s="36" t="s">
+      <c r="B43" s="47" t="s">
+        <v>72</v>
+      </c>
+      <c r="C43" s="48"/>
+      <c r="D43" s="22"/>
+      <c r="E43" s="149" t="s">
+        <v>75</v>
+      </c>
+      <c r="F43" s="150"/>
+      <c r="G43" s="151"/>
+      <c r="H43" s="152"/>
+      <c r="I43" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="J43" s="19"/>
+    </row>
+    <row r="44" spans="1:13" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B44" s="49" t="s">
         <v>73</v>
       </c>
-      <c r="C43" s="37"/>
-      <c r="D43" s="164"/>
-      <c r="E43" s="133" t="s">
-        <v>76</v>
-      </c>
-      <c r="F43" s="134"/>
-      <c r="G43" s="165"/>
-      <c r="H43" s="166"/>
-      <c r="I43" s="17" t="s">
-        <v>77</v>
-      </c>
-      <c r="J43" s="19"/>
-    </row>
-    <row r="44" spans="1:13" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B44" s="38" t="s">
+      <c r="C44" s="50"/>
+      <c r="D44" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="E44" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="C44" s="39"/>
-      <c r="D44" s="167" t="s">
-        <v>11</v>
-      </c>
-      <c r="E44" s="40" t="s">
-        <v>75</v>
-      </c>
-      <c r="F44" s="41"/>
-      <c r="G44" s="42"/>
-      <c r="H44" s="43"/>
-      <c r="I44" s="44"/>
-      <c r="J44" s="45"/>
+      <c r="F44" s="52"/>
+      <c r="G44" s="53"/>
+      <c r="H44" s="54"/>
+      <c r="I44" s="55"/>
+      <c r="J44" s="56"/>
     </row>
     <row r="45" spans="1:13" ht="2.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="46" spans="1:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="11"/>
-      <c r="B46" s="130" t="s">
+      <c r="B46" s="146" t="s">
         <v>45</v>
       </c>
-      <c r="C46" s="131"/>
-      <c r="D46" s="131"/>
-      <c r="E46" s="131"/>
-      <c r="F46" s="131"/>
-      <c r="G46" s="131"/>
-      <c r="H46" s="131"/>
-      <c r="I46" s="131"/>
-      <c r="J46" s="132"/>
+      <c r="C46" s="147"/>
+      <c r="D46" s="147"/>
+      <c r="E46" s="147"/>
+      <c r="F46" s="147"/>
+      <c r="G46" s="147"/>
+      <c r="H46" s="147"/>
+      <c r="I46" s="147"/>
+      <c r="J46" s="148"/>
       <c r="K46" s="11"/>
       <c r="L46" s="11"/>
       <c r="M46" s="11"/>
     </row>
     <row r="47" spans="1:13" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="11"/>
-      <c r="B47" s="121" t="s">
+      <c r="B47" s="137" t="s">
         <v>46</v>
       </c>
-      <c r="C47" s="122"/>
-      <c r="D47" s="103" t="s">
+      <c r="C47" s="138"/>
+      <c r="D47" s="119" t="s">
         <v>47</v>
       </c>
-      <c r="E47" s="123"/>
-      <c r="F47" s="123"/>
-      <c r="G47" s="104"/>
-      <c r="H47" s="108" t="s">
+      <c r="E47" s="139"/>
+      <c r="F47" s="139"/>
+      <c r="G47" s="120"/>
+      <c r="H47" s="124" t="s">
         <v>48</v>
       </c>
-      <c r="I47" s="112"/>
-      <c r="J47" s="109"/>
+      <c r="I47" s="128"/>
+      <c r="J47" s="125"/>
       <c r="K47" s="11"/>
       <c r="L47" s="11"/>
       <c r="M47" s="11"/>
     </row>
     <row r="48" spans="1:13" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="11"/>
-      <c r="B48" s="101"/>
-      <c r="C48" s="102"/>
-      <c r="D48" s="124" t="s">
+      <c r="B48" s="117"/>
+      <c r="C48" s="118"/>
+      <c r="D48" s="140" t="s">
         <v>49</v>
       </c>
-      <c r="E48" s="125"/>
-      <c r="F48" s="124" t="s">
+      <c r="E48" s="141"/>
+      <c r="F48" s="140" t="s">
         <v>50</v>
       </c>
-      <c r="G48" s="125"/>
-      <c r="H48" s="110"/>
-      <c r="I48" s="113"/>
-      <c r="J48" s="111"/>
+      <c r="G48" s="141"/>
+      <c r="H48" s="126"/>
+      <c r="I48" s="129"/>
+      <c r="J48" s="127"/>
       <c r="K48" s="11"/>
       <c r="L48" s="11"/>
       <c r="M48" s="11"/>
     </row>
     <row r="49" spans="1:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="13"/>
-      <c r="B49" s="84" t="s">
+      <c r="B49" s="100" t="s">
         <v>51</v>
       </c>
-      <c r="C49" s="85"/>
-      <c r="D49" s="86"/>
-      <c r="E49" s="87"/>
-      <c r="F49" s="86"/>
-      <c r="G49" s="87"/>
-      <c r="H49" s="126"/>
-      <c r="I49" s="127"/>
-      <c r="J49" s="128"/>
+      <c r="C49" s="101"/>
+      <c r="D49" s="102"/>
+      <c r="E49" s="103"/>
+      <c r="F49" s="102"/>
+      <c r="G49" s="103"/>
+      <c r="H49" s="142"/>
+      <c r="I49" s="143"/>
+      <c r="J49" s="144"/>
       <c r="K49" s="13"/>
       <c r="L49" s="13"/>
       <c r="M49" s="13"/>
     </row>
     <row r="50" spans="1:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="13"/>
-      <c r="B50" s="84" t="s">
+      <c r="B50" s="100" t="s">
         <v>52</v>
       </c>
-      <c r="C50" s="85"/>
-      <c r="D50" s="86"/>
-      <c r="E50" s="87"/>
-      <c r="F50" s="29"/>
-      <c r="G50" s="30"/>
-      <c r="H50" s="81"/>
-      <c r="I50" s="82"/>
-      <c r="J50" s="83"/>
+      <c r="C50" s="101"/>
+      <c r="D50" s="102"/>
+      <c r="E50" s="103"/>
+      <c r="F50" s="40"/>
+      <c r="G50" s="41"/>
+      <c r="H50" s="97"/>
+      <c r="I50" s="98"/>
+      <c r="J50" s="99"/>
       <c r="K50" s="13"/>
       <c r="L50" s="13"/>
       <c r="M50" s="13"/>
     </row>
     <row r="51" spans="1:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="13"/>
-      <c r="B51" s="84" t="s">
+      <c r="B51" s="100" t="s">
         <v>53</v>
       </c>
-      <c r="C51" s="85"/>
-      <c r="D51" s="86"/>
-      <c r="E51" s="87"/>
-      <c r="F51" s="86"/>
-      <c r="G51" s="87"/>
-      <c r="H51" s="81"/>
-      <c r="I51" s="82"/>
-      <c r="J51" s="83"/>
+      <c r="C51" s="101"/>
+      <c r="D51" s="102"/>
+      <c r="E51" s="103"/>
+      <c r="F51" s="102"/>
+      <c r="G51" s="103"/>
+      <c r="H51" s="97"/>
+      <c r="I51" s="98"/>
+      <c r="J51" s="99"/>
       <c r="K51" s="13"/>
       <c r="L51" s="13"/>
       <c r="M51" s="13"/>
     </row>
     <row r="52" spans="1:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="13"/>
-      <c r="B52" s="135" t="s">
+      <c r="B52" s="156" t="s">
         <v>64</v>
       </c>
-      <c r="C52" s="136"/>
-      <c r="D52" s="119"/>
-      <c r="E52" s="120"/>
-      <c r="F52" s="119"/>
-      <c r="G52" s="120"/>
-      <c r="H52" s="23"/>
-      <c r="I52" s="24"/>
-      <c r="J52" s="25"/>
+      <c r="C52" s="157"/>
+      <c r="D52" s="135"/>
+      <c r="E52" s="136"/>
+      <c r="F52" s="135"/>
+      <c r="G52" s="136"/>
+      <c r="H52" s="34"/>
+      <c r="I52" s="35"/>
+      <c r="J52" s="36"/>
       <c r="K52" s="13"/>
       <c r="L52" s="13"/>
       <c r="M52" s="13"/>
     </row>
     <row r="53" spans="1:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="13"/>
-      <c r="B53" s="84" t="s">
+      <c r="B53" s="100" t="s">
         <v>54</v>
       </c>
-      <c r="C53" s="85"/>
-      <c r="D53" s="86"/>
-      <c r="E53" s="87"/>
-      <c r="F53" s="86"/>
-      <c r="G53" s="87"/>
-      <c r="H53" s="105"/>
-      <c r="I53" s="106"/>
-      <c r="J53" s="107"/>
+      <c r="C53" s="101"/>
+      <c r="D53" s="102"/>
+      <c r="E53" s="103"/>
+      <c r="F53" s="102"/>
+      <c r="G53" s="103"/>
+      <c r="H53" s="121"/>
+      <c r="I53" s="122"/>
+      <c r="J53" s="123"/>
       <c r="K53" s="13"/>
       <c r="L53" s="13"/>
       <c r="M53" s="13"/>
     </row>
     <row r="54" spans="1:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="13"/>
-      <c r="B54" s="84" t="s">
+      <c r="B54" s="100" t="s">
         <v>55</v>
       </c>
-      <c r="C54" s="85"/>
-      <c r="D54" s="86"/>
-      <c r="E54" s="87"/>
-      <c r="F54" s="86"/>
-      <c r="G54" s="87"/>
-      <c r="H54" s="81"/>
-      <c r="I54" s="82"/>
-      <c r="J54" s="83"/>
+      <c r="C54" s="101"/>
+      <c r="D54" s="102"/>
+      <c r="E54" s="103"/>
+      <c r="F54" s="102"/>
+      <c r="G54" s="103"/>
+      <c r="H54" s="97"/>
+      <c r="I54" s="98"/>
+      <c r="J54" s="99"/>
       <c r="K54" s="13"/>
       <c r="L54" s="13"/>
       <c r="M54" s="13"/>
     </row>
     <row r="55" spans="1:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A55" s="13"/>
-      <c r="B55" s="84" t="s">
+      <c r="B55" s="100" t="s">
         <v>56</v>
       </c>
-      <c r="C55" s="85"/>
-      <c r="D55" s="86"/>
-      <c r="E55" s="87"/>
-      <c r="F55" s="86"/>
-      <c r="G55" s="87"/>
-      <c r="H55" s="81"/>
-      <c r="I55" s="82"/>
-      <c r="J55" s="83"/>
+      <c r="C55" s="101"/>
+      <c r="D55" s="102"/>
+      <c r="E55" s="103"/>
+      <c r="F55" s="102"/>
+      <c r="G55" s="103"/>
+      <c r="H55" s="97"/>
+      <c r="I55" s="98"/>
+      <c r="J55" s="99"/>
       <c r="K55" s="13"/>
       <c r="L55" s="13"/>
       <c r="M55" s="13"/>
     </row>
     <row r="56" spans="1:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A56" s="13"/>
-      <c r="B56" s="137" t="s">
+      <c r="B56" s="158" t="s">
         <v>57</v>
       </c>
-      <c r="C56" s="138"/>
-      <c r="D56" s="139"/>
-      <c r="E56" s="140"/>
-      <c r="F56" s="139"/>
-      <c r="G56" s="140"/>
-      <c r="H56" s="141"/>
-      <c r="I56" s="142"/>
-      <c r="J56" s="143"/>
+      <c r="C56" s="159"/>
+      <c r="D56" s="160"/>
+      <c r="E56" s="161"/>
+      <c r="F56" s="160"/>
+      <c r="G56" s="161"/>
+      <c r="H56" s="162"/>
+      <c r="I56" s="163"/>
+      <c r="J56" s="164"/>
       <c r="K56" s="13"/>
       <c r="L56" s="13"/>
       <c r="M56" s="13"/>
     </row>
     <row r="57" spans="1:13" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57" s="13"/>
-      <c r="B57" s="116" t="s">
+      <c r="B57" s="132" t="s">
         <v>58</v>
       </c>
-      <c r="C57" s="117"/>
-      <c r="D57" s="117"/>
-      <c r="E57" s="117"/>
-      <c r="F57" s="117"/>
-      <c r="G57" s="117"/>
-      <c r="H57" s="117"/>
-      <c r="I57" s="117"/>
-      <c r="J57" s="118"/>
+      <c r="C57" s="133"/>
+      <c r="D57" s="133"/>
+      <c r="E57" s="133"/>
+      <c r="F57" s="133"/>
+      <c r="G57" s="133"/>
+      <c r="H57" s="133"/>
+      <c r="I57" s="133"/>
+      <c r="J57" s="134"/>
       <c r="K57" s="13"/>
       <c r="L57" s="13"/>
       <c r="M57" s="13"/>
     </row>
     <row r="58" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A58" s="13"/>
-      <c r="B58" s="108" t="s">
+      <c r="B58" s="124" t="s">
         <v>46</v>
       </c>
-      <c r="C58" s="109"/>
-      <c r="D58" s="26" t="s">
+      <c r="C58" s="125"/>
+      <c r="D58" s="37" t="s">
         <v>47</v>
       </c>
-      <c r="E58" s="27"/>
-      <c r="F58" s="27"/>
-      <c r="G58" s="28"/>
-      <c r="H58" s="108" t="s">
+      <c r="E58" s="38"/>
+      <c r="F58" s="38"/>
+      <c r="G58" s="39"/>
+      <c r="H58" s="124" t="s">
         <v>48</v>
       </c>
-      <c r="I58" s="112"/>
-      <c r="J58" s="109"/>
+      <c r="I58" s="128"/>
+      <c r="J58" s="125"/>
       <c r="K58" s="13"/>
       <c r="L58" s="13"/>
       <c r="M58" s="13"/>
     </row>
     <row r="59" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A59" s="13"/>
-      <c r="B59" s="110"/>
-      <c r="C59" s="111"/>
-      <c r="D59" s="114" t="s">
+      <c r="B59" s="126"/>
+      <c r="C59" s="127"/>
+      <c r="D59" s="130" t="s">
         <v>49</v>
       </c>
-      <c r="E59" s="115"/>
-      <c r="F59" s="114" t="s">
+      <c r="E59" s="131"/>
+      <c r="F59" s="130" t="s">
         <v>50</v>
       </c>
-      <c r="G59" s="115"/>
-      <c r="H59" s="110"/>
-      <c r="I59" s="113"/>
-      <c r="J59" s="111"/>
+      <c r="G59" s="131"/>
+      <c r="H59" s="126"/>
+      <c r="I59" s="129"/>
+      <c r="J59" s="127"/>
       <c r="K59" s="13"/>
       <c r="L59" s="13"/>
       <c r="M59" s="13"/>
     </row>
     <row r="60" spans="1:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A60" s="13"/>
-      <c r="B60" s="84" t="s">
+      <c r="B60" s="100" t="s">
         <v>59</v>
       </c>
-      <c r="C60" s="85"/>
-      <c r="D60" s="86"/>
-      <c r="E60" s="87"/>
-      <c r="F60" s="86"/>
-      <c r="G60" s="87"/>
-      <c r="H60" s="105"/>
-      <c r="I60" s="106"/>
-      <c r="J60" s="107"/>
+      <c r="C60" s="101"/>
+      <c r="D60" s="102"/>
+      <c r="E60" s="103"/>
+      <c r="F60" s="102"/>
+      <c r="G60" s="103"/>
+      <c r="H60" s="121"/>
+      <c r="I60" s="122"/>
+      <c r="J60" s="123"/>
       <c r="K60" s="13"/>
       <c r="L60" s="13"/>
       <c r="M60" s="13"/>
     </row>
     <row r="61" spans="1:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A61" s="13"/>
-      <c r="B61" s="84" t="s">
+      <c r="B61" s="100" t="s">
         <v>60</v>
       </c>
-      <c r="C61" s="85"/>
-      <c r="D61" s="86"/>
-      <c r="E61" s="87"/>
-      <c r="F61" s="86"/>
-      <c r="G61" s="87"/>
-      <c r="H61" s="105"/>
-      <c r="I61" s="106"/>
-      <c r="J61" s="107"/>
+      <c r="C61" s="101"/>
+      <c r="D61" s="102"/>
+      <c r="E61" s="103"/>
+      <c r="F61" s="102"/>
+      <c r="G61" s="103"/>
+      <c r="H61" s="121"/>
+      <c r="I61" s="122"/>
+      <c r="J61" s="123"/>
       <c r="K61" s="13"/>
       <c r="L61" s="13"/>
       <c r="M61" s="13"/>
     </row>
     <row r="62" spans="1:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A62" s="13"/>
-      <c r="B62" s="84" t="s">
+      <c r="B62" s="100" t="s">
         <v>61</v>
       </c>
-      <c r="C62" s="85"/>
-      <c r="D62" s="86"/>
-      <c r="E62" s="87"/>
-      <c r="F62" s="86"/>
-      <c r="G62" s="87"/>
-      <c r="H62" s="105"/>
-      <c r="I62" s="106"/>
-      <c r="J62" s="107"/>
+      <c r="C62" s="101"/>
+      <c r="D62" s="102"/>
+      <c r="E62" s="103"/>
+      <c r="F62" s="102"/>
+      <c r="G62" s="103"/>
+      <c r="H62" s="121"/>
+      <c r="I62" s="122"/>
+      <c r="J62" s="123"/>
       <c r="K62" s="13"/>
       <c r="L62" s="13"/>
       <c r="M62" s="13"/>
     </row>
     <row r="63" spans="1:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A63" s="13"/>
-      <c r="B63" s="84" t="s">
+      <c r="B63" s="100" t="s">
         <v>62</v>
       </c>
-      <c r="C63" s="85"/>
-      <c r="D63" s="86"/>
-      <c r="E63" s="87"/>
-      <c r="F63" s="86"/>
-      <c r="G63" s="87"/>
-      <c r="H63" s="105"/>
-      <c r="I63" s="106"/>
-      <c r="J63" s="107"/>
+      <c r="C63" s="101"/>
+      <c r="D63" s="102"/>
+      <c r="E63" s="103"/>
+      <c r="F63" s="102"/>
+      <c r="G63" s="103"/>
+      <c r="H63" s="121"/>
+      <c r="I63" s="122"/>
+      <c r="J63" s="123"/>
       <c r="K63" s="13"/>
       <c r="L63" s="13"/>
       <c r="M63" s="13"/>
     </row>
     <row r="64" spans="1:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A64" s="13"/>
-      <c r="B64" s="84" t="s">
+      <c r="B64" s="100" t="s">
         <v>63</v>
       </c>
-      <c r="C64" s="85"/>
-      <c r="D64" s="86"/>
-      <c r="E64" s="87"/>
-      <c r="F64" s="86"/>
-      <c r="G64" s="87"/>
-      <c r="H64" s="105"/>
-      <c r="I64" s="106"/>
-      <c r="J64" s="107"/>
+      <c r="C64" s="101"/>
+      <c r="D64" s="102"/>
+      <c r="E64" s="103"/>
+      <c r="F64" s="102"/>
+      <c r="G64" s="103"/>
+      <c r="H64" s="121"/>
+      <c r="I64" s="122"/>
+      <c r="J64" s="123"/>
       <c r="K64" s="13"/>
       <c r="L64" s="13"/>
       <c r="M64" s="13"/>
@@ -3129,51 +3092,51 @@
     </row>
     <row r="66" spans="1:13" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A66" s="13"/>
-      <c r="B66" s="26" t="s">
+      <c r="B66" s="37" t="s">
         <v>67</v>
       </c>
-      <c r="C66" s="27"/>
-      <c r="D66" s="27"/>
-      <c r="E66" s="27"/>
-      <c r="F66" s="27"/>
-      <c r="G66" s="27"/>
-      <c r="H66" s="27"/>
-      <c r="I66" s="27"/>
-      <c r="J66" s="28"/>
+      <c r="C66" s="38"/>
+      <c r="D66" s="38"/>
+      <c r="E66" s="38"/>
+      <c r="F66" s="38"/>
+      <c r="G66" s="38"/>
+      <c r="H66" s="38"/>
+      <c r="I66" s="38"/>
+      <c r="J66" s="39"/>
       <c r="K66" s="13"/>
       <c r="L66" s="13"/>
       <c r="M66" s="13"/>
     </row>
     <row r="67" spans="1:13" ht="72" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A67" s="13"/>
-      <c r="B67" s="49" t="s">
+      <c r="B67" s="60" t="s">
         <v>68</v>
       </c>
-      <c r="C67" s="51"/>
-      <c r="D67" s="144"/>
-      <c r="E67" s="145"/>
-      <c r="F67" s="145"/>
-      <c r="G67" s="145"/>
-      <c r="H67" s="145"/>
-      <c r="I67" s="145"/>
-      <c r="J67" s="146"/>
+      <c r="C67" s="62"/>
+      <c r="D67" s="153"/>
+      <c r="E67" s="154"/>
+      <c r="F67" s="154"/>
+      <c r="G67" s="154"/>
+      <c r="H67" s="154"/>
+      <c r="I67" s="154"/>
+      <c r="J67" s="155"/>
       <c r="K67" s="13"/>
       <c r="L67" s="13"/>
       <c r="M67" s="13"/>
     </row>
     <row r="68" spans="1:13" ht="72" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A68" s="13"/>
-      <c r="B68" s="49" t="s">
+      <c r="B68" s="60" t="s">
         <v>69</v>
       </c>
-      <c r="C68" s="51"/>
-      <c r="D68" s="144"/>
-      <c r="E68" s="145"/>
-      <c r="F68" s="145"/>
-      <c r="G68" s="145"/>
-      <c r="H68" s="145"/>
-      <c r="I68" s="145"/>
-      <c r="J68" s="146"/>
+      <c r="C68" s="62"/>
+      <c r="D68" s="153"/>
+      <c r="E68" s="154"/>
+      <c r="F68" s="154"/>
+      <c r="G68" s="154"/>
+      <c r="H68" s="154"/>
+      <c r="I68" s="154"/>
+      <c r="J68" s="155"/>
       <c r="K68" s="13"/>
       <c r="L68" s="13"/>
       <c r="M68" s="13"/>
@@ -3195,51 +3158,51 @@
     </row>
     <row r="70" spans="1:13" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A70" s="13"/>
-      <c r="B70" s="26" t="s">
+      <c r="B70" s="37" t="s">
         <v>70</v>
       </c>
-      <c r="C70" s="27"/>
-      <c r="D70" s="27"/>
-      <c r="E70" s="27"/>
-      <c r="F70" s="27"/>
-      <c r="G70" s="27"/>
-      <c r="H70" s="27"/>
-      <c r="I70" s="27"/>
-      <c r="J70" s="28"/>
+      <c r="C70" s="38"/>
+      <c r="D70" s="38"/>
+      <c r="E70" s="38"/>
+      <c r="F70" s="38"/>
+      <c r="G70" s="38"/>
+      <c r="H70" s="38"/>
+      <c r="I70" s="38"/>
+      <c r="J70" s="39"/>
       <c r="K70" s="13"/>
       <c r="L70" s="13"/>
       <c r="M70" s="13"/>
     </row>
     <row r="71" spans="1:13" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A71" s="13"/>
-      <c r="B71" s="49" t="s">
+      <c r="B71" s="60" t="s">
         <v>68</v>
       </c>
-      <c r="C71" s="51"/>
-      <c r="D71" s="144"/>
-      <c r="E71" s="145"/>
-      <c r="F71" s="145"/>
-      <c r="G71" s="145"/>
-      <c r="H71" s="145"/>
-      <c r="I71" s="145"/>
-      <c r="J71" s="146"/>
+      <c r="C71" s="62"/>
+      <c r="D71" s="153"/>
+      <c r="E71" s="154"/>
+      <c r="F71" s="154"/>
+      <c r="G71" s="154"/>
+      <c r="H71" s="154"/>
+      <c r="I71" s="154"/>
+      <c r="J71" s="155"/>
       <c r="K71" s="13"/>
       <c r="L71" s="13"/>
       <c r="M71" s="13"/>
     </row>
     <row r="72" spans="1:13" ht="72" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A72" s="13"/>
-      <c r="B72" s="49" t="s">
+      <c r="B72" s="60" t="s">
         <v>69</v>
       </c>
-      <c r="C72" s="51"/>
-      <c r="D72" s="144"/>
-      <c r="E72" s="145"/>
-      <c r="F72" s="145"/>
-      <c r="G72" s="145"/>
-      <c r="H72" s="145"/>
-      <c r="I72" s="145"/>
-      <c r="J72" s="146"/>
+      <c r="C72" s="62"/>
+      <c r="D72" s="153"/>
+      <c r="E72" s="154"/>
+      <c r="F72" s="154"/>
+      <c r="G72" s="154"/>
+      <c r="H72" s="154"/>
+      <c r="I72" s="154"/>
+      <c r="J72" s="155"/>
       <c r="K72" s="13"/>
       <c r="L72" s="13"/>
       <c r="M72" s="13"/>
@@ -3261,51 +3224,51 @@
     </row>
     <row r="74" spans="1:13" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A74" s="13"/>
-      <c r="B74" s="26" t="s">
+      <c r="B74" s="37" t="s">
         <v>71</v>
       </c>
-      <c r="C74" s="27"/>
-      <c r="D74" s="27"/>
-      <c r="E74" s="27"/>
-      <c r="F74" s="27"/>
-      <c r="G74" s="27"/>
-      <c r="H74" s="27"/>
-      <c r="I74" s="27"/>
-      <c r="J74" s="28"/>
+      <c r="C74" s="38"/>
+      <c r="D74" s="38"/>
+      <c r="E74" s="38"/>
+      <c r="F74" s="38"/>
+      <c r="G74" s="38"/>
+      <c r="H74" s="38"/>
+      <c r="I74" s="38"/>
+      <c r="J74" s="39"/>
       <c r="K74" s="13"/>
       <c r="L74" s="13"/>
       <c r="M74" s="13"/>
     </row>
     <row r="75" spans="1:13" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A75" s="13"/>
-      <c r="B75" s="49" t="s">
+      <c r="B75" s="60" t="s">
         <v>68</v>
       </c>
-      <c r="C75" s="51"/>
-      <c r="D75" s="144"/>
-      <c r="E75" s="145"/>
-      <c r="F75" s="145"/>
-      <c r="G75" s="145"/>
-      <c r="H75" s="145"/>
-      <c r="I75" s="145"/>
-      <c r="J75" s="146"/>
+      <c r="C75" s="62"/>
+      <c r="D75" s="153"/>
+      <c r="E75" s="154"/>
+      <c r="F75" s="154"/>
+      <c r="G75" s="154"/>
+      <c r="H75" s="154"/>
+      <c r="I75" s="154"/>
+      <c r="J75" s="155"/>
       <c r="K75" s="13"/>
       <c r="L75" s="13"/>
       <c r="M75" s="13"/>
     </row>
     <row r="76" spans="1:13" ht="71.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A76" s="13"/>
-      <c r="B76" s="49" t="s">
+      <c r="B76" s="60" t="s">
         <v>69</v>
       </c>
-      <c r="C76" s="51"/>
-      <c r="D76" s="144"/>
-      <c r="E76" s="145"/>
-      <c r="F76" s="145"/>
-      <c r="G76" s="145"/>
-      <c r="H76" s="145"/>
-      <c r="I76" s="145"/>
-      <c r="J76" s="146"/>
+      <c r="C76" s="62"/>
+      <c r="D76" s="153"/>
+      <c r="E76" s="154"/>
+      <c r="F76" s="154"/>
+      <c r="G76" s="154"/>
+      <c r="H76" s="154"/>
+      <c r="I76" s="154"/>
+      <c r="J76" s="155"/>
       <c r="K76" s="13"/>
       <c r="L76" s="13"/>
       <c r="M76" s="13"/>
@@ -3325,166 +3288,160 @@
       <c r="L77" s="13"/>
       <c r="M77" s="13"/>
     </row>
-    <row r="78" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="13"/>
-      <c r="B78" s="147" t="s">
-        <v>72</v>
-      </c>
-      <c r="C78" s="147"/>
-      <c r="D78" s="147"/>
-      <c r="E78" s="147"/>
-      <c r="F78" s="147"/>
-      <c r="G78" s="147"/>
-      <c r="H78" s="147"/>
-      <c r="I78" s="147"/>
-      <c r="J78" s="147"/>
-      <c r="K78" s="13"/>
-      <c r="L78" s="13"/>
-      <c r="M78" s="13"/>
-    </row>
-    <row r="79" spans="1:13" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="11"/>
-      <c r="B79" s="12"/>
-      <c r="C79" s="12"/>
-      <c r="D79" s="12"/>
-      <c r="E79" s="12"/>
-      <c r="F79" s="12"/>
-      <c r="G79" s="12"/>
-      <c r="H79" s="12"/>
-      <c r="I79" s="12"/>
-      <c r="J79" s="12"/>
-      <c r="K79" s="11"/>
-      <c r="L79" s="11"/>
-      <c r="M79" s="11"/>
-    </row>
-    <row r="80" spans="1:13" ht="48.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="34"/>
-      <c r="B80" s="34"/>
-      <c r="C80" s="34"/>
-      <c r="D80" s="34"/>
-      <c r="E80" s="32"/>
-      <c r="F80" s="32"/>
-      <c r="G80" s="34"/>
-      <c r="H80" s="34"/>
-      <c r="I80" s="32"/>
-      <c r="J80" s="32"/>
-      <c r="K80" s="34"/>
-      <c r="L80" s="34"/>
-      <c r="M80" s="34"/>
+    <row r="78" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="11"/>
+      <c r="B78" s="12"/>
+      <c r="C78" s="66" t="s">
+        <v>99</v>
+      </c>
+      <c r="D78" s="67"/>
+      <c r="E78" s="67"/>
+      <c r="F78" s="67"/>
+      <c r="G78" s="31" t="s">
+        <v>98</v>
+      </c>
+      <c r="H78" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="I78" s="31" t="s">
+        <v>97</v>
+      </c>
+      <c r="J78" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="K78" s="11"/>
+      <c r="L78" s="11"/>
+      <c r="M78" s="11"/>
+    </row>
+    <row r="79" spans="1:13" ht="48.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A79" s="45"/>
+      <c r="B79" s="45"/>
+      <c r="C79" s="45"/>
+      <c r="D79" s="45"/>
+      <c r="E79" s="43"/>
+      <c r="F79" s="43"/>
+      <c r="G79" s="45"/>
+      <c r="H79" s="45"/>
+      <c r="I79" s="43"/>
+      <c r="J79" s="43"/>
+      <c r="K79" s="45"/>
+      <c r="L79" s="45"/>
+      <c r="M79" s="45"/>
+    </row>
+    <row r="80" spans="1:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A80" s="45"/>
+      <c r="B80" s="45"/>
+      <c r="C80" s="45"/>
+      <c r="D80" s="45"/>
+      <c r="E80" s="43"/>
+      <c r="F80" s="43"/>
+      <c r="G80" s="45"/>
+      <c r="H80" s="45"/>
+      <c r="I80" s="43"/>
+      <c r="J80" s="43"/>
+      <c r="K80" s="45"/>
+      <c r="L80" s="45"/>
+      <c r="M80" s="45"/>
     </row>
     <row r="81" spans="1:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="34"/>
-      <c r="B81" s="34"/>
-      <c r="C81" s="34"/>
-      <c r="D81" s="34"/>
-      <c r="E81" s="32"/>
-      <c r="F81" s="32"/>
-      <c r="G81" s="34"/>
-      <c r="H81" s="34"/>
-      <c r="I81" s="32"/>
-      <c r="J81" s="32"/>
-      <c r="K81" s="34"/>
-      <c r="L81" s="34"/>
-      <c r="M81" s="34"/>
+      <c r="A81" s="45"/>
+      <c r="B81" s="45"/>
+      <c r="C81" s="45"/>
+      <c r="D81" s="45"/>
+      <c r="E81" s="43"/>
+      <c r="F81" s="43"/>
+      <c r="G81" s="45"/>
+      <c r="H81" s="45"/>
+      <c r="I81" s="43"/>
+      <c r="J81" s="43"/>
+      <c r="K81" s="45"/>
+      <c r="L81" s="45"/>
+      <c r="M81" s="45"/>
     </row>
     <row r="82" spans="1:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="34"/>
-      <c r="B82" s="34"/>
-      <c r="C82" s="34"/>
-      <c r="D82" s="34"/>
-      <c r="E82" s="32"/>
-      <c r="F82" s="32"/>
-      <c r="G82" s="34"/>
-      <c r="H82" s="34"/>
-      <c r="I82" s="32"/>
-      <c r="J82" s="32"/>
-      <c r="K82" s="34"/>
-      <c r="L82" s="34"/>
-      <c r="M82" s="34"/>
+      <c r="A82" s="45"/>
+      <c r="B82" s="45"/>
+      <c r="C82" s="45"/>
+      <c r="D82" s="45"/>
+      <c r="E82" s="43"/>
+      <c r="F82" s="43"/>
+      <c r="G82" s="45"/>
+      <c r="H82" s="45"/>
+      <c r="I82" s="43"/>
+      <c r="J82" s="43"/>
+      <c r="K82" s="45"/>
+      <c r="L82" s="45"/>
+      <c r="M82" s="45"/>
     </row>
     <row r="83" spans="1:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="34"/>
-      <c r="B83" s="34"/>
-      <c r="C83" s="34"/>
-      <c r="D83" s="34"/>
-      <c r="E83" s="32"/>
-      <c r="F83" s="32"/>
-      <c r="G83" s="34"/>
-      <c r="H83" s="34"/>
-      <c r="I83" s="32"/>
-      <c r="J83" s="32"/>
-      <c r="K83" s="34"/>
-      <c r="L83" s="34"/>
-      <c r="M83" s="34"/>
-    </row>
-    <row r="84" spans="1:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="35"/>
-      <c r="B84" s="35"/>
-      <c r="C84" s="35"/>
-      <c r="D84" s="35"/>
-      <c r="E84" s="32"/>
-      <c r="F84" s="32"/>
-      <c r="G84" s="35"/>
-      <c r="H84" s="35"/>
-      <c r="I84" s="32"/>
-      <c r="J84" s="32"/>
-      <c r="K84" s="35"/>
-      <c r="L84" s="35"/>
-      <c r="M84" s="35"/>
-    </row>
-    <row r="85" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="31"/>
-      <c r="B85" s="31"/>
-      <c r="C85" s="31"/>
-      <c r="D85" s="31"/>
-      <c r="E85" s="32"/>
-      <c r="F85" s="32"/>
-      <c r="G85" s="33" t="s">
+      <c r="A83" s="46"/>
+      <c r="B83" s="46"/>
+      <c r="C83" s="46"/>
+      <c r="D83" s="46"/>
+      <c r="E83" s="43"/>
+      <c r="F83" s="43"/>
+      <c r="G83" s="46"/>
+      <c r="H83" s="46"/>
+      <c r="I83" s="43"/>
+      <c r="J83" s="43"/>
+      <c r="K83" s="46"/>
+      <c r="L83" s="46"/>
+      <c r="M83" s="46"/>
+    </row>
+    <row r="84" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="42"/>
+      <c r="B84" s="42"/>
+      <c r="C84" s="42"/>
+      <c r="D84" s="42"/>
+      <c r="E84" s="43"/>
+      <c r="F84" s="43"/>
+      <c r="G84" s="44" t="s">
         <v>27</v>
       </c>
-      <c r="H85" s="33"/>
-      <c r="I85" s="32"/>
-      <c r="J85" s="32"/>
-      <c r="K85" s="31"/>
-      <c r="L85" s="31"/>
-      <c r="M85" s="31"/>
+      <c r="H84" s="44"/>
+      <c r="I84" s="43"/>
+      <c r="J84" s="43"/>
+      <c r="K84" s="42"/>
+      <c r="L84" s="42"/>
+      <c r="M84" s="42"/>
+    </row>
+    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A85" s="12"/>
+      <c r="B85" s="12"/>
+      <c r="C85" s="12"/>
+      <c r="D85" s="12"/>
+      <c r="E85" s="12"/>
+      <c r="F85" s="12"/>
+      <c r="G85" s="12"/>
+      <c r="H85" s="12"/>
+      <c r="I85" s="12"/>
+      <c r="J85" s="12"/>
+      <c r="K85" s="12"/>
+      <c r="L85" s="12"/>
+      <c r="M85" s="12"/>
     </row>
     <row r="86" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A86" s="12"/>
-      <c r="B86" s="12"/>
-      <c r="C86" s="12"/>
-      <c r="D86" s="12"/>
-      <c r="E86" s="12"/>
-      <c r="F86" s="12"/>
-      <c r="G86" s="12"/>
-      <c r="H86" s="12"/>
-      <c r="I86" s="12"/>
-      <c r="J86" s="12"/>
-      <c r="K86" s="12"/>
-      <c r="L86" s="12"/>
-      <c r="M86" s="12"/>
+      <c r="A86" s="24"/>
+      <c r="B86" s="176"/>
+      <c r="C86" s="176"/>
+      <c r="D86" s="176"/>
+      <c r="E86" s="176"/>
+      <c r="F86" s="176"/>
+      <c r="G86" s="176"/>
+      <c r="H86" s="176"/>
+      <c r="I86" s="176"/>
+      <c r="J86" s="176"/>
+      <c r="K86" s="24"/>
+      <c r="L86" s="24"/>
+      <c r="M86" s="24"/>
     </row>
     <row r="87" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A87" s="168"/>
-      <c r="B87" s="22"/>
-      <c r="C87" s="22"/>
-      <c r="D87" s="22"/>
-      <c r="E87" s="22"/>
-      <c r="F87" s="22"/>
-      <c r="G87" s="22"/>
-      <c r="H87" s="22"/>
-      <c r="I87" s="22"/>
-      <c r="J87" s="22"/>
-      <c r="K87" s="168"/>
-      <c r="L87" s="168"/>
-      <c r="M87" s="168"/>
-    </row>
-    <row r="88" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="F88" s="20" t="s">
+      <c r="F87" s="32" t="s">
         <v>44</v>
       </c>
-      <c r="G88" s="20"/>
-    </row>
+      <c r="G87" s="32"/>
+    </row>
+    <row r="88" spans="1:13" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="178">
     <mergeCell ref="B1:K1"/>
@@ -3495,13 +3452,12 @@
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="E6:G6"/>
     <mergeCell ref="I6:J6"/>
-    <mergeCell ref="B87:J87"/>
+    <mergeCell ref="B86:J86"/>
     <mergeCell ref="B74:J74"/>
     <mergeCell ref="B75:C75"/>
     <mergeCell ref="D75:J75"/>
     <mergeCell ref="B76:C76"/>
     <mergeCell ref="D76:J76"/>
-    <mergeCell ref="B78:J78"/>
     <mergeCell ref="B64:C64"/>
     <mergeCell ref="D64:E64"/>
     <mergeCell ref="F64:G64"/>
@@ -3642,21 +3598,21 @@
     <mergeCell ref="E31:M31"/>
     <mergeCell ref="B26:D26"/>
     <mergeCell ref="B27:D27"/>
-    <mergeCell ref="F88:G88"/>
+    <mergeCell ref="F87:G87"/>
     <mergeCell ref="A38:M40"/>
     <mergeCell ref="I10:M10"/>
     <mergeCell ref="B70:J70"/>
     <mergeCell ref="F50:G50"/>
-    <mergeCell ref="A85:D85"/>
-    <mergeCell ref="E85:F85"/>
-    <mergeCell ref="G85:H85"/>
-    <mergeCell ref="I85:J85"/>
-    <mergeCell ref="K85:M85"/>
-    <mergeCell ref="A80:D84"/>
-    <mergeCell ref="E80:F84"/>
-    <mergeCell ref="G80:H84"/>
-    <mergeCell ref="I80:J84"/>
-    <mergeCell ref="K80:M84"/>
+    <mergeCell ref="A84:D84"/>
+    <mergeCell ref="E84:F84"/>
+    <mergeCell ref="G84:H84"/>
+    <mergeCell ref="I84:J84"/>
+    <mergeCell ref="K84:M84"/>
+    <mergeCell ref="A79:D83"/>
+    <mergeCell ref="E79:F83"/>
+    <mergeCell ref="G79:H83"/>
+    <mergeCell ref="I79:J83"/>
+    <mergeCell ref="K79:M83"/>
     <mergeCell ref="B43:C43"/>
     <mergeCell ref="B44:C44"/>
     <mergeCell ref="E44:G44"/>
@@ -3665,55 +3621,56 @@
     <mergeCell ref="B36:D36"/>
     <mergeCell ref="B37:D37"/>
     <mergeCell ref="E35:M35"/>
+    <mergeCell ref="C78:F78"/>
   </mergeCells>
-  <conditionalFormatting sqref="A85:D85 K85:M85">
+  <conditionalFormatting sqref="A84:D84 K84:M84">
     <cfRule type="containsBlanks" dxfId="9" priority="14" stopIfTrue="1">
-      <formula>LEN(TRIM(A85))=0</formula>
+      <formula>LEN(TRIM(A84))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A85:D85">
+  <conditionalFormatting sqref="A84:D84">
     <cfRule type="containsBlanks" dxfId="8" priority="9">
-      <formula>LEN(TRIM(A85))=0</formula>
+      <formula>LEN(TRIM(A84))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B86:J86">
+    <cfRule type="containsBlanks" dxfId="7" priority="1">
+      <formula>LEN(TRIM(B86))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D43:D44">
-    <cfRule type="containsBlanks" dxfId="7" priority="5">
+    <cfRule type="containsBlanks" dxfId="6" priority="5">
       <formula>LEN(TRIM(D43))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D49:J56 D60:J64">
-    <cfRule type="containsBlanks" dxfId="6" priority="3">
+    <cfRule type="containsBlanks" dxfId="5" priority="3">
       <formula>LEN(TRIM(D49))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D67:J68">
-    <cfRule type="containsBlanks" dxfId="5" priority="2">
+    <cfRule type="containsBlanks" dxfId="4" priority="2">
       <formula>LEN(TRIM(D67))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G43:H43 J43">
-    <cfRule type="containsBlanks" dxfId="4" priority="4">
+    <cfRule type="containsBlanks" dxfId="3" priority="4">
       <formula>LEN(TRIM(G43))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I10:M10 C11:H11 K11:M11 J13:M13 E14:M22 E26:M37 D75:J76 A85:D85 K85:M85">
-    <cfRule type="containsBlanks" dxfId="3" priority="6">
+  <conditionalFormatting sqref="I10:M10 C11:H11 K11:M11 J13:M13 E14:M22 E26:M37 D75:J76 A84:D84 K84:M84">
+    <cfRule type="containsBlanks" dxfId="2" priority="6">
       <formula>LEN(TRIM(A10))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I10:M10 C11:H11 K11:M11 J13:M13 E14:M22 E26:M37">
-    <cfRule type="containsBlanks" dxfId="2" priority="13" stopIfTrue="1">
+    <cfRule type="containsBlanks" dxfId="1" priority="13" stopIfTrue="1">
       <formula>LEN(TRIM(C10))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K85:M85">
-    <cfRule type="containsBlanks" dxfId="1" priority="8">
-      <formula>LEN(TRIM(K85))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B87:J87">
-    <cfRule type="containsBlanks" dxfId="0" priority="1">
-      <formula>LEN(TRIM(B87))=0</formula>
+  <conditionalFormatting sqref="K84:M84">
+    <cfRule type="containsBlanks" dxfId="0" priority="8">
+      <formula>LEN(TRIM(K84))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations xWindow="756" yWindow="874" count="48">
@@ -3739,12 +3696,11 @@
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Registrar el número del celular del jefe inmediato o supervisor y el número fijo de la empresa con extensión" sqref="E32:M32" xr:uid="{D17896B5-5299-404D-BF06-0A7409E6BB11}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="En caso de que aplique, registrar el nombre de otro contacto en la empresa. De no tener digitar N/A" sqref="E33:M33" xr:uid="{A6F4976B-257F-4E38-96A4-122163F2BCDA}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Registrar el teléfono institucional al cual contactarse en caso que el ente coformador no responda" sqref="E34:M34" xr:uid="{A593241B-15E7-4EA6-B9DE-E0DF01ED6DB9}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="En caso de que el aprendiz sea una persona en situación de discapacidad, diligencie este espacio con el nombre de la persona que le asiste." sqref="E35:M35" xr:uid="{C19946D2-B571-4104-A1EA-FEF5A7253596}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Aquí se especifica el tipo de asistencia brindada al aprendiz para que desempeñe la totalidad de sus tareas asegurando un ambiente laboral inclusivo adecuado a sus necesidades. Puede incluir asistencias como lenguaje de señas, soporte visual etc" sqref="E36:M36" xr:uid="{B635F5F5-108B-409C-BCAD-0AA5A654CF02}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Registrar el número del celular de la persona que asiste al aprendiz " sqref="E37:M37" xr:uid="{77AEF51E-4966-4ADA-B94D-7E72C6BE4FFA}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Registrar el nombre completo del aprendiz y en la parte superior la Firma manuscrita o digital." sqref="A85:D85" xr:uid="{A7FEFB2B-7370-4FA2-8820-7EB89B730FD1}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Registrar el nombre completo del co-formador y en la parte superior de esta la Firma manuscrita o digital." sqref="K85:M85" xr:uid="{DAE2A968-2309-42D5-952C-BC599D7BE50F}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Indique las razones por las que se brinda dicha valoración (indispensable en las valoradas por mejorar)." sqref="H49:J49" xr:uid="{2775CE5B-7882-46E3-9B64-A1DCACE5C767}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Si no aplica colocar N/A" prompt="En caso de que el aprendiz sea una persona en situación de discapacidad, diligencie este espacio con el nombre de la persona que le asiste." sqref="E35:M35" xr:uid="{C19946D2-B571-4104-A1EA-FEF5A7253596}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Si no aplica colocar N/A" prompt="Aquí se especifica el tipo de asistencia brindada al aprendiz para que desempeñe la totalidad de sus tareas asegurando un ambiente laboral inclusivo adecuado a sus necesidades. Puede incluir asistencias como lenguaje de señas, soporte visual etc" sqref="E36:M36" xr:uid="{B635F5F5-108B-409C-BCAD-0AA5A654CF02}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Si no aplica colocar N/A" prompt="Registrar el número del celular de la persona que asiste al aprendiz " sqref="E37:M37" xr:uid="{77AEF51E-4966-4ADA-B94D-7E72C6BE4FFA}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Registrar el nombre completo del aprendiz y en la parte superior la Firma manuscrita o digital." sqref="A84:D84" xr:uid="{A7FEFB2B-7370-4FA2-8820-7EB89B730FD1}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Registrar el nombre completo del co-formador y en la parte superior de esta la Firma manuscrita o digital." sqref="K84:M84" xr:uid="{DAE2A968-2309-42D5-952C-BC599D7BE50F}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Aporta activamente al mejoramiento de sus habilidades técnicas y métodos de trabajo." sqref="D50:F50" xr:uid="{A8FCB973-8FC0-4BDD-BF0E-CC9BB61BE366}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Marcar con una X según correspon" prompt="Demuestra las competencias específicas del programa de formación en situaciones reales de trabajo. " sqref="D49:G49" xr:uid="{948FA747-4CF8-48C4-8768-F9CADBC3F362}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Realiza acciones que fortalezcan su perfil ocupacional potenciando sus competencias en el marco de su proyecto de vida." sqref="D51:G51" xr:uid="{379961D4-6BD4-47A0-B009-E49C8B35A883}"/>
@@ -3758,15 +3714,108 @@
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Propone alternativas de solución a situaciones problemáticas, en el contexto del desarrollo de su etapa productiva. " sqref="D62:G62" xr:uid="{8CFCA47A-7FFB-4C81-B160-32FC56FE753D}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Es comprometido con las actividades asignadas y con la empresa, demostrando puntualidad, proactividad y buena presentación personal en el desarrollo de su etapa productiva" sqref="D63:G63" xr:uid="{C5D9BB00-F014-4DE5-B59C-090440CDA5FD}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Demuestra capacidad para ordenar y disponer los elementos necesarios e información que facilite la ejecución del trabajo y el logro de los objetivos." sqref="D64:G65" xr:uid="{B8588CD4-9B9C-4123-8FA4-B0191CFB9CEA}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Registrar la retroalimentación sobre el proceso de formación realizado por parte del aprendiz, así como las recomendaciones u oportunidades de mejora." sqref="D75:J75" xr:uid="{BB60E4B5-FB76-4B94-9BA7-36C763570B67}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Registrar observaciones finales del procesos por parte del aprendiz" sqref="D76:J76" xr:uid="{979A95D0-1B6C-4B96-AED2-E0EA9955374B}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Registrar la retroalimentación sobre el proceso de formación realizado por parte del ente co-formador, así como las recomendaciones u oportunidades de mejora. De la misma manera, si el aprendiz tiene o no reconocimientos especiales frente a su desempeño." sqref="D71:J71 D67:J67" xr:uid="{F2874302-4049-43C8-A0B5-AB713683C70D}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Registrar si el aprendiz tiene o no reconocimientos especiales frente a su desempeño. registrar otras observaciones , recomendaciones u oportunidades de mejora sobre las competencias del programa desarrolladas por el aprendiz" sqref="D72:J72 D68:J68" xr:uid="{31FFF10E-CBCB-44E0-A79A-920B54E65B68}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="OBLIGATORIO" prompt="Registrar la retroalimentación sobre el proceso de formación realizado por parte del aprendiz, así como las recomendaciones u oportunidades de mejora." sqref="D75:J75" xr:uid="{BB60E4B5-FB76-4B94-9BA7-36C763570B67}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="OBLIGATORIO" prompt="Registrar observaciones finales del procesos por parte del aprendiz" sqref="D76:J76" xr:uid="{979A95D0-1B6C-4B96-AED2-E0EA9955374B}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="OBLIGATORIO" prompt="Registrar la retroalimentación sobre el proceso de formación realizado por parte del ente co-formador, así como las recomendaciones u oportunidades de mejora. De la misma manera, si el aprendiz tiene o no reconocimientos especiales frente a su desempeño." sqref="D67:J67" xr:uid="{F2874302-4049-43C8-A0B5-AB713683C70D}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="OBLIGATORIO" prompt="Registrar si el aprendiz tiene o no reconocimientos especiales frente a su desempeño. registrar otras observaciones , recomendaciones u oportunidades de mejora sobre las competencias del programa desarrolladas por el aprendiz" sqref="D68:J68" xr:uid="{31FFF10E-CBCB-44E0-A79A-920B54E65B68}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Ingresar el Link de la Grabacion del teams" sqref="H44:J44" xr:uid="{F2C9EF6C-D3FF-4587-A8E6-606880F942C2}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Virtual o Presencial?" sqref="D44" xr:uid="{5D446980-EFCB-4F87-AF79-7C40D04D4175}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Diligenciar fecha de la sesión en este espacio. Ejemplo: Bogotá dia/mes/año Virtual" sqref="B87:J87" xr:uid="{DB281D4A-1D51-4243-9BC5-E0F3B032B581}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Bogotá dd/mm/aaaa Virtual" prompt="Diligenciar fecha de la visita en este espacio. Ejemplo: Bogotá dia/mes/año Virtual" sqref="B86:J86" xr:uid="{DB281D4A-1D51-4243-9BC5-E0F3B032B581}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Diligenciar si hay por mejorar" prompt="Si hay factores por mejorar favor escribir las observaciones o los compromisos de mejora" sqref="H60:J64 H49:J56" xr:uid="{77BDF12C-BD40-4BBD-8AD2-2B5F2F7C6B93}"/>
   </dataValidations>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="5" scale="68" fitToHeight="0" orientation="portrait" r:id="rId1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xWindow="756" yWindow="874" count="2">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Registrar la retroalimentación sobre el proceso de formación realizado por parte del ente co-formador, así como las recomendaciones u oportunidades de mejora. De la misma manera, si el aprendiz tiene o no reconocimientos especiales frente a su desempeño." xr:uid="{DFDB9D40-B1FA-44FD-A0C7-E2D5BEF09BF0}">
+          <x14:formula1>
+            <xm:f>Hoja2!$A$2:$A$6</xm:f>
+          </x14:formula1>
+          <xm:sqref>D71:J71</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Registrar si el aprendiz tiene o no reconocimientos especiales frente a su desempeño. registrar otras observaciones , recomendaciones u oportunidades de mejora sobre las competencias del programa desarrolladas por el aprendiz" xr:uid="{6FC7E188-4A10-41FD-B8AC-C0605E33F3DB}">
+          <x14:formula1>
+            <xm:f>Hoja2!$B$2:$B$6</xm:f>
+          </x14:formula1>
+          <xm:sqref>D72:J72</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD084F5C-E38C-43A0-89E7-11C36CA4FEFC}">
+  <dimension ref="A1:B10"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="64.5703125" customWidth="1"/>
+    <col min="2" max="2" width="94.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="26" t="s">
+        <v>85</v>
+      </c>
+      <c r="B1" s="27" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="90" x14ac:dyDescent="0.25">
+      <c r="A2" s="25" t="s">
+        <v>88</v>
+      </c>
+      <c r="B2" s="29" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="90" x14ac:dyDescent="0.25">
+      <c r="A3" s="25" t="s">
+        <v>87</v>
+      </c>
+      <c r="B3" s="28" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="90" x14ac:dyDescent="0.25">
+      <c r="A4" s="25" t="s">
+        <v>91</v>
+      </c>
+      <c r="B4" s="28" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="75" x14ac:dyDescent="0.25">
+      <c r="A5" s="25" t="s">
+        <v>89</v>
+      </c>
+      <c r="B5" s="28" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="75" x14ac:dyDescent="0.25">
+      <c r="A6" s="25" t="s">
+        <v>90</v>
+      </c>
+      <c r="B6" s="28" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="25"/>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="25"/>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="25"/>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="25"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Formatos/Visita 3 GFPI-F023.xlsx
+++ b/Formatos/Visita 3 GFPI-F023.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SEANT\3D Objects\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SEANT\OneDrive\Documents\Seto 2026\sena\Manual SENA Etapa Productiva\manual-aprendiz-sena\Formatos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAB61486-BA46-46E5-9645-FAD2FBFB33E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8726567-7195-433A-A879-F216B9BE4E06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{BC3553EE-4E49-4F2A-B03E-CFAC4EB3009B}"/>
   </bookViews>
@@ -1052,33 +1052,419 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="15" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="15" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="15" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
@@ -1147,397 +1533,11 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="15" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="15" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="15" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="15" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="15" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1987,1090 +1987,1090 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B1" s="165" t="s">
+      <c r="B1" s="32" t="s">
         <v>77</v>
       </c>
-      <c r="C1" s="166"/>
-      <c r="D1" s="166"/>
-      <c r="E1" s="166"/>
-      <c r="F1" s="166"/>
-      <c r="G1" s="166"/>
-      <c r="H1" s="166"/>
-      <c r="I1" s="166"/>
-      <c r="J1" s="166"/>
-      <c r="K1" s="167"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
+      <c r="H1" s="33"/>
+      <c r="I1" s="33"/>
+      <c r="J1" s="33"/>
+      <c r="K1" s="34"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B2" s="168" t="s">
+      <c r="B2" s="35" t="s">
         <v>78</v>
       </c>
-      <c r="C2" s="32"/>
-      <c r="D2" s="32"/>
-      <c r="E2" s="32"/>
-      <c r="F2" s="32"/>
-      <c r="G2" s="32"/>
-      <c r="H2" s="32"/>
-      <c r="I2" s="32"/>
-      <c r="J2" s="32"/>
-      <c r="K2" s="169"/>
+      <c r="C2" s="36"/>
+      <c r="D2" s="36"/>
+      <c r="E2" s="36"/>
+      <c r="F2" s="36"/>
+      <c r="G2" s="36"/>
+      <c r="H2" s="36"/>
+      <c r="I2" s="36"/>
+      <c r="J2" s="36"/>
+      <c r="K2" s="37"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B3" s="170" t="s">
+      <c r="B3" s="38" t="s">
         <v>79</v>
       </c>
-      <c r="C3" s="171"/>
-      <c r="D3" s="171"/>
-      <c r="E3" s="171"/>
-      <c r="F3" s="171"/>
-      <c r="G3" s="171"/>
-      <c r="H3" s="171"/>
-      <c r="I3" s="171"/>
-      <c r="J3" s="171"/>
-      <c r="K3" s="172"/>
+      <c r="C3" s="39"/>
+      <c r="D3" s="39"/>
+      <c r="E3" s="39"/>
+      <c r="F3" s="39"/>
+      <c r="G3" s="39"/>
+      <c r="H3" s="39"/>
+      <c r="I3" s="39"/>
+      <c r="J3" s="39"/>
+      <c r="K3" s="40"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B4" s="168" t="s">
+      <c r="B4" s="35" t="s">
         <v>80</v>
       </c>
-      <c r="C4" s="32"/>
-      <c r="D4" s="32"/>
-      <c r="E4" s="32"/>
-      <c r="F4" s="32"/>
-      <c r="G4" s="32"/>
-      <c r="H4" s="32"/>
-      <c r="I4" s="32"/>
-      <c r="J4" s="32"/>
-      <c r="K4" s="169"/>
+      <c r="C4" s="36"/>
+      <c r="D4" s="36"/>
+      <c r="E4" s="36"/>
+      <c r="F4" s="36"/>
+      <c r="G4" s="36"/>
+      <c r="H4" s="36"/>
+      <c r="I4" s="36"/>
+      <c r="J4" s="36"/>
+      <c r="K4" s="37"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B5" s="170" t="s">
+      <c r="B5" s="38" t="s">
         <v>81</v>
       </c>
-      <c r="C5" s="171"/>
-      <c r="D5" s="171"/>
-      <c r="E5" s="171"/>
-      <c r="F5" s="171"/>
-      <c r="G5" s="171"/>
-      <c r="H5" s="171"/>
-      <c r="I5" s="171"/>
-      <c r="J5" s="171"/>
-      <c r="K5" s="172"/>
+      <c r="C5" s="39"/>
+      <c r="D5" s="39"/>
+      <c r="E5" s="39"/>
+      <c r="F5" s="39"/>
+      <c r="G5" s="39"/>
+      <c r="H5" s="39"/>
+      <c r="I5" s="39"/>
+      <c r="J5" s="39"/>
+      <c r="K5" s="40"/>
     </row>
     <row r="6" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="173" t="s">
+      <c r="B6" s="41" t="s">
         <v>82</v>
       </c>
-      <c r="C6" s="174"/>
+      <c r="C6" s="42"/>
       <c r="D6" s="20" t="b">
         <v>0</v>
       </c>
-      <c r="E6" s="175" t="s">
+      <c r="E6" s="43" t="s">
         <v>83</v>
       </c>
-      <c r="F6" s="174"/>
-      <c r="G6" s="174"/>
+      <c r="F6" s="42"/>
+      <c r="G6" s="42"/>
       <c r="H6" s="20" t="b">
         <v>0</v>
       </c>
-      <c r="I6" s="175" t="s">
+      <c r="I6" s="43" t="s">
         <v>84</v>
       </c>
-      <c r="J6" s="174"/>
+      <c r="J6" s="42"/>
       <c r="K6" s="21" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25"/>
     <row r="8" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="71" t="s">
+      <c r="A8" s="137" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="72"/>
-      <c r="C8" s="72"/>
-      <c r="D8" s="72"/>
-      <c r="E8" s="72"/>
-      <c r="F8" s="72"/>
-      <c r="G8" s="72"/>
-      <c r="H8" s="72"/>
-      <c r="I8" s="72"/>
-      <c r="J8" s="72"/>
-      <c r="K8" s="72"/>
-      <c r="L8" s="72"/>
-      <c r="M8" s="72"/>
+      <c r="B8" s="138"/>
+      <c r="C8" s="138"/>
+      <c r="D8" s="138"/>
+      <c r="E8" s="138"/>
+      <c r="F8" s="138"/>
+      <c r="G8" s="138"/>
+      <c r="H8" s="138"/>
+      <c r="I8" s="138"/>
+      <c r="J8" s="138"/>
+      <c r="K8" s="138"/>
+      <c r="L8" s="138"/>
+      <c r="M8" s="138"/>
     </row>
     <row r="9" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="60" t="s">
+      <c r="A9" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="B9" s="62"/>
-      <c r="C9" s="68" t="s">
+      <c r="B9" s="49"/>
+      <c r="C9" s="124" t="s">
         <v>2</v>
       </c>
-      <c r="D9" s="69"/>
-      <c r="E9" s="69"/>
-      <c r="F9" s="69"/>
-      <c r="G9" s="69"/>
-      <c r="H9" s="69"/>
-      <c r="I9" s="69"/>
-      <c r="J9" s="69"/>
-      <c r="K9" s="69"/>
-      <c r="L9" s="69"/>
-      <c r="M9" s="70"/>
+      <c r="D9" s="136"/>
+      <c r="E9" s="136"/>
+      <c r="F9" s="136"/>
+      <c r="G9" s="136"/>
+      <c r="H9" s="136"/>
+      <c r="I9" s="136"/>
+      <c r="J9" s="136"/>
+      <c r="K9" s="136"/>
+      <c r="L9" s="136"/>
+      <c r="M9" s="125"/>
     </row>
     <row r="10" spans="1:13" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="60" t="s">
+      <c r="A10" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="B10" s="62"/>
-      <c r="C10" s="104" t="s">
+      <c r="B10" s="49"/>
+      <c r="C10" s="108" t="s">
         <v>4</v>
       </c>
-      <c r="D10" s="105"/>
-      <c r="E10" s="105"/>
-      <c r="F10" s="105"/>
-      <c r="G10" s="106"/>
+      <c r="D10" s="109"/>
+      <c r="E10" s="109"/>
+      <c r="F10" s="109"/>
+      <c r="G10" s="110"/>
       <c r="H10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="I10" s="34"/>
-      <c r="J10" s="35"/>
-      <c r="K10" s="35"/>
-      <c r="L10" s="35"/>
-      <c r="M10" s="36"/>
+      <c r="I10" s="105"/>
+      <c r="J10" s="106"/>
+      <c r="K10" s="106"/>
+      <c r="L10" s="106"/>
+      <c r="M10" s="107"/>
     </row>
     <row r="11" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="60" t="s">
+      <c r="A11" s="48" t="s">
         <v>6</v>
       </c>
-      <c r="B11" s="62"/>
-      <c r="C11" s="114"/>
-      <c r="D11" s="115"/>
-      <c r="E11" s="115"/>
-      <c r="F11" s="115"/>
-      <c r="G11" s="115"/>
-      <c r="H11" s="116"/>
-      <c r="I11" s="117" t="s">
+      <c r="B11" s="49"/>
+      <c r="C11" s="121"/>
+      <c r="D11" s="122"/>
+      <c r="E11" s="122"/>
+      <c r="F11" s="122"/>
+      <c r="G11" s="122"/>
+      <c r="H11" s="123"/>
+      <c r="I11" s="74" t="s">
         <v>7</v>
       </c>
-      <c r="J11" s="118"/>
-      <c r="K11" s="76"/>
-      <c r="L11" s="77"/>
-      <c r="M11" s="78"/>
+      <c r="J11" s="75"/>
+      <c r="K11" s="139"/>
+      <c r="L11" s="140"/>
+      <c r="M11" s="141"/>
     </row>
     <row r="12" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="60" t="s">
+      <c r="A12" s="48" t="s">
         <v>8</v>
       </c>
-      <c r="B12" s="62"/>
+      <c r="B12" s="49"/>
       <c r="C12" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D12" s="68" t="s">
+      <c r="D12" s="124" t="s">
         <v>10</v>
       </c>
-      <c r="E12" s="70"/>
-      <c r="F12" s="119" t="s">
+      <c r="E12" s="125"/>
+      <c r="F12" s="76" t="s">
         <v>11</v>
       </c>
-      <c r="G12" s="120"/>
+      <c r="G12" s="78"/>
       <c r="H12" s="1"/>
-      <c r="I12" s="119" t="s">
+      <c r="I12" s="76" t="s">
         <v>12</v>
       </c>
-      <c r="J12" s="120"/>
-      <c r="K12" s="79"/>
-      <c r="L12" s="80"/>
-      <c r="M12" s="81"/>
+      <c r="J12" s="78"/>
+      <c r="K12" s="142"/>
+      <c r="L12" s="143"/>
+      <c r="M12" s="144"/>
     </row>
     <row r="13" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="60" t="s">
+      <c r="A13" s="48" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="62"/>
-      <c r="C13" s="107"/>
-      <c r="D13" s="108"/>
-      <c r="E13" s="108"/>
-      <c r="F13" s="109"/>
-      <c r="G13" s="107" t="s">
+      <c r="B13" s="49"/>
+      <c r="C13" s="111"/>
+      <c r="D13" s="112"/>
+      <c r="E13" s="112"/>
+      <c r="F13" s="113"/>
+      <c r="G13" s="111" t="s">
         <v>14</v>
       </c>
-      <c r="H13" s="108"/>
-      <c r="I13" s="109"/>
-      <c r="J13" s="82"/>
-      <c r="K13" s="83"/>
-      <c r="L13" s="83"/>
-      <c r="M13" s="84"/>
+      <c r="H13" s="112"/>
+      <c r="I13" s="113"/>
+      <c r="J13" s="145"/>
+      <c r="K13" s="146"/>
+      <c r="L13" s="146"/>
+      <c r="M13" s="147"/>
     </row>
     <row r="14" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="110" t="s">
+      <c r="A14" s="114" t="s">
         <v>15</v>
       </c>
-      <c r="B14" s="60" t="s">
+      <c r="B14" s="48" t="s">
         <v>16</v>
       </c>
-      <c r="C14" s="61"/>
-      <c r="D14" s="62"/>
-      <c r="E14" s="73"/>
-      <c r="F14" s="74"/>
-      <c r="G14" s="74"/>
-      <c r="H14" s="74"/>
-      <c r="I14" s="74"/>
-      <c r="J14" s="74"/>
-      <c r="K14" s="74"/>
-      <c r="L14" s="74"/>
-      <c r="M14" s="75"/>
+      <c r="C14" s="117"/>
+      <c r="D14" s="49"/>
+      <c r="E14" s="129"/>
+      <c r="F14" s="130"/>
+      <c r="G14" s="130"/>
+      <c r="H14" s="130"/>
+      <c r="I14" s="130"/>
+      <c r="J14" s="130"/>
+      <c r="K14" s="130"/>
+      <c r="L14" s="130"/>
+      <c r="M14" s="131"/>
     </row>
     <row r="15" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="92"/>
-      <c r="B15" s="111" t="s">
+      <c r="A15" s="115"/>
+      <c r="B15" s="118" t="s">
         <v>17</v>
       </c>
-      <c r="C15" s="112"/>
-      <c r="D15" s="113"/>
-      <c r="E15" s="85"/>
-      <c r="F15" s="86"/>
-      <c r="G15" s="86"/>
-      <c r="H15" s="86"/>
-      <c r="I15" s="86"/>
-      <c r="J15" s="86"/>
-      <c r="K15" s="86"/>
-      <c r="L15" s="86"/>
-      <c r="M15" s="87"/>
+      <c r="C15" s="119"/>
+      <c r="D15" s="120"/>
+      <c r="E15" s="148"/>
+      <c r="F15" s="149"/>
+      <c r="G15" s="149"/>
+      <c r="H15" s="149"/>
+      <c r="I15" s="149"/>
+      <c r="J15" s="149"/>
+      <c r="K15" s="149"/>
+      <c r="L15" s="149"/>
+      <c r="M15" s="150"/>
     </row>
     <row r="16" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="92"/>
-      <c r="B16" s="60" t="s">
+      <c r="A16" s="115"/>
+      <c r="B16" s="48" t="s">
         <v>18</v>
       </c>
-      <c r="C16" s="61"/>
-      <c r="D16" s="62"/>
-      <c r="E16" s="73"/>
-      <c r="F16" s="74"/>
-      <c r="G16" s="74"/>
-      <c r="H16" s="74"/>
-      <c r="I16" s="74"/>
-      <c r="J16" s="74"/>
-      <c r="K16" s="74"/>
-      <c r="L16" s="74"/>
-      <c r="M16" s="75"/>
+      <c r="C16" s="117"/>
+      <c r="D16" s="49"/>
+      <c r="E16" s="129"/>
+      <c r="F16" s="130"/>
+      <c r="G16" s="130"/>
+      <c r="H16" s="130"/>
+      <c r="I16" s="130"/>
+      <c r="J16" s="130"/>
+      <c r="K16" s="130"/>
+      <c r="L16" s="130"/>
+      <c r="M16" s="131"/>
     </row>
     <row r="17" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="92"/>
-      <c r="B17" s="60" t="s">
+      <c r="A17" s="115"/>
+      <c r="B17" s="48" t="s">
         <v>19</v>
       </c>
-      <c r="C17" s="61"/>
-      <c r="D17" s="62"/>
-      <c r="E17" s="73"/>
-      <c r="F17" s="74"/>
-      <c r="G17" s="74"/>
-      <c r="H17" s="74"/>
-      <c r="I17" s="74"/>
-      <c r="J17" s="74"/>
-      <c r="K17" s="74"/>
-      <c r="L17" s="74"/>
-      <c r="M17" s="75"/>
+      <c r="C17" s="117"/>
+      <c r="D17" s="49"/>
+      <c r="E17" s="129"/>
+      <c r="F17" s="130"/>
+      <c r="G17" s="130"/>
+      <c r="H17" s="130"/>
+      <c r="I17" s="130"/>
+      <c r="J17" s="130"/>
+      <c r="K17" s="130"/>
+      <c r="L17" s="130"/>
+      <c r="M17" s="131"/>
     </row>
     <row r="18" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="92"/>
-      <c r="B18" s="60" t="s">
+      <c r="A18" s="115"/>
+      <c r="B18" s="48" t="s">
         <v>20</v>
       </c>
-      <c r="C18" s="61"/>
-      <c r="D18" s="62"/>
-      <c r="E18" s="73"/>
-      <c r="F18" s="74"/>
-      <c r="G18" s="74"/>
-      <c r="H18" s="74"/>
-      <c r="I18" s="74"/>
-      <c r="J18" s="74"/>
-      <c r="K18" s="74"/>
-      <c r="L18" s="74"/>
-      <c r="M18" s="75"/>
+      <c r="C18" s="117"/>
+      <c r="D18" s="49"/>
+      <c r="E18" s="129"/>
+      <c r="F18" s="130"/>
+      <c r="G18" s="130"/>
+      <c r="H18" s="130"/>
+      <c r="I18" s="130"/>
+      <c r="J18" s="130"/>
+      <c r="K18" s="130"/>
+      <c r="L18" s="130"/>
+      <c r="M18" s="131"/>
     </row>
     <row r="19" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="92"/>
-      <c r="B19" s="60" t="s">
+      <c r="A19" s="115"/>
+      <c r="B19" s="48" t="s">
         <v>21</v>
       </c>
-      <c r="C19" s="61"/>
-      <c r="D19" s="62"/>
-      <c r="E19" s="73"/>
-      <c r="F19" s="74"/>
-      <c r="G19" s="74"/>
-      <c r="H19" s="74"/>
-      <c r="I19" s="74"/>
-      <c r="J19" s="74"/>
-      <c r="K19" s="74"/>
-      <c r="L19" s="74"/>
-      <c r="M19" s="75"/>
+      <c r="C19" s="117"/>
+      <c r="D19" s="49"/>
+      <c r="E19" s="129"/>
+      <c r="F19" s="130"/>
+      <c r="G19" s="130"/>
+      <c r="H19" s="130"/>
+      <c r="I19" s="130"/>
+      <c r="J19" s="130"/>
+      <c r="K19" s="130"/>
+      <c r="L19" s="130"/>
+      <c r="M19" s="131"/>
     </row>
     <row r="20" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="92"/>
-      <c r="B20" s="60" t="s">
+      <c r="A20" s="115"/>
+      <c r="B20" s="48" t="s">
         <v>22</v>
       </c>
-      <c r="C20" s="61"/>
-      <c r="D20" s="62"/>
-      <c r="E20" s="63"/>
-      <c r="F20" s="64"/>
-      <c r="G20" s="64"/>
-      <c r="H20" s="64"/>
-      <c r="I20" s="64"/>
-      <c r="J20" s="64"/>
-      <c r="K20" s="64"/>
-      <c r="L20" s="64"/>
-      <c r="M20" s="65"/>
+      <c r="C20" s="117"/>
+      <c r="D20" s="49"/>
+      <c r="E20" s="126"/>
+      <c r="F20" s="127"/>
+      <c r="G20" s="127"/>
+      <c r="H20" s="127"/>
+      <c r="I20" s="127"/>
+      <c r="J20" s="127"/>
+      <c r="K20" s="127"/>
+      <c r="L20" s="127"/>
+      <c r="M20" s="128"/>
     </row>
     <row r="21" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="92"/>
-      <c r="B21" s="60" t="s">
+      <c r="A21" s="115"/>
+      <c r="B21" s="48" t="s">
         <v>23</v>
       </c>
-      <c r="C21" s="61"/>
-      <c r="D21" s="62"/>
-      <c r="E21" s="63"/>
-      <c r="F21" s="64"/>
-      <c r="G21" s="64"/>
-      <c r="H21" s="64"/>
-      <c r="I21" s="64"/>
-      <c r="J21" s="64"/>
-      <c r="K21" s="64"/>
-      <c r="L21" s="64"/>
-      <c r="M21" s="65"/>
+      <c r="C21" s="117"/>
+      <c r="D21" s="49"/>
+      <c r="E21" s="126"/>
+      <c r="F21" s="127"/>
+      <c r="G21" s="127"/>
+      <c r="H21" s="127"/>
+      <c r="I21" s="127"/>
+      <c r="J21" s="127"/>
+      <c r="K21" s="127"/>
+      <c r="L21" s="127"/>
+      <c r="M21" s="128"/>
     </row>
     <row r="22" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="93"/>
-      <c r="B22" s="60" t="s">
+      <c r="A22" s="116"/>
+      <c r="B22" s="48" t="s">
         <v>24</v>
       </c>
-      <c r="C22" s="61"/>
-      <c r="D22" s="62"/>
-      <c r="E22" s="63"/>
-      <c r="F22" s="64"/>
-      <c r="G22" s="64"/>
-      <c r="H22" s="64"/>
-      <c r="I22" s="64"/>
-      <c r="J22" s="64"/>
-      <c r="K22" s="64"/>
-      <c r="L22" s="64"/>
-      <c r="M22" s="65"/>
+      <c r="C22" s="117"/>
+      <c r="D22" s="49"/>
+      <c r="E22" s="126"/>
+      <c r="F22" s="127"/>
+      <c r="G22" s="127"/>
+      <c r="H22" s="127"/>
+      <c r="I22" s="127"/>
+      <c r="J22" s="127"/>
+      <c r="K22" s="127"/>
+      <c r="L22" s="127"/>
+      <c r="M22" s="128"/>
     </row>
     <row r="23" spans="1:13" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="91" t="s">
+      <c r="A23" s="132" t="s">
         <v>25</v>
       </c>
-      <c r="B23" s="60" t="s">
+      <c r="B23" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="C23" s="61"/>
-      <c r="D23" s="62"/>
-      <c r="E23" s="94" t="s">
+      <c r="C23" s="117"/>
+      <c r="D23" s="49"/>
+      <c r="E23" s="133" t="s">
         <v>27</v>
       </c>
-      <c r="F23" s="95"/>
-      <c r="G23" s="95"/>
-      <c r="H23" s="95"/>
-      <c r="I23" s="95"/>
-      <c r="J23" s="95"/>
-      <c r="K23" s="95"/>
-      <c r="L23" s="95"/>
-      <c r="M23" s="96"/>
+      <c r="F23" s="134"/>
+      <c r="G23" s="134"/>
+      <c r="H23" s="134"/>
+      <c r="I23" s="134"/>
+      <c r="J23" s="134"/>
+      <c r="K23" s="134"/>
+      <c r="L23" s="134"/>
+      <c r="M23" s="135"/>
     </row>
     <row r="24" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="92"/>
-      <c r="B24" s="60" t="s">
+      <c r="A24" s="115"/>
+      <c r="B24" s="48" t="s">
         <v>19</v>
       </c>
-      <c r="C24" s="61"/>
-      <c r="D24" s="62"/>
-      <c r="E24" s="37"/>
-      <c r="F24" s="38"/>
-      <c r="G24" s="38"/>
-      <c r="H24" s="38"/>
-      <c r="I24" s="38"/>
-      <c r="J24" s="38"/>
-      <c r="K24" s="38"/>
-      <c r="L24" s="38"/>
-      <c r="M24" s="39"/>
+      <c r="C24" s="117"/>
+      <c r="D24" s="49"/>
+      <c r="E24" s="45"/>
+      <c r="F24" s="46"/>
+      <c r="G24" s="46"/>
+      <c r="H24" s="46"/>
+      <c r="I24" s="46"/>
+      <c r="J24" s="46"/>
+      <c r="K24" s="46"/>
+      <c r="L24" s="46"/>
+      <c r="M24" s="47"/>
     </row>
     <row r="25" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="93"/>
-      <c r="B25" s="60" t="s">
+      <c r="A25" s="116"/>
+      <c r="B25" s="48" t="s">
         <v>22</v>
       </c>
-      <c r="C25" s="61"/>
-      <c r="D25" s="62"/>
-      <c r="E25" s="94" t="s">
+      <c r="C25" s="117"/>
+      <c r="D25" s="49"/>
+      <c r="E25" s="133" t="s">
         <v>28</v>
       </c>
-      <c r="F25" s="95"/>
-      <c r="G25" s="95"/>
-      <c r="H25" s="95"/>
-      <c r="I25" s="95"/>
-      <c r="J25" s="95"/>
-      <c r="K25" s="95"/>
-      <c r="L25" s="95"/>
-      <c r="M25" s="96"/>
+      <c r="F25" s="134"/>
+      <c r="G25" s="134"/>
+      <c r="H25" s="134"/>
+      <c r="I25" s="134"/>
+      <c r="J25" s="134"/>
+      <c r="K25" s="134"/>
+      <c r="L25" s="134"/>
+      <c r="M25" s="135"/>
     </row>
     <row r="26" spans="1:13" ht="25.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B26" s="60" t="s">
+      <c r="B26" s="48" t="s">
         <v>32</v>
       </c>
-      <c r="C26" s="61"/>
-      <c r="D26" s="62"/>
-      <c r="E26" s="73"/>
-      <c r="F26" s="74"/>
-      <c r="G26" s="74"/>
-      <c r="H26" s="74"/>
-      <c r="I26" s="74"/>
-      <c r="J26" s="74"/>
-      <c r="K26" s="74"/>
-      <c r="L26" s="74"/>
-      <c r="M26" s="75"/>
+      <c r="C26" s="117"/>
+      <c r="D26" s="49"/>
+      <c r="E26" s="129"/>
+      <c r="F26" s="130"/>
+      <c r="G26" s="130"/>
+      <c r="H26" s="130"/>
+      <c r="I26" s="130"/>
+      <c r="J26" s="130"/>
+      <c r="K26" s="130"/>
+      <c r="L26" s="130"/>
+      <c r="M26" s="131"/>
     </row>
     <row r="27" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="B27" s="60" t="s">
+      <c r="B27" s="48" t="s">
         <v>20</v>
       </c>
-      <c r="C27" s="61"/>
-      <c r="D27" s="62"/>
-      <c r="E27" s="73"/>
-      <c r="F27" s="74"/>
-      <c r="G27" s="74"/>
-      <c r="H27" s="74"/>
-      <c r="I27" s="74"/>
-      <c r="J27" s="74"/>
-      <c r="K27" s="74"/>
-      <c r="L27" s="74"/>
-      <c r="M27" s="75"/>
+      <c r="C27" s="117"/>
+      <c r="D27" s="49"/>
+      <c r="E27" s="129"/>
+      <c r="F27" s="130"/>
+      <c r="G27" s="130"/>
+      <c r="H27" s="130"/>
+      <c r="I27" s="130"/>
+      <c r="J27" s="130"/>
+      <c r="K27" s="130"/>
+      <c r="L27" s="130"/>
+      <c r="M27" s="131"/>
     </row>
     <row r="28" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="3"/>
-      <c r="B28" s="60" t="s">
+      <c r="B28" s="48" t="s">
         <v>33</v>
       </c>
-      <c r="C28" s="61"/>
-      <c r="D28" s="62"/>
-      <c r="E28" s="73"/>
-      <c r="F28" s="74"/>
-      <c r="G28" s="74"/>
-      <c r="H28" s="74"/>
-      <c r="I28" s="74"/>
-      <c r="J28" s="74"/>
-      <c r="K28" s="74"/>
-      <c r="L28" s="74"/>
-      <c r="M28" s="75"/>
+      <c r="C28" s="117"/>
+      <c r="D28" s="49"/>
+      <c r="E28" s="129"/>
+      <c r="F28" s="130"/>
+      <c r="G28" s="130"/>
+      <c r="H28" s="130"/>
+      <c r="I28" s="130"/>
+      <c r="J28" s="130"/>
+      <c r="K28" s="130"/>
+      <c r="L28" s="130"/>
+      <c r="M28" s="131"/>
     </row>
     <row r="29" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="3"/>
-      <c r="B29" s="60" t="s">
+      <c r="B29" s="48" t="s">
         <v>34</v>
       </c>
-      <c r="C29" s="61"/>
-      <c r="D29" s="62"/>
-      <c r="E29" s="73"/>
-      <c r="F29" s="74"/>
-      <c r="G29" s="74"/>
-      <c r="H29" s="74"/>
-      <c r="I29" s="74"/>
-      <c r="J29" s="74"/>
-      <c r="K29" s="74"/>
-      <c r="L29" s="74"/>
-      <c r="M29" s="75"/>
+      <c r="C29" s="117"/>
+      <c r="D29" s="49"/>
+      <c r="E29" s="129"/>
+      <c r="F29" s="130"/>
+      <c r="G29" s="130"/>
+      <c r="H29" s="130"/>
+      <c r="I29" s="130"/>
+      <c r="J29" s="130"/>
+      <c r="K29" s="130"/>
+      <c r="L29" s="130"/>
+      <c r="M29" s="131"/>
     </row>
     <row r="30" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="B30" s="60" t="s">
+      <c r="B30" s="48" t="s">
         <v>35</v>
       </c>
-      <c r="C30" s="61"/>
-      <c r="D30" s="62"/>
-      <c r="E30" s="73"/>
-      <c r="F30" s="74"/>
-      <c r="G30" s="74"/>
-      <c r="H30" s="74"/>
-      <c r="I30" s="74"/>
-      <c r="J30" s="74"/>
-      <c r="K30" s="74"/>
-      <c r="L30" s="74"/>
-      <c r="M30" s="75"/>
+      <c r="C30" s="117"/>
+      <c r="D30" s="49"/>
+      <c r="E30" s="129"/>
+      <c r="F30" s="130"/>
+      <c r="G30" s="130"/>
+      <c r="H30" s="130"/>
+      <c r="I30" s="130"/>
+      <c r="J30" s="130"/>
+      <c r="K30" s="130"/>
+      <c r="L30" s="130"/>
+      <c r="M30" s="131"/>
     </row>
     <row r="31" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="6"/>
-      <c r="B31" s="60" t="s">
+      <c r="B31" s="48" t="s">
         <v>36</v>
       </c>
-      <c r="C31" s="61"/>
-      <c r="D31" s="62"/>
-      <c r="E31" s="73"/>
-      <c r="F31" s="74"/>
-      <c r="G31" s="74"/>
-      <c r="H31" s="74"/>
-      <c r="I31" s="74"/>
-      <c r="J31" s="74"/>
-      <c r="K31" s="74"/>
-      <c r="L31" s="74"/>
-      <c r="M31" s="75"/>
+      <c r="C31" s="117"/>
+      <c r="D31" s="49"/>
+      <c r="E31" s="129"/>
+      <c r="F31" s="130"/>
+      <c r="G31" s="130"/>
+      <c r="H31" s="130"/>
+      <c r="I31" s="130"/>
+      <c r="J31" s="130"/>
+      <c r="K31" s="130"/>
+      <c r="L31" s="130"/>
+      <c r="M31" s="131"/>
     </row>
     <row r="32" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="6"/>
-      <c r="B32" s="60" t="s">
+      <c r="B32" s="48" t="s">
         <v>19</v>
       </c>
-      <c r="C32" s="61"/>
-      <c r="D32" s="62"/>
-      <c r="E32" s="63"/>
-      <c r="F32" s="64"/>
-      <c r="G32" s="64"/>
-      <c r="H32" s="64"/>
-      <c r="I32" s="64"/>
-      <c r="J32" s="64"/>
-      <c r="K32" s="64"/>
-      <c r="L32" s="64"/>
-      <c r="M32" s="65"/>
+      <c r="C32" s="117"/>
+      <c r="D32" s="49"/>
+      <c r="E32" s="126"/>
+      <c r="F32" s="127"/>
+      <c r="G32" s="127"/>
+      <c r="H32" s="127"/>
+      <c r="I32" s="127"/>
+      <c r="J32" s="127"/>
+      <c r="K32" s="127"/>
+      <c r="L32" s="127"/>
+      <c r="M32" s="128"/>
     </row>
     <row r="33" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="6"/>
-      <c r="B33" s="60" t="s">
+      <c r="B33" s="48" t="s">
         <v>37</v>
       </c>
-      <c r="C33" s="61"/>
-      <c r="D33" s="62"/>
-      <c r="E33" s="73"/>
-      <c r="F33" s="74"/>
-      <c r="G33" s="74"/>
-      <c r="H33" s="74"/>
-      <c r="I33" s="74"/>
-      <c r="J33" s="74"/>
-      <c r="K33" s="74"/>
-      <c r="L33" s="74"/>
-      <c r="M33" s="75"/>
+      <c r="C33" s="117"/>
+      <c r="D33" s="49"/>
+      <c r="E33" s="129"/>
+      <c r="F33" s="130"/>
+      <c r="G33" s="130"/>
+      <c r="H33" s="130"/>
+      <c r="I33" s="130"/>
+      <c r="J33" s="130"/>
+      <c r="K33" s="130"/>
+      <c r="L33" s="130"/>
+      <c r="M33" s="131"/>
     </row>
     <row r="34" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="7"/>
-      <c r="B34" s="88" t="s">
+      <c r="B34" s="151" t="s">
         <v>38</v>
       </c>
-      <c r="C34" s="89"/>
-      <c r="D34" s="90"/>
-      <c r="E34" s="63"/>
-      <c r="F34" s="64"/>
-      <c r="G34" s="64"/>
-      <c r="H34" s="64"/>
-      <c r="I34" s="64"/>
-      <c r="J34" s="64"/>
-      <c r="K34" s="64"/>
-      <c r="L34" s="64"/>
-      <c r="M34" s="65"/>
+      <c r="C34" s="152"/>
+      <c r="D34" s="153"/>
+      <c r="E34" s="126"/>
+      <c r="F34" s="127"/>
+      <c r="G34" s="127"/>
+      <c r="H34" s="127"/>
+      <c r="I34" s="127"/>
+      <c r="J34" s="127"/>
+      <c r="K34" s="127"/>
+      <c r="L34" s="127"/>
+      <c r="M34" s="128"/>
     </row>
     <row r="35" spans="1:13" ht="25.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="B35" s="57" t="s">
+      <c r="B35" s="172" t="s">
         <v>41</v>
       </c>
-      <c r="C35" s="58"/>
-      <c r="D35" s="59"/>
-      <c r="E35" s="63"/>
-      <c r="F35" s="64"/>
-      <c r="G35" s="64"/>
-      <c r="H35" s="64"/>
-      <c r="I35" s="64"/>
-      <c r="J35" s="64"/>
-      <c r="K35" s="64"/>
-      <c r="L35" s="64"/>
-      <c r="M35" s="65"/>
+      <c r="C35" s="173"/>
+      <c r="D35" s="174"/>
+      <c r="E35" s="126"/>
+      <c r="F35" s="127"/>
+      <c r="G35" s="127"/>
+      <c r="H35" s="127"/>
+      <c r="I35" s="127"/>
+      <c r="J35" s="127"/>
+      <c r="K35" s="127"/>
+      <c r="L35" s="127"/>
+      <c r="M35" s="128"/>
     </row>
     <row r="36" spans="1:13" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="B36" s="60" t="s">
+      <c r="B36" s="48" t="s">
         <v>42</v>
       </c>
-      <c r="C36" s="61"/>
-      <c r="D36" s="62"/>
-      <c r="E36" s="63"/>
-      <c r="F36" s="64"/>
-      <c r="G36" s="64"/>
-      <c r="H36" s="64"/>
-      <c r="I36" s="64"/>
-      <c r="J36" s="64"/>
-      <c r="K36" s="64"/>
-      <c r="L36" s="64"/>
-      <c r="M36" s="65"/>
+      <c r="C36" s="117"/>
+      <c r="D36" s="49"/>
+      <c r="E36" s="126"/>
+      <c r="F36" s="127"/>
+      <c r="G36" s="127"/>
+      <c r="H36" s="127"/>
+      <c r="I36" s="127"/>
+      <c r="J36" s="127"/>
+      <c r="K36" s="127"/>
+      <c r="L36" s="127"/>
+      <c r="M36" s="128"/>
     </row>
     <row r="37" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="10"/>
-      <c r="B37" s="60" t="s">
+      <c r="B37" s="48" t="s">
         <v>19</v>
       </c>
-      <c r="C37" s="61"/>
-      <c r="D37" s="62"/>
-      <c r="E37" s="63"/>
-      <c r="F37" s="64"/>
-      <c r="G37" s="64"/>
-      <c r="H37" s="64"/>
-      <c r="I37" s="64"/>
-      <c r="J37" s="64"/>
-      <c r="K37" s="64"/>
-      <c r="L37" s="64"/>
-      <c r="M37" s="65"/>
+      <c r="C37" s="117"/>
+      <c r="D37" s="49"/>
+      <c r="E37" s="126"/>
+      <c r="F37" s="127"/>
+      <c r="G37" s="127"/>
+      <c r="H37" s="127"/>
+      <c r="I37" s="127"/>
+      <c r="J37" s="127"/>
+      <c r="K37" s="127"/>
+      <c r="L37" s="127"/>
+      <c r="M37" s="128"/>
     </row>
     <row r="38" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="33" t="s">
+      <c r="A38" s="154" t="s">
         <v>43</v>
       </c>
-      <c r="B38" s="33"/>
-      <c r="C38" s="33"/>
-      <c r="D38" s="33"/>
-      <c r="E38" s="33"/>
-      <c r="F38" s="33"/>
-      <c r="G38" s="33"/>
-      <c r="H38" s="33"/>
-      <c r="I38" s="33"/>
-      <c r="J38" s="33"/>
-      <c r="K38" s="33"/>
-      <c r="L38" s="33"/>
-      <c r="M38" s="33"/>
+      <c r="B38" s="154"/>
+      <c r="C38" s="154"/>
+      <c r="D38" s="154"/>
+      <c r="E38" s="154"/>
+      <c r="F38" s="154"/>
+      <c r="G38" s="154"/>
+      <c r="H38" s="154"/>
+      <c r="I38" s="154"/>
+      <c r="J38" s="154"/>
+      <c r="K38" s="154"/>
+      <c r="L38" s="154"/>
+      <c r="M38" s="154"/>
     </row>
     <row r="39" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="33"/>
-      <c r="B39" s="33"/>
-      <c r="C39" s="33"/>
-      <c r="D39" s="33"/>
-      <c r="E39" s="33"/>
-      <c r="F39" s="33"/>
-      <c r="G39" s="33"/>
-      <c r="H39" s="33"/>
-      <c r="I39" s="33"/>
-      <c r="J39" s="33"/>
-      <c r="K39" s="33"/>
-      <c r="L39" s="33"/>
-      <c r="M39" s="33"/>
+      <c r="A39" s="154"/>
+      <c r="B39" s="154"/>
+      <c r="C39" s="154"/>
+      <c r="D39" s="154"/>
+      <c r="E39" s="154"/>
+      <c r="F39" s="154"/>
+      <c r="G39" s="154"/>
+      <c r="H39" s="154"/>
+      <c r="I39" s="154"/>
+      <c r="J39" s="154"/>
+      <c r="K39" s="154"/>
+      <c r="L39" s="154"/>
+      <c r="M39" s="154"/>
     </row>
     <row r="40" spans="1:13" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="33"/>
-      <c r="B40" s="33"/>
-      <c r="C40" s="33"/>
-      <c r="D40" s="33"/>
-      <c r="E40" s="33"/>
-      <c r="F40" s="33"/>
-      <c r="G40" s="33"/>
-      <c r="H40" s="33"/>
-      <c r="I40" s="33"/>
-      <c r="J40" s="33"/>
-      <c r="K40" s="33"/>
-      <c r="L40" s="33"/>
-      <c r="M40" s="33"/>
+      <c r="A40" s="154"/>
+      <c r="B40" s="154"/>
+      <c r="C40" s="154"/>
+      <c r="D40" s="154"/>
+      <c r="E40" s="154"/>
+      <c r="F40" s="154"/>
+      <c r="G40" s="154"/>
+      <c r="H40" s="154"/>
+      <c r="I40" s="154"/>
+      <c r="J40" s="154"/>
+      <c r="K40" s="154"/>
+      <c r="L40" s="154"/>
+      <c r="M40" s="154"/>
     </row>
     <row r="41" spans="1:13" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="11"/>
-      <c r="B41" s="145" t="s">
+      <c r="B41" s="90" t="s">
         <v>65</v>
       </c>
-      <c r="C41" s="145"/>
-      <c r="D41" s="145"/>
-      <c r="E41" s="145"/>
-      <c r="F41" s="145"/>
-      <c r="G41" s="145"/>
-      <c r="H41" s="145"/>
-      <c r="I41" s="145"/>
-      <c r="J41" s="145"/>
+      <c r="C41" s="90"/>
+      <c r="D41" s="90"/>
+      <c r="E41" s="90"/>
+      <c r="F41" s="90"/>
+      <c r="G41" s="90"/>
+      <c r="H41" s="90"/>
+      <c r="I41" s="90"/>
+      <c r="J41" s="90"/>
       <c r="K41" s="11"/>
       <c r="L41" s="11"/>
       <c r="M41" s="11"/>
     </row>
     <row r="42" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B42" s="145" t="s">
+      <c r="B42" s="90" t="s">
         <v>66</v>
       </c>
-      <c r="C42" s="145"/>
-      <c r="D42" s="145"/>
-      <c r="E42" s="145"/>
-      <c r="F42" s="145"/>
-      <c r="G42" s="145"/>
-      <c r="H42" s="145"/>
-      <c r="I42" s="145"/>
-      <c r="J42" s="145"/>
+      <c r="C42" s="90"/>
+      <c r="D42" s="90"/>
+      <c r="E42" s="90"/>
+      <c r="F42" s="90"/>
+      <c r="G42" s="90"/>
+      <c r="H42" s="90"/>
+      <c r="I42" s="90"/>
+      <c r="J42" s="90"/>
       <c r="L42" s="18"/>
     </row>
     <row r="43" spans="1:13" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B43" s="47" t="s">
+      <c r="B43" s="162" t="s">
         <v>72</v>
       </c>
-      <c r="C43" s="48"/>
+      <c r="C43" s="163"/>
       <c r="D43" s="22"/>
-      <c r="E43" s="149" t="s">
+      <c r="E43" s="94" t="s">
         <v>75</v>
       </c>
-      <c r="F43" s="150"/>
-      <c r="G43" s="151"/>
-      <c r="H43" s="152"/>
+      <c r="F43" s="95"/>
+      <c r="G43" s="96"/>
+      <c r="H43" s="97"/>
       <c r="I43" s="17" t="s">
         <v>76</v>
       </c>
       <c r="J43" s="19"/>
     </row>
     <row r="44" spans="1:13" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B44" s="49" t="s">
+      <c r="B44" s="164" t="s">
         <v>73</v>
       </c>
-      <c r="C44" s="50"/>
+      <c r="C44" s="165"/>
       <c r="D44" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="E44" s="51" t="s">
+      <c r="E44" s="166" t="s">
         <v>74</v>
       </c>
-      <c r="F44" s="52"/>
-      <c r="G44" s="53"/>
-      <c r="H44" s="54"/>
-      <c r="I44" s="55"/>
-      <c r="J44" s="56"/>
+      <c r="F44" s="167"/>
+      <c r="G44" s="168"/>
+      <c r="H44" s="169"/>
+      <c r="I44" s="170"/>
+      <c r="J44" s="171"/>
     </row>
     <row r="45" spans="1:13" ht="2.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="46" spans="1:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="11"/>
-      <c r="B46" s="146" t="s">
+      <c r="B46" s="91" t="s">
         <v>45</v>
       </c>
-      <c r="C46" s="147"/>
-      <c r="D46" s="147"/>
-      <c r="E46" s="147"/>
-      <c r="F46" s="147"/>
-      <c r="G46" s="147"/>
-      <c r="H46" s="147"/>
-      <c r="I46" s="147"/>
-      <c r="J46" s="148"/>
+      <c r="C46" s="92"/>
+      <c r="D46" s="92"/>
+      <c r="E46" s="92"/>
+      <c r="F46" s="92"/>
+      <c r="G46" s="92"/>
+      <c r="H46" s="92"/>
+      <c r="I46" s="92"/>
+      <c r="J46" s="93"/>
       <c r="K46" s="11"/>
       <c r="L46" s="11"/>
       <c r="M46" s="11"/>
     </row>
     <row r="47" spans="1:13" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="11"/>
-      <c r="B47" s="137" t="s">
+      <c r="B47" s="72" t="s">
         <v>46</v>
       </c>
-      <c r="C47" s="138"/>
-      <c r="D47" s="119" t="s">
+      <c r="C47" s="73"/>
+      <c r="D47" s="76" t="s">
         <v>47</v>
       </c>
-      <c r="E47" s="139"/>
-      <c r="F47" s="139"/>
-      <c r="G47" s="120"/>
-      <c r="H47" s="124" t="s">
+      <c r="E47" s="77"/>
+      <c r="F47" s="77"/>
+      <c r="G47" s="78"/>
+      <c r="H47" s="79" t="s">
         <v>48</v>
       </c>
-      <c r="I47" s="128"/>
-      <c r="J47" s="125"/>
+      <c r="I47" s="80"/>
+      <c r="J47" s="81"/>
       <c r="K47" s="11"/>
       <c r="L47" s="11"/>
       <c r="M47" s="11"/>
     </row>
     <row r="48" spans="1:13" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="11"/>
-      <c r="B48" s="117"/>
-      <c r="C48" s="118"/>
-      <c r="D48" s="140" t="s">
+      <c r="B48" s="74"/>
+      <c r="C48" s="75"/>
+      <c r="D48" s="85" t="s">
         <v>49</v>
       </c>
-      <c r="E48" s="141"/>
-      <c r="F48" s="140" t="s">
+      <c r="E48" s="86"/>
+      <c r="F48" s="85" t="s">
         <v>50</v>
       </c>
-      <c r="G48" s="141"/>
-      <c r="H48" s="126"/>
-      <c r="I48" s="129"/>
-      <c r="J48" s="127"/>
+      <c r="G48" s="86"/>
+      <c r="H48" s="82"/>
+      <c r="I48" s="83"/>
+      <c r="J48" s="84"/>
       <c r="K48" s="11"/>
       <c r="L48" s="11"/>
       <c r="M48" s="11"/>
     </row>
     <row r="49" spans="1:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="13"/>
-      <c r="B49" s="100" t="s">
+      <c r="B49" s="53" t="s">
         <v>51</v>
       </c>
-      <c r="C49" s="101"/>
-      <c r="D49" s="102"/>
-      <c r="E49" s="103"/>
-      <c r="F49" s="102"/>
-      <c r="G49" s="103"/>
-      <c r="H49" s="142"/>
-      <c r="I49" s="143"/>
-      <c r="J49" s="144"/>
+      <c r="C49" s="54"/>
+      <c r="D49" s="55"/>
+      <c r="E49" s="56"/>
+      <c r="F49" s="55"/>
+      <c r="G49" s="56"/>
+      <c r="H49" s="87"/>
+      <c r="I49" s="88"/>
+      <c r="J49" s="89"/>
       <c r="K49" s="13"/>
       <c r="L49" s="13"/>
       <c r="M49" s="13"/>
     </row>
     <row r="50" spans="1:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="13"/>
-      <c r="B50" s="100" t="s">
+      <c r="B50" s="53" t="s">
         <v>52</v>
       </c>
-      <c r="C50" s="101"/>
-      <c r="D50" s="102"/>
-      <c r="E50" s="103"/>
-      <c r="F50" s="40"/>
-      <c r="G50" s="41"/>
-      <c r="H50" s="97"/>
-      <c r="I50" s="98"/>
-      <c r="J50" s="99"/>
+      <c r="C50" s="54"/>
+      <c r="D50" s="55"/>
+      <c r="E50" s="56"/>
+      <c r="F50" s="155"/>
+      <c r="G50" s="156"/>
+      <c r="H50" s="62"/>
+      <c r="I50" s="63"/>
+      <c r="J50" s="64"/>
       <c r="K50" s="13"/>
       <c r="L50" s="13"/>
       <c r="M50" s="13"/>
     </row>
     <row r="51" spans="1:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="13"/>
-      <c r="B51" s="100" t="s">
+      <c r="B51" s="53" t="s">
         <v>53</v>
       </c>
-      <c r="C51" s="101"/>
-      <c r="D51" s="102"/>
-      <c r="E51" s="103"/>
-      <c r="F51" s="102"/>
-      <c r="G51" s="103"/>
-      <c r="H51" s="97"/>
-      <c r="I51" s="98"/>
-      <c r="J51" s="99"/>
+      <c r="C51" s="54"/>
+      <c r="D51" s="55"/>
+      <c r="E51" s="56"/>
+      <c r="F51" s="55"/>
+      <c r="G51" s="56"/>
+      <c r="H51" s="62"/>
+      <c r="I51" s="63"/>
+      <c r="J51" s="64"/>
       <c r="K51" s="13"/>
       <c r="L51" s="13"/>
       <c r="M51" s="13"/>
     </row>
     <row r="52" spans="1:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="13"/>
-      <c r="B52" s="156" t="s">
+      <c r="B52" s="60" t="s">
         <v>64</v>
       </c>
-      <c r="C52" s="157"/>
-      <c r="D52" s="135"/>
-      <c r="E52" s="136"/>
-      <c r="F52" s="135"/>
-      <c r="G52" s="136"/>
-      <c r="H52" s="34"/>
-      <c r="I52" s="35"/>
-      <c r="J52" s="36"/>
+      <c r="C52" s="61"/>
+      <c r="D52" s="103"/>
+      <c r="E52" s="104"/>
+      <c r="F52" s="103"/>
+      <c r="G52" s="104"/>
+      <c r="H52" s="105"/>
+      <c r="I52" s="106"/>
+      <c r="J52" s="107"/>
       <c r="K52" s="13"/>
       <c r="L52" s="13"/>
       <c r="M52" s="13"/>
     </row>
     <row r="53" spans="1:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="13"/>
-      <c r="B53" s="100" t="s">
+      <c r="B53" s="53" t="s">
         <v>54</v>
       </c>
-      <c r="C53" s="101"/>
-      <c r="D53" s="102"/>
-      <c r="E53" s="103"/>
-      <c r="F53" s="102"/>
-      <c r="G53" s="103"/>
-      <c r="H53" s="121"/>
-      <c r="I53" s="122"/>
-      <c r="J53" s="123"/>
+      <c r="C53" s="54"/>
+      <c r="D53" s="55"/>
+      <c r="E53" s="56"/>
+      <c r="F53" s="55"/>
+      <c r="G53" s="56"/>
+      <c r="H53" s="57"/>
+      <c r="I53" s="58"/>
+      <c r="J53" s="59"/>
       <c r="K53" s="13"/>
       <c r="L53" s="13"/>
       <c r="M53" s="13"/>
     </row>
     <row r="54" spans="1:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="13"/>
-      <c r="B54" s="100" t="s">
+      <c r="B54" s="53" t="s">
         <v>55</v>
       </c>
-      <c r="C54" s="101"/>
-      <c r="D54" s="102"/>
-      <c r="E54" s="103"/>
-      <c r="F54" s="102"/>
-      <c r="G54" s="103"/>
-      <c r="H54" s="97"/>
-      <c r="I54" s="98"/>
-      <c r="J54" s="99"/>
+      <c r="C54" s="54"/>
+      <c r="D54" s="55"/>
+      <c r="E54" s="56"/>
+      <c r="F54" s="55"/>
+      <c r="G54" s="56"/>
+      <c r="H54" s="62"/>
+      <c r="I54" s="63"/>
+      <c r="J54" s="64"/>
       <c r="K54" s="13"/>
       <c r="L54" s="13"/>
       <c r="M54" s="13"/>
     </row>
     <row r="55" spans="1:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A55" s="13"/>
-      <c r="B55" s="100" t="s">
+      <c r="B55" s="53" t="s">
         <v>56</v>
       </c>
-      <c r="C55" s="101"/>
-      <c r="D55" s="102"/>
-      <c r="E55" s="103"/>
-      <c r="F55" s="102"/>
-      <c r="G55" s="103"/>
-      <c r="H55" s="97"/>
-      <c r="I55" s="98"/>
-      <c r="J55" s="99"/>
+      <c r="C55" s="54"/>
+      <c r="D55" s="55"/>
+      <c r="E55" s="56"/>
+      <c r="F55" s="55"/>
+      <c r="G55" s="56"/>
+      <c r="H55" s="62"/>
+      <c r="I55" s="63"/>
+      <c r="J55" s="64"/>
       <c r="K55" s="13"/>
       <c r="L55" s="13"/>
       <c r="M55" s="13"/>
     </row>
     <row r="56" spans="1:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A56" s="13"/>
-      <c r="B56" s="158" t="s">
+      <c r="B56" s="65" t="s">
         <v>57</v>
       </c>
-      <c r="C56" s="159"/>
-      <c r="D56" s="160"/>
-      <c r="E56" s="161"/>
-      <c r="F56" s="160"/>
-      <c r="G56" s="161"/>
-      <c r="H56" s="162"/>
-      <c r="I56" s="163"/>
-      <c r="J56" s="164"/>
+      <c r="C56" s="66"/>
+      <c r="D56" s="67"/>
+      <c r="E56" s="68"/>
+      <c r="F56" s="67"/>
+      <c r="G56" s="68"/>
+      <c r="H56" s="69"/>
+      <c r="I56" s="70"/>
+      <c r="J56" s="71"/>
       <c r="K56" s="13"/>
       <c r="L56" s="13"/>
       <c r="M56" s="13"/>
     </row>
     <row r="57" spans="1:13" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57" s="13"/>
-      <c r="B57" s="132" t="s">
+      <c r="B57" s="100" t="s">
         <v>58</v>
       </c>
-      <c r="C57" s="133"/>
-      <c r="D57" s="133"/>
-      <c r="E57" s="133"/>
-      <c r="F57" s="133"/>
-      <c r="G57" s="133"/>
-      <c r="H57" s="133"/>
-      <c r="I57" s="133"/>
-      <c r="J57" s="134"/>
+      <c r="C57" s="101"/>
+      <c r="D57" s="101"/>
+      <c r="E57" s="101"/>
+      <c r="F57" s="101"/>
+      <c r="G57" s="101"/>
+      <c r="H57" s="101"/>
+      <c r="I57" s="101"/>
+      <c r="J57" s="102"/>
       <c r="K57" s="13"/>
       <c r="L57" s="13"/>
       <c r="M57" s="13"/>
     </row>
     <row r="58" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A58" s="13"/>
-      <c r="B58" s="124" t="s">
+      <c r="B58" s="79" t="s">
         <v>46</v>
       </c>
-      <c r="C58" s="125"/>
-      <c r="D58" s="37" t="s">
+      <c r="C58" s="81"/>
+      <c r="D58" s="45" t="s">
         <v>47</v>
       </c>
-      <c r="E58" s="38"/>
-      <c r="F58" s="38"/>
-      <c r="G58" s="39"/>
-      <c r="H58" s="124" t="s">
+      <c r="E58" s="46"/>
+      <c r="F58" s="46"/>
+      <c r="G58" s="47"/>
+      <c r="H58" s="79" t="s">
         <v>48</v>
       </c>
-      <c r="I58" s="128"/>
-      <c r="J58" s="125"/>
+      <c r="I58" s="80"/>
+      <c r="J58" s="81"/>
       <c r="K58" s="13"/>
       <c r="L58" s="13"/>
       <c r="M58" s="13"/>
     </row>
     <row r="59" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A59" s="13"/>
-      <c r="B59" s="126"/>
-      <c r="C59" s="127"/>
-      <c r="D59" s="130" t="s">
+      <c r="B59" s="82"/>
+      <c r="C59" s="84"/>
+      <c r="D59" s="98" t="s">
         <v>49</v>
       </c>
-      <c r="E59" s="131"/>
-      <c r="F59" s="130" t="s">
+      <c r="E59" s="99"/>
+      <c r="F59" s="98" t="s">
         <v>50</v>
       </c>
-      <c r="G59" s="131"/>
-      <c r="H59" s="126"/>
-      <c r="I59" s="129"/>
-      <c r="J59" s="127"/>
+      <c r="G59" s="99"/>
+      <c r="H59" s="82"/>
+      <c r="I59" s="83"/>
+      <c r="J59" s="84"/>
       <c r="K59" s="13"/>
       <c r="L59" s="13"/>
       <c r="M59" s="13"/>
     </row>
     <row r="60" spans="1:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A60" s="13"/>
-      <c r="B60" s="100" t="s">
+      <c r="B60" s="53" t="s">
         <v>59</v>
       </c>
-      <c r="C60" s="101"/>
-      <c r="D60" s="102"/>
-      <c r="E60" s="103"/>
-      <c r="F60" s="102"/>
-      <c r="G60" s="103"/>
-      <c r="H60" s="121"/>
-      <c r="I60" s="122"/>
-      <c r="J60" s="123"/>
+      <c r="C60" s="54"/>
+      <c r="D60" s="55"/>
+      <c r="E60" s="56"/>
+      <c r="F60" s="55"/>
+      <c r="G60" s="56"/>
+      <c r="H60" s="57"/>
+      <c r="I60" s="58"/>
+      <c r="J60" s="59"/>
       <c r="K60" s="13"/>
       <c r="L60" s="13"/>
       <c r="M60" s="13"/>
     </row>
     <row r="61" spans="1:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A61" s="13"/>
-      <c r="B61" s="100" t="s">
+      <c r="B61" s="53" t="s">
         <v>60</v>
       </c>
-      <c r="C61" s="101"/>
-      <c r="D61" s="102"/>
-      <c r="E61" s="103"/>
-      <c r="F61" s="102"/>
-      <c r="G61" s="103"/>
-      <c r="H61" s="121"/>
-      <c r="I61" s="122"/>
-      <c r="J61" s="123"/>
+      <c r="C61" s="54"/>
+      <c r="D61" s="55"/>
+      <c r="E61" s="56"/>
+      <c r="F61" s="55"/>
+      <c r="G61" s="56"/>
+      <c r="H61" s="57"/>
+      <c r="I61" s="58"/>
+      <c r="J61" s="59"/>
       <c r="K61" s="13"/>
       <c r="L61" s="13"/>
       <c r="M61" s="13"/>
     </row>
     <row r="62" spans="1:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A62" s="13"/>
-      <c r="B62" s="100" t="s">
+      <c r="B62" s="53" t="s">
         <v>61</v>
       </c>
-      <c r="C62" s="101"/>
-      <c r="D62" s="102"/>
-      <c r="E62" s="103"/>
-      <c r="F62" s="102"/>
-      <c r="G62" s="103"/>
-      <c r="H62" s="121"/>
-      <c r="I62" s="122"/>
-      <c r="J62" s="123"/>
+      <c r="C62" s="54"/>
+      <c r="D62" s="55"/>
+      <c r="E62" s="56"/>
+      <c r="F62" s="55"/>
+      <c r="G62" s="56"/>
+      <c r="H62" s="57"/>
+      <c r="I62" s="58"/>
+      <c r="J62" s="59"/>
       <c r="K62" s="13"/>
       <c r="L62" s="13"/>
       <c r="M62" s="13"/>
     </row>
     <row r="63" spans="1:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A63" s="13"/>
-      <c r="B63" s="100" t="s">
+      <c r="B63" s="53" t="s">
         <v>62</v>
       </c>
-      <c r="C63" s="101"/>
-      <c r="D63" s="102"/>
-      <c r="E63" s="103"/>
-      <c r="F63" s="102"/>
-      <c r="G63" s="103"/>
-      <c r="H63" s="121"/>
-      <c r="I63" s="122"/>
-      <c r="J63" s="123"/>
+      <c r="C63" s="54"/>
+      <c r="D63" s="55"/>
+      <c r="E63" s="56"/>
+      <c r="F63" s="55"/>
+      <c r="G63" s="56"/>
+      <c r="H63" s="57"/>
+      <c r="I63" s="58"/>
+      <c r="J63" s="59"/>
       <c r="K63" s="13"/>
       <c r="L63" s="13"/>
       <c r="M63" s="13"/>
     </row>
     <row r="64" spans="1:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A64" s="13"/>
-      <c r="B64" s="100" t="s">
+      <c r="B64" s="53" t="s">
         <v>63</v>
       </c>
-      <c r="C64" s="101"/>
-      <c r="D64" s="102"/>
-      <c r="E64" s="103"/>
-      <c r="F64" s="102"/>
-      <c r="G64" s="103"/>
-      <c r="H64" s="121"/>
-      <c r="I64" s="122"/>
-      <c r="J64" s="123"/>
+      <c r="C64" s="54"/>
+      <c r="D64" s="55"/>
+      <c r="E64" s="56"/>
+      <c r="F64" s="55"/>
+      <c r="G64" s="56"/>
+      <c r="H64" s="57"/>
+      <c r="I64" s="58"/>
+      <c r="J64" s="59"/>
       <c r="K64" s="13"/>
       <c r="L64" s="13"/>
       <c r="M64" s="13"/>
@@ -3092,51 +3092,51 @@
     </row>
     <row r="66" spans="1:13" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A66" s="13"/>
-      <c r="B66" s="37" t="s">
+      <c r="B66" s="45" t="s">
         <v>67</v>
       </c>
-      <c r="C66" s="38"/>
-      <c r="D66" s="38"/>
-      <c r="E66" s="38"/>
-      <c r="F66" s="38"/>
-      <c r="G66" s="38"/>
-      <c r="H66" s="38"/>
-      <c r="I66" s="38"/>
-      <c r="J66" s="39"/>
+      <c r="C66" s="46"/>
+      <c r="D66" s="46"/>
+      <c r="E66" s="46"/>
+      <c r="F66" s="46"/>
+      <c r="G66" s="46"/>
+      <c r="H66" s="46"/>
+      <c r="I66" s="46"/>
+      <c r="J66" s="47"/>
       <c r="K66" s="13"/>
       <c r="L66" s="13"/>
       <c r="M66" s="13"/>
     </row>
     <row r="67" spans="1:13" ht="72" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A67" s="13"/>
-      <c r="B67" s="60" t="s">
+      <c r="B67" s="48" t="s">
         <v>68</v>
       </c>
-      <c r="C67" s="62"/>
-      <c r="D67" s="153"/>
-      <c r="E67" s="154"/>
-      <c r="F67" s="154"/>
-      <c r="G67" s="154"/>
-      <c r="H67" s="154"/>
-      <c r="I67" s="154"/>
-      <c r="J67" s="155"/>
+      <c r="C67" s="49"/>
+      <c r="D67" s="50"/>
+      <c r="E67" s="51"/>
+      <c r="F67" s="51"/>
+      <c r="G67" s="51"/>
+      <c r="H67" s="51"/>
+      <c r="I67" s="51"/>
+      <c r="J67" s="52"/>
       <c r="K67" s="13"/>
       <c r="L67" s="13"/>
       <c r="M67" s="13"/>
     </row>
     <row r="68" spans="1:13" ht="72" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A68" s="13"/>
-      <c r="B68" s="60" t="s">
+      <c r="B68" s="48" t="s">
         <v>69</v>
       </c>
-      <c r="C68" s="62"/>
-      <c r="D68" s="153"/>
-      <c r="E68" s="154"/>
-      <c r="F68" s="154"/>
-      <c r="G68" s="154"/>
-      <c r="H68" s="154"/>
-      <c r="I68" s="154"/>
-      <c r="J68" s="155"/>
+      <c r="C68" s="49"/>
+      <c r="D68" s="50"/>
+      <c r="E68" s="51"/>
+      <c r="F68" s="51"/>
+      <c r="G68" s="51"/>
+      <c r="H68" s="51"/>
+      <c r="I68" s="51"/>
+      <c r="J68" s="52"/>
       <c r="K68" s="13"/>
       <c r="L68" s="13"/>
       <c r="M68" s="13"/>
@@ -3158,51 +3158,51 @@
     </row>
     <row r="70" spans="1:13" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A70" s="13"/>
-      <c r="B70" s="37" t="s">
+      <c r="B70" s="45" t="s">
         <v>70</v>
       </c>
-      <c r="C70" s="38"/>
-      <c r="D70" s="38"/>
-      <c r="E70" s="38"/>
-      <c r="F70" s="38"/>
-      <c r="G70" s="38"/>
-      <c r="H70" s="38"/>
-      <c r="I70" s="38"/>
-      <c r="J70" s="39"/>
+      <c r="C70" s="46"/>
+      <c r="D70" s="46"/>
+      <c r="E70" s="46"/>
+      <c r="F70" s="46"/>
+      <c r="G70" s="46"/>
+      <c r="H70" s="46"/>
+      <c r="I70" s="46"/>
+      <c r="J70" s="47"/>
       <c r="K70" s="13"/>
       <c r="L70" s="13"/>
       <c r="M70" s="13"/>
     </row>
     <row r="71" spans="1:13" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A71" s="13"/>
-      <c r="B71" s="60" t="s">
+      <c r="B71" s="48" t="s">
         <v>68</v>
       </c>
-      <c r="C71" s="62"/>
-      <c r="D71" s="153"/>
-      <c r="E71" s="154"/>
-      <c r="F71" s="154"/>
-      <c r="G71" s="154"/>
-      <c r="H71" s="154"/>
-      <c r="I71" s="154"/>
-      <c r="J71" s="155"/>
+      <c r="C71" s="49"/>
+      <c r="D71" s="50"/>
+      <c r="E71" s="51"/>
+      <c r="F71" s="51"/>
+      <c r="G71" s="51"/>
+      <c r="H71" s="51"/>
+      <c r="I71" s="51"/>
+      <c r="J71" s="52"/>
       <c r="K71" s="13"/>
       <c r="L71" s="13"/>
       <c r="M71" s="13"/>
     </row>
     <row r="72" spans="1:13" ht="72" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A72" s="13"/>
-      <c r="B72" s="60" t="s">
+      <c r="B72" s="48" t="s">
         <v>69</v>
       </c>
-      <c r="C72" s="62"/>
-      <c r="D72" s="153"/>
-      <c r="E72" s="154"/>
-      <c r="F72" s="154"/>
-      <c r="G72" s="154"/>
-      <c r="H72" s="154"/>
-      <c r="I72" s="154"/>
-      <c r="J72" s="155"/>
+      <c r="C72" s="49"/>
+      <c r="D72" s="50"/>
+      <c r="E72" s="51"/>
+      <c r="F72" s="51"/>
+      <c r="G72" s="51"/>
+      <c r="H72" s="51"/>
+      <c r="I72" s="51"/>
+      <c r="J72" s="52"/>
       <c r="K72" s="13"/>
       <c r="L72" s="13"/>
       <c r="M72" s="13"/>
@@ -3224,51 +3224,51 @@
     </row>
     <row r="74" spans="1:13" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A74" s="13"/>
-      <c r="B74" s="37" t="s">
+      <c r="B74" s="45" t="s">
         <v>71</v>
       </c>
-      <c r="C74" s="38"/>
-      <c r="D74" s="38"/>
-      <c r="E74" s="38"/>
-      <c r="F74" s="38"/>
-      <c r="G74" s="38"/>
-      <c r="H74" s="38"/>
-      <c r="I74" s="38"/>
-      <c r="J74" s="39"/>
+      <c r="C74" s="46"/>
+      <c r="D74" s="46"/>
+      <c r="E74" s="46"/>
+      <c r="F74" s="46"/>
+      <c r="G74" s="46"/>
+      <c r="H74" s="46"/>
+      <c r="I74" s="46"/>
+      <c r="J74" s="47"/>
       <c r="K74" s="13"/>
       <c r="L74" s="13"/>
       <c r="M74" s="13"/>
     </row>
     <row r="75" spans="1:13" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A75" s="13"/>
-      <c r="B75" s="60" t="s">
+      <c r="B75" s="48" t="s">
         <v>68</v>
       </c>
-      <c r="C75" s="62"/>
-      <c r="D75" s="153"/>
-      <c r="E75" s="154"/>
-      <c r="F75" s="154"/>
-      <c r="G75" s="154"/>
-      <c r="H75" s="154"/>
-      <c r="I75" s="154"/>
-      <c r="J75" s="155"/>
+      <c r="C75" s="49"/>
+      <c r="D75" s="50"/>
+      <c r="E75" s="51"/>
+      <c r="F75" s="51"/>
+      <c r="G75" s="51"/>
+      <c r="H75" s="51"/>
+      <c r="I75" s="51"/>
+      <c r="J75" s="52"/>
       <c r="K75" s="13"/>
       <c r="L75" s="13"/>
       <c r="M75" s="13"/>
     </row>
     <row r="76" spans="1:13" ht="71.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A76" s="13"/>
-      <c r="B76" s="60" t="s">
+      <c r="B76" s="48" t="s">
         <v>69</v>
       </c>
-      <c r="C76" s="62"/>
-      <c r="D76" s="153"/>
-      <c r="E76" s="154"/>
-      <c r="F76" s="154"/>
-      <c r="G76" s="154"/>
-      <c r="H76" s="154"/>
-      <c r="I76" s="154"/>
-      <c r="J76" s="155"/>
+      <c r="C76" s="49"/>
+      <c r="D76" s="50"/>
+      <c r="E76" s="51"/>
+      <c r="F76" s="51"/>
+      <c r="G76" s="51"/>
+      <c r="H76" s="51"/>
+      <c r="I76" s="51"/>
+      <c r="J76" s="52"/>
       <c r="K76" s="13"/>
       <c r="L76" s="13"/>
       <c r="M76" s="13"/>
@@ -3291,12 +3291,12 @@
     <row r="78" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="11"/>
       <c r="B78" s="12"/>
-      <c r="C78" s="66" t="s">
+      <c r="C78" s="175" t="s">
         <v>99</v>
       </c>
-      <c r="D78" s="67"/>
-      <c r="E78" s="67"/>
-      <c r="F78" s="67"/>
+      <c r="D78" s="176"/>
+      <c r="E78" s="176"/>
+      <c r="F78" s="176"/>
       <c r="G78" s="31" t="s">
         <v>98</v>
       </c>
@@ -3314,96 +3314,96 @@
       <c r="M78" s="11"/>
     </row>
     <row r="79" spans="1:13" ht="48.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="45"/>
-      <c r="B79" s="45"/>
-      <c r="C79" s="45"/>
-      <c r="D79" s="45"/>
-      <c r="E79" s="43"/>
-      <c r="F79" s="43"/>
-      <c r="G79" s="45"/>
-      <c r="H79" s="45"/>
-      <c r="I79" s="43"/>
-      <c r="J79" s="43"/>
-      <c r="K79" s="45"/>
-      <c r="L79" s="45"/>
-      <c r="M79" s="45"/>
+      <c r="A79" s="160"/>
+      <c r="B79" s="160"/>
+      <c r="C79" s="160"/>
+      <c r="D79" s="160"/>
+      <c r="E79" s="158"/>
+      <c r="F79" s="158"/>
+      <c r="G79" s="160"/>
+      <c r="H79" s="160"/>
+      <c r="I79" s="158"/>
+      <c r="J79" s="158"/>
+      <c r="K79" s="160"/>
+      <c r="L79" s="160"/>
+      <c r="M79" s="160"/>
     </row>
     <row r="80" spans="1:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="45"/>
-      <c r="B80" s="45"/>
-      <c r="C80" s="45"/>
-      <c r="D80" s="45"/>
-      <c r="E80" s="43"/>
-      <c r="F80" s="43"/>
-      <c r="G80" s="45"/>
-      <c r="H80" s="45"/>
-      <c r="I80" s="43"/>
-      <c r="J80" s="43"/>
-      <c r="K80" s="45"/>
-      <c r="L80" s="45"/>
-      <c r="M80" s="45"/>
+      <c r="A80" s="160"/>
+      <c r="B80" s="160"/>
+      <c r="C80" s="160"/>
+      <c r="D80" s="160"/>
+      <c r="E80" s="158"/>
+      <c r="F80" s="158"/>
+      <c r="G80" s="160"/>
+      <c r="H80" s="160"/>
+      <c r="I80" s="158"/>
+      <c r="J80" s="158"/>
+      <c r="K80" s="160"/>
+      <c r="L80" s="160"/>
+      <c r="M80" s="160"/>
     </row>
     <row r="81" spans="1:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="45"/>
-      <c r="B81" s="45"/>
-      <c r="C81" s="45"/>
-      <c r="D81" s="45"/>
-      <c r="E81" s="43"/>
-      <c r="F81" s="43"/>
-      <c r="G81" s="45"/>
-      <c r="H81" s="45"/>
-      <c r="I81" s="43"/>
-      <c r="J81" s="43"/>
-      <c r="K81" s="45"/>
-      <c r="L81" s="45"/>
-      <c r="M81" s="45"/>
+      <c r="A81" s="160"/>
+      <c r="B81" s="160"/>
+      <c r="C81" s="160"/>
+      <c r="D81" s="160"/>
+      <c r="E81" s="158"/>
+      <c r="F81" s="158"/>
+      <c r="G81" s="160"/>
+      <c r="H81" s="160"/>
+      <c r="I81" s="158"/>
+      <c r="J81" s="158"/>
+      <c r="K81" s="160"/>
+      <c r="L81" s="160"/>
+      <c r="M81" s="160"/>
     </row>
     <row r="82" spans="1:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="45"/>
-      <c r="B82" s="45"/>
-      <c r="C82" s="45"/>
-      <c r="D82" s="45"/>
-      <c r="E82" s="43"/>
-      <c r="F82" s="43"/>
-      <c r="G82" s="45"/>
-      <c r="H82" s="45"/>
-      <c r="I82" s="43"/>
-      <c r="J82" s="43"/>
-      <c r="K82" s="45"/>
-      <c r="L82" s="45"/>
-      <c r="M82" s="45"/>
+      <c r="A82" s="160"/>
+      <c r="B82" s="160"/>
+      <c r="C82" s="160"/>
+      <c r="D82" s="160"/>
+      <c r="E82" s="158"/>
+      <c r="F82" s="158"/>
+      <c r="G82" s="160"/>
+      <c r="H82" s="160"/>
+      <c r="I82" s="158"/>
+      <c r="J82" s="158"/>
+      <c r="K82" s="160"/>
+      <c r="L82" s="160"/>
+      <c r="M82" s="160"/>
     </row>
     <row r="83" spans="1:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="46"/>
-      <c r="B83" s="46"/>
-      <c r="C83" s="46"/>
-      <c r="D83" s="46"/>
-      <c r="E83" s="43"/>
-      <c r="F83" s="43"/>
-      <c r="G83" s="46"/>
-      <c r="H83" s="46"/>
-      <c r="I83" s="43"/>
-      <c r="J83" s="43"/>
-      <c r="K83" s="46"/>
-      <c r="L83" s="46"/>
-      <c r="M83" s="46"/>
+      <c r="A83" s="161"/>
+      <c r="B83" s="161"/>
+      <c r="C83" s="161"/>
+      <c r="D83" s="161"/>
+      <c r="E83" s="158"/>
+      <c r="F83" s="158"/>
+      <c r="G83" s="161"/>
+      <c r="H83" s="161"/>
+      <c r="I83" s="158"/>
+      <c r="J83" s="158"/>
+      <c r="K83" s="161"/>
+      <c r="L83" s="161"/>
+      <c r="M83" s="161"/>
     </row>
     <row r="84" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="42"/>
-      <c r="B84" s="42"/>
-      <c r="C84" s="42"/>
-      <c r="D84" s="42"/>
-      <c r="E84" s="43"/>
-      <c r="F84" s="43"/>
-      <c r="G84" s="44" t="s">
+      <c r="A84" s="157"/>
+      <c r="B84" s="157"/>
+      <c r="C84" s="157"/>
+      <c r="D84" s="157"/>
+      <c r="E84" s="158"/>
+      <c r="F84" s="158"/>
+      <c r="G84" s="159" t="s">
         <v>27</v>
       </c>
-      <c r="H84" s="44"/>
-      <c r="I84" s="43"/>
-      <c r="J84" s="43"/>
-      <c r="K84" s="42"/>
-      <c r="L84" s="42"/>
-      <c r="M84" s="42"/>
+      <c r="H84" s="159"/>
+      <c r="I84" s="158"/>
+      <c r="J84" s="158"/>
+      <c r="K84" s="157"/>
+      <c r="L84" s="157"/>
+      <c r="M84" s="157"/>
     </row>
     <row r="85" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A85" s="12"/>
@@ -3422,28 +3422,182 @@
     </row>
     <row r="86" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A86" s="24"/>
-      <c r="B86" s="176"/>
-      <c r="C86" s="176"/>
-      <c r="D86" s="176"/>
-      <c r="E86" s="176"/>
-      <c r="F86" s="176"/>
-      <c r="G86" s="176"/>
-      <c r="H86" s="176"/>
-      <c r="I86" s="176"/>
-      <c r="J86" s="176"/>
+      <c r="B86" s="44"/>
+      <c r="C86" s="44"/>
+      <c r="D86" s="44"/>
+      <c r="E86" s="44"/>
+      <c r="F86" s="44"/>
+      <c r="G86" s="44"/>
+      <c r="H86" s="44"/>
+      <c r="I86" s="44"/>
+      <c r="J86" s="44"/>
       <c r="K86" s="24"/>
       <c r="L86" s="24"/>
       <c r="M86" s="24"/>
     </row>
     <row r="87" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="F87" s="32" t="s">
+      <c r="F87" s="36" t="s">
         <v>44</v>
       </c>
-      <c r="G87" s="32"/>
+      <c r="G87" s="36"/>
     </row>
     <row r="88" spans="1:13" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="178">
+    <mergeCell ref="F87:G87"/>
+    <mergeCell ref="A38:M40"/>
+    <mergeCell ref="I10:M10"/>
+    <mergeCell ref="B70:J70"/>
+    <mergeCell ref="F50:G50"/>
+    <mergeCell ref="A84:D84"/>
+    <mergeCell ref="E84:F84"/>
+    <mergeCell ref="G84:H84"/>
+    <mergeCell ref="I84:J84"/>
+    <mergeCell ref="K84:M84"/>
+    <mergeCell ref="A79:D83"/>
+    <mergeCell ref="E79:F83"/>
+    <mergeCell ref="G79:H83"/>
+    <mergeCell ref="I79:J83"/>
+    <mergeCell ref="K79:M83"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="E44:G44"/>
+    <mergeCell ref="H44:J44"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="E35:M35"/>
+    <mergeCell ref="C78:F78"/>
+    <mergeCell ref="E36:M36"/>
+    <mergeCell ref="E37:M37"/>
+    <mergeCell ref="C9:M9"/>
+    <mergeCell ref="A8:M8"/>
+    <mergeCell ref="E14:M14"/>
+    <mergeCell ref="K11:M11"/>
+    <mergeCell ref="K12:M12"/>
+    <mergeCell ref="J13:M13"/>
+    <mergeCell ref="E15:M15"/>
+    <mergeCell ref="E16:M16"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="E32:M32"/>
+    <mergeCell ref="E33:M33"/>
+    <mergeCell ref="E34:M34"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="E29:M29"/>
+    <mergeCell ref="E30:M30"/>
+    <mergeCell ref="E31:M31"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="E26:M26"/>
+    <mergeCell ref="E27:M27"/>
+    <mergeCell ref="E28:M28"/>
+    <mergeCell ref="A23:A25"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="E23:M23"/>
+    <mergeCell ref="E24:M24"/>
+    <mergeCell ref="E25:M25"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="E20:M20"/>
+    <mergeCell ref="E21:M21"/>
+    <mergeCell ref="E22:M22"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="E17:M17"/>
+    <mergeCell ref="E18:M18"/>
+    <mergeCell ref="E19:M19"/>
+    <mergeCell ref="H50:J50"/>
+    <mergeCell ref="B51:C51"/>
+    <mergeCell ref="D51:E51"/>
+    <mergeCell ref="F51:G51"/>
+    <mergeCell ref="H51:J51"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="C13:F13"/>
+    <mergeCell ref="G13:I13"/>
+    <mergeCell ref="A14:A22"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="C11:H11"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="D50:E50"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="D61:E61"/>
+    <mergeCell ref="F61:G61"/>
+    <mergeCell ref="H61:J61"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="D62:E62"/>
+    <mergeCell ref="F62:G62"/>
+    <mergeCell ref="H62:J62"/>
+    <mergeCell ref="B58:C59"/>
+    <mergeCell ref="D58:G58"/>
+    <mergeCell ref="H58:J59"/>
+    <mergeCell ref="D59:E59"/>
+    <mergeCell ref="F59:G59"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="D60:E60"/>
+    <mergeCell ref="F60:G60"/>
+    <mergeCell ref="H60:J60"/>
+    <mergeCell ref="B57:J57"/>
+    <mergeCell ref="D52:E52"/>
+    <mergeCell ref="F52:G52"/>
+    <mergeCell ref="H52:J52"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="B47:C48"/>
+    <mergeCell ref="D47:G47"/>
+    <mergeCell ref="H47:J48"/>
+    <mergeCell ref="D48:E48"/>
+    <mergeCell ref="F48:G48"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="D49:E49"/>
+    <mergeCell ref="H49:J49"/>
+    <mergeCell ref="B41:J41"/>
+    <mergeCell ref="B46:J46"/>
+    <mergeCell ref="B42:J42"/>
+    <mergeCell ref="F49:G49"/>
+    <mergeCell ref="E43:F43"/>
+    <mergeCell ref="G43:H43"/>
+    <mergeCell ref="D71:J71"/>
+    <mergeCell ref="B72:C72"/>
+    <mergeCell ref="D72:J72"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="H54:J54"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="D55:E55"/>
+    <mergeCell ref="F55:G55"/>
+    <mergeCell ref="H55:J55"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="D56:E56"/>
+    <mergeCell ref="F56:G56"/>
+    <mergeCell ref="H56:J56"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="D63:E63"/>
+    <mergeCell ref="F63:G63"/>
+    <mergeCell ref="H63:J63"/>
+    <mergeCell ref="D53:E53"/>
+    <mergeCell ref="F53:G53"/>
+    <mergeCell ref="H53:J53"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="D54:E54"/>
+    <mergeCell ref="F54:G54"/>
     <mergeCell ref="B1:K1"/>
     <mergeCell ref="B2:K2"/>
     <mergeCell ref="B3:K3"/>
@@ -3468,160 +3622,6 @@
     <mergeCell ref="D67:J67"/>
     <mergeCell ref="D68:J68"/>
     <mergeCell ref="B71:C71"/>
-    <mergeCell ref="D71:J71"/>
-    <mergeCell ref="B72:C72"/>
-    <mergeCell ref="D72:J72"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="H54:J54"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="D55:E55"/>
-    <mergeCell ref="F55:G55"/>
-    <mergeCell ref="H55:J55"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="D56:E56"/>
-    <mergeCell ref="F56:G56"/>
-    <mergeCell ref="H56:J56"/>
-    <mergeCell ref="B63:C63"/>
-    <mergeCell ref="D63:E63"/>
-    <mergeCell ref="F63:G63"/>
-    <mergeCell ref="H63:J63"/>
-    <mergeCell ref="D53:E53"/>
-    <mergeCell ref="F53:G53"/>
-    <mergeCell ref="H53:J53"/>
-    <mergeCell ref="B54:C54"/>
-    <mergeCell ref="D54:E54"/>
-    <mergeCell ref="F54:G54"/>
-    <mergeCell ref="B47:C48"/>
-    <mergeCell ref="D47:G47"/>
-    <mergeCell ref="H47:J48"/>
-    <mergeCell ref="D48:E48"/>
-    <mergeCell ref="F48:G48"/>
-    <mergeCell ref="B49:C49"/>
-    <mergeCell ref="D49:E49"/>
-    <mergeCell ref="H49:J49"/>
-    <mergeCell ref="B41:J41"/>
-    <mergeCell ref="B46:J46"/>
-    <mergeCell ref="B42:J42"/>
-    <mergeCell ref="F49:G49"/>
-    <mergeCell ref="E43:F43"/>
-    <mergeCell ref="G43:H43"/>
-    <mergeCell ref="B50:C50"/>
-    <mergeCell ref="D50:E50"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="D61:E61"/>
-    <mergeCell ref="F61:G61"/>
-    <mergeCell ref="H61:J61"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="D62:E62"/>
-    <mergeCell ref="F62:G62"/>
-    <mergeCell ref="H62:J62"/>
-    <mergeCell ref="B58:C59"/>
-    <mergeCell ref="D58:G58"/>
-    <mergeCell ref="H58:J59"/>
-    <mergeCell ref="D59:E59"/>
-    <mergeCell ref="F59:G59"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="D60:E60"/>
-    <mergeCell ref="F60:G60"/>
-    <mergeCell ref="H60:J60"/>
-    <mergeCell ref="B57:J57"/>
-    <mergeCell ref="D52:E52"/>
-    <mergeCell ref="F52:G52"/>
-    <mergeCell ref="H52:J52"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="H50:J50"/>
-    <mergeCell ref="B51:C51"/>
-    <mergeCell ref="D51:E51"/>
-    <mergeCell ref="F51:G51"/>
-    <mergeCell ref="H51:J51"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="C13:F13"/>
-    <mergeCell ref="G13:I13"/>
-    <mergeCell ref="A14:A22"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="C11:H11"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="E20:M20"/>
-    <mergeCell ref="E21:M21"/>
-    <mergeCell ref="E22:M22"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="E17:M17"/>
-    <mergeCell ref="E18:M18"/>
-    <mergeCell ref="E19:M19"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="E26:M26"/>
-    <mergeCell ref="E27:M27"/>
-    <mergeCell ref="E28:M28"/>
-    <mergeCell ref="A23:A25"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="E23:M23"/>
-    <mergeCell ref="E24:M24"/>
-    <mergeCell ref="E25:M25"/>
-    <mergeCell ref="E36:M36"/>
-    <mergeCell ref="E37:M37"/>
-    <mergeCell ref="C9:M9"/>
-    <mergeCell ref="A8:M8"/>
-    <mergeCell ref="E14:M14"/>
-    <mergeCell ref="K11:M11"/>
-    <mergeCell ref="K12:M12"/>
-    <mergeCell ref="J13:M13"/>
-    <mergeCell ref="E15:M15"/>
-    <mergeCell ref="E16:M16"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="E32:M32"/>
-    <mergeCell ref="E33:M33"/>
-    <mergeCell ref="E34:M34"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="E29:M29"/>
-    <mergeCell ref="E30:M30"/>
-    <mergeCell ref="E31:M31"/>
-    <mergeCell ref="B26:D26"/>
-    <mergeCell ref="B27:D27"/>
-    <mergeCell ref="F87:G87"/>
-    <mergeCell ref="A38:M40"/>
-    <mergeCell ref="I10:M10"/>
-    <mergeCell ref="B70:J70"/>
-    <mergeCell ref="F50:G50"/>
-    <mergeCell ref="A84:D84"/>
-    <mergeCell ref="E84:F84"/>
-    <mergeCell ref="G84:H84"/>
-    <mergeCell ref="I84:J84"/>
-    <mergeCell ref="K84:M84"/>
-    <mergeCell ref="A79:D83"/>
-    <mergeCell ref="E79:F83"/>
-    <mergeCell ref="G79:H83"/>
-    <mergeCell ref="I79:J83"/>
-    <mergeCell ref="K79:M83"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="E44:G44"/>
-    <mergeCell ref="H44:J44"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="B37:D37"/>
-    <mergeCell ref="E35:M35"/>
-    <mergeCell ref="C78:F78"/>
   </mergeCells>
   <conditionalFormatting sqref="A84:D84 K84:M84">
     <cfRule type="containsBlanks" dxfId="9" priority="14" stopIfTrue="1">
@@ -3686,7 +3686,7 @@
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Registrar el correo electrónico personal del aprendiz" sqref="E19:M19" xr:uid="{CEDF05F3-A498-464C-AF78-C83490E95D67}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Registrar el correo electrónico institucional del aprendiz @sena.edu.co , @soysena.edu.co" sqref="E20:M20" xr:uid="{8AC0CC91-D06D-4D82-A06B-CEDFF66185FC}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Registrar el nombre de la alternativa de etapa productiva, de acuerdo con las alternativas descritas en el reglamento del aprendiz vigente" sqref="E21:M21" xr:uid="{48CA359C-CBBE-4B45-B681-EA4693D12177}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Indicar la fecha en que quedó registrada la alternativa en el aplicativo SofiaPlus.  Gestione con la coordinación académica el reporte del SVP para obtener la información requerida en este apartado" sqref="E22:M22" xr:uid="{A4B53DE5-4CEE-4C8C-A08B-9C6344C18954}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="OBLIGATORIO" prompt="Indicar la fecha de registro en el aplicativo SofiaPlus. RUTA: INGRESAR A SOFIAPLUS-APRENDIZ-CONSULTAR INSCRIPCIONES A PROGRAMAS...----DETALLE DE INSCRIPCION // PARTE INFERIOR INDICA LA FECHA DE INSCRIPCION" sqref="E22:M22" xr:uid="{A4B53DE5-4CEE-4C8C-A08B-9C6344C18954}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Registrar el nombre completo de la empresa o entidad co-formadora (empresa, entidad o institución gubernamental o no gubernamental)." sqref="E26:M26" xr:uid="{35AC5BC6-659F-4E4C-B567-3C3F16C509BD}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Registrar la dirección de la empresa, entidad o institución gubernamental o no gubernamental." sqref="E27:M27" xr:uid="{18FD205E-10DD-4EB5-8E57-F8B0C00BF5BC}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Registrar el numero NIT de la empresa, entidad o institución gubernamental o no gubernamental." sqref="E28:M28" xr:uid="{0E9499EA-A21D-4209-94F0-6561C0BEA458}"/>
@@ -3699,8 +3699,8 @@
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Si no aplica colocar N/A" prompt="En caso de que el aprendiz sea una persona en situación de discapacidad, diligencie este espacio con el nombre de la persona que le asiste." sqref="E35:M35" xr:uid="{C19946D2-B571-4104-A1EA-FEF5A7253596}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Si no aplica colocar N/A" prompt="Aquí se especifica el tipo de asistencia brindada al aprendiz para que desempeñe la totalidad de sus tareas asegurando un ambiente laboral inclusivo adecuado a sus necesidades. Puede incluir asistencias como lenguaje de señas, soporte visual etc" sqref="E36:M36" xr:uid="{B635F5F5-108B-409C-BCAD-0AA5A654CF02}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Si no aplica colocar N/A" prompt="Registrar el número del celular de la persona que asiste al aprendiz " sqref="E37:M37" xr:uid="{77AEF51E-4966-4ADA-B94D-7E72C6BE4FFA}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Registrar el nombre completo del aprendiz y en la parte superior la Firma manuscrita o digital." sqref="A84:D84" xr:uid="{A7FEFB2B-7370-4FA2-8820-7EB89B730FD1}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Registrar el nombre completo del co-formador y en la parte superior de esta la Firma manuscrita o digital." sqref="K84:M84" xr:uid="{DAE2A968-2309-42D5-952C-BC599D7BE50F}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="NOMBRE Y FIRMA APRENDIZ" prompt="Registrar el nombre completo del aprendiz y en la parte superior la Firma manuscrita o digital." sqref="A84:D84" xr:uid="{A7FEFB2B-7370-4FA2-8820-7EB89B730FD1}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="NOMBRE Y FIRMA CO FORMADOR" prompt="Registrar el nombre completo del co-formador y en la parte superior de esta la Firma manuscrita o digital." sqref="K84:M84" xr:uid="{DAE2A968-2309-42D5-952C-BC599D7BE50F}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Aporta activamente al mejoramiento de sus habilidades técnicas y métodos de trabajo." sqref="D50:F50" xr:uid="{A8FCB973-8FC0-4BDD-BF0E-CC9BB61BE366}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Marcar con una X según correspon" prompt="Demuestra las competencias específicas del programa de formación en situaciones reales de trabajo. " sqref="D49:G49" xr:uid="{948FA747-4CF8-48C4-8768-F9CADBC3F362}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Realiza acciones que fortalezcan su perfil ocupacional potenciando sus competencias en el marco de su proyecto de vida." sqref="D51:G51" xr:uid="{379961D4-6BD4-47A0-B009-E49C8B35A883}"/>
@@ -3728,13 +3728,13 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xWindow="756" yWindow="874" count="2">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Registrar la retroalimentación sobre el proceso de formación realizado por parte del ente co-formador, así como las recomendaciones u oportunidades de mejora. De la misma manera, si el aprendiz tiene o no reconocimientos especiales frente a su desempeño." xr:uid="{DFDB9D40-B1FA-44FD-A0C7-E2D5BEF09BF0}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{DFDB9D40-B1FA-44FD-A0C7-E2D5BEF09BF0}">
           <x14:formula1>
             <xm:f>Hoja2!$A$2:$A$6</xm:f>
           </x14:formula1>
           <xm:sqref>D71:J71</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Registrar si el aprendiz tiene o no reconocimientos especiales frente a su desempeño. registrar otras observaciones , recomendaciones u oportunidades de mejora sobre las competencias del programa desarrolladas por el aprendiz" xr:uid="{6FC7E188-4A10-41FD-B8AC-C0605E33F3DB}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{6FC7E188-4A10-41FD-B8AC-C0605E33F3DB}">
           <x14:formula1>
             <xm:f>Hoja2!$B$2:$B$6</xm:f>
           </x14:formula1>

--- a/Formatos/Visita 3 GFPI-F023.xlsx
+++ b/Formatos/Visita 3 GFPI-F023.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SEANT\OneDrive\Documents\Seto 2026\sena\Manual SENA Etapa Productiva\manual-aprendiz-sena\Formatos\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uniminuto0-my.sharepoint.com/personal/sergio_torres_mar_uniminuto_edu_co/Documents/Documentos/Seto 2026/SETO/sena/Manual SENA Etapa Productiva/manual-aprendiz-sena/Formatos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8726567-7195-433A-A879-F216B9BE4E06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="30" documentId="13_ncr:1_{B8726567-7195-433A-A879-F216B9BE4E06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1EDF43B8-555A-4801-88B2-2B3F8EF29CE4}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{BC3553EE-4E49-4F2A-B03E-CFAC4EB3009B}"/>
+    <workbookView xWindow="28680" yWindow="-105" windowWidth="29040" windowHeight="15720" xr2:uid="{BC3553EE-4E49-4F2A-B03E-CFAC4EB3009B}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -406,7 +406,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="22" x14ac:knownFonts="1">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -563,6 +563,12 @@
       <name val="Aptos"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF747474"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -939,7 +945,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="177">
+  <cellXfs count="167">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
@@ -1001,20 +1007,6 @@
       <alignment vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1">
-      <extLst>
-        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
-          <xfpb:xfComplement i="0"/>
-        </ext>
-      </extLst>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1">
-      <extLst>
-        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
-          <xfpb:xfComplement i="0"/>
-        </ext>
-      </extLst>
-    </xf>
     <xf numFmtId="15" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
@@ -1041,17 +1033,400 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-      <extLst>
-        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
-          <xfpb:xfComplement i="0"/>
-        </ext>
-      </extLst>
-    </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="15" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="15" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="15" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1064,9 +1439,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1091,459 +1463,107 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="15" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="15" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="15" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="15" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="15" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="10">
+  <dxfs count="20">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFEEEC9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE4EE5C"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -1631,23 +1651,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/featurePropertyBag/featurePropertyBag.xml><?xml version="1.0" encoding="utf-8"?>
-<FeaturePropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag">
-  <bag type="Checkbox"/>
-  <bag type="XFControls">
-    <bagId k="CellControl">0</bagId>
-  </bag>
-  <bag type="XFComplement">
-    <bagId k="XFControls">1</bagId>
-  </bag>
-  <bag type="XFComplements" extRef="XFComplementsMapperExtRef">
-    <a k="MappedFeaturePropertyBags">
-      <bagId>2</bagId>
-    </a>
-  </bag>
-</FeaturePropertyBags>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1970,7 +1973,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O88"/>
+  <dimension ref="A1:XFD88"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="15" zeroHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.5703125" customWidth="1"/>
@@ -1983,1094 +1986,1089 @@
     <col min="12" max="12" width="3.7109375" customWidth="1"/>
     <col min="13" max="13" width="13.28515625" customWidth="1"/>
     <col min="14" max="15" width="0" hidden="1" customWidth="1"/>
-    <col min="16" max="16384" width="11.42578125" hidden="1"/>
+    <col min="16" max="16383" width="11.42578125" hidden="1"/>
+    <col min="16384" max="16384" width="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B1" s="32" t="s">
+      <c r="B1" s="147" t="s">
         <v>77</v>
       </c>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-      <c r="H1" s="33"/>
-      <c r="I1" s="33"/>
-      <c r="J1" s="33"/>
-      <c r="K1" s="34"/>
+      <c r="C1" s="148"/>
+      <c r="D1" s="148"/>
+      <c r="E1" s="148"/>
+      <c r="F1" s="148"/>
+      <c r="G1" s="148"/>
+      <c r="H1" s="148"/>
+      <c r="I1" s="148"/>
+      <c r="J1" s="148"/>
+      <c r="K1" s="149"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B2" s="35" t="s">
+      <c r="B2" s="150" t="s">
         <v>78</v>
       </c>
-      <c r="C2" s="36"/>
-      <c r="D2" s="36"/>
-      <c r="E2" s="36"/>
-      <c r="F2" s="36"/>
-      <c r="G2" s="36"/>
-      <c r="H2" s="36"/>
-      <c r="I2" s="36"/>
-      <c r="J2" s="36"/>
-      <c r="K2" s="37"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
+      <c r="G2" s="29"/>
+      <c r="H2" s="29"/>
+      <c r="I2" s="29"/>
+      <c r="J2" s="29"/>
+      <c r="K2" s="151"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B3" s="38" t="s">
+      <c r="B3" s="152" t="s">
         <v>79</v>
       </c>
-      <c r="C3" s="39"/>
-      <c r="D3" s="39"/>
-      <c r="E3" s="39"/>
-      <c r="F3" s="39"/>
-      <c r="G3" s="39"/>
-      <c r="H3" s="39"/>
-      <c r="I3" s="39"/>
-      <c r="J3" s="39"/>
-      <c r="K3" s="40"/>
+      <c r="C3" s="153"/>
+      <c r="D3" s="153"/>
+      <c r="E3" s="153"/>
+      <c r="F3" s="153"/>
+      <c r="G3" s="153"/>
+      <c r="H3" s="153"/>
+      <c r="I3" s="153"/>
+      <c r="J3" s="153"/>
+      <c r="K3" s="154"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B4" s="35" t="s">
+      <c r="B4" s="150" t="s">
         <v>80</v>
       </c>
-      <c r="C4" s="36"/>
-      <c r="D4" s="36"/>
-      <c r="E4" s="36"/>
-      <c r="F4" s="36"/>
-      <c r="G4" s="36"/>
-      <c r="H4" s="36"/>
-      <c r="I4" s="36"/>
-      <c r="J4" s="36"/>
-      <c r="K4" s="37"/>
+      <c r="C4" s="29"/>
+      <c r="D4" s="29"/>
+      <c r="E4" s="29"/>
+      <c r="F4" s="29"/>
+      <c r="G4" s="29"/>
+      <c r="H4" s="29"/>
+      <c r="I4" s="29"/>
+      <c r="J4" s="29"/>
+      <c r="K4" s="151"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B5" s="38" t="s">
+      <c r="B5" s="152" t="s">
         <v>81</v>
       </c>
-      <c r="C5" s="39"/>
-      <c r="D5" s="39"/>
-      <c r="E5" s="39"/>
-      <c r="F5" s="39"/>
-      <c r="G5" s="39"/>
-      <c r="H5" s="39"/>
-      <c r="I5" s="39"/>
-      <c r="J5" s="39"/>
-      <c r="K5" s="40"/>
+      <c r="C5" s="153"/>
+      <c r="D5" s="153"/>
+      <c r="E5" s="153"/>
+      <c r="F5" s="153"/>
+      <c r="G5" s="153"/>
+      <c r="H5" s="153"/>
+      <c r="I5" s="153"/>
+      <c r="J5" s="153"/>
+      <c r="K5" s="154"/>
     </row>
     <row r="6" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="41" t="s">
+      <c r="B6" s="155" t="s">
         <v>82</v>
       </c>
-      <c r="C6" s="42"/>
-      <c r="D6" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="E6" s="43" t="s">
+      <c r="C6" s="156"/>
+      <c r="D6" s="159"/>
+      <c r="E6" s="157" t="s">
         <v>83</v>
       </c>
-      <c r="F6" s="42"/>
-      <c r="G6" s="42"/>
-      <c r="H6" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="I6" s="43" t="s">
+      <c r="F6" s="156"/>
+      <c r="G6" s="156"/>
+      <c r="H6" s="159"/>
+      <c r="I6" s="157" t="s">
         <v>84</v>
       </c>
-      <c r="J6" s="42"/>
-      <c r="K6" s="21" t="b">
-        <v>0</v>
-      </c>
+      <c r="J6" s="156"/>
+      <c r="K6" s="160"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25"/>
     <row r="8" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="137" t="s">
+      <c r="A8" s="68" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="138"/>
-      <c r="C8" s="138"/>
-      <c r="D8" s="138"/>
-      <c r="E8" s="138"/>
-      <c r="F8" s="138"/>
-      <c r="G8" s="138"/>
-      <c r="H8" s="138"/>
-      <c r="I8" s="138"/>
-      <c r="J8" s="138"/>
-      <c r="K8" s="138"/>
-      <c r="L8" s="138"/>
-      <c r="M8" s="138"/>
+      <c r="B8" s="69"/>
+      <c r="C8" s="69"/>
+      <c r="D8" s="69"/>
+      <c r="E8" s="69"/>
+      <c r="F8" s="69"/>
+      <c r="G8" s="69"/>
+      <c r="H8" s="69"/>
+      <c r="I8" s="69"/>
+      <c r="J8" s="69"/>
+      <c r="K8" s="69"/>
+      <c r="L8" s="69"/>
+      <c r="M8" s="69"/>
     </row>
     <row r="9" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="48" t="s">
+      <c r="A9" s="57" t="s">
         <v>1</v>
       </c>
-      <c r="B9" s="49"/>
-      <c r="C9" s="124" t="s">
+      <c r="B9" s="59"/>
+      <c r="C9" s="65" t="s">
         <v>2</v>
       </c>
-      <c r="D9" s="136"/>
-      <c r="E9" s="136"/>
-      <c r="F9" s="136"/>
-      <c r="G9" s="136"/>
-      <c r="H9" s="136"/>
-      <c r="I9" s="136"/>
-      <c r="J9" s="136"/>
-      <c r="K9" s="136"/>
-      <c r="L9" s="136"/>
-      <c r="M9" s="125"/>
+      <c r="D9" s="66"/>
+      <c r="E9" s="66"/>
+      <c r="F9" s="66"/>
+      <c r="G9" s="66"/>
+      <c r="H9" s="66"/>
+      <c r="I9" s="66"/>
+      <c r="J9" s="66"/>
+      <c r="K9" s="66"/>
+      <c r="L9" s="66"/>
+      <c r="M9" s="67"/>
     </row>
     <row r="10" spans="1:13" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="48" t="s">
+      <c r="A10" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="B10" s="49"/>
-      <c r="C10" s="108" t="s">
+      <c r="B10" s="59"/>
+      <c r="C10" s="98" t="s">
         <v>4</v>
       </c>
-      <c r="D10" s="109"/>
-      <c r="E10" s="109"/>
-      <c r="F10" s="109"/>
-      <c r="G10" s="110"/>
+      <c r="D10" s="99"/>
+      <c r="E10" s="99"/>
+      <c r="F10" s="99"/>
+      <c r="G10" s="100"/>
       <c r="H10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="I10" s="105"/>
-      <c r="J10" s="106"/>
-      <c r="K10" s="106"/>
-      <c r="L10" s="106"/>
-      <c r="M10" s="107"/>
+      <c r="I10" s="31"/>
+      <c r="J10" s="32"/>
+      <c r="K10" s="32"/>
+      <c r="L10" s="32"/>
+      <c r="M10" s="33"/>
     </row>
     <row r="11" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="48" t="s">
+      <c r="A11" s="57" t="s">
         <v>6</v>
       </c>
-      <c r="B11" s="49"/>
-      <c r="C11" s="121"/>
-      <c r="D11" s="122"/>
-      <c r="E11" s="122"/>
-      <c r="F11" s="122"/>
-      <c r="G11" s="122"/>
-      <c r="H11" s="123"/>
-      <c r="I11" s="74" t="s">
+      <c r="B11" s="59"/>
+      <c r="C11" s="108"/>
+      <c r="D11" s="109"/>
+      <c r="E11" s="109"/>
+      <c r="F11" s="109"/>
+      <c r="G11" s="109"/>
+      <c r="H11" s="110"/>
+      <c r="I11" s="111" t="s">
         <v>7</v>
       </c>
-      <c r="J11" s="75"/>
-      <c r="K11" s="139"/>
-      <c r="L11" s="140"/>
-      <c r="M11" s="141"/>
+      <c r="J11" s="112"/>
+      <c r="K11" s="73"/>
+      <c r="L11" s="74"/>
+      <c r="M11" s="75"/>
     </row>
     <row r="12" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="48" t="s">
+      <c r="A12" s="57" t="s">
         <v>8</v>
       </c>
-      <c r="B12" s="49"/>
+      <c r="B12" s="59"/>
       <c r="C12" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D12" s="124" t="s">
+      <c r="D12" s="65" t="s">
         <v>10</v>
       </c>
-      <c r="E12" s="125"/>
-      <c r="F12" s="76" t="s">
+      <c r="E12" s="67"/>
+      <c r="F12" s="113" t="s">
         <v>11</v>
       </c>
-      <c r="G12" s="78"/>
+      <c r="G12" s="114"/>
       <c r="H12" s="1"/>
-      <c r="I12" s="76" t="s">
+      <c r="I12" s="113" t="s">
         <v>12</v>
       </c>
-      <c r="J12" s="78"/>
-      <c r="K12" s="142"/>
-      <c r="L12" s="143"/>
-      <c r="M12" s="144"/>
+      <c r="J12" s="114"/>
+      <c r="K12" s="76"/>
+      <c r="L12" s="77"/>
+      <c r="M12" s="78"/>
     </row>
     <row r="13" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="48" t="s">
+      <c r="A13" s="57" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="49"/>
-      <c r="C13" s="111"/>
-      <c r="D13" s="112"/>
-      <c r="E13" s="112"/>
-      <c r="F13" s="113"/>
-      <c r="G13" s="111" t="s">
+      <c r="B13" s="59"/>
+      <c r="C13" s="101"/>
+      <c r="D13" s="102"/>
+      <c r="E13" s="102"/>
+      <c r="F13" s="103"/>
+      <c r="G13" s="101" t="s">
         <v>14</v>
       </c>
-      <c r="H13" s="112"/>
-      <c r="I13" s="113"/>
-      <c r="J13" s="145"/>
-      <c r="K13" s="146"/>
-      <c r="L13" s="146"/>
-      <c r="M13" s="147"/>
+      <c r="H13" s="102"/>
+      <c r="I13" s="103"/>
+      <c r="J13" s="79"/>
+      <c r="K13" s="80"/>
+      <c r="L13" s="80"/>
+      <c r="M13" s="81"/>
     </row>
     <row r="14" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="114" t="s">
+      <c r="A14" s="104" t="s">
         <v>15</v>
       </c>
-      <c r="B14" s="48" t="s">
+      <c r="B14" s="57" t="s">
         <v>16</v>
       </c>
-      <c r="C14" s="117"/>
-      <c r="D14" s="49"/>
-      <c r="E14" s="129"/>
-      <c r="F14" s="130"/>
-      <c r="G14" s="130"/>
-      <c r="H14" s="130"/>
-      <c r="I14" s="130"/>
-      <c r="J14" s="130"/>
-      <c r="K14" s="130"/>
-      <c r="L14" s="130"/>
-      <c r="M14" s="131"/>
+      <c r="C14" s="58"/>
+      <c r="D14" s="59"/>
+      <c r="E14" s="70"/>
+      <c r="F14" s="71"/>
+      <c r="G14" s="71"/>
+      <c r="H14" s="71"/>
+      <c r="I14" s="71"/>
+      <c r="J14" s="71"/>
+      <c r="K14" s="71"/>
+      <c r="L14" s="71"/>
+      <c r="M14" s="72"/>
     </row>
     <row r="15" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="115"/>
-      <c r="B15" s="118" t="s">
+      <c r="A15" s="89"/>
+      <c r="B15" s="105" t="s">
         <v>17</v>
       </c>
-      <c r="C15" s="119"/>
-      <c r="D15" s="120"/>
-      <c r="E15" s="148"/>
-      <c r="F15" s="149"/>
-      <c r="G15" s="149"/>
-      <c r="H15" s="149"/>
-      <c r="I15" s="149"/>
-      <c r="J15" s="149"/>
-      <c r="K15" s="149"/>
-      <c r="L15" s="149"/>
-      <c r="M15" s="150"/>
+      <c r="C15" s="106"/>
+      <c r="D15" s="107"/>
+      <c r="E15" s="82"/>
+      <c r="F15" s="83"/>
+      <c r="G15" s="83"/>
+      <c r="H15" s="83"/>
+      <c r="I15" s="83"/>
+      <c r="J15" s="83"/>
+      <c r="K15" s="83"/>
+      <c r="L15" s="83"/>
+      <c r="M15" s="84"/>
     </row>
     <row r="16" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="115"/>
-      <c r="B16" s="48" t="s">
+      <c r="A16" s="89"/>
+      <c r="B16" s="57" t="s">
         <v>18</v>
       </c>
-      <c r="C16" s="117"/>
-      <c r="D16" s="49"/>
-      <c r="E16" s="129"/>
-      <c r="F16" s="130"/>
-      <c r="G16" s="130"/>
-      <c r="H16" s="130"/>
-      <c r="I16" s="130"/>
-      <c r="J16" s="130"/>
-      <c r="K16" s="130"/>
-      <c r="L16" s="130"/>
-      <c r="M16" s="131"/>
+      <c r="C16" s="58"/>
+      <c r="D16" s="59"/>
+      <c r="E16" s="70"/>
+      <c r="F16" s="71"/>
+      <c r="G16" s="71"/>
+      <c r="H16" s="71"/>
+      <c r="I16" s="71"/>
+      <c r="J16" s="71"/>
+      <c r="K16" s="71"/>
+      <c r="L16" s="71"/>
+      <c r="M16" s="72"/>
     </row>
     <row r="17" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="115"/>
-      <c r="B17" s="48" t="s">
+      <c r="A17" s="89"/>
+      <c r="B17" s="57" t="s">
         <v>19</v>
       </c>
-      <c r="C17" s="117"/>
-      <c r="D17" s="49"/>
-      <c r="E17" s="129"/>
-      <c r="F17" s="130"/>
-      <c r="G17" s="130"/>
-      <c r="H17" s="130"/>
-      <c r="I17" s="130"/>
-      <c r="J17" s="130"/>
-      <c r="K17" s="130"/>
-      <c r="L17" s="130"/>
-      <c r="M17" s="131"/>
+      <c r="C17" s="58"/>
+      <c r="D17" s="59"/>
+      <c r="E17" s="70"/>
+      <c r="F17" s="71"/>
+      <c r="G17" s="71"/>
+      <c r="H17" s="71"/>
+      <c r="I17" s="71"/>
+      <c r="J17" s="71"/>
+      <c r="K17" s="71"/>
+      <c r="L17" s="71"/>
+      <c r="M17" s="72"/>
     </row>
     <row r="18" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="115"/>
-      <c r="B18" s="48" t="s">
+      <c r="A18" s="89"/>
+      <c r="B18" s="57" t="s">
         <v>20</v>
       </c>
-      <c r="C18" s="117"/>
-      <c r="D18" s="49"/>
-      <c r="E18" s="129"/>
-      <c r="F18" s="130"/>
-      <c r="G18" s="130"/>
-      <c r="H18" s="130"/>
-      <c r="I18" s="130"/>
-      <c r="J18" s="130"/>
-      <c r="K18" s="130"/>
-      <c r="L18" s="130"/>
-      <c r="M18" s="131"/>
+      <c r="C18" s="58"/>
+      <c r="D18" s="59"/>
+      <c r="E18" s="70"/>
+      <c r="F18" s="71"/>
+      <c r="G18" s="71"/>
+      <c r="H18" s="71"/>
+      <c r="I18" s="71"/>
+      <c r="J18" s="71"/>
+      <c r="K18" s="71"/>
+      <c r="L18" s="71"/>
+      <c r="M18" s="72"/>
     </row>
     <row r="19" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="115"/>
-      <c r="B19" s="48" t="s">
+      <c r="A19" s="89"/>
+      <c r="B19" s="57" t="s">
         <v>21</v>
       </c>
-      <c r="C19" s="117"/>
-      <c r="D19" s="49"/>
-      <c r="E19" s="129"/>
-      <c r="F19" s="130"/>
-      <c r="G19" s="130"/>
-      <c r="H19" s="130"/>
-      <c r="I19" s="130"/>
-      <c r="J19" s="130"/>
-      <c r="K19" s="130"/>
-      <c r="L19" s="130"/>
-      <c r="M19" s="131"/>
+      <c r="C19" s="58"/>
+      <c r="D19" s="59"/>
+      <c r="E19" s="70"/>
+      <c r="F19" s="71"/>
+      <c r="G19" s="71"/>
+      <c r="H19" s="71"/>
+      <c r="I19" s="71"/>
+      <c r="J19" s="71"/>
+      <c r="K19" s="71"/>
+      <c r="L19" s="71"/>
+      <c r="M19" s="72"/>
     </row>
     <row r="20" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="115"/>
-      <c r="B20" s="48" t="s">
+      <c r="A20" s="89"/>
+      <c r="B20" s="57" t="s">
         <v>22</v>
       </c>
-      <c r="C20" s="117"/>
-      <c r="D20" s="49"/>
-      <c r="E20" s="126"/>
-      <c r="F20" s="127"/>
-      <c r="G20" s="127"/>
-      <c r="H20" s="127"/>
-      <c r="I20" s="127"/>
-      <c r="J20" s="127"/>
-      <c r="K20" s="127"/>
-      <c r="L20" s="127"/>
-      <c r="M20" s="128"/>
+      <c r="C20" s="58"/>
+      <c r="D20" s="59"/>
+      <c r="E20" s="60"/>
+      <c r="F20" s="61"/>
+      <c r="G20" s="61"/>
+      <c r="H20" s="61"/>
+      <c r="I20" s="61"/>
+      <c r="J20" s="61"/>
+      <c r="K20" s="61"/>
+      <c r="L20" s="61"/>
+      <c r="M20" s="62"/>
     </row>
     <row r="21" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="115"/>
-      <c r="B21" s="48" t="s">
+      <c r="A21" s="89"/>
+      <c r="B21" s="57" t="s">
         <v>23</v>
       </c>
-      <c r="C21" s="117"/>
-      <c r="D21" s="49"/>
-      <c r="E21" s="126"/>
-      <c r="F21" s="127"/>
-      <c r="G21" s="127"/>
-      <c r="H21" s="127"/>
-      <c r="I21" s="127"/>
-      <c r="J21" s="127"/>
-      <c r="K21" s="127"/>
-      <c r="L21" s="127"/>
-      <c r="M21" s="128"/>
+      <c r="C21" s="58"/>
+      <c r="D21" s="59"/>
+      <c r="E21" s="60"/>
+      <c r="F21" s="61"/>
+      <c r="G21" s="61"/>
+      <c r="H21" s="61"/>
+      <c r="I21" s="61"/>
+      <c r="J21" s="61"/>
+      <c r="K21" s="61"/>
+      <c r="L21" s="61"/>
+      <c r="M21" s="62"/>
     </row>
     <row r="22" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="116"/>
-      <c r="B22" s="48" t="s">
+      <c r="A22" s="90"/>
+      <c r="B22" s="57" t="s">
         <v>24</v>
       </c>
-      <c r="C22" s="117"/>
-      <c r="D22" s="49"/>
-      <c r="E22" s="126"/>
-      <c r="F22" s="127"/>
-      <c r="G22" s="127"/>
-      <c r="H22" s="127"/>
-      <c r="I22" s="127"/>
-      <c r="J22" s="127"/>
-      <c r="K22" s="127"/>
-      <c r="L22" s="127"/>
-      <c r="M22" s="128"/>
+      <c r="C22" s="58"/>
+      <c r="D22" s="59"/>
+      <c r="E22" s="60"/>
+      <c r="F22" s="61"/>
+      <c r="G22" s="61"/>
+      <c r="H22" s="61"/>
+      <c r="I22" s="61"/>
+      <c r="J22" s="61"/>
+      <c r="K22" s="61"/>
+      <c r="L22" s="61"/>
+      <c r="M22" s="62"/>
     </row>
     <row r="23" spans="1:13" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="132" t="s">
+      <c r="A23" s="88" t="s">
         <v>25</v>
       </c>
-      <c r="B23" s="48" t="s">
+      <c r="B23" s="57" t="s">
         <v>26</v>
       </c>
-      <c r="C23" s="117"/>
-      <c r="D23" s="49"/>
-      <c r="E23" s="133" t="s">
+      <c r="C23" s="58"/>
+      <c r="D23" s="59"/>
+      <c r="E23" s="91" t="s">
         <v>27</v>
       </c>
-      <c r="F23" s="134"/>
-      <c r="G23" s="134"/>
-      <c r="H23" s="134"/>
-      <c r="I23" s="134"/>
-      <c r="J23" s="134"/>
-      <c r="K23" s="134"/>
-      <c r="L23" s="134"/>
-      <c r="M23" s="135"/>
+      <c r="F23" s="92"/>
+      <c r="G23" s="92"/>
+      <c r="H23" s="92"/>
+      <c r="I23" s="92"/>
+      <c r="J23" s="92"/>
+      <c r="K23" s="92"/>
+      <c r="L23" s="92"/>
+      <c r="M23" s="93"/>
     </row>
     <row r="24" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="115"/>
-      <c r="B24" s="48" t="s">
+      <c r="A24" s="89"/>
+      <c r="B24" s="57" t="s">
         <v>19</v>
       </c>
-      <c r="C24" s="117"/>
-      <c r="D24" s="49"/>
-      <c r="E24" s="45"/>
-      <c r="F24" s="46"/>
-      <c r="G24" s="46"/>
-      <c r="H24" s="46"/>
-      <c r="I24" s="46"/>
-      <c r="J24" s="46"/>
-      <c r="K24" s="46"/>
-      <c r="L24" s="46"/>
-      <c r="M24" s="47"/>
+      <c r="C24" s="58"/>
+      <c r="D24" s="59"/>
+      <c r="E24" s="34"/>
+      <c r="F24" s="35"/>
+      <c r="G24" s="35"/>
+      <c r="H24" s="35"/>
+      <c r="I24" s="35"/>
+      <c r="J24" s="35"/>
+      <c r="K24" s="35"/>
+      <c r="L24" s="35"/>
+      <c r="M24" s="36"/>
     </row>
     <row r="25" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="116"/>
-      <c r="B25" s="48" t="s">
+      <c r="A25" s="90"/>
+      <c r="B25" s="57" t="s">
         <v>22</v>
       </c>
-      <c r="C25" s="117"/>
-      <c r="D25" s="49"/>
-      <c r="E25" s="133" t="s">
+      <c r="C25" s="58"/>
+      <c r="D25" s="59"/>
+      <c r="E25" s="91" t="s">
         <v>28</v>
       </c>
-      <c r="F25" s="134"/>
-      <c r="G25" s="134"/>
-      <c r="H25" s="134"/>
-      <c r="I25" s="134"/>
-      <c r="J25" s="134"/>
-      <c r="K25" s="134"/>
-      <c r="L25" s="134"/>
-      <c r="M25" s="135"/>
+      <c r="F25" s="92"/>
+      <c r="G25" s="92"/>
+      <c r="H25" s="92"/>
+      <c r="I25" s="92"/>
+      <c r="J25" s="92"/>
+      <c r="K25" s="92"/>
+      <c r="L25" s="92"/>
+      <c r="M25" s="93"/>
     </row>
     <row r="26" spans="1:13" ht="25.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B26" s="48" t="s">
+      <c r="B26" s="57" t="s">
         <v>32</v>
       </c>
-      <c r="C26" s="117"/>
-      <c r="D26" s="49"/>
-      <c r="E26" s="129"/>
-      <c r="F26" s="130"/>
-      <c r="G26" s="130"/>
-      <c r="H26" s="130"/>
-      <c r="I26" s="130"/>
-      <c r="J26" s="130"/>
-      <c r="K26" s="130"/>
-      <c r="L26" s="130"/>
-      <c r="M26" s="131"/>
+      <c r="C26" s="58"/>
+      <c r="D26" s="59"/>
+      <c r="E26" s="70"/>
+      <c r="F26" s="71"/>
+      <c r="G26" s="71"/>
+      <c r="H26" s="71"/>
+      <c r="I26" s="71"/>
+      <c r="J26" s="71"/>
+      <c r="K26" s="71"/>
+      <c r="L26" s="71"/>
+      <c r="M26" s="72"/>
     </row>
     <row r="27" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="B27" s="48" t="s">
+      <c r="B27" s="57" t="s">
         <v>20</v>
       </c>
-      <c r="C27" s="117"/>
-      <c r="D27" s="49"/>
-      <c r="E27" s="129"/>
-      <c r="F27" s="130"/>
-      <c r="G27" s="130"/>
-      <c r="H27" s="130"/>
-      <c r="I27" s="130"/>
-      <c r="J27" s="130"/>
-      <c r="K27" s="130"/>
-      <c r="L27" s="130"/>
-      <c r="M27" s="131"/>
+      <c r="C27" s="58"/>
+      <c r="D27" s="59"/>
+      <c r="E27" s="70"/>
+      <c r="F27" s="71"/>
+      <c r="G27" s="71"/>
+      <c r="H27" s="71"/>
+      <c r="I27" s="71"/>
+      <c r="J27" s="71"/>
+      <c r="K27" s="71"/>
+      <c r="L27" s="71"/>
+      <c r="M27" s="72"/>
     </row>
     <row r="28" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="3"/>
-      <c r="B28" s="48" t="s">
+      <c r="B28" s="57" t="s">
         <v>33</v>
       </c>
-      <c r="C28" s="117"/>
-      <c r="D28" s="49"/>
-      <c r="E28" s="129"/>
-      <c r="F28" s="130"/>
-      <c r="G28" s="130"/>
-      <c r="H28" s="130"/>
-      <c r="I28" s="130"/>
-      <c r="J28" s="130"/>
-      <c r="K28" s="130"/>
-      <c r="L28" s="130"/>
-      <c r="M28" s="131"/>
+      <c r="C28" s="58"/>
+      <c r="D28" s="59"/>
+      <c r="E28" s="70"/>
+      <c r="F28" s="71"/>
+      <c r="G28" s="71"/>
+      <c r="H28" s="71"/>
+      <c r="I28" s="71"/>
+      <c r="J28" s="71"/>
+      <c r="K28" s="71"/>
+      <c r="L28" s="71"/>
+      <c r="M28" s="72"/>
     </row>
     <row r="29" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="3"/>
-      <c r="B29" s="48" t="s">
+      <c r="B29" s="57" t="s">
         <v>34</v>
       </c>
-      <c r="C29" s="117"/>
-      <c r="D29" s="49"/>
-      <c r="E29" s="129"/>
-      <c r="F29" s="130"/>
-      <c r="G29" s="130"/>
-      <c r="H29" s="130"/>
-      <c r="I29" s="130"/>
-      <c r="J29" s="130"/>
-      <c r="K29" s="130"/>
-      <c r="L29" s="130"/>
-      <c r="M29" s="131"/>
+      <c r="C29" s="58"/>
+      <c r="D29" s="59"/>
+      <c r="E29" s="70"/>
+      <c r="F29" s="71"/>
+      <c r="G29" s="71"/>
+      <c r="H29" s="71"/>
+      <c r="I29" s="71"/>
+      <c r="J29" s="71"/>
+      <c r="K29" s="71"/>
+      <c r="L29" s="71"/>
+      <c r="M29" s="72"/>
     </row>
     <row r="30" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="B30" s="48" t="s">
+      <c r="B30" s="57" t="s">
         <v>35</v>
       </c>
-      <c r="C30" s="117"/>
-      <c r="D30" s="49"/>
-      <c r="E30" s="129"/>
-      <c r="F30" s="130"/>
-      <c r="G30" s="130"/>
-      <c r="H30" s="130"/>
-      <c r="I30" s="130"/>
-      <c r="J30" s="130"/>
-      <c r="K30" s="130"/>
-      <c r="L30" s="130"/>
-      <c r="M30" s="131"/>
+      <c r="C30" s="58"/>
+      <c r="D30" s="59"/>
+      <c r="E30" s="70"/>
+      <c r="F30" s="71"/>
+      <c r="G30" s="71"/>
+      <c r="H30" s="71"/>
+      <c r="I30" s="71"/>
+      <c r="J30" s="71"/>
+      <c r="K30" s="71"/>
+      <c r="L30" s="71"/>
+      <c r="M30" s="72"/>
     </row>
     <row r="31" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="6"/>
-      <c r="B31" s="48" t="s">
+      <c r="B31" s="57" t="s">
         <v>36</v>
       </c>
-      <c r="C31" s="117"/>
-      <c r="D31" s="49"/>
-      <c r="E31" s="129"/>
-      <c r="F31" s="130"/>
-      <c r="G31" s="130"/>
-      <c r="H31" s="130"/>
-      <c r="I31" s="130"/>
-      <c r="J31" s="130"/>
-      <c r="K31" s="130"/>
-      <c r="L31" s="130"/>
-      <c r="M31" s="131"/>
+      <c r="C31" s="58"/>
+      <c r="D31" s="59"/>
+      <c r="E31" s="70"/>
+      <c r="F31" s="71"/>
+      <c r="G31" s="71"/>
+      <c r="H31" s="71"/>
+      <c r="I31" s="71"/>
+      <c r="J31" s="71"/>
+      <c r="K31" s="71"/>
+      <c r="L31" s="71"/>
+      <c r="M31" s="72"/>
     </row>
     <row r="32" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="6"/>
-      <c r="B32" s="48" t="s">
+      <c r="B32" s="57" t="s">
         <v>19</v>
       </c>
-      <c r="C32" s="117"/>
-      <c r="D32" s="49"/>
-      <c r="E32" s="126"/>
-      <c r="F32" s="127"/>
-      <c r="G32" s="127"/>
-      <c r="H32" s="127"/>
-      <c r="I32" s="127"/>
-      <c r="J32" s="127"/>
-      <c r="K32" s="127"/>
-      <c r="L32" s="127"/>
-      <c r="M32" s="128"/>
+      <c r="C32" s="58"/>
+      <c r="D32" s="59"/>
+      <c r="E32" s="60"/>
+      <c r="F32" s="61"/>
+      <c r="G32" s="61"/>
+      <c r="H32" s="61"/>
+      <c r="I32" s="61"/>
+      <c r="J32" s="61"/>
+      <c r="K32" s="61"/>
+      <c r="L32" s="61"/>
+      <c r="M32" s="62"/>
     </row>
     <row r="33" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="6"/>
-      <c r="B33" s="48" t="s">
+      <c r="B33" s="57" t="s">
         <v>37</v>
       </c>
-      <c r="C33" s="117"/>
-      <c r="D33" s="49"/>
-      <c r="E33" s="129"/>
-      <c r="F33" s="130"/>
-      <c r="G33" s="130"/>
-      <c r="H33" s="130"/>
-      <c r="I33" s="130"/>
-      <c r="J33" s="130"/>
-      <c r="K33" s="130"/>
-      <c r="L33" s="130"/>
-      <c r="M33" s="131"/>
+      <c r="C33" s="58"/>
+      <c r="D33" s="59"/>
+      <c r="E33" s="70"/>
+      <c r="F33" s="71"/>
+      <c r="G33" s="71"/>
+      <c r="H33" s="71"/>
+      <c r="I33" s="71"/>
+      <c r="J33" s="71"/>
+      <c r="K33" s="71"/>
+      <c r="L33" s="71"/>
+      <c r="M33" s="72"/>
     </row>
     <row r="34" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="7"/>
-      <c r="B34" s="151" t="s">
+      <c r="B34" s="85" t="s">
         <v>38</v>
       </c>
-      <c r="C34" s="152"/>
-      <c r="D34" s="153"/>
-      <c r="E34" s="126"/>
-      <c r="F34" s="127"/>
-      <c r="G34" s="127"/>
-      <c r="H34" s="127"/>
-      <c r="I34" s="127"/>
-      <c r="J34" s="127"/>
-      <c r="K34" s="127"/>
-      <c r="L34" s="127"/>
-      <c r="M34" s="128"/>
+      <c r="C34" s="86"/>
+      <c r="D34" s="87"/>
+      <c r="E34" s="60"/>
+      <c r="F34" s="61"/>
+      <c r="G34" s="61"/>
+      <c r="H34" s="61"/>
+      <c r="I34" s="61"/>
+      <c r="J34" s="61"/>
+      <c r="K34" s="61"/>
+      <c r="L34" s="61"/>
+      <c r="M34" s="62"/>
     </row>
     <row r="35" spans="1:13" ht="25.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="B35" s="172" t="s">
+      <c r="B35" s="54" t="s">
         <v>41</v>
       </c>
-      <c r="C35" s="173"/>
-      <c r="D35" s="174"/>
-      <c r="E35" s="126"/>
-      <c r="F35" s="127"/>
-      <c r="G35" s="127"/>
-      <c r="H35" s="127"/>
-      <c r="I35" s="127"/>
-      <c r="J35" s="127"/>
-      <c r="K35" s="127"/>
-      <c r="L35" s="127"/>
-      <c r="M35" s="128"/>
+      <c r="C35" s="55"/>
+      <c r="D35" s="56"/>
+      <c r="E35" s="60"/>
+      <c r="F35" s="61"/>
+      <c r="G35" s="61"/>
+      <c r="H35" s="61"/>
+      <c r="I35" s="61"/>
+      <c r="J35" s="61"/>
+      <c r="K35" s="61"/>
+      <c r="L35" s="61"/>
+      <c r="M35" s="62"/>
     </row>
     <row r="36" spans="1:13" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="B36" s="48" t="s">
+      <c r="B36" s="57" t="s">
         <v>42</v>
       </c>
-      <c r="C36" s="117"/>
-      <c r="D36" s="49"/>
-      <c r="E36" s="126"/>
-      <c r="F36" s="127"/>
-      <c r="G36" s="127"/>
-      <c r="H36" s="127"/>
-      <c r="I36" s="127"/>
-      <c r="J36" s="127"/>
-      <c r="K36" s="127"/>
-      <c r="L36" s="127"/>
-      <c r="M36" s="128"/>
+      <c r="C36" s="58"/>
+      <c r="D36" s="59"/>
+      <c r="E36" s="60"/>
+      <c r="F36" s="61"/>
+      <c r="G36" s="61"/>
+      <c r="H36" s="61"/>
+      <c r="I36" s="61"/>
+      <c r="J36" s="61"/>
+      <c r="K36" s="61"/>
+      <c r="L36" s="61"/>
+      <c r="M36" s="62"/>
     </row>
     <row r="37" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="10"/>
-      <c r="B37" s="48" t="s">
+      <c r="B37" s="57" t="s">
         <v>19</v>
       </c>
-      <c r="C37" s="117"/>
-      <c r="D37" s="49"/>
-      <c r="E37" s="126"/>
-      <c r="F37" s="127"/>
-      <c r="G37" s="127"/>
-      <c r="H37" s="127"/>
-      <c r="I37" s="127"/>
-      <c r="J37" s="127"/>
-      <c r="K37" s="127"/>
-      <c r="L37" s="127"/>
-      <c r="M37" s="128"/>
+      <c r="C37" s="58"/>
+      <c r="D37" s="59"/>
+      <c r="E37" s="60"/>
+      <c r="F37" s="61"/>
+      <c r="G37" s="61"/>
+      <c r="H37" s="61"/>
+      <c r="I37" s="61"/>
+      <c r="J37" s="61"/>
+      <c r="K37" s="61"/>
+      <c r="L37" s="61"/>
+      <c r="M37" s="62"/>
     </row>
     <row r="38" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="154" t="s">
+      <c r="A38" s="30" t="s">
         <v>43</v>
       </c>
-      <c r="B38" s="154"/>
-      <c r="C38" s="154"/>
-      <c r="D38" s="154"/>
-      <c r="E38" s="154"/>
-      <c r="F38" s="154"/>
-      <c r="G38" s="154"/>
-      <c r="H38" s="154"/>
-      <c r="I38" s="154"/>
-      <c r="J38" s="154"/>
-      <c r="K38" s="154"/>
-      <c r="L38" s="154"/>
-      <c r="M38" s="154"/>
+      <c r="B38" s="30"/>
+      <c r="C38" s="30"/>
+      <c r="D38" s="30"/>
+      <c r="E38" s="30"/>
+      <c r="F38" s="30"/>
+      <c r="G38" s="30"/>
+      <c r="H38" s="30"/>
+      <c r="I38" s="30"/>
+      <c r="J38" s="30"/>
+      <c r="K38" s="30"/>
+      <c r="L38" s="30"/>
+      <c r="M38" s="30"/>
     </row>
     <row r="39" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="154"/>
-      <c r="B39" s="154"/>
-      <c r="C39" s="154"/>
-      <c r="D39" s="154"/>
-      <c r="E39" s="154"/>
-      <c r="F39" s="154"/>
-      <c r="G39" s="154"/>
-      <c r="H39" s="154"/>
-      <c r="I39" s="154"/>
-      <c r="J39" s="154"/>
-      <c r="K39" s="154"/>
-      <c r="L39" s="154"/>
-      <c r="M39" s="154"/>
+      <c r="A39" s="30"/>
+      <c r="B39" s="30"/>
+      <c r="C39" s="30"/>
+      <c r="D39" s="30"/>
+      <c r="E39" s="30"/>
+      <c r="F39" s="30"/>
+      <c r="G39" s="30"/>
+      <c r="H39" s="30"/>
+      <c r="I39" s="30"/>
+      <c r="J39" s="30"/>
+      <c r="K39" s="30"/>
+      <c r="L39" s="30"/>
+      <c r="M39" s="30"/>
     </row>
     <row r="40" spans="1:13" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="154"/>
-      <c r="B40" s="154"/>
-      <c r="C40" s="154"/>
-      <c r="D40" s="154"/>
-      <c r="E40" s="154"/>
-      <c r="F40" s="154"/>
-      <c r="G40" s="154"/>
-      <c r="H40" s="154"/>
-      <c r="I40" s="154"/>
-      <c r="J40" s="154"/>
-      <c r="K40" s="154"/>
-      <c r="L40" s="154"/>
-      <c r="M40" s="154"/>
+      <c r="A40" s="30"/>
+      <c r="B40" s="30"/>
+      <c r="C40" s="30"/>
+      <c r="D40" s="30"/>
+      <c r="E40" s="30"/>
+      <c r="F40" s="30"/>
+      <c r="G40" s="30"/>
+      <c r="H40" s="30"/>
+      <c r="I40" s="30"/>
+      <c r="J40" s="30"/>
+      <c r="K40" s="30"/>
+      <c r="L40" s="30"/>
+      <c r="M40" s="30"/>
     </row>
     <row r="41" spans="1:13" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="11"/>
-      <c r="B41" s="90" t="s">
+      <c r="B41" s="133" t="s">
         <v>65</v>
       </c>
-      <c r="C41" s="90"/>
-      <c r="D41" s="90"/>
-      <c r="E41" s="90"/>
-      <c r="F41" s="90"/>
-      <c r="G41" s="90"/>
-      <c r="H41" s="90"/>
-      <c r="I41" s="90"/>
-      <c r="J41" s="90"/>
+      <c r="C41" s="133"/>
+      <c r="D41" s="133"/>
+      <c r="E41" s="133"/>
+      <c r="F41" s="133"/>
+      <c r="G41" s="133"/>
+      <c r="H41" s="133"/>
+      <c r="I41" s="133"/>
+      <c r="J41" s="133"/>
       <c r="K41" s="11"/>
       <c r="L41" s="11"/>
       <c r="M41" s="11"/>
     </row>
     <row r="42" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B42" s="90" t="s">
+      <c r="B42" s="133" t="s">
         <v>66</v>
       </c>
-      <c r="C42" s="90"/>
-      <c r="D42" s="90"/>
-      <c r="E42" s="90"/>
-      <c r="F42" s="90"/>
-      <c r="G42" s="90"/>
-      <c r="H42" s="90"/>
-      <c r="I42" s="90"/>
-      <c r="J42" s="90"/>
+      <c r="C42" s="133"/>
+      <c r="D42" s="133"/>
+      <c r="E42" s="133"/>
+      <c r="F42" s="133"/>
+      <c r="G42" s="133"/>
+      <c r="H42" s="133"/>
+      <c r="I42" s="133"/>
+      <c r="J42" s="133"/>
       <c r="L42" s="18"/>
     </row>
     <row r="43" spans="1:13" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B43" s="162" t="s">
+      <c r="B43" s="44" t="s">
         <v>72</v>
       </c>
-      <c r="C43" s="163"/>
-      <c r="D43" s="22"/>
-      <c r="E43" s="94" t="s">
+      <c r="C43" s="45"/>
+      <c r="D43" s="20"/>
+      <c r="E43" s="137" t="s">
         <v>75</v>
       </c>
-      <c r="F43" s="95"/>
-      <c r="G43" s="96"/>
-      <c r="H43" s="97"/>
+      <c r="F43" s="138"/>
+      <c r="G43" s="139"/>
+      <c r="H43" s="140"/>
       <c r="I43" s="17" t="s">
         <v>76</v>
       </c>
       <c r="J43" s="19"/>
     </row>
     <row r="44" spans="1:13" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B44" s="164" t="s">
+      <c r="B44" s="46" t="s">
         <v>73</v>
       </c>
-      <c r="C44" s="165"/>
-      <c r="D44" s="23" t="s">
+      <c r="C44" s="47"/>
+      <c r="D44" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="E44" s="166" t="s">
+      <c r="E44" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F44" s="167"/>
-      <c r="G44" s="168"/>
-      <c r="H44" s="169"/>
-      <c r="I44" s="170"/>
-      <c r="J44" s="171"/>
+      <c r="F44" s="49"/>
+      <c r="G44" s="50"/>
+      <c r="H44" s="51"/>
+      <c r="I44" s="52"/>
+      <c r="J44" s="53"/>
     </row>
     <row r="45" spans="1:13" ht="2.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="46" spans="1:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="11"/>
-      <c r="B46" s="91" t="s">
+      <c r="B46" s="134" t="s">
         <v>45</v>
       </c>
-      <c r="C46" s="92"/>
-      <c r="D46" s="92"/>
-      <c r="E46" s="92"/>
-      <c r="F46" s="92"/>
-      <c r="G46" s="92"/>
-      <c r="H46" s="92"/>
-      <c r="I46" s="92"/>
-      <c r="J46" s="93"/>
+      <c r="C46" s="135"/>
+      <c r="D46" s="135"/>
+      <c r="E46" s="135"/>
+      <c r="F46" s="135"/>
+      <c r="G46" s="135"/>
+      <c r="H46" s="135"/>
+      <c r="I46" s="135"/>
+      <c r="J46" s="136"/>
       <c r="K46" s="11"/>
       <c r="L46" s="11"/>
       <c r="M46" s="11"/>
     </row>
     <row r="47" spans="1:13" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="11"/>
-      <c r="B47" s="72" t="s">
+      <c r="B47" s="128" t="s">
         <v>46</v>
       </c>
-      <c r="C47" s="73"/>
-      <c r="D47" s="76" t="s">
+      <c r="C47" s="129"/>
+      <c r="D47" s="113" t="s">
         <v>47</v>
       </c>
-      <c r="E47" s="77"/>
-      <c r="F47" s="77"/>
-      <c r="G47" s="78"/>
-      <c r="H47" s="79" t="s">
+      <c r="E47" s="130"/>
+      <c r="F47" s="130"/>
+      <c r="G47" s="114"/>
+      <c r="H47" s="115" t="s">
         <v>48</v>
       </c>
-      <c r="I47" s="80"/>
-      <c r="J47" s="81"/>
+      <c r="I47" s="119"/>
+      <c r="J47" s="116"/>
       <c r="K47" s="11"/>
       <c r="L47" s="11"/>
       <c r="M47" s="11"/>
     </row>
     <row r="48" spans="1:13" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="11"/>
-      <c r="B48" s="74"/>
-      <c r="C48" s="75"/>
-      <c r="D48" s="85" t="s">
+      <c r="B48" s="111"/>
+      <c r="C48" s="112"/>
+      <c r="D48" s="131" t="s">
         <v>49</v>
       </c>
-      <c r="E48" s="86"/>
-      <c r="F48" s="85" t="s">
+      <c r="E48" s="132"/>
+      <c r="F48" s="131" t="s">
         <v>50</v>
       </c>
-      <c r="G48" s="86"/>
-      <c r="H48" s="82"/>
-      <c r="I48" s="83"/>
-      <c r="J48" s="84"/>
+      <c r="G48" s="132"/>
+      <c r="H48" s="117"/>
+      <c r="I48" s="120"/>
+      <c r="J48" s="118"/>
       <c r="K48" s="11"/>
       <c r="L48" s="11"/>
       <c r="M48" s="11"/>
     </row>
-    <row r="49" spans="1:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:13" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="13"/>
-      <c r="B49" s="53" t="s">
+      <c r="B49" s="94" t="s">
         <v>51</v>
       </c>
-      <c r="C49" s="54"/>
-      <c r="D49" s="55"/>
-      <c r="E49" s="56"/>
-      <c r="F49" s="55"/>
-      <c r="G49" s="56"/>
-      <c r="H49" s="87"/>
-      <c r="I49" s="88"/>
-      <c r="J49" s="89"/>
+      <c r="C49" s="95"/>
+      <c r="D49" s="96"/>
+      <c r="E49" s="97"/>
+      <c r="F49" s="96"/>
+      <c r="G49" s="97"/>
+      <c r="H49" s="161"/>
+      <c r="I49" s="162"/>
+      <c r="J49" s="163"/>
       <c r="K49" s="13"/>
       <c r="L49" s="13"/>
       <c r="M49" s="13"/>
     </row>
-    <row r="50" spans="1:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:13" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="13"/>
-      <c r="B50" s="53" t="s">
+      <c r="B50" s="94" t="s">
         <v>52</v>
       </c>
-      <c r="C50" s="54"/>
-      <c r="D50" s="55"/>
-      <c r="E50" s="56"/>
-      <c r="F50" s="155"/>
-      <c r="G50" s="156"/>
-      <c r="H50" s="62"/>
-      <c r="I50" s="63"/>
-      <c r="J50" s="64"/>
+      <c r="C50" s="95"/>
+      <c r="D50" s="96"/>
+      <c r="E50" s="97"/>
+      <c r="F50" s="37"/>
+      <c r="G50" s="38"/>
+      <c r="H50" s="161"/>
+      <c r="I50" s="162"/>
+      <c r="J50" s="163"/>
       <c r="K50" s="13"/>
       <c r="L50" s="13"/>
       <c r="M50" s="13"/>
     </row>
-    <row r="51" spans="1:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:13" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="13"/>
-      <c r="B51" s="53" t="s">
+      <c r="B51" s="94" t="s">
         <v>53</v>
       </c>
-      <c r="C51" s="54"/>
-      <c r="D51" s="55"/>
-      <c r="E51" s="56"/>
-      <c r="F51" s="55"/>
-      <c r="G51" s="56"/>
-      <c r="H51" s="62"/>
-      <c r="I51" s="63"/>
-      <c r="J51" s="64"/>
+      <c r="C51" s="95"/>
+      <c r="D51" s="96"/>
+      <c r="E51" s="97"/>
+      <c r="F51" s="96"/>
+      <c r="G51" s="97"/>
+      <c r="H51" s="161"/>
+      <c r="I51" s="162"/>
+      <c r="J51" s="163"/>
       <c r="K51" s="13"/>
       <c r="L51" s="13"/>
       <c r="M51" s="13"/>
     </row>
-    <row r="52" spans="1:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:13" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="13"/>
-      <c r="B52" s="60" t="s">
+      <c r="B52" s="141" t="s">
         <v>64</v>
       </c>
-      <c r="C52" s="61"/>
-      <c r="D52" s="103"/>
-      <c r="E52" s="104"/>
-      <c r="F52" s="103"/>
-      <c r="G52" s="104"/>
-      <c r="H52" s="105"/>
-      <c r="I52" s="106"/>
-      <c r="J52" s="107"/>
+      <c r="C52" s="142"/>
+      <c r="D52" s="126"/>
+      <c r="E52" s="127"/>
+      <c r="F52" s="126"/>
+      <c r="G52" s="127"/>
+      <c r="H52" s="161"/>
+      <c r="I52" s="162"/>
+      <c r="J52" s="163"/>
       <c r="K52" s="13"/>
       <c r="L52" s="13"/>
       <c r="M52" s="13"/>
     </row>
-    <row r="53" spans="1:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:13" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="13"/>
-      <c r="B53" s="53" t="s">
+      <c r="B53" s="94" t="s">
         <v>54</v>
       </c>
-      <c r="C53" s="54"/>
-      <c r="D53" s="55"/>
-      <c r="E53" s="56"/>
-      <c r="F53" s="55"/>
-      <c r="G53" s="56"/>
-      <c r="H53" s="57"/>
-      <c r="I53" s="58"/>
-      <c r="J53" s="59"/>
+      <c r="C53" s="95"/>
+      <c r="D53" s="96"/>
+      <c r="E53" s="97"/>
+      <c r="F53" s="96"/>
+      <c r="G53" s="97"/>
+      <c r="H53" s="161"/>
+      <c r="I53" s="162"/>
+      <c r="J53" s="163"/>
       <c r="K53" s="13"/>
       <c r="L53" s="13"/>
       <c r="M53" s="13"/>
     </row>
-    <row r="54" spans="1:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:13" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="13"/>
-      <c r="B54" s="53" t="s">
+      <c r="B54" s="94" t="s">
         <v>55</v>
       </c>
-      <c r="C54" s="54"/>
-      <c r="D54" s="55"/>
-      <c r="E54" s="56"/>
-      <c r="F54" s="55"/>
-      <c r="G54" s="56"/>
-      <c r="H54" s="62"/>
-      <c r="I54" s="63"/>
-      <c r="J54" s="64"/>
+      <c r="C54" s="95"/>
+      <c r="D54" s="96"/>
+      <c r="E54" s="97"/>
+      <c r="F54" s="96"/>
+      <c r="G54" s="97"/>
+      <c r="H54" s="161"/>
+      <c r="I54" s="162"/>
+      <c r="J54" s="163"/>
       <c r="K54" s="13"/>
       <c r="L54" s="13"/>
       <c r="M54" s="13"/>
     </row>
-    <row r="55" spans="1:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:13" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A55" s="13"/>
-      <c r="B55" s="53" t="s">
+      <c r="B55" s="94" t="s">
         <v>56</v>
       </c>
-      <c r="C55" s="54"/>
-      <c r="D55" s="55"/>
-      <c r="E55" s="56"/>
-      <c r="F55" s="55"/>
-      <c r="G55" s="56"/>
-      <c r="H55" s="62"/>
-      <c r="I55" s="63"/>
-      <c r="J55" s="64"/>
+      <c r="C55" s="95"/>
+      <c r="D55" s="96"/>
+      <c r="E55" s="97"/>
+      <c r="F55" s="96"/>
+      <c r="G55" s="97"/>
+      <c r="H55" s="161"/>
+      <c r="I55" s="162"/>
+      <c r="J55" s="163"/>
       <c r="K55" s="13"/>
       <c r="L55" s="13"/>
       <c r="M55" s="13"/>
     </row>
-    <row r="56" spans="1:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:13" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A56" s="13"/>
-      <c r="B56" s="65" t="s">
+      <c r="B56" s="143" t="s">
         <v>57</v>
       </c>
-      <c r="C56" s="66"/>
-      <c r="D56" s="67"/>
-      <c r="E56" s="68"/>
-      <c r="F56" s="67"/>
-      <c r="G56" s="68"/>
-      <c r="H56" s="69"/>
-      <c r="I56" s="70"/>
-      <c r="J56" s="71"/>
+      <c r="C56" s="144"/>
+      <c r="D56" s="145"/>
+      <c r="E56" s="146"/>
+      <c r="F56" s="145"/>
+      <c r="G56" s="146"/>
+      <c r="H56" s="161"/>
+      <c r="I56" s="162"/>
+      <c r="J56" s="163"/>
       <c r="K56" s="13"/>
       <c r="L56" s="13"/>
       <c r="M56" s="13"/>
     </row>
     <row r="57" spans="1:13" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57" s="13"/>
-      <c r="B57" s="100" t="s">
+      <c r="B57" s="123" t="s">
         <v>58</v>
       </c>
-      <c r="C57" s="101"/>
-      <c r="D57" s="101"/>
-      <c r="E57" s="101"/>
-      <c r="F57" s="101"/>
-      <c r="G57" s="101"/>
-      <c r="H57" s="101"/>
-      <c r="I57" s="101"/>
-      <c r="J57" s="102"/>
+      <c r="C57" s="124"/>
+      <c r="D57" s="124"/>
+      <c r="E57" s="124"/>
+      <c r="F57" s="124"/>
+      <c r="G57" s="124"/>
+      <c r="H57" s="124"/>
+      <c r="I57" s="124"/>
+      <c r="J57" s="125"/>
       <c r="K57" s="13"/>
       <c r="L57" s="13"/>
       <c r="M57" s="13"/>
     </row>
     <row r="58" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A58" s="13"/>
-      <c r="B58" s="79" t="s">
+      <c r="B58" s="115" t="s">
         <v>46</v>
       </c>
-      <c r="C58" s="81"/>
-      <c r="D58" s="45" t="s">
+      <c r="C58" s="116"/>
+      <c r="D58" s="34" t="s">
         <v>47</v>
       </c>
-      <c r="E58" s="46"/>
-      <c r="F58" s="46"/>
-      <c r="G58" s="47"/>
-      <c r="H58" s="79" t="s">
+      <c r="E58" s="35"/>
+      <c r="F58" s="35"/>
+      <c r="G58" s="36"/>
+      <c r="H58" s="115" t="s">
         <v>48</v>
       </c>
-      <c r="I58" s="80"/>
-      <c r="J58" s="81"/>
+      <c r="I58" s="119"/>
+      <c r="J58" s="116"/>
       <c r="K58" s="13"/>
       <c r="L58" s="13"/>
       <c r="M58" s="13"/>
     </row>
     <row r="59" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A59" s="13"/>
-      <c r="B59" s="82"/>
-      <c r="C59" s="84"/>
-      <c r="D59" s="98" t="s">
+      <c r="B59" s="117"/>
+      <c r="C59" s="118"/>
+      <c r="D59" s="121" t="s">
         <v>49</v>
       </c>
-      <c r="E59" s="99"/>
-      <c r="F59" s="98" t="s">
+      <c r="E59" s="122"/>
+      <c r="F59" s="121" t="s">
         <v>50</v>
       </c>
-      <c r="G59" s="99"/>
-      <c r="H59" s="82"/>
-      <c r="I59" s="83"/>
-      <c r="J59" s="84"/>
+      <c r="G59" s="122"/>
+      <c r="H59" s="117"/>
+      <c r="I59" s="120"/>
+      <c r="J59" s="118"/>
       <c r="K59" s="13"/>
       <c r="L59" s="13"/>
       <c r="M59" s="13"/>
     </row>
-    <row r="60" spans="1:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:13" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A60" s="13"/>
-      <c r="B60" s="53" t="s">
+      <c r="B60" s="94" t="s">
         <v>59</v>
       </c>
-      <c r="C60" s="54"/>
-      <c r="D60" s="55"/>
-      <c r="E60" s="56"/>
-      <c r="F60" s="55"/>
-      <c r="G60" s="56"/>
-      <c r="H60" s="57"/>
-      <c r="I60" s="58"/>
-      <c r="J60" s="59"/>
+      <c r="C60" s="95"/>
+      <c r="D60" s="96"/>
+      <c r="E60" s="97"/>
+      <c r="F60" s="96"/>
+      <c r="G60" s="97"/>
+      <c r="H60" s="161"/>
+      <c r="I60" s="162"/>
+      <c r="J60" s="163"/>
       <c r="K60" s="13"/>
       <c r="L60" s="13"/>
       <c r="M60" s="13"/>
     </row>
-    <row r="61" spans="1:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:13" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A61" s="13"/>
-      <c r="B61" s="53" t="s">
+      <c r="B61" s="94" t="s">
         <v>60</v>
       </c>
-      <c r="C61" s="54"/>
-      <c r="D61" s="55"/>
-      <c r="E61" s="56"/>
-      <c r="F61" s="55"/>
-      <c r="G61" s="56"/>
-      <c r="H61" s="57"/>
-      <c r="I61" s="58"/>
-      <c r="J61" s="59"/>
+      <c r="C61" s="95"/>
+      <c r="D61" s="96"/>
+      <c r="E61" s="97"/>
+      <c r="F61" s="96"/>
+      <c r="G61" s="97"/>
+      <c r="H61" s="161"/>
+      <c r="I61" s="162"/>
+      <c r="J61" s="163"/>
       <c r="K61" s="13"/>
       <c r="L61" s="13"/>
       <c r="M61" s="13"/>
     </row>
-    <row r="62" spans="1:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:13" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A62" s="13"/>
-      <c r="B62" s="53" t="s">
+      <c r="B62" s="94" t="s">
         <v>61</v>
       </c>
-      <c r="C62" s="54"/>
-      <c r="D62" s="55"/>
-      <c r="E62" s="56"/>
-      <c r="F62" s="55"/>
-      <c r="G62" s="56"/>
-      <c r="H62" s="57"/>
-      <c r="I62" s="58"/>
-      <c r="J62" s="59"/>
+      <c r="C62" s="95"/>
+      <c r="D62" s="96"/>
+      <c r="E62" s="97"/>
+      <c r="F62" s="96"/>
+      <c r="G62" s="97"/>
+      <c r="H62" s="161"/>
+      <c r="I62" s="162"/>
+      <c r="J62" s="163"/>
       <c r="K62" s="13"/>
       <c r="L62" s="13"/>
       <c r="M62" s="13"/>
     </row>
-    <row r="63" spans="1:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:13" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A63" s="13"/>
-      <c r="B63" s="53" t="s">
+      <c r="B63" s="94" t="s">
         <v>62</v>
       </c>
-      <c r="C63" s="54"/>
-      <c r="D63" s="55"/>
-      <c r="E63" s="56"/>
-      <c r="F63" s="55"/>
-      <c r="G63" s="56"/>
-      <c r="H63" s="57"/>
-      <c r="I63" s="58"/>
-      <c r="J63" s="59"/>
+      <c r="C63" s="95"/>
+      <c r="D63" s="96"/>
+      <c r="E63" s="97"/>
+      <c r="F63" s="96"/>
+      <c r="G63" s="97"/>
+      <c r="H63" s="161"/>
+      <c r="I63" s="162"/>
+      <c r="J63" s="163"/>
       <c r="K63" s="13"/>
       <c r="L63" s="13"/>
       <c r="M63" s="13"/>
     </row>
-    <row r="64" spans="1:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:13" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A64" s="13"/>
-      <c r="B64" s="53" t="s">
+      <c r="B64" s="94" t="s">
         <v>63</v>
       </c>
-      <c r="C64" s="54"/>
-      <c r="D64" s="55"/>
-      <c r="E64" s="56"/>
-      <c r="F64" s="55"/>
-      <c r="G64" s="56"/>
-      <c r="H64" s="57"/>
-      <c r="I64" s="58"/>
-      <c r="J64" s="59"/>
+      <c r="C64" s="95"/>
+      <c r="D64" s="96"/>
+      <c r="E64" s="97"/>
+      <c r="F64" s="96"/>
+      <c r="G64" s="97"/>
+      <c r="H64" s="161"/>
+      <c r="I64" s="162"/>
+      <c r="J64" s="163"/>
       <c r="K64" s="13"/>
       <c r="L64" s="13"/>
       <c r="M64" s="13"/>
@@ -3092,51 +3090,51 @@
     </row>
     <row r="66" spans="1:13" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A66" s="13"/>
-      <c r="B66" s="45" t="s">
+      <c r="B66" s="34" t="s">
         <v>67</v>
       </c>
-      <c r="C66" s="46"/>
-      <c r="D66" s="46"/>
-      <c r="E66" s="46"/>
-      <c r="F66" s="46"/>
-      <c r="G66" s="46"/>
-      <c r="H66" s="46"/>
-      <c r="I66" s="46"/>
-      <c r="J66" s="47"/>
+      <c r="C66" s="35"/>
+      <c r="D66" s="35"/>
+      <c r="E66" s="35"/>
+      <c r="F66" s="35"/>
+      <c r="G66" s="35"/>
+      <c r="H66" s="35"/>
+      <c r="I66" s="35"/>
+      <c r="J66" s="36"/>
       <c r="K66" s="13"/>
       <c r="L66" s="13"/>
       <c r="M66" s="13"/>
     </row>
     <row r="67" spans="1:13" ht="72" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A67" s="13"/>
-      <c r="B67" s="48" t="s">
+      <c r="B67" s="57" t="s">
         <v>68</v>
       </c>
-      <c r="C67" s="49"/>
-      <c r="D67" s="50"/>
-      <c r="E67" s="51"/>
-      <c r="F67" s="51"/>
-      <c r="G67" s="51"/>
-      <c r="H67" s="51"/>
-      <c r="I67" s="51"/>
-      <c r="J67" s="52"/>
+      <c r="C67" s="59"/>
+      <c r="D67" s="164"/>
+      <c r="E67" s="165"/>
+      <c r="F67" s="165"/>
+      <c r="G67" s="165"/>
+      <c r="H67" s="165"/>
+      <c r="I67" s="165"/>
+      <c r="J67" s="166"/>
       <c r="K67" s="13"/>
       <c r="L67" s="13"/>
       <c r="M67" s="13"/>
     </row>
     <row r="68" spans="1:13" ht="72" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A68" s="13"/>
-      <c r="B68" s="48" t="s">
+      <c r="B68" s="57" t="s">
         <v>69</v>
       </c>
-      <c r="C68" s="49"/>
-      <c r="D68" s="50"/>
-      <c r="E68" s="51"/>
-      <c r="F68" s="51"/>
-      <c r="G68" s="51"/>
-      <c r="H68" s="51"/>
-      <c r="I68" s="51"/>
-      <c r="J68" s="52"/>
+      <c r="C68" s="59"/>
+      <c r="D68" s="164"/>
+      <c r="E68" s="165"/>
+      <c r="F68" s="165"/>
+      <c r="G68" s="165"/>
+      <c r="H68" s="165"/>
+      <c r="I68" s="165"/>
+      <c r="J68" s="166"/>
       <c r="K68" s="13"/>
       <c r="L68" s="13"/>
       <c r="M68" s="13"/>
@@ -3158,51 +3156,51 @@
     </row>
     <row r="70" spans="1:13" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A70" s="13"/>
-      <c r="B70" s="45" t="s">
+      <c r="B70" s="34" t="s">
         <v>70</v>
       </c>
-      <c r="C70" s="46"/>
-      <c r="D70" s="46"/>
-      <c r="E70" s="46"/>
-      <c r="F70" s="46"/>
-      <c r="G70" s="46"/>
-      <c r="H70" s="46"/>
-      <c r="I70" s="46"/>
-      <c r="J70" s="47"/>
+      <c r="C70" s="35"/>
+      <c r="D70" s="35"/>
+      <c r="E70" s="35"/>
+      <c r="F70" s="35"/>
+      <c r="G70" s="35"/>
+      <c r="H70" s="35"/>
+      <c r="I70" s="35"/>
+      <c r="J70" s="36"/>
       <c r="K70" s="13"/>
       <c r="L70" s="13"/>
       <c r="M70" s="13"/>
     </row>
     <row r="71" spans="1:13" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A71" s="13"/>
-      <c r="B71" s="48" t="s">
+      <c r="B71" s="57" t="s">
         <v>68</v>
       </c>
-      <c r="C71" s="49"/>
-      <c r="D71" s="50"/>
-      <c r="E71" s="51"/>
-      <c r="F71" s="51"/>
-      <c r="G71" s="51"/>
-      <c r="H71" s="51"/>
-      <c r="I71" s="51"/>
-      <c r="J71" s="52"/>
+      <c r="C71" s="59"/>
+      <c r="D71" s="164"/>
+      <c r="E71" s="165"/>
+      <c r="F71" s="165"/>
+      <c r="G71" s="165"/>
+      <c r="H71" s="165"/>
+      <c r="I71" s="165"/>
+      <c r="J71" s="166"/>
       <c r="K71" s="13"/>
       <c r="L71" s="13"/>
       <c r="M71" s="13"/>
     </row>
     <row r="72" spans="1:13" ht="72" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A72" s="13"/>
-      <c r="B72" s="48" t="s">
+      <c r="B72" s="57" t="s">
         <v>69</v>
       </c>
-      <c r="C72" s="49"/>
-      <c r="D72" s="50"/>
-      <c r="E72" s="51"/>
-      <c r="F72" s="51"/>
-      <c r="G72" s="51"/>
-      <c r="H72" s="51"/>
-      <c r="I72" s="51"/>
-      <c r="J72" s="52"/>
+      <c r="C72" s="59"/>
+      <c r="D72" s="164"/>
+      <c r="E72" s="165"/>
+      <c r="F72" s="165"/>
+      <c r="G72" s="165"/>
+      <c r="H72" s="165"/>
+      <c r="I72" s="165"/>
+      <c r="J72" s="166"/>
       <c r="K72" s="13"/>
       <c r="L72" s="13"/>
       <c r="M72" s="13"/>
@@ -3224,51 +3222,51 @@
     </row>
     <row r="74" spans="1:13" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A74" s="13"/>
-      <c r="B74" s="45" t="s">
+      <c r="B74" s="34" t="s">
         <v>71</v>
       </c>
-      <c r="C74" s="46"/>
-      <c r="D74" s="46"/>
-      <c r="E74" s="46"/>
-      <c r="F74" s="46"/>
-      <c r="G74" s="46"/>
-      <c r="H74" s="46"/>
-      <c r="I74" s="46"/>
-      <c r="J74" s="47"/>
+      <c r="C74" s="35"/>
+      <c r="D74" s="35"/>
+      <c r="E74" s="35"/>
+      <c r="F74" s="35"/>
+      <c r="G74" s="35"/>
+      <c r="H74" s="35"/>
+      <c r="I74" s="35"/>
+      <c r="J74" s="36"/>
       <c r="K74" s="13"/>
       <c r="L74" s="13"/>
       <c r="M74" s="13"/>
     </row>
     <row r="75" spans="1:13" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A75" s="13"/>
-      <c r="B75" s="48" t="s">
+      <c r="B75" s="57" t="s">
         <v>68</v>
       </c>
-      <c r="C75" s="49"/>
-      <c r="D75" s="50"/>
-      <c r="E75" s="51"/>
-      <c r="F75" s="51"/>
-      <c r="G75" s="51"/>
-      <c r="H75" s="51"/>
-      <c r="I75" s="51"/>
-      <c r="J75" s="52"/>
+      <c r="C75" s="59"/>
+      <c r="D75" s="164"/>
+      <c r="E75" s="165"/>
+      <c r="F75" s="165"/>
+      <c r="G75" s="165"/>
+      <c r="H75" s="165"/>
+      <c r="I75" s="165"/>
+      <c r="J75" s="166"/>
       <c r="K75" s="13"/>
       <c r="L75" s="13"/>
       <c r="M75" s="13"/>
     </row>
     <row r="76" spans="1:13" ht="71.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A76" s="13"/>
-      <c r="B76" s="48" t="s">
+      <c r="B76" s="57" t="s">
         <v>69</v>
       </c>
-      <c r="C76" s="49"/>
-      <c r="D76" s="50"/>
-      <c r="E76" s="51"/>
-      <c r="F76" s="51"/>
-      <c r="G76" s="51"/>
-      <c r="H76" s="51"/>
-      <c r="I76" s="51"/>
-      <c r="J76" s="52"/>
+      <c r="C76" s="59"/>
+      <c r="D76" s="164"/>
+      <c r="E76" s="165"/>
+      <c r="F76" s="165"/>
+      <c r="G76" s="165"/>
+      <c r="H76" s="165"/>
+      <c r="I76" s="165"/>
+      <c r="J76" s="166"/>
       <c r="K76" s="13"/>
       <c r="L76" s="13"/>
       <c r="M76" s="13"/>
@@ -3291,119 +3289,115 @@
     <row r="78" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="11"/>
       <c r="B78" s="12"/>
-      <c r="C78" s="175" t="s">
+      <c r="C78" s="63" t="s">
         <v>99</v>
       </c>
-      <c r="D78" s="176"/>
-      <c r="E78" s="176"/>
-      <c r="F78" s="176"/>
-      <c r="G78" s="31" t="s">
+      <c r="D78" s="64"/>
+      <c r="E78" s="64"/>
+      <c r="F78" s="64"/>
+      <c r="G78" s="28" t="s">
         <v>98</v>
       </c>
-      <c r="H78" s="30" t="b">
-        <v>0</v>
-      </c>
-      <c r="I78" s="31" t="s">
+      <c r="H78" s="12"/>
+      <c r="I78" s="28" t="s">
         <v>97</v>
       </c>
-      <c r="J78" s="30" t="b">
-        <v>0</v>
-      </c>
+      <c r="J78" s="12"/>
       <c r="K78" s="11"/>
       <c r="L78" s="11"/>
       <c r="M78" s="11"/>
     </row>
     <row r="79" spans="1:13" ht="48.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="160"/>
-      <c r="B79" s="160"/>
-      <c r="C79" s="160"/>
-      <c r="D79" s="160"/>
-      <c r="E79" s="158"/>
-      <c r="F79" s="158"/>
-      <c r="G79" s="160"/>
-      <c r="H79" s="160"/>
-      <c r="I79" s="158"/>
-      <c r="J79" s="158"/>
-      <c r="K79" s="160"/>
-      <c r="L79" s="160"/>
-      <c r="M79" s="160"/>
+      <c r="A79" s="42"/>
+      <c r="B79" s="42"/>
+      <c r="C79" s="42"/>
+      <c r="D79" s="42"/>
+      <c r="E79" s="40"/>
+      <c r="F79" s="40"/>
+      <c r="G79" s="42"/>
+      <c r="H79" s="42"/>
+      <c r="I79" s="40"/>
+      <c r="J79" s="40"/>
+      <c r="K79" s="42"/>
+      <c r="L79" s="42"/>
+      <c r="M79" s="42"/>
     </row>
     <row r="80" spans="1:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="160"/>
-      <c r="B80" s="160"/>
-      <c r="C80" s="160"/>
-      <c r="D80" s="160"/>
-      <c r="E80" s="158"/>
-      <c r="F80" s="158"/>
-      <c r="G80" s="160"/>
-      <c r="H80" s="160"/>
-      <c r="I80" s="158"/>
-      <c r="J80" s="158"/>
-      <c r="K80" s="160"/>
-      <c r="L80" s="160"/>
-      <c r="M80" s="160"/>
+      <c r="A80" s="42"/>
+      <c r="B80" s="42"/>
+      <c r="C80" s="42"/>
+      <c r="D80" s="42"/>
+      <c r="E80" s="40"/>
+      <c r="F80" s="40"/>
+      <c r="G80" s="42"/>
+      <c r="H80" s="42"/>
+      <c r="I80" s="40"/>
+      <c r="J80" s="40"/>
+      <c r="K80" s="42"/>
+      <c r="L80" s="42"/>
+      <c r="M80" s="42"/>
     </row>
     <row r="81" spans="1:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="160"/>
-      <c r="B81" s="160"/>
-      <c r="C81" s="160"/>
-      <c r="D81" s="160"/>
-      <c r="E81" s="158"/>
-      <c r="F81" s="158"/>
-      <c r="G81" s="160"/>
-      <c r="H81" s="160"/>
-      <c r="I81" s="158"/>
-      <c r="J81" s="158"/>
-      <c r="K81" s="160"/>
-      <c r="L81" s="160"/>
-      <c r="M81" s="160"/>
+      <c r="A81" s="42"/>
+      <c r="B81" s="42"/>
+      <c r="C81" s="42"/>
+      <c r="D81" s="42"/>
+      <c r="E81" s="40"/>
+      <c r="F81" s="40"/>
+      <c r="G81" s="42"/>
+      <c r="H81" s="42"/>
+      <c r="I81" s="40"/>
+      <c r="J81" s="40"/>
+      <c r="K81" s="42"/>
+      <c r="L81" s="42"/>
+      <c r="M81" s="42"/>
     </row>
     <row r="82" spans="1:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="160"/>
-      <c r="B82" s="160"/>
-      <c r="C82" s="160"/>
-      <c r="D82" s="160"/>
-      <c r="E82" s="158"/>
-      <c r="F82" s="158"/>
-      <c r="G82" s="160"/>
-      <c r="H82" s="160"/>
-      <c r="I82" s="158"/>
-      <c r="J82" s="158"/>
-      <c r="K82" s="160"/>
-      <c r="L82" s="160"/>
-      <c r="M82" s="160"/>
+      <c r="A82" s="42"/>
+      <c r="B82" s="42"/>
+      <c r="C82" s="42"/>
+      <c r="D82" s="42"/>
+      <c r="E82" s="40"/>
+      <c r="F82" s="40"/>
+      <c r="G82" s="42"/>
+      <c r="H82" s="42"/>
+      <c r="I82" s="40"/>
+      <c r="J82" s="40"/>
+      <c r="K82" s="42"/>
+      <c r="L82" s="42"/>
+      <c r="M82" s="42"/>
     </row>
     <row r="83" spans="1:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="161"/>
-      <c r="B83" s="161"/>
-      <c r="C83" s="161"/>
-      <c r="D83" s="161"/>
-      <c r="E83" s="158"/>
-      <c r="F83" s="158"/>
-      <c r="G83" s="161"/>
-      <c r="H83" s="161"/>
-      <c r="I83" s="158"/>
-      <c r="J83" s="158"/>
-      <c r="K83" s="161"/>
-      <c r="L83" s="161"/>
-      <c r="M83" s="161"/>
+      <c r="A83" s="43"/>
+      <c r="B83" s="43"/>
+      <c r="C83" s="43"/>
+      <c r="D83" s="43"/>
+      <c r="E83" s="40"/>
+      <c r="F83" s="40"/>
+      <c r="G83" s="43"/>
+      <c r="H83" s="43"/>
+      <c r="I83" s="40"/>
+      <c r="J83" s="40"/>
+      <c r="K83" s="43"/>
+      <c r="L83" s="43"/>
+      <c r="M83" s="43"/>
     </row>
     <row r="84" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="157"/>
-      <c r="B84" s="157"/>
-      <c r="C84" s="157"/>
-      <c r="D84" s="157"/>
-      <c r="E84" s="158"/>
-      <c r="F84" s="158"/>
-      <c r="G84" s="159" t="s">
+      <c r="A84" s="39"/>
+      <c r="B84" s="39"/>
+      <c r="C84" s="39"/>
+      <c r="D84" s="39"/>
+      <c r="E84" s="40"/>
+      <c r="F84" s="40"/>
+      <c r="G84" s="41" t="s">
         <v>27</v>
       </c>
-      <c r="H84" s="159"/>
-      <c r="I84" s="158"/>
-      <c r="J84" s="158"/>
-      <c r="K84" s="157"/>
-      <c r="L84" s="157"/>
-      <c r="M84" s="157"/>
+      <c r="H84" s="41"/>
+      <c r="I84" s="40"/>
+      <c r="J84" s="40"/>
+      <c r="K84" s="39"/>
+      <c r="L84" s="39"/>
+      <c r="M84" s="39"/>
     </row>
     <row r="85" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A85" s="12"/>
@@ -3421,29 +3415,183 @@
       <c r="M85" s="12"/>
     </row>
     <row r="86" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A86" s="24"/>
-      <c r="B86" s="44"/>
-      <c r="C86" s="44"/>
-      <c r="D86" s="44"/>
-      <c r="E86" s="44"/>
-      <c r="F86" s="44"/>
-      <c r="G86" s="44"/>
-      <c r="H86" s="44"/>
-      <c r="I86" s="44"/>
-      <c r="J86" s="44"/>
-      <c r="K86" s="24"/>
-      <c r="L86" s="24"/>
-      <c r="M86" s="24"/>
+      <c r="A86" s="22"/>
+      <c r="B86" s="158"/>
+      <c r="C86" s="158"/>
+      <c r="D86" s="158"/>
+      <c r="E86" s="158"/>
+      <c r="F86" s="158"/>
+      <c r="G86" s="158"/>
+      <c r="H86" s="158"/>
+      <c r="I86" s="158"/>
+      <c r="J86" s="158"/>
+      <c r="K86" s="22"/>
+      <c r="L86" s="22"/>
+      <c r="M86" s="22"/>
     </row>
     <row r="87" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="F87" s="36" t="s">
+      <c r="F87" s="29" t="s">
         <v>44</v>
       </c>
-      <c r="G87" s="36"/>
+      <c r="G87" s="29"/>
     </row>
     <row r="88" spans="1:13" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="178">
+    <mergeCell ref="B1:K1"/>
+    <mergeCell ref="B2:K2"/>
+    <mergeCell ref="B3:K3"/>
+    <mergeCell ref="B4:K4"/>
+    <mergeCell ref="B5:K5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="E6:G6"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="B86:J86"/>
+    <mergeCell ref="B74:J74"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="D75:J75"/>
+    <mergeCell ref="B76:C76"/>
+    <mergeCell ref="D76:J76"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="D64:E64"/>
+    <mergeCell ref="F64:G64"/>
+    <mergeCell ref="H64:J64"/>
+    <mergeCell ref="B66:J66"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="D67:J67"/>
+    <mergeCell ref="D68:J68"/>
+    <mergeCell ref="B71:C71"/>
+    <mergeCell ref="D71:J71"/>
+    <mergeCell ref="B72:C72"/>
+    <mergeCell ref="D72:J72"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="H54:J54"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="D55:E55"/>
+    <mergeCell ref="F55:G55"/>
+    <mergeCell ref="H55:J55"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="D56:E56"/>
+    <mergeCell ref="F56:G56"/>
+    <mergeCell ref="H56:J56"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="D63:E63"/>
+    <mergeCell ref="F63:G63"/>
+    <mergeCell ref="H63:J63"/>
+    <mergeCell ref="D53:E53"/>
+    <mergeCell ref="F53:G53"/>
+    <mergeCell ref="H53:J53"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="D54:E54"/>
+    <mergeCell ref="F54:G54"/>
+    <mergeCell ref="B47:C48"/>
+    <mergeCell ref="D47:G47"/>
+    <mergeCell ref="H47:J48"/>
+    <mergeCell ref="D48:E48"/>
+    <mergeCell ref="F48:G48"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="D49:E49"/>
+    <mergeCell ref="H49:J49"/>
+    <mergeCell ref="B41:J41"/>
+    <mergeCell ref="B46:J46"/>
+    <mergeCell ref="B42:J42"/>
+    <mergeCell ref="F49:G49"/>
+    <mergeCell ref="E43:F43"/>
+    <mergeCell ref="G43:H43"/>
+    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="D50:E50"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="D61:E61"/>
+    <mergeCell ref="F61:G61"/>
+    <mergeCell ref="H61:J61"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="D62:E62"/>
+    <mergeCell ref="F62:G62"/>
+    <mergeCell ref="H62:J62"/>
+    <mergeCell ref="B58:C59"/>
+    <mergeCell ref="D58:G58"/>
+    <mergeCell ref="H58:J59"/>
+    <mergeCell ref="D59:E59"/>
+    <mergeCell ref="F59:G59"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="D60:E60"/>
+    <mergeCell ref="F60:G60"/>
+    <mergeCell ref="H60:J60"/>
+    <mergeCell ref="B57:J57"/>
+    <mergeCell ref="D52:E52"/>
+    <mergeCell ref="F52:G52"/>
+    <mergeCell ref="H52:J52"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="H50:J50"/>
+    <mergeCell ref="B51:C51"/>
+    <mergeCell ref="D51:E51"/>
+    <mergeCell ref="F51:G51"/>
+    <mergeCell ref="H51:J51"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="C13:F13"/>
+    <mergeCell ref="G13:I13"/>
+    <mergeCell ref="A14:A22"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="C11:H11"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="E20:M20"/>
+    <mergeCell ref="E21:M21"/>
+    <mergeCell ref="E22:M22"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="E17:M17"/>
+    <mergeCell ref="E18:M18"/>
+    <mergeCell ref="E19:M19"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="E26:M26"/>
+    <mergeCell ref="E27:M27"/>
+    <mergeCell ref="E28:M28"/>
+    <mergeCell ref="A23:A25"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="E23:M23"/>
+    <mergeCell ref="E24:M24"/>
+    <mergeCell ref="E25:M25"/>
+    <mergeCell ref="E36:M36"/>
+    <mergeCell ref="E37:M37"/>
+    <mergeCell ref="C9:M9"/>
+    <mergeCell ref="A8:M8"/>
+    <mergeCell ref="E14:M14"/>
+    <mergeCell ref="K11:M11"/>
+    <mergeCell ref="K12:M12"/>
+    <mergeCell ref="J13:M13"/>
+    <mergeCell ref="E15:M15"/>
+    <mergeCell ref="E16:M16"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="E32:M32"/>
+    <mergeCell ref="E33:M33"/>
+    <mergeCell ref="E34:M34"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="E29:M29"/>
+    <mergeCell ref="E30:M30"/>
+    <mergeCell ref="E31:M31"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="F87:G87"/>
     <mergeCell ref="A38:M40"/>
     <mergeCell ref="I10:M10"/>
@@ -3468,212 +3616,58 @@
     <mergeCell ref="B37:D37"/>
     <mergeCell ref="E35:M35"/>
     <mergeCell ref="C78:F78"/>
-    <mergeCell ref="E36:M36"/>
-    <mergeCell ref="E37:M37"/>
-    <mergeCell ref="C9:M9"/>
-    <mergeCell ref="A8:M8"/>
-    <mergeCell ref="E14:M14"/>
-    <mergeCell ref="K11:M11"/>
-    <mergeCell ref="K12:M12"/>
-    <mergeCell ref="J13:M13"/>
-    <mergeCell ref="E15:M15"/>
-    <mergeCell ref="E16:M16"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="E32:M32"/>
-    <mergeCell ref="E33:M33"/>
-    <mergeCell ref="E34:M34"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="E29:M29"/>
-    <mergeCell ref="E30:M30"/>
-    <mergeCell ref="E31:M31"/>
-    <mergeCell ref="B26:D26"/>
-    <mergeCell ref="B27:D27"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="E26:M26"/>
-    <mergeCell ref="E27:M27"/>
-    <mergeCell ref="E28:M28"/>
-    <mergeCell ref="A23:A25"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="E23:M23"/>
-    <mergeCell ref="E24:M24"/>
-    <mergeCell ref="E25:M25"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="E20:M20"/>
-    <mergeCell ref="E21:M21"/>
-    <mergeCell ref="E22:M22"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="E17:M17"/>
-    <mergeCell ref="E18:M18"/>
-    <mergeCell ref="E19:M19"/>
-    <mergeCell ref="H50:J50"/>
-    <mergeCell ref="B51:C51"/>
-    <mergeCell ref="D51:E51"/>
-    <mergeCell ref="F51:G51"/>
-    <mergeCell ref="H51:J51"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="C13:F13"/>
-    <mergeCell ref="G13:I13"/>
-    <mergeCell ref="A14:A22"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="C11:H11"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="B50:C50"/>
-    <mergeCell ref="D50:E50"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="D61:E61"/>
-    <mergeCell ref="F61:G61"/>
-    <mergeCell ref="H61:J61"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="D62:E62"/>
-    <mergeCell ref="F62:G62"/>
-    <mergeCell ref="H62:J62"/>
-    <mergeCell ref="B58:C59"/>
-    <mergeCell ref="D58:G58"/>
-    <mergeCell ref="H58:J59"/>
-    <mergeCell ref="D59:E59"/>
-    <mergeCell ref="F59:G59"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="D60:E60"/>
-    <mergeCell ref="F60:G60"/>
-    <mergeCell ref="H60:J60"/>
-    <mergeCell ref="B57:J57"/>
-    <mergeCell ref="D52:E52"/>
-    <mergeCell ref="F52:G52"/>
-    <mergeCell ref="H52:J52"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="B47:C48"/>
-    <mergeCell ref="D47:G47"/>
-    <mergeCell ref="H47:J48"/>
-    <mergeCell ref="D48:E48"/>
-    <mergeCell ref="F48:G48"/>
-    <mergeCell ref="B49:C49"/>
-    <mergeCell ref="D49:E49"/>
-    <mergeCell ref="H49:J49"/>
-    <mergeCell ref="B41:J41"/>
-    <mergeCell ref="B46:J46"/>
-    <mergeCell ref="B42:J42"/>
-    <mergeCell ref="F49:G49"/>
-    <mergeCell ref="E43:F43"/>
-    <mergeCell ref="G43:H43"/>
-    <mergeCell ref="D71:J71"/>
-    <mergeCell ref="B72:C72"/>
-    <mergeCell ref="D72:J72"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="H54:J54"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="D55:E55"/>
-    <mergeCell ref="F55:G55"/>
-    <mergeCell ref="H55:J55"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="D56:E56"/>
-    <mergeCell ref="F56:G56"/>
-    <mergeCell ref="H56:J56"/>
-    <mergeCell ref="B63:C63"/>
-    <mergeCell ref="D63:E63"/>
-    <mergeCell ref="F63:G63"/>
-    <mergeCell ref="H63:J63"/>
-    <mergeCell ref="D53:E53"/>
-    <mergeCell ref="F53:G53"/>
-    <mergeCell ref="H53:J53"/>
-    <mergeCell ref="B54:C54"/>
-    <mergeCell ref="D54:E54"/>
-    <mergeCell ref="F54:G54"/>
-    <mergeCell ref="B1:K1"/>
-    <mergeCell ref="B2:K2"/>
-    <mergeCell ref="B3:K3"/>
-    <mergeCell ref="B4:K4"/>
-    <mergeCell ref="B5:K5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="E6:G6"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="B86:J86"/>
-    <mergeCell ref="B74:J74"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="D75:J75"/>
-    <mergeCell ref="B76:C76"/>
-    <mergeCell ref="D76:J76"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="D64:E64"/>
-    <mergeCell ref="F64:G64"/>
-    <mergeCell ref="H64:J64"/>
-    <mergeCell ref="B66:J66"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="B68:C68"/>
-    <mergeCell ref="D67:J67"/>
-    <mergeCell ref="D68:J68"/>
-    <mergeCell ref="B71:C71"/>
   </mergeCells>
   <conditionalFormatting sqref="A84:D84 K84:M84">
-    <cfRule type="containsBlanks" dxfId="9" priority="14" stopIfTrue="1">
+    <cfRule type="containsBlanks" dxfId="19" priority="14" stopIfTrue="1">
       <formula>LEN(TRIM(A84))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A84:D84">
-    <cfRule type="containsBlanks" dxfId="8" priority="9">
+    <cfRule type="containsBlanks" dxfId="18" priority="9">
       <formula>LEN(TRIM(A84))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B86:J86">
-    <cfRule type="containsBlanks" dxfId="7" priority="1">
+    <cfRule type="containsBlanks" dxfId="17" priority="1">
       <formula>LEN(TRIM(B86))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D43:D44">
-    <cfRule type="containsBlanks" dxfId="6" priority="5">
+    <cfRule type="containsBlanks" dxfId="16" priority="5">
       <formula>LEN(TRIM(D43))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D49:J56 D60:J64">
-    <cfRule type="containsBlanks" dxfId="5" priority="3">
+  <conditionalFormatting sqref="D60:J64 D49:J56">
+    <cfRule type="containsBlanks" dxfId="15" priority="3">
       <formula>LEN(TRIM(D49))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D67:J68">
-    <cfRule type="containsBlanks" dxfId="4" priority="2">
+    <cfRule type="containsBlanks" dxfId="14" priority="2">
       <formula>LEN(TRIM(D67))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G43:H43 J43">
-    <cfRule type="containsBlanks" dxfId="3" priority="4">
+    <cfRule type="containsBlanks" dxfId="13" priority="4">
       <formula>LEN(TRIM(G43))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I10:M10 C11:H11 K11:M11 J13:M13 E14:M22 E26:M37 D75:J76 A84:D84 K84:M84">
-    <cfRule type="containsBlanks" dxfId="2" priority="6">
+  <conditionalFormatting sqref="I10:M10 C11:H11 K11:M11 J13:M13 E14:M22 E26:M34 D75:J76 A84:D84 K84:M84">
+    <cfRule type="containsBlanks" dxfId="12" priority="6">
       <formula>LEN(TRIM(A10))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I10:M10 C11:H11 K11:M11 J13:M13 E14:M22 E26:M37">
-    <cfRule type="containsBlanks" dxfId="1" priority="13" stopIfTrue="1">
+  <conditionalFormatting sqref="I10:M10 C11:H11 K11:M11 J13:M13 E14:M22 E26:M34">
+    <cfRule type="containsBlanks" dxfId="11" priority="13" stopIfTrue="1">
       <formula>LEN(TRIM(C10))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K84:M84">
-    <cfRule type="containsBlanks" dxfId="0" priority="8">
+    <cfRule type="containsBlanks" dxfId="10" priority="8">
       <formula>LEN(TRIM(K84))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations xWindow="756" yWindow="874" count="48">
+  <dataValidations xWindow="756" yWindow="874" count="50">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Indicar el nivel formativo en el cual se encuentra el aprendiz. Técnio o Tecnólogo" sqref="I10:M10" xr:uid="{FDFD4240-B4E4-40FA-8880-3E4E045C5084}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Registrar el nombre del programa" prompt="Registrar el nombre del programa" sqref="C11:H11" xr:uid="{34EF5BAD-650F-4FA7-AB25-B4A5694BB4C0}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Número Ficha" prompt="Registre el número de ficha en el que se encuentra matriculado según el programa de formación." sqref="K11:M11" xr:uid="{C295E52F-E427-4103-89DB-18FF195E95C6}"/>
@@ -3721,7 +3715,9 @@
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Ingresar el Link de la Grabacion del teams" sqref="H44:J44" xr:uid="{F2C9EF6C-D3FF-4587-A8E6-606880F942C2}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Virtual o Presencial?" sqref="D44" xr:uid="{5D446980-EFCB-4F87-AF79-7C40D04D4175}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Bogotá dd/mm/aaaa Virtual" prompt="Diligenciar fecha de la visita en este espacio. Ejemplo: Bogotá dia/mes/año Virtual" sqref="B86:J86" xr:uid="{DB281D4A-1D51-4243-9BC5-E0F3B032B581}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Diligenciar si hay por mejorar" prompt="Si hay factores por mejorar favor escribir las observaciones o los compromisos de mejora" sqref="H60:J64 H49:J56" xr:uid="{77BDF12C-BD40-4BBD-8AD2-2B5F2F7C6B93}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Diligenciar si hay por mejorar" prompt="Si hay factores por mejorar favor escribir las observaciones o los compromisos de mejora" sqref="H61:J64" xr:uid="{77BDF12C-BD40-4BBD-8AD2-2B5F2F7C6B93}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="SIEMPRE DEBE HABER OBSERVACIONEs" prompt="SIEMPRE DEBE HABER OBSERVACIONES, COMO FUE EL PROCESO, Si hay factores por mejorar favor escribir las observaciones o los compromisos de mejora" sqref="H49:J53 H55:J56 H54:J54" xr:uid="{EECA5301-E9F4-4503-BD9A-9195E3DC2368}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="SIEMPRE DEBE HABER OBSERVACIONES" prompt="SIEMPRE DEBE HABER OBSERVACIONES, COMO FUE EL PROCESO, Si hay factores por mejorar favor escribir las observaciones o los compromisos de mejora" sqref="H60:J60" xr:uid="{32775E1C-D08B-4F67-8718-8BE41F674436}"/>
   </dataValidations>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="5" scale="68" fitToHeight="0" orientation="portrait" r:id="rId1"/>
@@ -3756,64 +3752,64 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="24" t="s">
         <v>85</v>
       </c>
-      <c r="B1" s="27" t="s">
+      <c r="B1" s="25" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="90" x14ac:dyDescent="0.25">
-      <c r="A2" s="25" t="s">
+      <c r="A2" s="23" t="s">
         <v>88</v>
       </c>
-      <c r="B2" s="29" t="s">
+      <c r="B2" s="27" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="90" x14ac:dyDescent="0.25">
-      <c r="A3" s="25" t="s">
+      <c r="A3" s="23" t="s">
         <v>87</v>
       </c>
-      <c r="B3" s="28" t="s">
+      <c r="B3" s="26" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="90" x14ac:dyDescent="0.25">
-      <c r="A4" s="25" t="s">
+      <c r="A4" s="23" t="s">
         <v>91</v>
       </c>
-      <c r="B4" s="28" t="s">
+      <c r="B4" s="26" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="75" x14ac:dyDescent="0.25">
-      <c r="A5" s="25" t="s">
+      <c r="A5" s="23" t="s">
         <v>89</v>
       </c>
-      <c r="B5" s="28" t="s">
+      <c r="B5" s="26" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="75" x14ac:dyDescent="0.25">
-      <c r="A6" s="25" t="s">
+      <c r="A6" s="23" t="s">
         <v>90</v>
       </c>
-      <c r="B6" s="28" t="s">
+      <c r="B6" s="26" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="25"/>
+      <c r="A7" s="23"/>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="25"/>
+      <c r="A8" s="23"/>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="25"/>
+      <c r="A9" s="23"/>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="25"/>
+      <c r="A10" s="23"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Formatos/Visita 3 GFPI-F023.xlsx
+++ b/Formatos/Visita 3 GFPI-F023.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uniminuto0-my.sharepoint.com/personal/sergio_torres_mar_uniminuto_edu_co/Documents/Documentos/Seto 2026/SETO/sena/Manual SENA Etapa Productiva/manual-aprendiz-sena/Formatos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="30" documentId="13_ncr:1_{B8726567-7195-433A-A879-F216B9BE4E06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1EDF43B8-555A-4801-88B2-2B3F8EF29CE4}"/>
+  <xr:revisionPtr revIDLastSave="53" documentId="13_ncr:1_{B8726567-7195-433A-A879-F216B9BE4E06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EF8A4525-65DF-44E6-AEA5-D4D60DBCA02F}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-105" windowWidth="29040" windowHeight="15720" xr2:uid="{BC3553EE-4E49-4F2A-B03E-CFAC4EB3009B}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="101">
   <si>
     <t>Información general</t>
   </si>
@@ -401,12 +401,15 @@
   <si>
     <t>Juicio de evaluación de la etapa productiva (seleccione):</t>
   </si>
+  <si>
+    <t>x</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="23" x14ac:knownFonts="1">
+  <fonts count="24" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -569,6 +572,14 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="28"/>
+      <color theme="1"/>
+      <name val="Bradley Hand ITC"/>
+      <family val="4"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -945,7 +956,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="167">
+  <cellXfs count="168">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
@@ -1036,9 +1047,370 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="15" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="15" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="15" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1054,15 +1426,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
@@ -1131,439 +1494,20 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="15" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="15" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="15" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="15" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="15" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="20">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFEEEC9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFE4EE5C"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="10">
     <dxf>
       <fill>
         <patternFill>
@@ -1973,7 +1917,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:XFD88"/>
+  <dimension ref="A1:XFC88"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="15" zeroHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.5703125" customWidth="1"/>
@@ -1991,1084 +1935,1084 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B1" s="147" t="s">
+      <c r="B1" s="31" t="s">
         <v>77</v>
       </c>
-      <c r="C1" s="148"/>
-      <c r="D1" s="148"/>
-      <c r="E1" s="148"/>
-      <c r="F1" s="148"/>
-      <c r="G1" s="148"/>
-      <c r="H1" s="148"/>
-      <c r="I1" s="148"/>
-      <c r="J1" s="148"/>
-      <c r="K1" s="149"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="32"/>
+      <c r="I1" s="32"/>
+      <c r="J1" s="32"/>
+      <c r="K1" s="33"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B2" s="150" t="s">
+      <c r="B2" s="34" t="s">
         <v>78</v>
       </c>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="29"/>
-      <c r="F2" s="29"/>
-      <c r="G2" s="29"/>
-      <c r="H2" s="29"/>
-      <c r="I2" s="29"/>
-      <c r="J2" s="29"/>
-      <c r="K2" s="151"/>
+      <c r="C2" s="35"/>
+      <c r="D2" s="35"/>
+      <c r="E2" s="35"/>
+      <c r="F2" s="35"/>
+      <c r="G2" s="35"/>
+      <c r="H2" s="35"/>
+      <c r="I2" s="35"/>
+      <c r="J2" s="35"/>
+      <c r="K2" s="36"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B3" s="152" t="s">
+      <c r="B3" s="37" t="s">
         <v>79</v>
       </c>
-      <c r="C3" s="153"/>
-      <c r="D3" s="153"/>
-      <c r="E3" s="153"/>
-      <c r="F3" s="153"/>
-      <c r="G3" s="153"/>
-      <c r="H3" s="153"/>
-      <c r="I3" s="153"/>
-      <c r="J3" s="153"/>
-      <c r="K3" s="154"/>
+      <c r="C3" s="38"/>
+      <c r="D3" s="38"/>
+      <c r="E3" s="38"/>
+      <c r="F3" s="38"/>
+      <c r="G3" s="38"/>
+      <c r="H3" s="38"/>
+      <c r="I3" s="38"/>
+      <c r="J3" s="38"/>
+      <c r="K3" s="39"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B4" s="150" t="s">
+      <c r="B4" s="34" t="s">
         <v>80</v>
       </c>
-      <c r="C4" s="29"/>
-      <c r="D4" s="29"/>
-      <c r="E4" s="29"/>
-      <c r="F4" s="29"/>
-      <c r="G4" s="29"/>
-      <c r="H4" s="29"/>
-      <c r="I4" s="29"/>
-      <c r="J4" s="29"/>
-      <c r="K4" s="151"/>
+      <c r="C4" s="35"/>
+      <c r="D4" s="35"/>
+      <c r="E4" s="35"/>
+      <c r="F4" s="35"/>
+      <c r="G4" s="35"/>
+      <c r="H4" s="35"/>
+      <c r="I4" s="35"/>
+      <c r="J4" s="35"/>
+      <c r="K4" s="36"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B5" s="152" t="s">
+      <c r="B5" s="37" t="s">
         <v>81</v>
       </c>
-      <c r="C5" s="153"/>
-      <c r="D5" s="153"/>
-      <c r="E5" s="153"/>
-      <c r="F5" s="153"/>
-      <c r="G5" s="153"/>
-      <c r="H5" s="153"/>
-      <c r="I5" s="153"/>
-      <c r="J5" s="153"/>
-      <c r="K5" s="154"/>
+      <c r="C5" s="38"/>
+      <c r="D5" s="38"/>
+      <c r="E5" s="38"/>
+      <c r="F5" s="38"/>
+      <c r="G5" s="38"/>
+      <c r="H5" s="38"/>
+      <c r="I5" s="38"/>
+      <c r="J5" s="38"/>
+      <c r="K5" s="39"/>
     </row>
     <row r="6" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="155" t="s">
+      <c r="B6" s="40" t="s">
         <v>82</v>
       </c>
-      <c r="C6" s="156"/>
-      <c r="D6" s="159"/>
-      <c r="E6" s="157" t="s">
+      <c r="C6" s="41"/>
+      <c r="D6" s="29"/>
+      <c r="E6" s="42" t="s">
         <v>83</v>
       </c>
-      <c r="F6" s="156"/>
-      <c r="G6" s="156"/>
-      <c r="H6" s="159"/>
-      <c r="I6" s="157" t="s">
+      <c r="F6" s="41"/>
+      <c r="G6" s="41"/>
+      <c r="H6" s="29"/>
+      <c r="I6" s="42" t="s">
         <v>84</v>
       </c>
-      <c r="J6" s="156"/>
-      <c r="K6" s="160"/>
+      <c r="J6" s="41"/>
+      <c r="K6" s="30"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25"/>
     <row r="8" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="68" t="s">
+      <c r="A8" s="124" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="69"/>
-      <c r="C8" s="69"/>
-      <c r="D8" s="69"/>
-      <c r="E8" s="69"/>
-      <c r="F8" s="69"/>
-      <c r="G8" s="69"/>
-      <c r="H8" s="69"/>
-      <c r="I8" s="69"/>
-      <c r="J8" s="69"/>
-      <c r="K8" s="69"/>
-      <c r="L8" s="69"/>
-      <c r="M8" s="69"/>
+      <c r="B8" s="125"/>
+      <c r="C8" s="125"/>
+      <c r="D8" s="125"/>
+      <c r="E8" s="125"/>
+      <c r="F8" s="125"/>
+      <c r="G8" s="125"/>
+      <c r="H8" s="125"/>
+      <c r="I8" s="125"/>
+      <c r="J8" s="125"/>
+      <c r="K8" s="125"/>
+      <c r="L8" s="125"/>
+      <c r="M8" s="125"/>
     </row>
     <row r="9" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="57" t="s">
+      <c r="A9" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="B9" s="59"/>
-      <c r="C9" s="65" t="s">
+      <c r="B9" s="48"/>
+      <c r="C9" s="111" t="s">
         <v>2</v>
       </c>
-      <c r="D9" s="66"/>
-      <c r="E9" s="66"/>
-      <c r="F9" s="66"/>
-      <c r="G9" s="66"/>
-      <c r="H9" s="66"/>
-      <c r="I9" s="66"/>
-      <c r="J9" s="66"/>
-      <c r="K9" s="66"/>
-      <c r="L9" s="66"/>
-      <c r="M9" s="67"/>
+      <c r="D9" s="123"/>
+      <c r="E9" s="123"/>
+      <c r="F9" s="123"/>
+      <c r="G9" s="123"/>
+      <c r="H9" s="123"/>
+      <c r="I9" s="123"/>
+      <c r="J9" s="123"/>
+      <c r="K9" s="123"/>
+      <c r="L9" s="123"/>
+      <c r="M9" s="112"/>
     </row>
     <row r="10" spans="1:13" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="57" t="s">
+      <c r="A10" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="B10" s="59"/>
-      <c r="C10" s="98" t="s">
+      <c r="B10" s="48"/>
+      <c r="C10" s="95" t="s">
         <v>4</v>
       </c>
-      <c r="D10" s="99"/>
-      <c r="E10" s="99"/>
-      <c r="F10" s="99"/>
-      <c r="G10" s="100"/>
+      <c r="D10" s="96"/>
+      <c r="E10" s="96"/>
+      <c r="F10" s="96"/>
+      <c r="G10" s="97"/>
       <c r="H10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="I10" s="31"/>
-      <c r="J10" s="32"/>
-      <c r="K10" s="32"/>
-      <c r="L10" s="32"/>
-      <c r="M10" s="33"/>
+      <c r="I10" s="142"/>
+      <c r="J10" s="143"/>
+      <c r="K10" s="143"/>
+      <c r="L10" s="143"/>
+      <c r="M10" s="144"/>
     </row>
     <row r="11" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="57" t="s">
+      <c r="A11" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="B11" s="59"/>
+      <c r="B11" s="48"/>
       <c r="C11" s="108"/>
       <c r="D11" s="109"/>
       <c r="E11" s="109"/>
       <c r="F11" s="109"/>
       <c r="G11" s="109"/>
       <c r="H11" s="110"/>
-      <c r="I11" s="111" t="s">
+      <c r="I11" s="67" t="s">
         <v>7</v>
       </c>
-      <c r="J11" s="112"/>
-      <c r="K11" s="73"/>
-      <c r="L11" s="74"/>
-      <c r="M11" s="75"/>
+      <c r="J11" s="68"/>
+      <c r="K11" s="126"/>
+      <c r="L11" s="127"/>
+      <c r="M11" s="128"/>
     </row>
     <row r="12" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="57" t="s">
+      <c r="A12" s="47" t="s">
         <v>8</v>
       </c>
-      <c r="B12" s="59"/>
+      <c r="B12" s="48"/>
       <c r="C12" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D12" s="65" t="s">
+      <c r="D12" s="111" t="s">
         <v>10</v>
       </c>
-      <c r="E12" s="67"/>
-      <c r="F12" s="113" t="s">
+      <c r="E12" s="112"/>
+      <c r="F12" s="69" t="s">
         <v>11</v>
       </c>
-      <c r="G12" s="114"/>
+      <c r="G12" s="71"/>
       <c r="H12" s="1"/>
-      <c r="I12" s="113" t="s">
+      <c r="I12" s="69" t="s">
         <v>12</v>
       </c>
-      <c r="J12" s="114"/>
-      <c r="K12" s="76"/>
-      <c r="L12" s="77"/>
-      <c r="M12" s="78"/>
+      <c r="J12" s="71"/>
+      <c r="K12" s="129"/>
+      <c r="L12" s="130"/>
+      <c r="M12" s="131"/>
     </row>
     <row r="13" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="57" t="s">
+      <c r="A13" s="47" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="59"/>
-      <c r="C13" s="101"/>
-      <c r="D13" s="102"/>
-      <c r="E13" s="102"/>
-      <c r="F13" s="103"/>
-      <c r="G13" s="101" t="s">
+      <c r="B13" s="48"/>
+      <c r="C13" s="98"/>
+      <c r="D13" s="99"/>
+      <c r="E13" s="99"/>
+      <c r="F13" s="100"/>
+      <c r="G13" s="98" t="s">
         <v>14</v>
       </c>
-      <c r="H13" s="102"/>
-      <c r="I13" s="103"/>
-      <c r="J13" s="79"/>
-      <c r="K13" s="80"/>
-      <c r="L13" s="80"/>
-      <c r="M13" s="81"/>
+      <c r="H13" s="99"/>
+      <c r="I13" s="100"/>
+      <c r="J13" s="132"/>
+      <c r="K13" s="133"/>
+      <c r="L13" s="133"/>
+      <c r="M13" s="134"/>
     </row>
     <row r="14" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="104" t="s">
+      <c r="A14" s="101" t="s">
         <v>15</v>
       </c>
-      <c r="B14" s="57" t="s">
+      <c r="B14" s="47" t="s">
         <v>16</v>
       </c>
-      <c r="C14" s="58"/>
-      <c r="D14" s="59"/>
-      <c r="E14" s="70"/>
-      <c r="F14" s="71"/>
-      <c r="G14" s="71"/>
-      <c r="H14" s="71"/>
-      <c r="I14" s="71"/>
-      <c r="J14" s="71"/>
-      <c r="K14" s="71"/>
-      <c r="L14" s="71"/>
-      <c r="M14" s="72"/>
+      <c r="C14" s="104"/>
+      <c r="D14" s="48"/>
+      <c r="E14" s="116"/>
+      <c r="F14" s="117"/>
+      <c r="G14" s="117"/>
+      <c r="H14" s="117"/>
+      <c r="I14" s="117"/>
+      <c r="J14" s="117"/>
+      <c r="K14" s="117"/>
+      <c r="L14" s="117"/>
+      <c r="M14" s="118"/>
     </row>
     <row r="15" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="89"/>
+      <c r="A15" s="102"/>
       <c r="B15" s="105" t="s">
         <v>17</v>
       </c>
       <c r="C15" s="106"/>
       <c r="D15" s="107"/>
-      <c r="E15" s="82"/>
-      <c r="F15" s="83"/>
-      <c r="G15" s="83"/>
-      <c r="H15" s="83"/>
-      <c r="I15" s="83"/>
-      <c r="J15" s="83"/>
-      <c r="K15" s="83"/>
-      <c r="L15" s="83"/>
-      <c r="M15" s="84"/>
+      <c r="E15" s="135"/>
+      <c r="F15" s="136"/>
+      <c r="G15" s="136"/>
+      <c r="H15" s="136"/>
+      <c r="I15" s="136"/>
+      <c r="J15" s="136"/>
+      <c r="K15" s="136"/>
+      <c r="L15" s="136"/>
+      <c r="M15" s="137"/>
     </row>
     <row r="16" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="89"/>
-      <c r="B16" s="57" t="s">
+      <c r="A16" s="102"/>
+      <c r="B16" s="47" t="s">
         <v>18</v>
       </c>
-      <c r="C16" s="58"/>
-      <c r="D16" s="59"/>
-      <c r="E16" s="70"/>
-      <c r="F16" s="71"/>
-      <c r="G16" s="71"/>
-      <c r="H16" s="71"/>
-      <c r="I16" s="71"/>
-      <c r="J16" s="71"/>
-      <c r="K16" s="71"/>
-      <c r="L16" s="71"/>
-      <c r="M16" s="72"/>
+      <c r="C16" s="104"/>
+      <c r="D16" s="48"/>
+      <c r="E16" s="116"/>
+      <c r="F16" s="117"/>
+      <c r="G16" s="117"/>
+      <c r="H16" s="117"/>
+      <c r="I16" s="117"/>
+      <c r="J16" s="117"/>
+      <c r="K16" s="117"/>
+      <c r="L16" s="117"/>
+      <c r="M16" s="118"/>
     </row>
     <row r="17" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="89"/>
-      <c r="B17" s="57" t="s">
+      <c r="A17" s="102"/>
+      <c r="B17" s="47" t="s">
         <v>19</v>
       </c>
-      <c r="C17" s="58"/>
-      <c r="D17" s="59"/>
-      <c r="E17" s="70"/>
-      <c r="F17" s="71"/>
-      <c r="G17" s="71"/>
-      <c r="H17" s="71"/>
-      <c r="I17" s="71"/>
-      <c r="J17" s="71"/>
-      <c r="K17" s="71"/>
-      <c r="L17" s="71"/>
-      <c r="M17" s="72"/>
+      <c r="C17" s="104"/>
+      <c r="D17" s="48"/>
+      <c r="E17" s="116"/>
+      <c r="F17" s="117"/>
+      <c r="G17" s="117"/>
+      <c r="H17" s="117"/>
+      <c r="I17" s="117"/>
+      <c r="J17" s="117"/>
+      <c r="K17" s="117"/>
+      <c r="L17" s="117"/>
+      <c r="M17" s="118"/>
     </row>
     <row r="18" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="89"/>
-      <c r="B18" s="57" t="s">
+      <c r="A18" s="102"/>
+      <c r="B18" s="47" t="s">
         <v>20</v>
       </c>
-      <c r="C18" s="58"/>
-      <c r="D18" s="59"/>
-      <c r="E18" s="70"/>
-      <c r="F18" s="71"/>
-      <c r="G18" s="71"/>
-      <c r="H18" s="71"/>
-      <c r="I18" s="71"/>
-      <c r="J18" s="71"/>
-      <c r="K18" s="71"/>
-      <c r="L18" s="71"/>
-      <c r="M18" s="72"/>
+      <c r="C18" s="104"/>
+      <c r="D18" s="48"/>
+      <c r="E18" s="116"/>
+      <c r="F18" s="117"/>
+      <c r="G18" s="117"/>
+      <c r="H18" s="117"/>
+      <c r="I18" s="117"/>
+      <c r="J18" s="117"/>
+      <c r="K18" s="117"/>
+      <c r="L18" s="117"/>
+      <c r="M18" s="118"/>
     </row>
     <row r="19" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="89"/>
-      <c r="B19" s="57" t="s">
+      <c r="A19" s="102"/>
+      <c r="B19" s="47" t="s">
         <v>21</v>
       </c>
-      <c r="C19" s="58"/>
-      <c r="D19" s="59"/>
-      <c r="E19" s="70"/>
-      <c r="F19" s="71"/>
-      <c r="G19" s="71"/>
-      <c r="H19" s="71"/>
-      <c r="I19" s="71"/>
-      <c r="J19" s="71"/>
-      <c r="K19" s="71"/>
-      <c r="L19" s="71"/>
-      <c r="M19" s="72"/>
+      <c r="C19" s="104"/>
+      <c r="D19" s="48"/>
+      <c r="E19" s="116"/>
+      <c r="F19" s="117"/>
+      <c r="G19" s="117"/>
+      <c r="H19" s="117"/>
+      <c r="I19" s="117"/>
+      <c r="J19" s="117"/>
+      <c r="K19" s="117"/>
+      <c r="L19" s="117"/>
+      <c r="M19" s="118"/>
     </row>
     <row r="20" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="89"/>
-      <c r="B20" s="57" t="s">
+      <c r="A20" s="102"/>
+      <c r="B20" s="47" t="s">
         <v>22</v>
       </c>
-      <c r="C20" s="58"/>
-      <c r="D20" s="59"/>
-      <c r="E20" s="60"/>
-      <c r="F20" s="61"/>
-      <c r="G20" s="61"/>
-      <c r="H20" s="61"/>
-      <c r="I20" s="61"/>
-      <c r="J20" s="61"/>
-      <c r="K20" s="61"/>
-      <c r="L20" s="61"/>
-      <c r="M20" s="62"/>
+      <c r="C20" s="104"/>
+      <c r="D20" s="48"/>
+      <c r="E20" s="113"/>
+      <c r="F20" s="114"/>
+      <c r="G20" s="114"/>
+      <c r="H20" s="114"/>
+      <c r="I20" s="114"/>
+      <c r="J20" s="114"/>
+      <c r="K20" s="114"/>
+      <c r="L20" s="114"/>
+      <c r="M20" s="115"/>
     </row>
     <row r="21" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="89"/>
-      <c r="B21" s="57" t="s">
+      <c r="A21" s="102"/>
+      <c r="B21" s="47" t="s">
         <v>23</v>
       </c>
-      <c r="C21" s="58"/>
-      <c r="D21" s="59"/>
-      <c r="E21" s="60"/>
-      <c r="F21" s="61"/>
-      <c r="G21" s="61"/>
-      <c r="H21" s="61"/>
-      <c r="I21" s="61"/>
-      <c r="J21" s="61"/>
-      <c r="K21" s="61"/>
-      <c r="L21" s="61"/>
-      <c r="M21" s="62"/>
+      <c r="C21" s="104"/>
+      <c r="D21" s="48"/>
+      <c r="E21" s="113"/>
+      <c r="F21" s="114"/>
+      <c r="G21" s="114"/>
+      <c r="H21" s="114"/>
+      <c r="I21" s="114"/>
+      <c r="J21" s="114"/>
+      <c r="K21" s="114"/>
+      <c r="L21" s="114"/>
+      <c r="M21" s="115"/>
     </row>
     <row r="22" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="90"/>
-      <c r="B22" s="57" t="s">
+      <c r="A22" s="103"/>
+      <c r="B22" s="47" t="s">
         <v>24</v>
       </c>
-      <c r="C22" s="58"/>
-      <c r="D22" s="59"/>
-      <c r="E22" s="60"/>
-      <c r="F22" s="61"/>
-      <c r="G22" s="61"/>
-      <c r="H22" s="61"/>
-      <c r="I22" s="61"/>
-      <c r="J22" s="61"/>
-      <c r="K22" s="61"/>
-      <c r="L22" s="61"/>
-      <c r="M22" s="62"/>
+      <c r="C22" s="104"/>
+      <c r="D22" s="48"/>
+      <c r="E22" s="113"/>
+      <c r="F22" s="114"/>
+      <c r="G22" s="114"/>
+      <c r="H22" s="114"/>
+      <c r="I22" s="114"/>
+      <c r="J22" s="114"/>
+      <c r="K22" s="114"/>
+      <c r="L22" s="114"/>
+      <c r="M22" s="115"/>
     </row>
     <row r="23" spans="1:13" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="88" t="s">
+      <c r="A23" s="119" t="s">
         <v>25</v>
       </c>
-      <c r="B23" s="57" t="s">
+      <c r="B23" s="47" t="s">
         <v>26</v>
       </c>
-      <c r="C23" s="58"/>
-      <c r="D23" s="59"/>
-      <c r="E23" s="91" t="s">
+      <c r="C23" s="104"/>
+      <c r="D23" s="48"/>
+      <c r="E23" s="120" t="s">
         <v>27</v>
       </c>
-      <c r="F23" s="92"/>
-      <c r="G23" s="92"/>
-      <c r="H23" s="92"/>
-      <c r="I23" s="92"/>
-      <c r="J23" s="92"/>
-      <c r="K23" s="92"/>
-      <c r="L23" s="92"/>
-      <c r="M23" s="93"/>
+      <c r="F23" s="121"/>
+      <c r="G23" s="121"/>
+      <c r="H23" s="121"/>
+      <c r="I23" s="121"/>
+      <c r="J23" s="121"/>
+      <c r="K23" s="121"/>
+      <c r="L23" s="121"/>
+      <c r="M23" s="122"/>
     </row>
     <row r="24" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="89"/>
-      <c r="B24" s="57" t="s">
+      <c r="A24" s="102"/>
+      <c r="B24" s="47" t="s">
         <v>19</v>
       </c>
-      <c r="C24" s="58"/>
-      <c r="D24" s="59"/>
-      <c r="E24" s="34"/>
-      <c r="F24" s="35"/>
-      <c r="G24" s="35"/>
-      <c r="H24" s="35"/>
-      <c r="I24" s="35"/>
-      <c r="J24" s="35"/>
-      <c r="K24" s="35"/>
-      <c r="L24" s="35"/>
-      <c r="M24" s="36"/>
+      <c r="C24" s="104"/>
+      <c r="D24" s="48"/>
+      <c r="E24" s="44"/>
+      <c r="F24" s="45"/>
+      <c r="G24" s="45"/>
+      <c r="H24" s="45"/>
+      <c r="I24" s="45"/>
+      <c r="J24" s="45"/>
+      <c r="K24" s="45"/>
+      <c r="L24" s="45"/>
+      <c r="M24" s="46"/>
     </row>
     <row r="25" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="90"/>
-      <c r="B25" s="57" t="s">
+      <c r="A25" s="103"/>
+      <c r="B25" s="47" t="s">
         <v>22</v>
       </c>
-      <c r="C25" s="58"/>
-      <c r="D25" s="59"/>
-      <c r="E25" s="91" t="s">
+      <c r="C25" s="104"/>
+      <c r="D25" s="48"/>
+      <c r="E25" s="120" t="s">
         <v>28</v>
       </c>
-      <c r="F25" s="92"/>
-      <c r="G25" s="92"/>
-      <c r="H25" s="92"/>
-      <c r="I25" s="92"/>
-      <c r="J25" s="92"/>
-      <c r="K25" s="92"/>
-      <c r="L25" s="92"/>
-      <c r="M25" s="93"/>
+      <c r="F25" s="121"/>
+      <c r="G25" s="121"/>
+      <c r="H25" s="121"/>
+      <c r="I25" s="121"/>
+      <c r="J25" s="121"/>
+      <c r="K25" s="121"/>
+      <c r="L25" s="121"/>
+      <c r="M25" s="122"/>
     </row>
     <row r="26" spans="1:13" ht="25.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B26" s="57" t="s">
+      <c r="B26" s="47" t="s">
         <v>32</v>
       </c>
-      <c r="C26" s="58"/>
-      <c r="D26" s="59"/>
-      <c r="E26" s="70"/>
-      <c r="F26" s="71"/>
-      <c r="G26" s="71"/>
-      <c r="H26" s="71"/>
-      <c r="I26" s="71"/>
-      <c r="J26" s="71"/>
-      <c r="K26" s="71"/>
-      <c r="L26" s="71"/>
-      <c r="M26" s="72"/>
+      <c r="C26" s="104"/>
+      <c r="D26" s="48"/>
+      <c r="E26" s="116"/>
+      <c r="F26" s="117"/>
+      <c r="G26" s="117"/>
+      <c r="H26" s="117"/>
+      <c r="I26" s="117"/>
+      <c r="J26" s="117"/>
+      <c r="K26" s="117"/>
+      <c r="L26" s="117"/>
+      <c r="M26" s="118"/>
     </row>
     <row r="27" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="B27" s="57" t="s">
+      <c r="B27" s="47" t="s">
         <v>20</v>
       </c>
-      <c r="C27" s="58"/>
-      <c r="D27" s="59"/>
-      <c r="E27" s="70"/>
-      <c r="F27" s="71"/>
-      <c r="G27" s="71"/>
-      <c r="H27" s="71"/>
-      <c r="I27" s="71"/>
-      <c r="J27" s="71"/>
-      <c r="K27" s="71"/>
-      <c r="L27" s="71"/>
-      <c r="M27" s="72"/>
+      <c r="C27" s="104"/>
+      <c r="D27" s="48"/>
+      <c r="E27" s="116"/>
+      <c r="F27" s="117"/>
+      <c r="G27" s="117"/>
+      <c r="H27" s="117"/>
+      <c r="I27" s="117"/>
+      <c r="J27" s="117"/>
+      <c r="K27" s="117"/>
+      <c r="L27" s="117"/>
+      <c r="M27" s="118"/>
     </row>
     <row r="28" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="3"/>
-      <c r="B28" s="57" t="s">
+      <c r="B28" s="47" t="s">
         <v>33</v>
       </c>
-      <c r="C28" s="58"/>
-      <c r="D28" s="59"/>
-      <c r="E28" s="70"/>
-      <c r="F28" s="71"/>
-      <c r="G28" s="71"/>
-      <c r="H28" s="71"/>
-      <c r="I28" s="71"/>
-      <c r="J28" s="71"/>
-      <c r="K28" s="71"/>
-      <c r="L28" s="71"/>
-      <c r="M28" s="72"/>
+      <c r="C28" s="104"/>
+      <c r="D28" s="48"/>
+      <c r="E28" s="116"/>
+      <c r="F28" s="117"/>
+      <c r="G28" s="117"/>
+      <c r="H28" s="117"/>
+      <c r="I28" s="117"/>
+      <c r="J28" s="117"/>
+      <c r="K28" s="117"/>
+      <c r="L28" s="117"/>
+      <c r="M28" s="118"/>
     </row>
     <row r="29" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="3"/>
-      <c r="B29" s="57" t="s">
+      <c r="B29" s="47" t="s">
         <v>34</v>
       </c>
-      <c r="C29" s="58"/>
-      <c r="D29" s="59"/>
-      <c r="E29" s="70"/>
-      <c r="F29" s="71"/>
-      <c r="G29" s="71"/>
-      <c r="H29" s="71"/>
-      <c r="I29" s="71"/>
-      <c r="J29" s="71"/>
-      <c r="K29" s="71"/>
-      <c r="L29" s="71"/>
-      <c r="M29" s="72"/>
+      <c r="C29" s="104"/>
+      <c r="D29" s="48"/>
+      <c r="E29" s="116"/>
+      <c r="F29" s="117"/>
+      <c r="G29" s="117"/>
+      <c r="H29" s="117"/>
+      <c r="I29" s="117"/>
+      <c r="J29" s="117"/>
+      <c r="K29" s="117"/>
+      <c r="L29" s="117"/>
+      <c r="M29" s="118"/>
     </row>
     <row r="30" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="B30" s="57" t="s">
+      <c r="B30" s="47" t="s">
         <v>35</v>
       </c>
-      <c r="C30" s="58"/>
-      <c r="D30" s="59"/>
-      <c r="E30" s="70"/>
-      <c r="F30" s="71"/>
-      <c r="G30" s="71"/>
-      <c r="H30" s="71"/>
-      <c r="I30" s="71"/>
-      <c r="J30" s="71"/>
-      <c r="K30" s="71"/>
-      <c r="L30" s="71"/>
-      <c r="M30" s="72"/>
+      <c r="C30" s="104"/>
+      <c r="D30" s="48"/>
+      <c r="E30" s="116"/>
+      <c r="F30" s="117"/>
+      <c r="G30" s="117"/>
+      <c r="H30" s="117"/>
+      <c r="I30" s="117"/>
+      <c r="J30" s="117"/>
+      <c r="K30" s="117"/>
+      <c r="L30" s="117"/>
+      <c r="M30" s="118"/>
     </row>
     <row r="31" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="6"/>
-      <c r="B31" s="57" t="s">
+      <c r="B31" s="47" t="s">
         <v>36</v>
       </c>
-      <c r="C31" s="58"/>
-      <c r="D31" s="59"/>
-      <c r="E31" s="70"/>
-      <c r="F31" s="71"/>
-      <c r="G31" s="71"/>
-      <c r="H31" s="71"/>
-      <c r="I31" s="71"/>
-      <c r="J31" s="71"/>
-      <c r="K31" s="71"/>
-      <c r="L31" s="71"/>
-      <c r="M31" s="72"/>
+      <c r="C31" s="104"/>
+      <c r="D31" s="48"/>
+      <c r="E31" s="116"/>
+      <c r="F31" s="117"/>
+      <c r="G31" s="117"/>
+      <c r="H31" s="117"/>
+      <c r="I31" s="117"/>
+      <c r="J31" s="117"/>
+      <c r="K31" s="117"/>
+      <c r="L31" s="117"/>
+      <c r="M31" s="118"/>
     </row>
     <row r="32" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="6"/>
-      <c r="B32" s="57" t="s">
+      <c r="B32" s="47" t="s">
         <v>19</v>
       </c>
-      <c r="C32" s="58"/>
-      <c r="D32" s="59"/>
-      <c r="E32" s="60"/>
-      <c r="F32" s="61"/>
-      <c r="G32" s="61"/>
-      <c r="H32" s="61"/>
-      <c r="I32" s="61"/>
-      <c r="J32" s="61"/>
-      <c r="K32" s="61"/>
-      <c r="L32" s="61"/>
-      <c r="M32" s="62"/>
+      <c r="C32" s="104"/>
+      <c r="D32" s="48"/>
+      <c r="E32" s="113"/>
+      <c r="F32" s="114"/>
+      <c r="G32" s="114"/>
+      <c r="H32" s="114"/>
+      <c r="I32" s="114"/>
+      <c r="J32" s="114"/>
+      <c r="K32" s="114"/>
+      <c r="L32" s="114"/>
+      <c r="M32" s="115"/>
     </row>
     <row r="33" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="6"/>
-      <c r="B33" s="57" t="s">
+      <c r="B33" s="47" t="s">
         <v>37</v>
       </c>
-      <c r="C33" s="58"/>
-      <c r="D33" s="59"/>
-      <c r="E33" s="70"/>
-      <c r="F33" s="71"/>
-      <c r="G33" s="71"/>
-      <c r="H33" s="71"/>
-      <c r="I33" s="71"/>
-      <c r="J33" s="71"/>
-      <c r="K33" s="71"/>
-      <c r="L33" s="71"/>
-      <c r="M33" s="72"/>
+      <c r="C33" s="104"/>
+      <c r="D33" s="48"/>
+      <c r="E33" s="116"/>
+      <c r="F33" s="117"/>
+      <c r="G33" s="117"/>
+      <c r="H33" s="117"/>
+      <c r="I33" s="117"/>
+      <c r="J33" s="117"/>
+      <c r="K33" s="117"/>
+      <c r="L33" s="117"/>
+      <c r="M33" s="118"/>
     </row>
     <row r="34" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="7"/>
-      <c r="B34" s="85" t="s">
+      <c r="B34" s="138" t="s">
         <v>38</v>
       </c>
-      <c r="C34" s="86"/>
-      <c r="D34" s="87"/>
-      <c r="E34" s="60"/>
-      <c r="F34" s="61"/>
-      <c r="G34" s="61"/>
-      <c r="H34" s="61"/>
-      <c r="I34" s="61"/>
-      <c r="J34" s="61"/>
-      <c r="K34" s="61"/>
-      <c r="L34" s="61"/>
-      <c r="M34" s="62"/>
+      <c r="C34" s="139"/>
+      <c r="D34" s="140"/>
+      <c r="E34" s="113"/>
+      <c r="F34" s="114"/>
+      <c r="G34" s="114"/>
+      <c r="H34" s="114"/>
+      <c r="I34" s="114"/>
+      <c r="J34" s="114"/>
+      <c r="K34" s="114"/>
+      <c r="L34" s="114"/>
+      <c r="M34" s="115"/>
     </row>
     <row r="35" spans="1:13" ht="25.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="B35" s="54" t="s">
+      <c r="B35" s="162" t="s">
         <v>41</v>
       </c>
-      <c r="C35" s="55"/>
-      <c r="D35" s="56"/>
-      <c r="E35" s="60"/>
-      <c r="F35" s="61"/>
-      <c r="G35" s="61"/>
-      <c r="H35" s="61"/>
-      <c r="I35" s="61"/>
-      <c r="J35" s="61"/>
-      <c r="K35" s="61"/>
-      <c r="L35" s="61"/>
-      <c r="M35" s="62"/>
+      <c r="C35" s="163"/>
+      <c r="D35" s="164"/>
+      <c r="E35" s="113"/>
+      <c r="F35" s="114"/>
+      <c r="G35" s="114"/>
+      <c r="H35" s="114"/>
+      <c r="I35" s="114"/>
+      <c r="J35" s="114"/>
+      <c r="K35" s="114"/>
+      <c r="L35" s="114"/>
+      <c r="M35" s="115"/>
     </row>
     <row r="36" spans="1:13" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="B36" s="57" t="s">
+      <c r="B36" s="47" t="s">
         <v>42</v>
       </c>
-      <c r="C36" s="58"/>
-      <c r="D36" s="59"/>
-      <c r="E36" s="60"/>
-      <c r="F36" s="61"/>
-      <c r="G36" s="61"/>
-      <c r="H36" s="61"/>
-      <c r="I36" s="61"/>
-      <c r="J36" s="61"/>
-      <c r="K36" s="61"/>
-      <c r="L36" s="61"/>
-      <c r="M36" s="62"/>
+      <c r="C36" s="104"/>
+      <c r="D36" s="48"/>
+      <c r="E36" s="113"/>
+      <c r="F36" s="114"/>
+      <c r="G36" s="114"/>
+      <c r="H36" s="114"/>
+      <c r="I36" s="114"/>
+      <c r="J36" s="114"/>
+      <c r="K36" s="114"/>
+      <c r="L36" s="114"/>
+      <c r="M36" s="115"/>
     </row>
     <row r="37" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="10"/>
-      <c r="B37" s="57" t="s">
+      <c r="B37" s="47" t="s">
         <v>19</v>
       </c>
-      <c r="C37" s="58"/>
-      <c r="D37" s="59"/>
-      <c r="E37" s="60"/>
-      <c r="F37" s="61"/>
-      <c r="G37" s="61"/>
-      <c r="H37" s="61"/>
-      <c r="I37" s="61"/>
-      <c r="J37" s="61"/>
-      <c r="K37" s="61"/>
-      <c r="L37" s="61"/>
-      <c r="M37" s="62"/>
+      <c r="C37" s="104"/>
+      <c r="D37" s="48"/>
+      <c r="E37" s="113"/>
+      <c r="F37" s="114"/>
+      <c r="G37" s="114"/>
+      <c r="H37" s="114"/>
+      <c r="I37" s="114"/>
+      <c r="J37" s="114"/>
+      <c r="K37" s="114"/>
+      <c r="L37" s="114"/>
+      <c r="M37" s="115"/>
     </row>
     <row r="38" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="30" t="s">
+      <c r="A38" s="141" t="s">
         <v>43</v>
       </c>
-      <c r="B38" s="30"/>
-      <c r="C38" s="30"/>
-      <c r="D38" s="30"/>
-      <c r="E38" s="30"/>
-      <c r="F38" s="30"/>
-      <c r="G38" s="30"/>
-      <c r="H38" s="30"/>
-      <c r="I38" s="30"/>
-      <c r="J38" s="30"/>
-      <c r="K38" s="30"/>
-      <c r="L38" s="30"/>
-      <c r="M38" s="30"/>
+      <c r="B38" s="141"/>
+      <c r="C38" s="141"/>
+      <c r="D38" s="141"/>
+      <c r="E38" s="141"/>
+      <c r="F38" s="141"/>
+      <c r="G38" s="141"/>
+      <c r="H38" s="141"/>
+      <c r="I38" s="141"/>
+      <c r="J38" s="141"/>
+      <c r="K38" s="141"/>
+      <c r="L38" s="141"/>
+      <c r="M38" s="141"/>
     </row>
     <row r="39" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="30"/>
-      <c r="B39" s="30"/>
-      <c r="C39" s="30"/>
-      <c r="D39" s="30"/>
-      <c r="E39" s="30"/>
-      <c r="F39" s="30"/>
-      <c r="G39" s="30"/>
-      <c r="H39" s="30"/>
-      <c r="I39" s="30"/>
-      <c r="J39" s="30"/>
-      <c r="K39" s="30"/>
-      <c r="L39" s="30"/>
-      <c r="M39" s="30"/>
+      <c r="A39" s="141"/>
+      <c r="B39" s="141"/>
+      <c r="C39" s="141"/>
+      <c r="D39" s="141"/>
+      <c r="E39" s="141"/>
+      <c r="F39" s="141"/>
+      <c r="G39" s="141"/>
+      <c r="H39" s="141"/>
+      <c r="I39" s="141"/>
+      <c r="J39" s="141"/>
+      <c r="K39" s="141"/>
+      <c r="L39" s="141"/>
+      <c r="M39" s="141"/>
     </row>
     <row r="40" spans="1:13" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="30"/>
-      <c r="B40" s="30"/>
-      <c r="C40" s="30"/>
-      <c r="D40" s="30"/>
-      <c r="E40" s="30"/>
-      <c r="F40" s="30"/>
-      <c r="G40" s="30"/>
-      <c r="H40" s="30"/>
-      <c r="I40" s="30"/>
-      <c r="J40" s="30"/>
-      <c r="K40" s="30"/>
-      <c r="L40" s="30"/>
-      <c r="M40" s="30"/>
+      <c r="A40" s="141"/>
+      <c r="B40" s="141"/>
+      <c r="C40" s="141"/>
+      <c r="D40" s="141"/>
+      <c r="E40" s="141"/>
+      <c r="F40" s="141"/>
+      <c r="G40" s="141"/>
+      <c r="H40" s="141"/>
+      <c r="I40" s="141"/>
+      <c r="J40" s="141"/>
+      <c r="K40" s="141"/>
+      <c r="L40" s="141"/>
+      <c r="M40" s="141"/>
     </row>
     <row r="41" spans="1:13" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="11"/>
-      <c r="B41" s="133" t="s">
+      <c r="B41" s="80" t="s">
         <v>65</v>
       </c>
-      <c r="C41" s="133"/>
-      <c r="D41" s="133"/>
-      <c r="E41" s="133"/>
-      <c r="F41" s="133"/>
-      <c r="G41" s="133"/>
-      <c r="H41" s="133"/>
-      <c r="I41" s="133"/>
-      <c r="J41" s="133"/>
+      <c r="C41" s="80"/>
+      <c r="D41" s="80"/>
+      <c r="E41" s="80"/>
+      <c r="F41" s="80"/>
+      <c r="G41" s="80"/>
+      <c r="H41" s="80"/>
+      <c r="I41" s="80"/>
+      <c r="J41" s="80"/>
       <c r="K41" s="11"/>
       <c r="L41" s="11"/>
       <c r="M41" s="11"/>
     </row>
     <row r="42" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B42" s="133" t="s">
+      <c r="B42" s="80" t="s">
         <v>66</v>
       </c>
-      <c r="C42" s="133"/>
-      <c r="D42" s="133"/>
-      <c r="E42" s="133"/>
-      <c r="F42" s="133"/>
-      <c r="G42" s="133"/>
-      <c r="H42" s="133"/>
-      <c r="I42" s="133"/>
-      <c r="J42" s="133"/>
+      <c r="C42" s="80"/>
+      <c r="D42" s="80"/>
+      <c r="E42" s="80"/>
+      <c r="F42" s="80"/>
+      <c r="G42" s="80"/>
+      <c r="H42" s="80"/>
+      <c r="I42" s="80"/>
+      <c r="J42" s="80"/>
       <c r="L42" s="18"/>
     </row>
     <row r="43" spans="1:13" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B43" s="44" t="s">
+      <c r="B43" s="152" t="s">
         <v>72</v>
       </c>
-      <c r="C43" s="45"/>
+      <c r="C43" s="153"/>
       <c r="D43" s="20"/>
-      <c r="E43" s="137" t="s">
+      <c r="E43" s="84" t="s">
         <v>75</v>
       </c>
-      <c r="F43" s="138"/>
-      <c r="G43" s="139"/>
-      <c r="H43" s="140"/>
+      <c r="F43" s="85"/>
+      <c r="G43" s="86"/>
+      <c r="H43" s="87"/>
       <c r="I43" s="17" t="s">
         <v>76</v>
       </c>
       <c r="J43" s="19"/>
     </row>
     <row r="44" spans="1:13" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B44" s="46" t="s">
+      <c r="B44" s="154" t="s">
         <v>73</v>
       </c>
-      <c r="C44" s="47"/>
+      <c r="C44" s="155"/>
       <c r="D44" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="E44" s="48" t="s">
+      <c r="E44" s="156" t="s">
         <v>74</v>
       </c>
-      <c r="F44" s="49"/>
-      <c r="G44" s="50"/>
-      <c r="H44" s="51"/>
-      <c r="I44" s="52"/>
-      <c r="J44" s="53"/>
+      <c r="F44" s="157"/>
+      <c r="G44" s="158"/>
+      <c r="H44" s="159"/>
+      <c r="I44" s="160"/>
+      <c r="J44" s="161"/>
     </row>
     <row r="45" spans="1:13" ht="2.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="46" spans="1:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="11"/>
-      <c r="B46" s="134" t="s">
+      <c r="B46" s="81" t="s">
         <v>45</v>
       </c>
-      <c r="C46" s="135"/>
-      <c r="D46" s="135"/>
-      <c r="E46" s="135"/>
-      <c r="F46" s="135"/>
-      <c r="G46" s="135"/>
-      <c r="H46" s="135"/>
-      <c r="I46" s="135"/>
-      <c r="J46" s="136"/>
+      <c r="C46" s="82"/>
+      <c r="D46" s="82"/>
+      <c r="E46" s="82"/>
+      <c r="F46" s="82"/>
+      <c r="G46" s="82"/>
+      <c r="H46" s="82"/>
+      <c r="I46" s="82"/>
+      <c r="J46" s="83"/>
       <c r="K46" s="11"/>
       <c r="L46" s="11"/>
       <c r="M46" s="11"/>
     </row>
     <row r="47" spans="1:13" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="11"/>
-      <c r="B47" s="128" t="s">
+      <c r="B47" s="65" t="s">
         <v>46</v>
       </c>
-      <c r="C47" s="129"/>
-      <c r="D47" s="113" t="s">
+      <c r="C47" s="66"/>
+      <c r="D47" s="69" t="s">
         <v>47</v>
       </c>
-      <c r="E47" s="130"/>
-      <c r="F47" s="130"/>
-      <c r="G47" s="114"/>
-      <c r="H47" s="115" t="s">
+      <c r="E47" s="70"/>
+      <c r="F47" s="70"/>
+      <c r="G47" s="71"/>
+      <c r="H47" s="72" t="s">
         <v>48</v>
       </c>
-      <c r="I47" s="119"/>
-      <c r="J47" s="116"/>
+      <c r="I47" s="73"/>
+      <c r="J47" s="74"/>
       <c r="K47" s="11"/>
       <c r="L47" s="11"/>
       <c r="M47" s="11"/>
     </row>
     <row r="48" spans="1:13" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="11"/>
-      <c r="B48" s="111"/>
-      <c r="C48" s="112"/>
-      <c r="D48" s="131" t="s">
+      <c r="B48" s="67"/>
+      <c r="C48" s="68"/>
+      <c r="D48" s="78" t="s">
         <v>49</v>
       </c>
-      <c r="E48" s="132"/>
-      <c r="F48" s="131" t="s">
+      <c r="E48" s="79"/>
+      <c r="F48" s="78" t="s">
         <v>50</v>
       </c>
-      <c r="G48" s="132"/>
-      <c r="H48" s="117"/>
-      <c r="I48" s="120"/>
-      <c r="J48" s="118"/>
+      <c r="G48" s="79"/>
+      <c r="H48" s="75"/>
+      <c r="I48" s="76"/>
+      <c r="J48" s="77"/>
       <c r="K48" s="11"/>
       <c r="L48" s="11"/>
       <c r="M48" s="11"/>
     </row>
     <row r="49" spans="1:13" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="13"/>
-      <c r="B49" s="94" t="s">
+      <c r="B49" s="52" t="s">
         <v>51</v>
       </c>
-      <c r="C49" s="95"/>
-      <c r="D49" s="96"/>
-      <c r="E49" s="97"/>
-      <c r="F49" s="96"/>
-      <c r="G49" s="97"/>
-      <c r="H49" s="161"/>
-      <c r="I49" s="162"/>
-      <c r="J49" s="163"/>
+      <c r="C49" s="53"/>
+      <c r="D49" s="54"/>
+      <c r="E49" s="55"/>
+      <c r="F49" s="54"/>
+      <c r="G49" s="55"/>
+      <c r="H49" s="56"/>
+      <c r="I49" s="57"/>
+      <c r="J49" s="58"/>
       <c r="K49" s="13"/>
       <c r="L49" s="13"/>
       <c r="M49" s="13"/>
     </row>
     <row r="50" spans="1:13" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="13"/>
-      <c r="B50" s="94" t="s">
+      <c r="B50" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="C50" s="95"/>
-      <c r="D50" s="96"/>
-      <c r="E50" s="97"/>
-      <c r="F50" s="37"/>
-      <c r="G50" s="38"/>
-      <c r="H50" s="161"/>
-      <c r="I50" s="162"/>
-      <c r="J50" s="163"/>
+      <c r="C50" s="53"/>
+      <c r="D50" s="54"/>
+      <c r="E50" s="55"/>
+      <c r="F50" s="145"/>
+      <c r="G50" s="146"/>
+      <c r="H50" s="56"/>
+      <c r="I50" s="57"/>
+      <c r="J50" s="58"/>
       <c r="K50" s="13"/>
       <c r="L50" s="13"/>
       <c r="M50" s="13"/>
     </row>
     <row r="51" spans="1:13" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="13"/>
-      <c r="B51" s="94" t="s">
+      <c r="B51" s="52" t="s">
         <v>53</v>
       </c>
-      <c r="C51" s="95"/>
-      <c r="D51" s="96"/>
-      <c r="E51" s="97"/>
-      <c r="F51" s="96"/>
-      <c r="G51" s="97"/>
-      <c r="H51" s="161"/>
-      <c r="I51" s="162"/>
-      <c r="J51" s="163"/>
+      <c r="C51" s="53"/>
+      <c r="D51" s="54"/>
+      <c r="E51" s="55"/>
+      <c r="F51" s="54"/>
+      <c r="G51" s="55"/>
+      <c r="H51" s="56"/>
+      <c r="I51" s="57"/>
+      <c r="J51" s="58"/>
       <c r="K51" s="13"/>
       <c r="L51" s="13"/>
       <c r="M51" s="13"/>
     </row>
     <row r="52" spans="1:13" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="13"/>
-      <c r="B52" s="141" t="s">
+      <c r="B52" s="59" t="s">
         <v>64</v>
       </c>
-      <c r="C52" s="142"/>
-      <c r="D52" s="126"/>
-      <c r="E52" s="127"/>
-      <c r="F52" s="126"/>
-      <c r="G52" s="127"/>
-      <c r="H52" s="161"/>
-      <c r="I52" s="162"/>
-      <c r="J52" s="163"/>
+      <c r="C52" s="60"/>
+      <c r="D52" s="93"/>
+      <c r="E52" s="94"/>
+      <c r="F52" s="93"/>
+      <c r="G52" s="94"/>
+      <c r="H52" s="56"/>
+      <c r="I52" s="57"/>
+      <c r="J52" s="58"/>
       <c r="K52" s="13"/>
       <c r="L52" s="13"/>
       <c r="M52" s="13"/>
     </row>
     <row r="53" spans="1:13" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="13"/>
-      <c r="B53" s="94" t="s">
+      <c r="B53" s="52" t="s">
         <v>54</v>
       </c>
-      <c r="C53" s="95"/>
-      <c r="D53" s="96"/>
-      <c r="E53" s="97"/>
-      <c r="F53" s="96"/>
-      <c r="G53" s="97"/>
-      <c r="H53" s="161"/>
-      <c r="I53" s="162"/>
-      <c r="J53" s="163"/>
+      <c r="C53" s="53"/>
+      <c r="D53" s="54"/>
+      <c r="E53" s="55"/>
+      <c r="F53" s="54"/>
+      <c r="G53" s="55"/>
+      <c r="H53" s="56"/>
+      <c r="I53" s="57"/>
+      <c r="J53" s="58"/>
       <c r="K53" s="13"/>
       <c r="L53" s="13"/>
       <c r="M53" s="13"/>
     </row>
     <row r="54" spans="1:13" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="13"/>
-      <c r="B54" s="94" t="s">
+      <c r="B54" s="52" t="s">
         <v>55</v>
       </c>
-      <c r="C54" s="95"/>
-      <c r="D54" s="96"/>
-      <c r="E54" s="97"/>
-      <c r="F54" s="96"/>
-      <c r="G54" s="97"/>
-      <c r="H54" s="161"/>
-      <c r="I54" s="162"/>
-      <c r="J54" s="163"/>
+      <c r="C54" s="53"/>
+      <c r="D54" s="54"/>
+      <c r="E54" s="55"/>
+      <c r="F54" s="54"/>
+      <c r="G54" s="55"/>
+      <c r="H54" s="56"/>
+      <c r="I54" s="57"/>
+      <c r="J54" s="58"/>
       <c r="K54" s="13"/>
       <c r="L54" s="13"/>
       <c r="M54" s="13"/>
     </row>
     <row r="55" spans="1:13" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A55" s="13"/>
-      <c r="B55" s="94" t="s">
+      <c r="B55" s="52" t="s">
         <v>56</v>
       </c>
-      <c r="C55" s="95"/>
-      <c r="D55" s="96"/>
-      <c r="E55" s="97"/>
-      <c r="F55" s="96"/>
-      <c r="G55" s="97"/>
-      <c r="H55" s="161"/>
-      <c r="I55" s="162"/>
-      <c r="J55" s="163"/>
+      <c r="C55" s="53"/>
+      <c r="D55" s="54"/>
+      <c r="E55" s="55"/>
+      <c r="F55" s="54"/>
+      <c r="G55" s="55"/>
+      <c r="H55" s="56"/>
+      <c r="I55" s="57"/>
+      <c r="J55" s="58"/>
       <c r="K55" s="13"/>
       <c r="L55" s="13"/>
       <c r="M55" s="13"/>
     </row>
     <row r="56" spans="1:13" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A56" s="13"/>
-      <c r="B56" s="143" t="s">
+      <c r="B56" s="61" t="s">
         <v>57</v>
       </c>
-      <c r="C56" s="144"/>
-      <c r="D56" s="145"/>
-      <c r="E56" s="146"/>
-      <c r="F56" s="145"/>
-      <c r="G56" s="146"/>
-      <c r="H56" s="161"/>
-      <c r="I56" s="162"/>
-      <c r="J56" s="163"/>
+      <c r="C56" s="62"/>
+      <c r="D56" s="63"/>
+      <c r="E56" s="64"/>
+      <c r="F56" s="63"/>
+      <c r="G56" s="64"/>
+      <c r="H56" s="56"/>
+      <c r="I56" s="57"/>
+      <c r="J56" s="58"/>
       <c r="K56" s="13"/>
       <c r="L56" s="13"/>
       <c r="M56" s="13"/>
     </row>
     <row r="57" spans="1:13" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57" s="13"/>
-      <c r="B57" s="123" t="s">
+      <c r="B57" s="90" t="s">
         <v>58</v>
       </c>
-      <c r="C57" s="124"/>
-      <c r="D57" s="124"/>
-      <c r="E57" s="124"/>
-      <c r="F57" s="124"/>
-      <c r="G57" s="124"/>
-      <c r="H57" s="124"/>
-      <c r="I57" s="124"/>
-      <c r="J57" s="125"/>
+      <c r="C57" s="91"/>
+      <c r="D57" s="91"/>
+      <c r="E57" s="91"/>
+      <c r="F57" s="91"/>
+      <c r="G57" s="91"/>
+      <c r="H57" s="91"/>
+      <c r="I57" s="91"/>
+      <c r="J57" s="92"/>
       <c r="K57" s="13"/>
       <c r="L57" s="13"/>
       <c r="M57" s="13"/>
     </row>
     <row r="58" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A58" s="13"/>
-      <c r="B58" s="115" t="s">
+      <c r="B58" s="72" t="s">
         <v>46</v>
       </c>
-      <c r="C58" s="116"/>
-      <c r="D58" s="34" t="s">
+      <c r="C58" s="74"/>
+      <c r="D58" s="44" t="s">
         <v>47</v>
       </c>
-      <c r="E58" s="35"/>
-      <c r="F58" s="35"/>
-      <c r="G58" s="36"/>
-      <c r="H58" s="115" t="s">
+      <c r="E58" s="45"/>
+      <c r="F58" s="45"/>
+      <c r="G58" s="46"/>
+      <c r="H58" s="72" t="s">
         <v>48</v>
       </c>
-      <c r="I58" s="119"/>
-      <c r="J58" s="116"/>
+      <c r="I58" s="73"/>
+      <c r="J58" s="74"/>
       <c r="K58" s="13"/>
       <c r="L58" s="13"/>
       <c r="M58" s="13"/>
     </row>
     <row r="59" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A59" s="13"/>
-      <c r="B59" s="117"/>
-      <c r="C59" s="118"/>
-      <c r="D59" s="121" t="s">
+      <c r="B59" s="75"/>
+      <c r="C59" s="77"/>
+      <c r="D59" s="88" t="s">
         <v>49</v>
       </c>
-      <c r="E59" s="122"/>
-      <c r="F59" s="121" t="s">
+      <c r="E59" s="89"/>
+      <c r="F59" s="88" t="s">
         <v>50</v>
       </c>
-      <c r="G59" s="122"/>
-      <c r="H59" s="117"/>
-      <c r="I59" s="120"/>
-      <c r="J59" s="118"/>
+      <c r="G59" s="89"/>
+      <c r="H59" s="75"/>
+      <c r="I59" s="76"/>
+      <c r="J59" s="77"/>
       <c r="K59" s="13"/>
       <c r="L59" s="13"/>
       <c r="M59" s="13"/>
     </row>
     <row r="60" spans="1:13" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A60" s="13"/>
-      <c r="B60" s="94" t="s">
+      <c r="B60" s="52" t="s">
         <v>59</v>
       </c>
-      <c r="C60" s="95"/>
-      <c r="D60" s="96"/>
-      <c r="E60" s="97"/>
-      <c r="F60" s="96"/>
-      <c r="G60" s="97"/>
-      <c r="H60" s="161"/>
-      <c r="I60" s="162"/>
-      <c r="J60" s="163"/>
+      <c r="C60" s="53"/>
+      <c r="D60" s="54"/>
+      <c r="E60" s="55"/>
+      <c r="F60" s="54"/>
+      <c r="G60" s="55"/>
+      <c r="H60" s="56"/>
+      <c r="I60" s="57"/>
+      <c r="J60" s="58"/>
       <c r="K60" s="13"/>
       <c r="L60" s="13"/>
       <c r="M60" s="13"/>
     </row>
     <row r="61" spans="1:13" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A61" s="13"/>
-      <c r="B61" s="94" t="s">
+      <c r="B61" s="52" t="s">
         <v>60</v>
       </c>
-      <c r="C61" s="95"/>
-      <c r="D61" s="96"/>
-      <c r="E61" s="97"/>
-      <c r="F61" s="96"/>
-      <c r="G61" s="97"/>
-      <c r="H61" s="161"/>
-      <c r="I61" s="162"/>
-      <c r="J61" s="163"/>
+      <c r="C61" s="53"/>
+      <c r="D61" s="54"/>
+      <c r="E61" s="55"/>
+      <c r="F61" s="54"/>
+      <c r="G61" s="55"/>
+      <c r="H61" s="56"/>
+      <c r="I61" s="57"/>
+      <c r="J61" s="58"/>
       <c r="K61" s="13"/>
       <c r="L61" s="13"/>
       <c r="M61" s="13"/>
     </row>
     <row r="62" spans="1:13" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A62" s="13"/>
-      <c r="B62" s="94" t="s">
+      <c r="B62" s="52" t="s">
         <v>61</v>
       </c>
-      <c r="C62" s="95"/>
-      <c r="D62" s="96"/>
-      <c r="E62" s="97"/>
-      <c r="F62" s="96"/>
-      <c r="G62" s="97"/>
-      <c r="H62" s="161"/>
-      <c r="I62" s="162"/>
-      <c r="J62" s="163"/>
+      <c r="C62" s="53"/>
+      <c r="D62" s="54"/>
+      <c r="E62" s="55"/>
+      <c r="F62" s="54"/>
+      <c r="G62" s="55"/>
+      <c r="H62" s="56"/>
+      <c r="I62" s="57"/>
+      <c r="J62" s="58"/>
       <c r="K62" s="13"/>
       <c r="L62" s="13"/>
       <c r="M62" s="13"/>
     </row>
     <row r="63" spans="1:13" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A63" s="13"/>
-      <c r="B63" s="94" t="s">
+      <c r="B63" s="52" t="s">
         <v>62</v>
       </c>
-      <c r="C63" s="95"/>
-      <c r="D63" s="96"/>
-      <c r="E63" s="97"/>
-      <c r="F63" s="96"/>
-      <c r="G63" s="97"/>
-      <c r="H63" s="161"/>
-      <c r="I63" s="162"/>
-      <c r="J63" s="163"/>
+      <c r="C63" s="53"/>
+      <c r="D63" s="54"/>
+      <c r="E63" s="55"/>
+      <c r="F63" s="54"/>
+      <c r="G63" s="55"/>
+      <c r="H63" s="56"/>
+      <c r="I63" s="57"/>
+      <c r="J63" s="58"/>
       <c r="K63" s="13"/>
       <c r="L63" s="13"/>
       <c r="M63" s="13"/>
     </row>
     <row r="64" spans="1:13" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A64" s="13"/>
-      <c r="B64" s="94" t="s">
+      <c r="B64" s="52" t="s">
         <v>63</v>
       </c>
-      <c r="C64" s="95"/>
-      <c r="D64" s="96"/>
-      <c r="E64" s="97"/>
-      <c r="F64" s="96"/>
-      <c r="G64" s="97"/>
-      <c r="H64" s="161"/>
-      <c r="I64" s="162"/>
-      <c r="J64" s="163"/>
+      <c r="C64" s="53"/>
+      <c r="D64" s="54"/>
+      <c r="E64" s="55"/>
+      <c r="F64" s="54"/>
+      <c r="G64" s="55"/>
+      <c r="H64" s="56"/>
+      <c r="I64" s="57"/>
+      <c r="J64" s="58"/>
       <c r="K64" s="13"/>
       <c r="L64" s="13"/>
       <c r="M64" s="13"/>
@@ -3090,51 +3034,51 @@
     </row>
     <row r="66" spans="1:13" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A66" s="13"/>
-      <c r="B66" s="34" t="s">
+      <c r="B66" s="44" t="s">
         <v>67</v>
       </c>
-      <c r="C66" s="35"/>
-      <c r="D66" s="35"/>
-      <c r="E66" s="35"/>
-      <c r="F66" s="35"/>
-      <c r="G66" s="35"/>
-      <c r="H66" s="35"/>
-      <c r="I66" s="35"/>
-      <c r="J66" s="36"/>
+      <c r="C66" s="45"/>
+      <c r="D66" s="45"/>
+      <c r="E66" s="45"/>
+      <c r="F66" s="45"/>
+      <c r="G66" s="45"/>
+      <c r="H66" s="45"/>
+      <c r="I66" s="45"/>
+      <c r="J66" s="46"/>
       <c r="K66" s="13"/>
       <c r="L66" s="13"/>
       <c r="M66" s="13"/>
     </row>
     <row r="67" spans="1:13" ht="72" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A67" s="13"/>
-      <c r="B67" s="57" t="s">
+      <c r="B67" s="47" t="s">
         <v>68</v>
       </c>
-      <c r="C67" s="59"/>
-      <c r="D67" s="164"/>
-      <c r="E67" s="165"/>
-      <c r="F67" s="165"/>
-      <c r="G67" s="165"/>
-      <c r="H67" s="165"/>
-      <c r="I67" s="165"/>
-      <c r="J67" s="166"/>
+      <c r="C67" s="48"/>
+      <c r="D67" s="49"/>
+      <c r="E67" s="50"/>
+      <c r="F67" s="50"/>
+      <c r="G67" s="50"/>
+      <c r="H67" s="50"/>
+      <c r="I67" s="50"/>
+      <c r="J67" s="51"/>
       <c r="K67" s="13"/>
       <c r="L67" s="13"/>
       <c r="M67" s="13"/>
     </row>
     <row r="68" spans="1:13" ht="72" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A68" s="13"/>
-      <c r="B68" s="57" t="s">
+      <c r="B68" s="47" t="s">
         <v>69</v>
       </c>
-      <c r="C68" s="59"/>
-      <c r="D68" s="164"/>
-      <c r="E68" s="165"/>
-      <c r="F68" s="165"/>
-      <c r="G68" s="165"/>
-      <c r="H68" s="165"/>
-      <c r="I68" s="165"/>
-      <c r="J68" s="166"/>
+      <c r="C68" s="48"/>
+      <c r="D68" s="49"/>
+      <c r="E68" s="50"/>
+      <c r="F68" s="50"/>
+      <c r="G68" s="50"/>
+      <c r="H68" s="50"/>
+      <c r="I68" s="50"/>
+      <c r="J68" s="51"/>
       <c r="K68" s="13"/>
       <c r="L68" s="13"/>
       <c r="M68" s="13"/>
@@ -3156,51 +3100,51 @@
     </row>
     <row r="70" spans="1:13" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A70" s="13"/>
-      <c r="B70" s="34" t="s">
+      <c r="B70" s="44" t="s">
         <v>70</v>
       </c>
-      <c r="C70" s="35"/>
-      <c r="D70" s="35"/>
-      <c r="E70" s="35"/>
-      <c r="F70" s="35"/>
-      <c r="G70" s="35"/>
-      <c r="H70" s="35"/>
-      <c r="I70" s="35"/>
-      <c r="J70" s="36"/>
+      <c r="C70" s="45"/>
+      <c r="D70" s="45"/>
+      <c r="E70" s="45"/>
+      <c r="F70" s="45"/>
+      <c r="G70" s="45"/>
+      <c r="H70" s="45"/>
+      <c r="I70" s="45"/>
+      <c r="J70" s="46"/>
       <c r="K70" s="13"/>
       <c r="L70" s="13"/>
       <c r="M70" s="13"/>
     </row>
     <row r="71" spans="1:13" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A71" s="13"/>
-      <c r="B71" s="57" t="s">
+      <c r="B71" s="47" t="s">
         <v>68</v>
       </c>
-      <c r="C71" s="59"/>
-      <c r="D71" s="164"/>
-      <c r="E71" s="165"/>
-      <c r="F71" s="165"/>
-      <c r="G71" s="165"/>
-      <c r="H71" s="165"/>
-      <c r="I71" s="165"/>
-      <c r="J71" s="166"/>
+      <c r="C71" s="48"/>
+      <c r="D71" s="49"/>
+      <c r="E71" s="50"/>
+      <c r="F71" s="50"/>
+      <c r="G71" s="50"/>
+      <c r="H71" s="50"/>
+      <c r="I71" s="50"/>
+      <c r="J71" s="51"/>
       <c r="K71" s="13"/>
       <c r="L71" s="13"/>
       <c r="M71" s="13"/>
     </row>
     <row r="72" spans="1:13" ht="72" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A72" s="13"/>
-      <c r="B72" s="57" t="s">
+      <c r="B72" s="47" t="s">
         <v>69</v>
       </c>
-      <c r="C72" s="59"/>
-      <c r="D72" s="164"/>
-      <c r="E72" s="165"/>
-      <c r="F72" s="165"/>
-      <c r="G72" s="165"/>
-      <c r="H72" s="165"/>
-      <c r="I72" s="165"/>
-      <c r="J72" s="166"/>
+      <c r="C72" s="48"/>
+      <c r="D72" s="49"/>
+      <c r="E72" s="50"/>
+      <c r="F72" s="50"/>
+      <c r="G72" s="50"/>
+      <c r="H72" s="50"/>
+      <c r="I72" s="50"/>
+      <c r="J72" s="51"/>
       <c r="K72" s="13"/>
       <c r="L72" s="13"/>
       <c r="M72" s="13"/>
@@ -3222,51 +3166,51 @@
     </row>
     <row r="74" spans="1:13" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A74" s="13"/>
-      <c r="B74" s="34" t="s">
+      <c r="B74" s="44" t="s">
         <v>71</v>
       </c>
-      <c r="C74" s="35"/>
-      <c r="D74" s="35"/>
-      <c r="E74" s="35"/>
-      <c r="F74" s="35"/>
-      <c r="G74" s="35"/>
-      <c r="H74" s="35"/>
-      <c r="I74" s="35"/>
-      <c r="J74" s="36"/>
+      <c r="C74" s="45"/>
+      <c r="D74" s="45"/>
+      <c r="E74" s="45"/>
+      <c r="F74" s="45"/>
+      <c r="G74" s="45"/>
+      <c r="H74" s="45"/>
+      <c r="I74" s="45"/>
+      <c r="J74" s="46"/>
       <c r="K74" s="13"/>
       <c r="L74" s="13"/>
       <c r="M74" s="13"/>
     </row>
     <row r="75" spans="1:13" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A75" s="13"/>
-      <c r="B75" s="57" t="s">
+      <c r="B75" s="47" t="s">
         <v>68</v>
       </c>
-      <c r="C75" s="59"/>
-      <c r="D75" s="164"/>
-      <c r="E75" s="165"/>
-      <c r="F75" s="165"/>
-      <c r="G75" s="165"/>
-      <c r="H75" s="165"/>
-      <c r="I75" s="165"/>
-      <c r="J75" s="166"/>
+      <c r="C75" s="48"/>
+      <c r="D75" s="49"/>
+      <c r="E75" s="50"/>
+      <c r="F75" s="50"/>
+      <c r="G75" s="50"/>
+      <c r="H75" s="50"/>
+      <c r="I75" s="50"/>
+      <c r="J75" s="51"/>
       <c r="K75" s="13"/>
       <c r="L75" s="13"/>
       <c r="M75" s="13"/>
     </row>
     <row r="76" spans="1:13" ht="71.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A76" s="13"/>
-      <c r="B76" s="57" t="s">
+      <c r="B76" s="47" t="s">
         <v>69</v>
       </c>
-      <c r="C76" s="59"/>
-      <c r="D76" s="164"/>
-      <c r="E76" s="165"/>
-      <c r="F76" s="165"/>
-      <c r="G76" s="165"/>
-      <c r="H76" s="165"/>
-      <c r="I76" s="165"/>
-      <c r="J76" s="166"/>
+      <c r="C76" s="48"/>
+      <c r="D76" s="49"/>
+      <c r="E76" s="50"/>
+      <c r="F76" s="50"/>
+      <c r="G76" s="50"/>
+      <c r="H76" s="50"/>
+      <c r="I76" s="50"/>
+      <c r="J76" s="51"/>
       <c r="K76" s="13"/>
       <c r="L76" s="13"/>
       <c r="M76" s="13"/>
@@ -3286,19 +3230,21 @@
       <c r="L77" s="13"/>
       <c r="M77" s="13"/>
     </row>
-    <row r="78" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:13" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="11"/>
       <c r="B78" s="12"/>
-      <c r="C78" s="63" t="s">
+      <c r="C78" s="165" t="s">
         <v>99</v>
       </c>
-      <c r="D78" s="64"/>
-      <c r="E78" s="64"/>
-      <c r="F78" s="64"/>
+      <c r="D78" s="166"/>
+      <c r="E78" s="166"/>
+      <c r="F78" s="166"/>
       <c r="G78" s="28" t="s">
         <v>98</v>
       </c>
-      <c r="H78" s="12"/>
+      <c r="H78" s="167" t="s">
+        <v>100</v>
+      </c>
       <c r="I78" s="28" t="s">
         <v>97</v>
       </c>
@@ -3308,96 +3254,96 @@
       <c r="M78" s="11"/>
     </row>
     <row r="79" spans="1:13" ht="48.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="42"/>
-      <c r="B79" s="42"/>
-      <c r="C79" s="42"/>
-      <c r="D79" s="42"/>
-      <c r="E79" s="40"/>
-      <c r="F79" s="40"/>
-      <c r="G79" s="42"/>
-      <c r="H79" s="42"/>
-      <c r="I79" s="40"/>
-      <c r="J79" s="40"/>
-      <c r="K79" s="42"/>
-      <c r="L79" s="42"/>
-      <c r="M79" s="42"/>
+      <c r="A79" s="150"/>
+      <c r="B79" s="150"/>
+      <c r="C79" s="150"/>
+      <c r="D79" s="150"/>
+      <c r="E79" s="148"/>
+      <c r="F79" s="148"/>
+      <c r="G79" s="150"/>
+      <c r="H79" s="150"/>
+      <c r="I79" s="148"/>
+      <c r="J79" s="148"/>
+      <c r="K79" s="150"/>
+      <c r="L79" s="150"/>
+      <c r="M79" s="150"/>
     </row>
     <row r="80" spans="1:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="42"/>
-      <c r="B80" s="42"/>
-      <c r="C80" s="42"/>
-      <c r="D80" s="42"/>
-      <c r="E80" s="40"/>
-      <c r="F80" s="40"/>
-      <c r="G80" s="42"/>
-      <c r="H80" s="42"/>
-      <c r="I80" s="40"/>
-      <c r="J80" s="40"/>
-      <c r="K80" s="42"/>
-      <c r="L80" s="42"/>
-      <c r="M80" s="42"/>
+      <c r="A80" s="150"/>
+      <c r="B80" s="150"/>
+      <c r="C80" s="150"/>
+      <c r="D80" s="150"/>
+      <c r="E80" s="148"/>
+      <c r="F80" s="148"/>
+      <c r="G80" s="150"/>
+      <c r="H80" s="150"/>
+      <c r="I80" s="148"/>
+      <c r="J80" s="148"/>
+      <c r="K80" s="150"/>
+      <c r="L80" s="150"/>
+      <c r="M80" s="150"/>
     </row>
     <row r="81" spans="1:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="42"/>
-      <c r="B81" s="42"/>
-      <c r="C81" s="42"/>
-      <c r="D81" s="42"/>
-      <c r="E81" s="40"/>
-      <c r="F81" s="40"/>
-      <c r="G81" s="42"/>
-      <c r="H81" s="42"/>
-      <c r="I81" s="40"/>
-      <c r="J81" s="40"/>
-      <c r="K81" s="42"/>
-      <c r="L81" s="42"/>
-      <c r="M81" s="42"/>
+      <c r="A81" s="150"/>
+      <c r="B81" s="150"/>
+      <c r="C81" s="150"/>
+      <c r="D81" s="150"/>
+      <c r="E81" s="148"/>
+      <c r="F81" s="148"/>
+      <c r="G81" s="150"/>
+      <c r="H81" s="150"/>
+      <c r="I81" s="148"/>
+      <c r="J81" s="148"/>
+      <c r="K81" s="150"/>
+      <c r="L81" s="150"/>
+      <c r="M81" s="150"/>
     </row>
     <row r="82" spans="1:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="42"/>
-      <c r="B82" s="42"/>
-      <c r="C82" s="42"/>
-      <c r="D82" s="42"/>
-      <c r="E82" s="40"/>
-      <c r="F82" s="40"/>
-      <c r="G82" s="42"/>
-      <c r="H82" s="42"/>
-      <c r="I82" s="40"/>
-      <c r="J82" s="40"/>
-      <c r="K82" s="42"/>
-      <c r="L82" s="42"/>
-      <c r="M82" s="42"/>
+      <c r="A82" s="150"/>
+      <c r="B82" s="150"/>
+      <c r="C82" s="150"/>
+      <c r="D82" s="150"/>
+      <c r="E82" s="148"/>
+      <c r="F82" s="148"/>
+      <c r="G82" s="150"/>
+      <c r="H82" s="150"/>
+      <c r="I82" s="148"/>
+      <c r="J82" s="148"/>
+      <c r="K82" s="150"/>
+      <c r="L82" s="150"/>
+      <c r="M82" s="150"/>
     </row>
     <row r="83" spans="1:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="43"/>
-      <c r="B83" s="43"/>
-      <c r="C83" s="43"/>
-      <c r="D83" s="43"/>
-      <c r="E83" s="40"/>
-      <c r="F83" s="40"/>
-      <c r="G83" s="43"/>
-      <c r="H83" s="43"/>
-      <c r="I83" s="40"/>
-      <c r="J83" s="40"/>
-      <c r="K83" s="43"/>
-      <c r="L83" s="43"/>
-      <c r="M83" s="43"/>
+      <c r="A83" s="151"/>
+      <c r="B83" s="151"/>
+      <c r="C83" s="151"/>
+      <c r="D83" s="151"/>
+      <c r="E83" s="148"/>
+      <c r="F83" s="148"/>
+      <c r="G83" s="151"/>
+      <c r="H83" s="151"/>
+      <c r="I83" s="148"/>
+      <c r="J83" s="148"/>
+      <c r="K83" s="151"/>
+      <c r="L83" s="151"/>
+      <c r="M83" s="151"/>
     </row>
     <row r="84" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="39"/>
-      <c r="B84" s="39"/>
-      <c r="C84" s="39"/>
-      <c r="D84" s="39"/>
-      <c r="E84" s="40"/>
-      <c r="F84" s="40"/>
-      <c r="G84" s="41" t="s">
+      <c r="A84" s="147"/>
+      <c r="B84" s="147"/>
+      <c r="C84" s="147"/>
+      <c r="D84" s="147"/>
+      <c r="E84" s="148"/>
+      <c r="F84" s="148"/>
+      <c r="G84" s="149" t="s">
         <v>27</v>
       </c>
-      <c r="H84" s="41"/>
-      <c r="I84" s="40"/>
-      <c r="J84" s="40"/>
-      <c r="K84" s="39"/>
-      <c r="L84" s="39"/>
-      <c r="M84" s="39"/>
+      <c r="H84" s="149"/>
+      <c r="I84" s="148"/>
+      <c r="J84" s="148"/>
+      <c r="K84" s="147"/>
+      <c r="L84" s="147"/>
+      <c r="M84" s="147"/>
     </row>
     <row r="85" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A85" s="12"/>
@@ -3416,28 +3362,182 @@
     </row>
     <row r="86" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A86" s="22"/>
-      <c r="B86" s="158"/>
-      <c r="C86" s="158"/>
-      <c r="D86" s="158"/>
-      <c r="E86" s="158"/>
-      <c r="F86" s="158"/>
-      <c r="G86" s="158"/>
-      <c r="H86" s="158"/>
-      <c r="I86" s="158"/>
-      <c r="J86" s="158"/>
+      <c r="B86" s="43"/>
+      <c r="C86" s="43"/>
+      <c r="D86" s="43"/>
+      <c r="E86" s="43"/>
+      <c r="F86" s="43"/>
+      <c r="G86" s="43"/>
+      <c r="H86" s="43"/>
+      <c r="I86" s="43"/>
+      <c r="J86" s="43"/>
       <c r="K86" s="22"/>
       <c r="L86" s="22"/>
       <c r="M86" s="22"/>
     </row>
     <row r="87" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="F87" s="29" t="s">
+      <c r="F87" s="35" t="s">
         <v>44</v>
       </c>
-      <c r="G87" s="29"/>
+      <c r="G87" s="35"/>
     </row>
     <row r="88" spans="1:13" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="178">
+    <mergeCell ref="F87:G87"/>
+    <mergeCell ref="A38:M40"/>
+    <mergeCell ref="I10:M10"/>
+    <mergeCell ref="B70:J70"/>
+    <mergeCell ref="F50:G50"/>
+    <mergeCell ref="A84:D84"/>
+    <mergeCell ref="E84:F84"/>
+    <mergeCell ref="G84:H84"/>
+    <mergeCell ref="I84:J84"/>
+    <mergeCell ref="K84:M84"/>
+    <mergeCell ref="A79:D83"/>
+    <mergeCell ref="E79:F83"/>
+    <mergeCell ref="G79:H83"/>
+    <mergeCell ref="I79:J83"/>
+    <mergeCell ref="K79:M83"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="E44:G44"/>
+    <mergeCell ref="H44:J44"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="E35:M35"/>
+    <mergeCell ref="C78:F78"/>
+    <mergeCell ref="E36:M36"/>
+    <mergeCell ref="E37:M37"/>
+    <mergeCell ref="C9:M9"/>
+    <mergeCell ref="A8:M8"/>
+    <mergeCell ref="E14:M14"/>
+    <mergeCell ref="K11:M11"/>
+    <mergeCell ref="K12:M12"/>
+    <mergeCell ref="J13:M13"/>
+    <mergeCell ref="E15:M15"/>
+    <mergeCell ref="E16:M16"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="E32:M32"/>
+    <mergeCell ref="E33:M33"/>
+    <mergeCell ref="E34:M34"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="E29:M29"/>
+    <mergeCell ref="E30:M30"/>
+    <mergeCell ref="E31:M31"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="E26:M26"/>
+    <mergeCell ref="E27:M27"/>
+    <mergeCell ref="E28:M28"/>
+    <mergeCell ref="A23:A25"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="E23:M23"/>
+    <mergeCell ref="E24:M24"/>
+    <mergeCell ref="E25:M25"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="E20:M20"/>
+    <mergeCell ref="E21:M21"/>
+    <mergeCell ref="E22:M22"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="E17:M17"/>
+    <mergeCell ref="E18:M18"/>
+    <mergeCell ref="E19:M19"/>
+    <mergeCell ref="H50:J50"/>
+    <mergeCell ref="B51:C51"/>
+    <mergeCell ref="D51:E51"/>
+    <mergeCell ref="F51:G51"/>
+    <mergeCell ref="H51:J51"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="C13:F13"/>
+    <mergeCell ref="G13:I13"/>
+    <mergeCell ref="A14:A22"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="C11:H11"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="D50:E50"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="D61:E61"/>
+    <mergeCell ref="F61:G61"/>
+    <mergeCell ref="H61:J61"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="D62:E62"/>
+    <mergeCell ref="F62:G62"/>
+    <mergeCell ref="H62:J62"/>
+    <mergeCell ref="B58:C59"/>
+    <mergeCell ref="D58:G58"/>
+    <mergeCell ref="H58:J59"/>
+    <mergeCell ref="D59:E59"/>
+    <mergeCell ref="F59:G59"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="D60:E60"/>
+    <mergeCell ref="F60:G60"/>
+    <mergeCell ref="H60:J60"/>
+    <mergeCell ref="B57:J57"/>
+    <mergeCell ref="D52:E52"/>
+    <mergeCell ref="F52:G52"/>
+    <mergeCell ref="H52:J52"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="B47:C48"/>
+    <mergeCell ref="D47:G47"/>
+    <mergeCell ref="H47:J48"/>
+    <mergeCell ref="D48:E48"/>
+    <mergeCell ref="F48:G48"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="D49:E49"/>
+    <mergeCell ref="H49:J49"/>
+    <mergeCell ref="B41:J41"/>
+    <mergeCell ref="B46:J46"/>
+    <mergeCell ref="B42:J42"/>
+    <mergeCell ref="F49:G49"/>
+    <mergeCell ref="E43:F43"/>
+    <mergeCell ref="G43:H43"/>
+    <mergeCell ref="D71:J71"/>
+    <mergeCell ref="B72:C72"/>
+    <mergeCell ref="D72:J72"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="H54:J54"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="D55:E55"/>
+    <mergeCell ref="F55:G55"/>
+    <mergeCell ref="H55:J55"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="D56:E56"/>
+    <mergeCell ref="F56:G56"/>
+    <mergeCell ref="H56:J56"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="D63:E63"/>
+    <mergeCell ref="F63:G63"/>
+    <mergeCell ref="H63:J63"/>
+    <mergeCell ref="D53:E53"/>
+    <mergeCell ref="F53:G53"/>
+    <mergeCell ref="H53:J53"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="D54:E54"/>
+    <mergeCell ref="F54:G54"/>
     <mergeCell ref="B1:K1"/>
     <mergeCell ref="B2:K2"/>
     <mergeCell ref="B3:K3"/>
@@ -3462,208 +3562,54 @@
     <mergeCell ref="D67:J67"/>
     <mergeCell ref="D68:J68"/>
     <mergeCell ref="B71:C71"/>
-    <mergeCell ref="D71:J71"/>
-    <mergeCell ref="B72:C72"/>
-    <mergeCell ref="D72:J72"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="H54:J54"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="D55:E55"/>
-    <mergeCell ref="F55:G55"/>
-    <mergeCell ref="H55:J55"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="D56:E56"/>
-    <mergeCell ref="F56:G56"/>
-    <mergeCell ref="H56:J56"/>
-    <mergeCell ref="B63:C63"/>
-    <mergeCell ref="D63:E63"/>
-    <mergeCell ref="F63:G63"/>
-    <mergeCell ref="H63:J63"/>
-    <mergeCell ref="D53:E53"/>
-    <mergeCell ref="F53:G53"/>
-    <mergeCell ref="H53:J53"/>
-    <mergeCell ref="B54:C54"/>
-    <mergeCell ref="D54:E54"/>
-    <mergeCell ref="F54:G54"/>
-    <mergeCell ref="B47:C48"/>
-    <mergeCell ref="D47:G47"/>
-    <mergeCell ref="H47:J48"/>
-    <mergeCell ref="D48:E48"/>
-    <mergeCell ref="F48:G48"/>
-    <mergeCell ref="B49:C49"/>
-    <mergeCell ref="D49:E49"/>
-    <mergeCell ref="H49:J49"/>
-    <mergeCell ref="B41:J41"/>
-    <mergeCell ref="B46:J46"/>
-    <mergeCell ref="B42:J42"/>
-    <mergeCell ref="F49:G49"/>
-    <mergeCell ref="E43:F43"/>
-    <mergeCell ref="G43:H43"/>
-    <mergeCell ref="B50:C50"/>
-    <mergeCell ref="D50:E50"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="D61:E61"/>
-    <mergeCell ref="F61:G61"/>
-    <mergeCell ref="H61:J61"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="D62:E62"/>
-    <mergeCell ref="F62:G62"/>
-    <mergeCell ref="H62:J62"/>
-    <mergeCell ref="B58:C59"/>
-    <mergeCell ref="D58:G58"/>
-    <mergeCell ref="H58:J59"/>
-    <mergeCell ref="D59:E59"/>
-    <mergeCell ref="F59:G59"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="D60:E60"/>
-    <mergeCell ref="F60:G60"/>
-    <mergeCell ref="H60:J60"/>
-    <mergeCell ref="B57:J57"/>
-    <mergeCell ref="D52:E52"/>
-    <mergeCell ref="F52:G52"/>
-    <mergeCell ref="H52:J52"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="H50:J50"/>
-    <mergeCell ref="B51:C51"/>
-    <mergeCell ref="D51:E51"/>
-    <mergeCell ref="F51:G51"/>
-    <mergeCell ref="H51:J51"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="C13:F13"/>
-    <mergeCell ref="G13:I13"/>
-    <mergeCell ref="A14:A22"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="C11:H11"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="E20:M20"/>
-    <mergeCell ref="E21:M21"/>
-    <mergeCell ref="E22:M22"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="E17:M17"/>
-    <mergeCell ref="E18:M18"/>
-    <mergeCell ref="E19:M19"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="E26:M26"/>
-    <mergeCell ref="E27:M27"/>
-    <mergeCell ref="E28:M28"/>
-    <mergeCell ref="A23:A25"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="E23:M23"/>
-    <mergeCell ref="E24:M24"/>
-    <mergeCell ref="E25:M25"/>
-    <mergeCell ref="E36:M36"/>
-    <mergeCell ref="E37:M37"/>
-    <mergeCell ref="C9:M9"/>
-    <mergeCell ref="A8:M8"/>
-    <mergeCell ref="E14:M14"/>
-    <mergeCell ref="K11:M11"/>
-    <mergeCell ref="K12:M12"/>
-    <mergeCell ref="J13:M13"/>
-    <mergeCell ref="E15:M15"/>
-    <mergeCell ref="E16:M16"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="E32:M32"/>
-    <mergeCell ref="E33:M33"/>
-    <mergeCell ref="E34:M34"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="E29:M29"/>
-    <mergeCell ref="E30:M30"/>
-    <mergeCell ref="E31:M31"/>
-    <mergeCell ref="B26:D26"/>
-    <mergeCell ref="B27:D27"/>
-    <mergeCell ref="F87:G87"/>
-    <mergeCell ref="A38:M40"/>
-    <mergeCell ref="I10:M10"/>
-    <mergeCell ref="B70:J70"/>
-    <mergeCell ref="F50:G50"/>
-    <mergeCell ref="A84:D84"/>
-    <mergeCell ref="E84:F84"/>
-    <mergeCell ref="G84:H84"/>
-    <mergeCell ref="I84:J84"/>
-    <mergeCell ref="K84:M84"/>
-    <mergeCell ref="A79:D83"/>
-    <mergeCell ref="E79:F83"/>
-    <mergeCell ref="G79:H83"/>
-    <mergeCell ref="I79:J83"/>
-    <mergeCell ref="K79:M83"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="E44:G44"/>
-    <mergeCell ref="H44:J44"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="B37:D37"/>
-    <mergeCell ref="E35:M35"/>
-    <mergeCell ref="C78:F78"/>
   </mergeCells>
   <conditionalFormatting sqref="A84:D84 K84:M84">
-    <cfRule type="containsBlanks" dxfId="19" priority="14" stopIfTrue="1">
+    <cfRule type="containsBlanks" dxfId="9" priority="14" stopIfTrue="1">
       <formula>LEN(TRIM(A84))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A84:D84">
-    <cfRule type="containsBlanks" dxfId="18" priority="9">
+    <cfRule type="containsBlanks" dxfId="8" priority="9">
       <formula>LEN(TRIM(A84))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B86:J86">
-    <cfRule type="containsBlanks" dxfId="17" priority="1">
+    <cfRule type="containsBlanks" dxfId="7" priority="1">
       <formula>LEN(TRIM(B86))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D43:D44">
-    <cfRule type="containsBlanks" dxfId="16" priority="5">
+    <cfRule type="containsBlanks" dxfId="6" priority="5">
       <formula>LEN(TRIM(D43))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D60:J64 D49:J56">
-    <cfRule type="containsBlanks" dxfId="15" priority="3">
+  <conditionalFormatting sqref="D49:J56 D60:J64">
+    <cfRule type="containsBlanks" dxfId="5" priority="3">
       <formula>LEN(TRIM(D49))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D67:J68">
-    <cfRule type="containsBlanks" dxfId="14" priority="2">
+    <cfRule type="containsBlanks" dxfId="4" priority="2">
       <formula>LEN(TRIM(D67))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G43:H43 J43">
-    <cfRule type="containsBlanks" dxfId="13" priority="4">
+    <cfRule type="containsBlanks" dxfId="3" priority="4">
       <formula>LEN(TRIM(G43))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I10:M10 C11:H11 K11:M11 J13:M13 E14:M22 E26:M34 D75:J76 A84:D84 K84:M84">
-    <cfRule type="containsBlanks" dxfId="12" priority="6">
+    <cfRule type="containsBlanks" dxfId="2" priority="6">
       <formula>LEN(TRIM(A10))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I10:M10 C11:H11 K11:M11 J13:M13 E14:M22 E26:M34">
-    <cfRule type="containsBlanks" dxfId="11" priority="13" stopIfTrue="1">
+    <cfRule type="containsBlanks" dxfId="1" priority="13" stopIfTrue="1">
       <formula>LEN(TRIM(C10))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K84:M84">
-    <cfRule type="containsBlanks" dxfId="10" priority="8">
+    <cfRule type="containsBlanks" dxfId="0" priority="8">
       <formula>LEN(TRIM(K84))=0</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Formatos/Visita 3 GFPI-F023.xlsx
+++ b/Formatos/Visita 3 GFPI-F023.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uniminuto0-my.sharepoint.com/personal/sergio_torres_mar_uniminuto_edu_co/Documents/Documentos/Seto 2026/SETO/sena/Manual SENA Etapa Productiva/manual-aprendiz-sena/Formatos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="53" documentId="13_ncr:1_{B8726567-7195-433A-A879-F216B9BE4E06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EF8A4525-65DF-44E6-AEA5-D4D60DBCA02F}"/>
+  <xr:revisionPtr revIDLastSave="82" documentId="13_ncr:1_{B8726567-7195-433A-A879-F216B9BE4E06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{12992CB3-EE30-4AD1-9580-E9326F29E5ED}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-105" windowWidth="29040" windowHeight="15720" xr2:uid="{BC3553EE-4E49-4F2A-B03E-CFAC4EB3009B}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{BC3553EE-4E49-4F2A-B03E-CFAC4EB3009B}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_Hlk197527663" localSheetId="0">Hoja1!#REF!</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Hoja1!$A$8:$M$87</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Hoja1!$A$1:$M$88</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1015,14 +1015,6 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="15" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -1049,6 +1041,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1294,18 +1289,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1474,15 +1457,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1500,8 +1483,25 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1595,6 +1595,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1935,1084 +1939,1084 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B1" s="31" t="s">
+      <c r="B1" s="30" t="s">
         <v>77</v>
       </c>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32"/>
-      <c r="H1" s="32"/>
-      <c r="I1" s="32"/>
-      <c r="J1" s="32"/>
-      <c r="K1" s="33"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="31"/>
+      <c r="H1" s="31"/>
+      <c r="I1" s="31"/>
+      <c r="J1" s="31"/>
+      <c r="K1" s="32"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B2" s="34" t="s">
+      <c r="B2" s="33" t="s">
         <v>78</v>
       </c>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
-      <c r="I2" s="35"/>
-      <c r="J2" s="35"/>
-      <c r="K2" s="36"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="34"/>
+      <c r="F2" s="34"/>
+      <c r="G2" s="34"/>
+      <c r="H2" s="34"/>
+      <c r="I2" s="34"/>
+      <c r="J2" s="34"/>
+      <c r="K2" s="35"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B3" s="37" t="s">
+      <c r="B3" s="36" t="s">
         <v>79</v>
       </c>
-      <c r="C3" s="38"/>
-      <c r="D3" s="38"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="38"/>
-      <c r="G3" s="38"/>
-      <c r="H3" s="38"/>
-      <c r="I3" s="38"/>
-      <c r="J3" s="38"/>
-      <c r="K3" s="39"/>
+      <c r="C3" s="37"/>
+      <c r="D3" s="37"/>
+      <c r="E3" s="37"/>
+      <c r="F3" s="37"/>
+      <c r="G3" s="37"/>
+      <c r="H3" s="37"/>
+      <c r="I3" s="37"/>
+      <c r="J3" s="37"/>
+      <c r="K3" s="38"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B4" s="34" t="s">
+      <c r="B4" s="33" t="s">
         <v>80</v>
       </c>
-      <c r="C4" s="35"/>
-      <c r="D4" s="35"/>
-      <c r="E4" s="35"/>
-      <c r="F4" s="35"/>
-      <c r="G4" s="35"/>
-      <c r="H4" s="35"/>
-      <c r="I4" s="35"/>
-      <c r="J4" s="35"/>
-      <c r="K4" s="36"/>
+      <c r="C4" s="34"/>
+      <c r="D4" s="34"/>
+      <c r="E4" s="34"/>
+      <c r="F4" s="34"/>
+      <c r="G4" s="34"/>
+      <c r="H4" s="34"/>
+      <c r="I4" s="34"/>
+      <c r="J4" s="34"/>
+      <c r="K4" s="35"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B5" s="37" t="s">
+      <c r="B5" s="36" t="s">
         <v>81</v>
       </c>
-      <c r="C5" s="38"/>
-      <c r="D5" s="38"/>
-      <c r="E5" s="38"/>
-      <c r="F5" s="38"/>
-      <c r="G5" s="38"/>
-      <c r="H5" s="38"/>
-      <c r="I5" s="38"/>
-      <c r="J5" s="38"/>
-      <c r="K5" s="39"/>
+      <c r="C5" s="37"/>
+      <c r="D5" s="37"/>
+      <c r="E5" s="37"/>
+      <c r="F5" s="37"/>
+      <c r="G5" s="37"/>
+      <c r="H5" s="37"/>
+      <c r="I5" s="37"/>
+      <c r="J5" s="37"/>
+      <c r="K5" s="38"/>
     </row>
     <row r="6" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="40" t="s">
+      <c r="B6" s="39" t="s">
         <v>82</v>
       </c>
-      <c r="C6" s="41"/>
-      <c r="D6" s="29"/>
-      <c r="E6" s="42" t="s">
+      <c r="C6" s="40"/>
+      <c r="D6" s="27"/>
+      <c r="E6" s="41" t="s">
         <v>83</v>
       </c>
-      <c r="F6" s="41"/>
-      <c r="G6" s="41"/>
-      <c r="H6" s="29"/>
-      <c r="I6" s="42" t="s">
+      <c r="F6" s="40"/>
+      <c r="G6" s="40"/>
+      <c r="H6" s="27"/>
+      <c r="I6" s="41" t="s">
         <v>84</v>
       </c>
-      <c r="J6" s="41"/>
-      <c r="K6" s="30"/>
+      <c r="J6" s="40"/>
+      <c r="K6" s="28"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25"/>
     <row r="8" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="124" t="s">
+      <c r="A8" s="120" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="125"/>
-      <c r="C8" s="125"/>
-      <c r="D8" s="125"/>
-      <c r="E8" s="125"/>
-      <c r="F8" s="125"/>
-      <c r="G8" s="125"/>
-      <c r="H8" s="125"/>
-      <c r="I8" s="125"/>
-      <c r="J8" s="125"/>
-      <c r="K8" s="125"/>
-      <c r="L8" s="125"/>
-      <c r="M8" s="125"/>
+      <c r="B8" s="121"/>
+      <c r="C8" s="121"/>
+      <c r="D8" s="121"/>
+      <c r="E8" s="121"/>
+      <c r="F8" s="121"/>
+      <c r="G8" s="121"/>
+      <c r="H8" s="121"/>
+      <c r="I8" s="121"/>
+      <c r="J8" s="121"/>
+      <c r="K8" s="121"/>
+      <c r="L8" s="121"/>
+      <c r="M8" s="121"/>
     </row>
     <row r="9" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="47" t="s">
+      <c r="A9" s="46" t="s">
         <v>1</v>
       </c>
-      <c r="B9" s="48"/>
-      <c r="C9" s="111" t="s">
+      <c r="B9" s="47"/>
+      <c r="C9" s="107" t="s">
         <v>2</v>
       </c>
-      <c r="D9" s="123"/>
-      <c r="E9" s="123"/>
-      <c r="F9" s="123"/>
-      <c r="G9" s="123"/>
-      <c r="H9" s="123"/>
-      <c r="I9" s="123"/>
-      <c r="J9" s="123"/>
-      <c r="K9" s="123"/>
-      <c r="L9" s="123"/>
-      <c r="M9" s="112"/>
+      <c r="D9" s="119"/>
+      <c r="E9" s="119"/>
+      <c r="F9" s="119"/>
+      <c r="G9" s="119"/>
+      <c r="H9" s="119"/>
+      <c r="I9" s="119"/>
+      <c r="J9" s="119"/>
+      <c r="K9" s="119"/>
+      <c r="L9" s="119"/>
+      <c r="M9" s="108"/>
     </row>
     <row r="10" spans="1:13" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="47" t="s">
+      <c r="A10" s="46" t="s">
         <v>3</v>
       </c>
-      <c r="B10" s="48"/>
-      <c r="C10" s="95" t="s">
+      <c r="B10" s="47"/>
+      <c r="C10" s="94" t="s">
         <v>4</v>
       </c>
-      <c r="D10" s="96"/>
-      <c r="E10" s="96"/>
-      <c r="F10" s="96"/>
-      <c r="G10" s="97"/>
+      <c r="D10" s="95"/>
+      <c r="E10" s="95"/>
+      <c r="F10" s="95"/>
+      <c r="G10" s="96"/>
       <c r="H10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="I10" s="142"/>
-      <c r="J10" s="143"/>
-      <c r="K10" s="143"/>
-      <c r="L10" s="143"/>
-      <c r="M10" s="144"/>
+      <c r="I10" s="138"/>
+      <c r="J10" s="139"/>
+      <c r="K10" s="139"/>
+      <c r="L10" s="139"/>
+      <c r="M10" s="140"/>
     </row>
     <row r="11" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="47" t="s">
+      <c r="A11" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="B11" s="48"/>
-      <c r="C11" s="108"/>
-      <c r="D11" s="109"/>
-      <c r="E11" s="109"/>
-      <c r="F11" s="109"/>
-      <c r="G11" s="109"/>
-      <c r="H11" s="110"/>
-      <c r="I11" s="67" t="s">
+      <c r="B11" s="47"/>
+      <c r="C11" s="163"/>
+      <c r="D11" s="164"/>
+      <c r="E11" s="164"/>
+      <c r="F11" s="164"/>
+      <c r="G11" s="164"/>
+      <c r="H11" s="165"/>
+      <c r="I11" s="66" t="s">
         <v>7</v>
       </c>
-      <c r="J11" s="68"/>
-      <c r="K11" s="126"/>
-      <c r="L11" s="127"/>
-      <c r="M11" s="128"/>
+      <c r="J11" s="67"/>
+      <c r="K11" s="122"/>
+      <c r="L11" s="123"/>
+      <c r="M11" s="124"/>
     </row>
     <row r="12" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="47" t="s">
+      <c r="A12" s="46" t="s">
         <v>8</v>
       </c>
-      <c r="B12" s="48"/>
+      <c r="B12" s="47"/>
       <c r="C12" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D12" s="111" t="s">
+      <c r="D12" s="107" t="s">
         <v>10</v>
       </c>
-      <c r="E12" s="112"/>
-      <c r="F12" s="69" t="s">
+      <c r="E12" s="108"/>
+      <c r="F12" s="68" t="s">
         <v>11</v>
       </c>
-      <c r="G12" s="71"/>
+      <c r="G12" s="70"/>
       <c r="H12" s="1"/>
-      <c r="I12" s="69" t="s">
+      <c r="I12" s="68" t="s">
         <v>12</v>
       </c>
-      <c r="J12" s="71"/>
-      <c r="K12" s="129"/>
-      <c r="L12" s="130"/>
-      <c r="M12" s="131"/>
+      <c r="J12" s="70"/>
+      <c r="K12" s="125"/>
+      <c r="L12" s="126"/>
+      <c r="M12" s="127"/>
     </row>
     <row r="13" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="47" t="s">
+      <c r="A13" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="48"/>
-      <c r="C13" s="98"/>
-      <c r="D13" s="99"/>
-      <c r="E13" s="99"/>
-      <c r="F13" s="100"/>
-      <c r="G13" s="98" t="s">
+      <c r="B13" s="47"/>
+      <c r="C13" s="97"/>
+      <c r="D13" s="98"/>
+      <c r="E13" s="98"/>
+      <c r="F13" s="99"/>
+      <c r="G13" s="97" t="s">
         <v>14</v>
       </c>
-      <c r="H13" s="99"/>
-      <c r="I13" s="100"/>
-      <c r="J13" s="132"/>
-      <c r="K13" s="133"/>
-      <c r="L13" s="133"/>
-      <c r="M13" s="134"/>
+      <c r="H13" s="98"/>
+      <c r="I13" s="99"/>
+      <c r="J13" s="128"/>
+      <c r="K13" s="129"/>
+      <c r="L13" s="129"/>
+      <c r="M13" s="130"/>
     </row>
     <row r="14" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="101" t="s">
+      <c r="A14" s="100" t="s">
         <v>15</v>
       </c>
-      <c r="B14" s="47" t="s">
+      <c r="B14" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="C14" s="104"/>
-      <c r="D14" s="48"/>
-      <c r="E14" s="116"/>
-      <c r="F14" s="117"/>
-      <c r="G14" s="117"/>
-      <c r="H14" s="117"/>
-      <c r="I14" s="117"/>
-      <c r="J14" s="117"/>
-      <c r="K14" s="117"/>
-      <c r="L14" s="117"/>
-      <c r="M14" s="118"/>
+      <c r="C14" s="103"/>
+      <c r="D14" s="47"/>
+      <c r="E14" s="112"/>
+      <c r="F14" s="113"/>
+      <c r="G14" s="113"/>
+      <c r="H14" s="113"/>
+      <c r="I14" s="113"/>
+      <c r="J14" s="113"/>
+      <c r="K14" s="113"/>
+      <c r="L14" s="113"/>
+      <c r="M14" s="114"/>
     </row>
     <row r="15" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="102"/>
-      <c r="B15" s="105" t="s">
+      <c r="A15" s="101"/>
+      <c r="B15" s="104" t="s">
         <v>17</v>
       </c>
-      <c r="C15" s="106"/>
-      <c r="D15" s="107"/>
-      <c r="E15" s="135"/>
-      <c r="F15" s="136"/>
-      <c r="G15" s="136"/>
-      <c r="H15" s="136"/>
-      <c r="I15" s="136"/>
-      <c r="J15" s="136"/>
-      <c r="K15" s="136"/>
-      <c r="L15" s="136"/>
-      <c r="M15" s="137"/>
+      <c r="C15" s="105"/>
+      <c r="D15" s="106"/>
+      <c r="E15" s="131"/>
+      <c r="F15" s="132"/>
+      <c r="G15" s="132"/>
+      <c r="H15" s="132"/>
+      <c r="I15" s="132"/>
+      <c r="J15" s="132"/>
+      <c r="K15" s="132"/>
+      <c r="L15" s="132"/>
+      <c r="M15" s="133"/>
     </row>
     <row r="16" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="102"/>
-      <c r="B16" s="47" t="s">
+      <c r="A16" s="101"/>
+      <c r="B16" s="46" t="s">
         <v>18</v>
       </c>
-      <c r="C16" s="104"/>
-      <c r="D16" s="48"/>
-      <c r="E16" s="116"/>
-      <c r="F16" s="117"/>
-      <c r="G16" s="117"/>
-      <c r="H16" s="117"/>
-      <c r="I16" s="117"/>
-      <c r="J16" s="117"/>
-      <c r="K16" s="117"/>
-      <c r="L16" s="117"/>
-      <c r="M16" s="118"/>
+      <c r="C16" s="103"/>
+      <c r="D16" s="47"/>
+      <c r="E16" s="112"/>
+      <c r="F16" s="113"/>
+      <c r="G16" s="113"/>
+      <c r="H16" s="113"/>
+      <c r="I16" s="113"/>
+      <c r="J16" s="113"/>
+      <c r="K16" s="113"/>
+      <c r="L16" s="113"/>
+      <c r="M16" s="114"/>
     </row>
     <row r="17" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="102"/>
-      <c r="B17" s="47" t="s">
+      <c r="A17" s="101"/>
+      <c r="B17" s="46" t="s">
         <v>19</v>
       </c>
-      <c r="C17" s="104"/>
-      <c r="D17" s="48"/>
-      <c r="E17" s="116"/>
-      <c r="F17" s="117"/>
-      <c r="G17" s="117"/>
-      <c r="H17" s="117"/>
-      <c r="I17" s="117"/>
-      <c r="J17" s="117"/>
-      <c r="K17" s="117"/>
-      <c r="L17" s="117"/>
-      <c r="M17" s="118"/>
+      <c r="C17" s="103"/>
+      <c r="D17" s="47"/>
+      <c r="E17" s="112"/>
+      <c r="F17" s="113"/>
+      <c r="G17" s="113"/>
+      <c r="H17" s="113"/>
+      <c r="I17" s="113"/>
+      <c r="J17" s="113"/>
+      <c r="K17" s="113"/>
+      <c r="L17" s="113"/>
+      <c r="M17" s="114"/>
     </row>
     <row r="18" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="102"/>
-      <c r="B18" s="47" t="s">
+      <c r="A18" s="101"/>
+      <c r="B18" s="46" t="s">
         <v>20</v>
       </c>
-      <c r="C18" s="104"/>
-      <c r="D18" s="48"/>
-      <c r="E18" s="116"/>
-      <c r="F18" s="117"/>
-      <c r="G18" s="117"/>
-      <c r="H18" s="117"/>
-      <c r="I18" s="117"/>
-      <c r="J18" s="117"/>
-      <c r="K18" s="117"/>
-      <c r="L18" s="117"/>
-      <c r="M18" s="118"/>
+      <c r="C18" s="103"/>
+      <c r="D18" s="47"/>
+      <c r="E18" s="112"/>
+      <c r="F18" s="113"/>
+      <c r="G18" s="113"/>
+      <c r="H18" s="113"/>
+      <c r="I18" s="113"/>
+      <c r="J18" s="113"/>
+      <c r="K18" s="113"/>
+      <c r="L18" s="113"/>
+      <c r="M18" s="114"/>
     </row>
     <row r="19" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="102"/>
-      <c r="B19" s="47" t="s">
+      <c r="A19" s="101"/>
+      <c r="B19" s="46" t="s">
         <v>21</v>
       </c>
-      <c r="C19" s="104"/>
-      <c r="D19" s="48"/>
-      <c r="E19" s="116"/>
-      <c r="F19" s="117"/>
-      <c r="G19" s="117"/>
-      <c r="H19" s="117"/>
-      <c r="I19" s="117"/>
-      <c r="J19" s="117"/>
-      <c r="K19" s="117"/>
-      <c r="L19" s="117"/>
-      <c r="M19" s="118"/>
+      <c r="C19" s="103"/>
+      <c r="D19" s="47"/>
+      <c r="E19" s="112"/>
+      <c r="F19" s="113"/>
+      <c r="G19" s="113"/>
+      <c r="H19" s="113"/>
+      <c r="I19" s="113"/>
+      <c r="J19" s="113"/>
+      <c r="K19" s="113"/>
+      <c r="L19" s="113"/>
+      <c r="M19" s="114"/>
     </row>
     <row r="20" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="102"/>
-      <c r="B20" s="47" t="s">
+      <c r="A20" s="101"/>
+      <c r="B20" s="46" t="s">
         <v>22</v>
       </c>
-      <c r="C20" s="104"/>
-      <c r="D20" s="48"/>
-      <c r="E20" s="113"/>
-      <c r="F20" s="114"/>
-      <c r="G20" s="114"/>
-      <c r="H20" s="114"/>
-      <c r="I20" s="114"/>
-      <c r="J20" s="114"/>
-      <c r="K20" s="114"/>
-      <c r="L20" s="114"/>
-      <c r="M20" s="115"/>
+      <c r="C20" s="103"/>
+      <c r="D20" s="47"/>
+      <c r="E20" s="109"/>
+      <c r="F20" s="110"/>
+      <c r="G20" s="110"/>
+      <c r="H20" s="110"/>
+      <c r="I20" s="110"/>
+      <c r="J20" s="110"/>
+      <c r="K20" s="110"/>
+      <c r="L20" s="110"/>
+      <c r="M20" s="111"/>
     </row>
     <row r="21" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="102"/>
-      <c r="B21" s="47" t="s">
+      <c r="A21" s="101"/>
+      <c r="B21" s="46" t="s">
         <v>23</v>
       </c>
-      <c r="C21" s="104"/>
-      <c r="D21" s="48"/>
-      <c r="E21" s="113"/>
-      <c r="F21" s="114"/>
-      <c r="G21" s="114"/>
-      <c r="H21" s="114"/>
-      <c r="I21" s="114"/>
-      <c r="J21" s="114"/>
-      <c r="K21" s="114"/>
-      <c r="L21" s="114"/>
-      <c r="M21" s="115"/>
+      <c r="C21" s="103"/>
+      <c r="D21" s="47"/>
+      <c r="E21" s="109"/>
+      <c r="F21" s="110"/>
+      <c r="G21" s="110"/>
+      <c r="H21" s="110"/>
+      <c r="I21" s="110"/>
+      <c r="J21" s="110"/>
+      <c r="K21" s="110"/>
+      <c r="L21" s="110"/>
+      <c r="M21" s="111"/>
     </row>
     <row r="22" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="103"/>
-      <c r="B22" s="47" t="s">
+      <c r="A22" s="102"/>
+      <c r="B22" s="46" t="s">
         <v>24</v>
       </c>
-      <c r="C22" s="104"/>
-      <c r="D22" s="48"/>
-      <c r="E22" s="113"/>
-      <c r="F22" s="114"/>
-      <c r="G22" s="114"/>
-      <c r="H22" s="114"/>
-      <c r="I22" s="114"/>
-      <c r="J22" s="114"/>
-      <c r="K22" s="114"/>
-      <c r="L22" s="114"/>
-      <c r="M22" s="115"/>
+      <c r="C22" s="103"/>
+      <c r="D22" s="47"/>
+      <c r="E22" s="109"/>
+      <c r="F22" s="110"/>
+      <c r="G22" s="110"/>
+      <c r="H22" s="110"/>
+      <c r="I22" s="110"/>
+      <c r="J22" s="110"/>
+      <c r="K22" s="110"/>
+      <c r="L22" s="110"/>
+      <c r="M22" s="111"/>
     </row>
     <row r="23" spans="1:13" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="119" t="s">
+      <c r="A23" s="115" t="s">
         <v>25</v>
       </c>
-      <c r="B23" s="47" t="s">
+      <c r="B23" s="46" t="s">
         <v>26</v>
       </c>
-      <c r="C23" s="104"/>
-      <c r="D23" s="48"/>
-      <c r="E23" s="120" t="s">
+      <c r="C23" s="103"/>
+      <c r="D23" s="47"/>
+      <c r="E23" s="116" t="s">
         <v>27</v>
       </c>
-      <c r="F23" s="121"/>
-      <c r="G23" s="121"/>
-      <c r="H23" s="121"/>
-      <c r="I23" s="121"/>
-      <c r="J23" s="121"/>
-      <c r="K23" s="121"/>
-      <c r="L23" s="121"/>
-      <c r="M23" s="122"/>
+      <c r="F23" s="117"/>
+      <c r="G23" s="117"/>
+      <c r="H23" s="117"/>
+      <c r="I23" s="117"/>
+      <c r="J23" s="117"/>
+      <c r="K23" s="117"/>
+      <c r="L23" s="117"/>
+      <c r="M23" s="118"/>
     </row>
     <row r="24" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="102"/>
-      <c r="B24" s="47" t="s">
+      <c r="A24" s="101"/>
+      <c r="B24" s="46" t="s">
         <v>19</v>
       </c>
-      <c r="C24" s="104"/>
-      <c r="D24" s="48"/>
-      <c r="E24" s="44"/>
-      <c r="F24" s="45"/>
-      <c r="G24" s="45"/>
-      <c r="H24" s="45"/>
-      <c r="I24" s="45"/>
-      <c r="J24" s="45"/>
-      <c r="K24" s="45"/>
-      <c r="L24" s="45"/>
-      <c r="M24" s="46"/>
+      <c r="C24" s="103"/>
+      <c r="D24" s="47"/>
+      <c r="E24" s="43"/>
+      <c r="F24" s="44"/>
+      <c r="G24" s="44"/>
+      <c r="H24" s="44"/>
+      <c r="I24" s="44"/>
+      <c r="J24" s="44"/>
+      <c r="K24" s="44"/>
+      <c r="L24" s="44"/>
+      <c r="M24" s="45"/>
     </row>
     <row r="25" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="103"/>
-      <c r="B25" s="47" t="s">
+      <c r="A25" s="102"/>
+      <c r="B25" s="46" t="s">
         <v>22</v>
       </c>
-      <c r="C25" s="104"/>
-      <c r="D25" s="48"/>
-      <c r="E25" s="120" t="s">
+      <c r="C25" s="103"/>
+      <c r="D25" s="47"/>
+      <c r="E25" s="116" t="s">
         <v>28</v>
       </c>
-      <c r="F25" s="121"/>
-      <c r="G25" s="121"/>
-      <c r="H25" s="121"/>
-      <c r="I25" s="121"/>
-      <c r="J25" s="121"/>
-      <c r="K25" s="121"/>
-      <c r="L25" s="121"/>
-      <c r="M25" s="122"/>
-    </row>
-    <row r="26" spans="1:13" ht="25.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F25" s="117"/>
+      <c r="G25" s="117"/>
+      <c r="H25" s="117"/>
+      <c r="I25" s="117"/>
+      <c r="J25" s="117"/>
+      <c r="K25" s="117"/>
+      <c r="L25" s="117"/>
+      <c r="M25" s="118"/>
+    </row>
+    <row r="26" spans="1:13" ht="23.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B26" s="47" t="s">
+      <c r="B26" s="46" t="s">
         <v>32</v>
       </c>
-      <c r="C26" s="104"/>
-      <c r="D26" s="48"/>
-      <c r="E26" s="116"/>
-      <c r="F26" s="117"/>
-      <c r="G26" s="117"/>
-      <c r="H26" s="117"/>
-      <c r="I26" s="117"/>
-      <c r="J26" s="117"/>
-      <c r="K26" s="117"/>
-      <c r="L26" s="117"/>
-      <c r="M26" s="118"/>
-    </row>
-    <row r="27" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C26" s="103"/>
+      <c r="D26" s="47"/>
+      <c r="E26" s="112"/>
+      <c r="F26" s="113"/>
+      <c r="G26" s="113"/>
+      <c r="H26" s="113"/>
+      <c r="I26" s="113"/>
+      <c r="J26" s="113"/>
+      <c r="K26" s="113"/>
+      <c r="L26" s="113"/>
+      <c r="M26" s="114"/>
+    </row>
+    <row r="27" spans="1:13" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="B27" s="47" t="s">
+      <c r="B27" s="46" t="s">
         <v>20</v>
       </c>
-      <c r="C27" s="104"/>
-      <c r="D27" s="48"/>
-      <c r="E27" s="116"/>
-      <c r="F27" s="117"/>
-      <c r="G27" s="117"/>
-      <c r="H27" s="117"/>
-      <c r="I27" s="117"/>
-      <c r="J27" s="117"/>
-      <c r="K27" s="117"/>
-      <c r="L27" s="117"/>
-      <c r="M27" s="118"/>
+      <c r="C27" s="103"/>
+      <c r="D27" s="47"/>
+      <c r="E27" s="112"/>
+      <c r="F27" s="113"/>
+      <c r="G27" s="113"/>
+      <c r="H27" s="113"/>
+      <c r="I27" s="113"/>
+      <c r="J27" s="113"/>
+      <c r="K27" s="113"/>
+      <c r="L27" s="113"/>
+      <c r="M27" s="114"/>
     </row>
     <row r="28" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="3"/>
-      <c r="B28" s="47" t="s">
+      <c r="B28" s="46" t="s">
         <v>33</v>
       </c>
-      <c r="C28" s="104"/>
-      <c r="D28" s="48"/>
-      <c r="E28" s="116"/>
-      <c r="F28" s="117"/>
-      <c r="G28" s="117"/>
-      <c r="H28" s="117"/>
-      <c r="I28" s="117"/>
-      <c r="J28" s="117"/>
-      <c r="K28" s="117"/>
-      <c r="L28" s="117"/>
-      <c r="M28" s="118"/>
+      <c r="C28" s="103"/>
+      <c r="D28" s="47"/>
+      <c r="E28" s="112"/>
+      <c r="F28" s="113"/>
+      <c r="G28" s="113"/>
+      <c r="H28" s="113"/>
+      <c r="I28" s="113"/>
+      <c r="J28" s="113"/>
+      <c r="K28" s="113"/>
+      <c r="L28" s="113"/>
+      <c r="M28" s="114"/>
     </row>
     <row r="29" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="3"/>
-      <c r="B29" s="47" t="s">
+      <c r="B29" s="46" t="s">
         <v>34</v>
       </c>
-      <c r="C29" s="104"/>
-      <c r="D29" s="48"/>
-      <c r="E29" s="116"/>
-      <c r="F29" s="117"/>
-      <c r="G29" s="117"/>
-      <c r="H29" s="117"/>
-      <c r="I29" s="117"/>
-      <c r="J29" s="117"/>
-      <c r="K29" s="117"/>
-      <c r="L29" s="117"/>
-      <c r="M29" s="118"/>
+      <c r="C29" s="103"/>
+      <c r="D29" s="47"/>
+      <c r="E29" s="112"/>
+      <c r="F29" s="113"/>
+      <c r="G29" s="113"/>
+      <c r="H29" s="113"/>
+      <c r="I29" s="113"/>
+      <c r="J29" s="113"/>
+      <c r="K29" s="113"/>
+      <c r="L29" s="113"/>
+      <c r="M29" s="114"/>
     </row>
     <row r="30" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="B30" s="47" t="s">
+      <c r="B30" s="46" t="s">
         <v>35</v>
       </c>
-      <c r="C30" s="104"/>
-      <c r="D30" s="48"/>
-      <c r="E30" s="116"/>
-      <c r="F30" s="117"/>
-      <c r="G30" s="117"/>
-      <c r="H30" s="117"/>
-      <c r="I30" s="117"/>
-      <c r="J30" s="117"/>
-      <c r="K30" s="117"/>
-      <c r="L30" s="117"/>
-      <c r="M30" s="118"/>
+      <c r="C30" s="103"/>
+      <c r="D30" s="47"/>
+      <c r="E30" s="112"/>
+      <c r="F30" s="113"/>
+      <c r="G30" s="113"/>
+      <c r="H30" s="113"/>
+      <c r="I30" s="113"/>
+      <c r="J30" s="113"/>
+      <c r="K30" s="113"/>
+      <c r="L30" s="113"/>
+      <c r="M30" s="114"/>
     </row>
     <row r="31" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="6"/>
-      <c r="B31" s="47" t="s">
+      <c r="B31" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="C31" s="104"/>
-      <c r="D31" s="48"/>
-      <c r="E31" s="116"/>
-      <c r="F31" s="117"/>
-      <c r="G31" s="117"/>
-      <c r="H31" s="117"/>
-      <c r="I31" s="117"/>
-      <c r="J31" s="117"/>
-      <c r="K31" s="117"/>
-      <c r="L31" s="117"/>
-      <c r="M31" s="118"/>
+      <c r="C31" s="103"/>
+      <c r="D31" s="47"/>
+      <c r="E31" s="112"/>
+      <c r="F31" s="113"/>
+      <c r="G31" s="113"/>
+      <c r="H31" s="113"/>
+      <c r="I31" s="113"/>
+      <c r="J31" s="113"/>
+      <c r="K31" s="113"/>
+      <c r="L31" s="113"/>
+      <c r="M31" s="114"/>
     </row>
     <row r="32" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="6"/>
-      <c r="B32" s="47" t="s">
+      <c r="B32" s="46" t="s">
         <v>19</v>
       </c>
-      <c r="C32" s="104"/>
-      <c r="D32" s="48"/>
-      <c r="E32" s="113"/>
-      <c r="F32" s="114"/>
-      <c r="G32" s="114"/>
-      <c r="H32" s="114"/>
-      <c r="I32" s="114"/>
-      <c r="J32" s="114"/>
-      <c r="K32" s="114"/>
-      <c r="L32" s="114"/>
-      <c r="M32" s="115"/>
+      <c r="C32" s="103"/>
+      <c r="D32" s="47"/>
+      <c r="E32" s="109"/>
+      <c r="F32" s="110"/>
+      <c r="G32" s="110"/>
+      <c r="H32" s="110"/>
+      <c r="I32" s="110"/>
+      <c r="J32" s="110"/>
+      <c r="K32" s="110"/>
+      <c r="L32" s="110"/>
+      <c r="M32" s="111"/>
     </row>
     <row r="33" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="6"/>
-      <c r="B33" s="47" t="s">
+      <c r="B33" s="46" t="s">
         <v>37</v>
       </c>
-      <c r="C33" s="104"/>
-      <c r="D33" s="48"/>
-      <c r="E33" s="116"/>
-      <c r="F33" s="117"/>
-      <c r="G33" s="117"/>
-      <c r="H33" s="117"/>
-      <c r="I33" s="117"/>
-      <c r="J33" s="117"/>
-      <c r="K33" s="117"/>
-      <c r="L33" s="117"/>
-      <c r="M33" s="118"/>
+      <c r="C33" s="103"/>
+      <c r="D33" s="47"/>
+      <c r="E33" s="112"/>
+      <c r="F33" s="113"/>
+      <c r="G33" s="113"/>
+      <c r="H33" s="113"/>
+      <c r="I33" s="113"/>
+      <c r="J33" s="113"/>
+      <c r="K33" s="113"/>
+      <c r="L33" s="113"/>
+      <c r="M33" s="114"/>
     </row>
     <row r="34" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="7"/>
-      <c r="B34" s="138" t="s">
+      <c r="B34" s="134" t="s">
         <v>38</v>
       </c>
-      <c r="C34" s="139"/>
-      <c r="D34" s="140"/>
-      <c r="E34" s="113"/>
-      <c r="F34" s="114"/>
-      <c r="G34" s="114"/>
-      <c r="H34" s="114"/>
-      <c r="I34" s="114"/>
-      <c r="J34" s="114"/>
-      <c r="K34" s="114"/>
-      <c r="L34" s="114"/>
-      <c r="M34" s="115"/>
+      <c r="C34" s="135"/>
+      <c r="D34" s="136"/>
+      <c r="E34" s="109"/>
+      <c r="F34" s="110"/>
+      <c r="G34" s="110"/>
+      <c r="H34" s="110"/>
+      <c r="I34" s="110"/>
+      <c r="J34" s="110"/>
+      <c r="K34" s="110"/>
+      <c r="L34" s="110"/>
+      <c r="M34" s="111"/>
     </row>
     <row r="35" spans="1:13" ht="25.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="B35" s="162" t="s">
+      <c r="B35" s="158" t="s">
         <v>41</v>
       </c>
-      <c r="C35" s="163"/>
-      <c r="D35" s="164"/>
-      <c r="E35" s="113"/>
-      <c r="F35" s="114"/>
-      <c r="G35" s="114"/>
-      <c r="H35" s="114"/>
-      <c r="I35" s="114"/>
-      <c r="J35" s="114"/>
-      <c r="K35" s="114"/>
-      <c r="L35" s="114"/>
-      <c r="M35" s="115"/>
+      <c r="C35" s="159"/>
+      <c r="D35" s="160"/>
+      <c r="E35" s="109"/>
+      <c r="F35" s="110"/>
+      <c r="G35" s="110"/>
+      <c r="H35" s="110"/>
+      <c r="I35" s="110"/>
+      <c r="J35" s="110"/>
+      <c r="K35" s="110"/>
+      <c r="L35" s="110"/>
+      <c r="M35" s="111"/>
     </row>
     <row r="36" spans="1:13" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="B36" s="47" t="s">
+      <c r="B36" s="46" t="s">
         <v>42</v>
       </c>
-      <c r="C36" s="104"/>
-      <c r="D36" s="48"/>
-      <c r="E36" s="113"/>
-      <c r="F36" s="114"/>
-      <c r="G36" s="114"/>
-      <c r="H36" s="114"/>
-      <c r="I36" s="114"/>
-      <c r="J36" s="114"/>
-      <c r="K36" s="114"/>
-      <c r="L36" s="114"/>
-      <c r="M36" s="115"/>
+      <c r="C36" s="103"/>
+      <c r="D36" s="47"/>
+      <c r="E36" s="109"/>
+      <c r="F36" s="110"/>
+      <c r="G36" s="110"/>
+      <c r="H36" s="110"/>
+      <c r="I36" s="110"/>
+      <c r="J36" s="110"/>
+      <c r="K36" s="110"/>
+      <c r="L36" s="110"/>
+      <c r="M36" s="111"/>
     </row>
     <row r="37" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="10"/>
-      <c r="B37" s="47" t="s">
+      <c r="B37" s="46" t="s">
         <v>19</v>
       </c>
-      <c r="C37" s="104"/>
-      <c r="D37" s="48"/>
-      <c r="E37" s="113"/>
-      <c r="F37" s="114"/>
-      <c r="G37" s="114"/>
-      <c r="H37" s="114"/>
-      <c r="I37" s="114"/>
-      <c r="J37" s="114"/>
-      <c r="K37" s="114"/>
-      <c r="L37" s="114"/>
-      <c r="M37" s="115"/>
+      <c r="C37" s="103"/>
+      <c r="D37" s="47"/>
+      <c r="E37" s="109"/>
+      <c r="F37" s="110"/>
+      <c r="G37" s="110"/>
+      <c r="H37" s="110"/>
+      <c r="I37" s="110"/>
+      <c r="J37" s="110"/>
+      <c r="K37" s="110"/>
+      <c r="L37" s="110"/>
+      <c r="M37" s="111"/>
     </row>
     <row r="38" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="141" t="s">
+      <c r="A38" s="137" t="s">
         <v>43</v>
       </c>
-      <c r="B38" s="141"/>
-      <c r="C38" s="141"/>
-      <c r="D38" s="141"/>
-      <c r="E38" s="141"/>
-      <c r="F38" s="141"/>
-      <c r="G38" s="141"/>
-      <c r="H38" s="141"/>
-      <c r="I38" s="141"/>
-      <c r="J38" s="141"/>
-      <c r="K38" s="141"/>
-      <c r="L38" s="141"/>
-      <c r="M38" s="141"/>
+      <c r="B38" s="137"/>
+      <c r="C38" s="137"/>
+      <c r="D38" s="137"/>
+      <c r="E38" s="137"/>
+      <c r="F38" s="137"/>
+      <c r="G38" s="137"/>
+      <c r="H38" s="137"/>
+      <c r="I38" s="137"/>
+      <c r="J38" s="137"/>
+      <c r="K38" s="137"/>
+      <c r="L38" s="137"/>
+      <c r="M38" s="137"/>
     </row>
     <row r="39" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="141"/>
-      <c r="B39" s="141"/>
-      <c r="C39" s="141"/>
-      <c r="D39" s="141"/>
-      <c r="E39" s="141"/>
-      <c r="F39" s="141"/>
-      <c r="G39" s="141"/>
-      <c r="H39" s="141"/>
-      <c r="I39" s="141"/>
-      <c r="J39" s="141"/>
-      <c r="K39" s="141"/>
-      <c r="L39" s="141"/>
-      <c r="M39" s="141"/>
+      <c r="A39" s="137"/>
+      <c r="B39" s="137"/>
+      <c r="C39" s="137"/>
+      <c r="D39" s="137"/>
+      <c r="E39" s="137"/>
+      <c r="F39" s="137"/>
+      <c r="G39" s="137"/>
+      <c r="H39" s="137"/>
+      <c r="I39" s="137"/>
+      <c r="J39" s="137"/>
+      <c r="K39" s="137"/>
+      <c r="L39" s="137"/>
+      <c r="M39" s="137"/>
     </row>
     <row r="40" spans="1:13" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="141"/>
-      <c r="B40" s="141"/>
-      <c r="C40" s="141"/>
-      <c r="D40" s="141"/>
-      <c r="E40" s="141"/>
-      <c r="F40" s="141"/>
-      <c r="G40" s="141"/>
-      <c r="H40" s="141"/>
-      <c r="I40" s="141"/>
-      <c r="J40" s="141"/>
-      <c r="K40" s="141"/>
-      <c r="L40" s="141"/>
-      <c r="M40" s="141"/>
+      <c r="A40" s="137"/>
+      <c r="B40" s="137"/>
+      <c r="C40" s="137"/>
+      <c r="D40" s="137"/>
+      <c r="E40" s="137"/>
+      <c r="F40" s="137"/>
+      <c r="G40" s="137"/>
+      <c r="H40" s="137"/>
+      <c r="I40" s="137"/>
+      <c r="J40" s="137"/>
+      <c r="K40" s="137"/>
+      <c r="L40" s="137"/>
+      <c r="M40" s="137"/>
     </row>
     <row r="41" spans="1:13" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="11"/>
-      <c r="B41" s="80" t="s">
+      <c r="B41" s="79" t="s">
         <v>65</v>
       </c>
-      <c r="C41" s="80"/>
-      <c r="D41" s="80"/>
-      <c r="E41" s="80"/>
-      <c r="F41" s="80"/>
-      <c r="G41" s="80"/>
-      <c r="H41" s="80"/>
-      <c r="I41" s="80"/>
-      <c r="J41" s="80"/>
+      <c r="C41" s="79"/>
+      <c r="D41" s="79"/>
+      <c r="E41" s="79"/>
+      <c r="F41" s="79"/>
+      <c r="G41" s="79"/>
+      <c r="H41" s="79"/>
+      <c r="I41" s="79"/>
+      <c r="J41" s="79"/>
       <c r="K41" s="11"/>
       <c r="L41" s="11"/>
       <c r="M41" s="11"/>
     </row>
     <row r="42" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B42" s="80" t="s">
+      <c r="B42" s="79" t="s">
         <v>66</v>
       </c>
-      <c r="C42" s="80"/>
-      <c r="D42" s="80"/>
-      <c r="E42" s="80"/>
-      <c r="F42" s="80"/>
-      <c r="G42" s="80"/>
-      <c r="H42" s="80"/>
-      <c r="I42" s="80"/>
-      <c r="J42" s="80"/>
+      <c r="C42" s="79"/>
+      <c r="D42" s="79"/>
+      <c r="E42" s="79"/>
+      <c r="F42" s="79"/>
+      <c r="G42" s="79"/>
+      <c r="H42" s="79"/>
+      <c r="I42" s="79"/>
+      <c r="J42" s="79"/>
       <c r="L42" s="18"/>
     </row>
     <row r="43" spans="1:13" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B43" s="152" t="s">
+      <c r="B43" s="148" t="s">
         <v>72</v>
       </c>
-      <c r="C43" s="153"/>
-      <c r="D43" s="20"/>
-      <c r="E43" s="84" t="s">
+      <c r="C43" s="149"/>
+      <c r="D43" s="166"/>
+      <c r="E43" s="83" t="s">
         <v>75</v>
       </c>
-      <c r="F43" s="85"/>
-      <c r="G43" s="86"/>
-      <c r="H43" s="87"/>
+      <c r="F43" s="84"/>
+      <c r="G43" s="85"/>
+      <c r="H43" s="86"/>
       <c r="I43" s="17" t="s">
         <v>76</v>
       </c>
-      <c r="J43" s="19"/>
+      <c r="J43" s="167"/>
     </row>
     <row r="44" spans="1:13" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B44" s="154" t="s">
+      <c r="B44" s="150" t="s">
         <v>73</v>
       </c>
-      <c r="C44" s="155"/>
-      <c r="D44" s="21" t="s">
+      <c r="C44" s="151"/>
+      <c r="D44" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="E44" s="156" t="s">
+      <c r="E44" s="152" t="s">
         <v>74</v>
       </c>
-      <c r="F44" s="157"/>
-      <c r="G44" s="158"/>
-      <c r="H44" s="159"/>
-      <c r="I44" s="160"/>
-      <c r="J44" s="161"/>
+      <c r="F44" s="153"/>
+      <c r="G44" s="154"/>
+      <c r="H44" s="155"/>
+      <c r="I44" s="156"/>
+      <c r="J44" s="157"/>
     </row>
     <row r="45" spans="1:13" ht="2.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="46" spans="1:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="11"/>
-      <c r="B46" s="81" t="s">
+      <c r="B46" s="80" t="s">
         <v>45</v>
       </c>
-      <c r="C46" s="82"/>
-      <c r="D46" s="82"/>
-      <c r="E46" s="82"/>
-      <c r="F46" s="82"/>
-      <c r="G46" s="82"/>
-      <c r="H46" s="82"/>
-      <c r="I46" s="82"/>
-      <c r="J46" s="83"/>
+      <c r="C46" s="81"/>
+      <c r="D46" s="81"/>
+      <c r="E46" s="81"/>
+      <c r="F46" s="81"/>
+      <c r="G46" s="81"/>
+      <c r="H46" s="81"/>
+      <c r="I46" s="81"/>
+      <c r="J46" s="82"/>
       <c r="K46" s="11"/>
       <c r="L46" s="11"/>
       <c r="M46" s="11"/>
     </row>
     <row r="47" spans="1:13" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="11"/>
-      <c r="B47" s="65" t="s">
+      <c r="B47" s="64" t="s">
         <v>46</v>
       </c>
-      <c r="C47" s="66"/>
-      <c r="D47" s="69" t="s">
+      <c r="C47" s="65"/>
+      <c r="D47" s="68" t="s">
         <v>47</v>
       </c>
-      <c r="E47" s="70"/>
-      <c r="F47" s="70"/>
-      <c r="G47" s="71"/>
-      <c r="H47" s="72" t="s">
+      <c r="E47" s="69"/>
+      <c r="F47" s="69"/>
+      <c r="G47" s="70"/>
+      <c r="H47" s="71" t="s">
         <v>48</v>
       </c>
-      <c r="I47" s="73"/>
-      <c r="J47" s="74"/>
+      <c r="I47" s="72"/>
+      <c r="J47" s="73"/>
       <c r="K47" s="11"/>
       <c r="L47" s="11"/>
       <c r="M47" s="11"/>
     </row>
     <row r="48" spans="1:13" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="11"/>
-      <c r="B48" s="67"/>
-      <c r="C48" s="68"/>
-      <c r="D48" s="78" t="s">
+      <c r="B48" s="66"/>
+      <c r="C48" s="67"/>
+      <c r="D48" s="77" t="s">
         <v>49</v>
       </c>
-      <c r="E48" s="79"/>
-      <c r="F48" s="78" t="s">
+      <c r="E48" s="78"/>
+      <c r="F48" s="77" t="s">
         <v>50</v>
       </c>
-      <c r="G48" s="79"/>
-      <c r="H48" s="75"/>
-      <c r="I48" s="76"/>
-      <c r="J48" s="77"/>
+      <c r="G48" s="78"/>
+      <c r="H48" s="74"/>
+      <c r="I48" s="75"/>
+      <c r="J48" s="76"/>
       <c r="K48" s="11"/>
       <c r="L48" s="11"/>
       <c r="M48" s="11"/>
     </row>
     <row r="49" spans="1:13" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="13"/>
-      <c r="B49" s="52" t="s">
+      <c r="B49" s="51" t="s">
         <v>51</v>
       </c>
-      <c r="C49" s="53"/>
-      <c r="D49" s="54"/>
-      <c r="E49" s="55"/>
-      <c r="F49" s="54"/>
-      <c r="G49" s="55"/>
-      <c r="H49" s="56"/>
-      <c r="I49" s="57"/>
-      <c r="J49" s="58"/>
+      <c r="C49" s="52"/>
+      <c r="D49" s="53"/>
+      <c r="E49" s="54"/>
+      <c r="F49" s="53"/>
+      <c r="G49" s="54"/>
+      <c r="H49" s="55"/>
+      <c r="I49" s="56"/>
+      <c r="J49" s="57"/>
       <c r="K49" s="13"/>
       <c r="L49" s="13"/>
       <c r="M49" s="13"/>
     </row>
     <row r="50" spans="1:13" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="13"/>
-      <c r="B50" s="52" t="s">
+      <c r="B50" s="51" t="s">
         <v>52</v>
       </c>
-      <c r="C50" s="53"/>
-      <c r="D50" s="54"/>
-      <c r="E50" s="55"/>
-      <c r="F50" s="145"/>
-      <c r="G50" s="146"/>
-      <c r="H50" s="56"/>
-      <c r="I50" s="57"/>
-      <c r="J50" s="58"/>
+      <c r="C50" s="52"/>
+      <c r="D50" s="53"/>
+      <c r="E50" s="54"/>
+      <c r="F50" s="141"/>
+      <c r="G50" s="142"/>
+      <c r="H50" s="55"/>
+      <c r="I50" s="56"/>
+      <c r="J50" s="57"/>
       <c r="K50" s="13"/>
       <c r="L50" s="13"/>
       <c r="M50" s="13"/>
     </row>
     <row r="51" spans="1:13" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="13"/>
-      <c r="B51" s="52" t="s">
+      <c r="B51" s="51" t="s">
         <v>53</v>
       </c>
-      <c r="C51" s="53"/>
-      <c r="D51" s="54"/>
-      <c r="E51" s="55"/>
-      <c r="F51" s="54"/>
-      <c r="G51" s="55"/>
-      <c r="H51" s="56"/>
-      <c r="I51" s="57"/>
-      <c r="J51" s="58"/>
+      <c r="C51" s="52"/>
+      <c r="D51" s="53"/>
+      <c r="E51" s="54"/>
+      <c r="F51" s="53"/>
+      <c r="G51" s="54"/>
+      <c r="H51" s="55"/>
+      <c r="I51" s="56"/>
+      <c r="J51" s="57"/>
       <c r="K51" s="13"/>
       <c r="L51" s="13"/>
       <c r="M51" s="13"/>
     </row>
     <row r="52" spans="1:13" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="13"/>
-      <c r="B52" s="59" t="s">
+      <c r="B52" s="58" t="s">
         <v>64</v>
       </c>
-      <c r="C52" s="60"/>
-      <c r="D52" s="93"/>
-      <c r="E52" s="94"/>
-      <c r="F52" s="93"/>
-      <c r="G52" s="94"/>
-      <c r="H52" s="56"/>
-      <c r="I52" s="57"/>
-      <c r="J52" s="58"/>
+      <c r="C52" s="59"/>
+      <c r="D52" s="92"/>
+      <c r="E52" s="93"/>
+      <c r="F52" s="92"/>
+      <c r="G52" s="93"/>
+      <c r="H52" s="55"/>
+      <c r="I52" s="56"/>
+      <c r="J52" s="57"/>
       <c r="K52" s="13"/>
       <c r="L52" s="13"/>
       <c r="M52" s="13"/>
     </row>
     <row r="53" spans="1:13" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="13"/>
-      <c r="B53" s="52" t="s">
+      <c r="B53" s="51" t="s">
         <v>54</v>
       </c>
-      <c r="C53" s="53"/>
-      <c r="D53" s="54"/>
-      <c r="E53" s="55"/>
-      <c r="F53" s="54"/>
-      <c r="G53" s="55"/>
-      <c r="H53" s="56"/>
-      <c r="I53" s="57"/>
-      <c r="J53" s="58"/>
+      <c r="C53" s="52"/>
+      <c r="D53" s="53"/>
+      <c r="E53" s="54"/>
+      <c r="F53" s="53"/>
+      <c r="G53" s="54"/>
+      <c r="H53" s="55"/>
+      <c r="I53" s="56"/>
+      <c r="J53" s="57"/>
       <c r="K53" s="13"/>
       <c r="L53" s="13"/>
       <c r="M53" s="13"/>
     </row>
     <row r="54" spans="1:13" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="13"/>
-      <c r="B54" s="52" t="s">
+      <c r="B54" s="51" t="s">
         <v>55</v>
       </c>
-      <c r="C54" s="53"/>
-      <c r="D54" s="54"/>
-      <c r="E54" s="55"/>
-      <c r="F54" s="54"/>
-      <c r="G54" s="55"/>
-      <c r="H54" s="56"/>
-      <c r="I54" s="57"/>
-      <c r="J54" s="58"/>
+      <c r="C54" s="52"/>
+      <c r="D54" s="53"/>
+      <c r="E54" s="54"/>
+      <c r="F54" s="53"/>
+      <c r="G54" s="54"/>
+      <c r="H54" s="55"/>
+      <c r="I54" s="56"/>
+      <c r="J54" s="57"/>
       <c r="K54" s="13"/>
       <c r="L54" s="13"/>
       <c r="M54" s="13"/>
     </row>
     <row r="55" spans="1:13" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A55" s="13"/>
-      <c r="B55" s="52" t="s">
+      <c r="B55" s="51" t="s">
         <v>56</v>
       </c>
-      <c r="C55" s="53"/>
-      <c r="D55" s="54"/>
-      <c r="E55" s="55"/>
-      <c r="F55" s="54"/>
-      <c r="G55" s="55"/>
-      <c r="H55" s="56"/>
-      <c r="I55" s="57"/>
-      <c r="J55" s="58"/>
+      <c r="C55" s="52"/>
+      <c r="D55" s="53"/>
+      <c r="E55" s="54"/>
+      <c r="F55" s="53"/>
+      <c r="G55" s="54"/>
+      <c r="H55" s="55"/>
+      <c r="I55" s="56"/>
+      <c r="J55" s="57"/>
       <c r="K55" s="13"/>
       <c r="L55" s="13"/>
       <c r="M55" s="13"/>
     </row>
     <row r="56" spans="1:13" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A56" s="13"/>
-      <c r="B56" s="61" t="s">
+      <c r="B56" s="60" t="s">
         <v>57</v>
       </c>
-      <c r="C56" s="62"/>
-      <c r="D56" s="63"/>
-      <c r="E56" s="64"/>
-      <c r="F56" s="63"/>
-      <c r="G56" s="64"/>
-      <c r="H56" s="56"/>
-      <c r="I56" s="57"/>
-      <c r="J56" s="58"/>
+      <c r="C56" s="61"/>
+      <c r="D56" s="62"/>
+      <c r="E56" s="63"/>
+      <c r="F56" s="62"/>
+      <c r="G56" s="63"/>
+      <c r="H56" s="55"/>
+      <c r="I56" s="56"/>
+      <c r="J56" s="57"/>
       <c r="K56" s="13"/>
       <c r="L56" s="13"/>
       <c r="M56" s="13"/>
     </row>
     <row r="57" spans="1:13" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57" s="13"/>
-      <c r="B57" s="90" t="s">
+      <c r="B57" s="89" t="s">
         <v>58</v>
       </c>
-      <c r="C57" s="91"/>
-      <c r="D57" s="91"/>
-      <c r="E57" s="91"/>
-      <c r="F57" s="91"/>
-      <c r="G57" s="91"/>
-      <c r="H57" s="91"/>
-      <c r="I57" s="91"/>
-      <c r="J57" s="92"/>
+      <c r="C57" s="90"/>
+      <c r="D57" s="90"/>
+      <c r="E57" s="90"/>
+      <c r="F57" s="90"/>
+      <c r="G57" s="90"/>
+      <c r="H57" s="90"/>
+      <c r="I57" s="90"/>
+      <c r="J57" s="91"/>
       <c r="K57" s="13"/>
       <c r="L57" s="13"/>
       <c r="M57" s="13"/>
     </row>
     <row r="58" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A58" s="13"/>
-      <c r="B58" s="72" t="s">
+      <c r="B58" s="71" t="s">
         <v>46</v>
       </c>
-      <c r="C58" s="74"/>
-      <c r="D58" s="44" t="s">
+      <c r="C58" s="73"/>
+      <c r="D58" s="43" t="s">
         <v>47</v>
       </c>
-      <c r="E58" s="45"/>
-      <c r="F58" s="45"/>
-      <c r="G58" s="46"/>
-      <c r="H58" s="72" t="s">
+      <c r="E58" s="44"/>
+      <c r="F58" s="44"/>
+      <c r="G58" s="45"/>
+      <c r="H58" s="71" t="s">
         <v>48</v>
       </c>
-      <c r="I58" s="73"/>
-      <c r="J58" s="74"/>
+      <c r="I58" s="72"/>
+      <c r="J58" s="73"/>
       <c r="K58" s="13"/>
       <c r="L58" s="13"/>
       <c r="M58" s="13"/>
     </row>
     <row r="59" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A59" s="13"/>
-      <c r="B59" s="75"/>
-      <c r="C59" s="77"/>
-      <c r="D59" s="88" t="s">
+      <c r="B59" s="74"/>
+      <c r="C59" s="76"/>
+      <c r="D59" s="87" t="s">
         <v>49</v>
       </c>
-      <c r="E59" s="89"/>
-      <c r="F59" s="88" t="s">
+      <c r="E59" s="88"/>
+      <c r="F59" s="87" t="s">
         <v>50</v>
       </c>
-      <c r="G59" s="89"/>
-      <c r="H59" s="75"/>
-      <c r="I59" s="76"/>
-      <c r="J59" s="77"/>
+      <c r="G59" s="88"/>
+      <c r="H59" s="74"/>
+      <c r="I59" s="75"/>
+      <c r="J59" s="76"/>
       <c r="K59" s="13"/>
       <c r="L59" s="13"/>
       <c r="M59" s="13"/>
     </row>
     <row r="60" spans="1:13" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A60" s="13"/>
-      <c r="B60" s="52" t="s">
+      <c r="B60" s="51" t="s">
         <v>59</v>
       </c>
-      <c r="C60" s="53"/>
-      <c r="D60" s="54"/>
-      <c r="E60" s="55"/>
-      <c r="F60" s="54"/>
-      <c r="G60" s="55"/>
-      <c r="H60" s="56"/>
-      <c r="I60" s="57"/>
-      <c r="J60" s="58"/>
+      <c r="C60" s="52"/>
+      <c r="D60" s="53"/>
+      <c r="E60" s="54"/>
+      <c r="F60" s="53"/>
+      <c r="G60" s="54"/>
+      <c r="H60" s="55"/>
+      <c r="I60" s="56"/>
+      <c r="J60" s="57"/>
       <c r="K60" s="13"/>
       <c r="L60" s="13"/>
       <c r="M60" s="13"/>
     </row>
     <row r="61" spans="1:13" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A61" s="13"/>
-      <c r="B61" s="52" t="s">
+      <c r="B61" s="51" t="s">
         <v>60</v>
       </c>
-      <c r="C61" s="53"/>
-      <c r="D61" s="54"/>
-      <c r="E61" s="55"/>
-      <c r="F61" s="54"/>
-      <c r="G61" s="55"/>
-      <c r="H61" s="56"/>
-      <c r="I61" s="57"/>
-      <c r="J61" s="58"/>
+      <c r="C61" s="52"/>
+      <c r="D61" s="53"/>
+      <c r="E61" s="54"/>
+      <c r="F61" s="53"/>
+      <c r="G61" s="54"/>
+      <c r="H61" s="55"/>
+      <c r="I61" s="56"/>
+      <c r="J61" s="57"/>
       <c r="K61" s="13"/>
       <c r="L61" s="13"/>
       <c r="M61" s="13"/>
     </row>
     <row r="62" spans="1:13" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A62" s="13"/>
-      <c r="B62" s="52" t="s">
+      <c r="B62" s="51" t="s">
         <v>61</v>
       </c>
-      <c r="C62" s="53"/>
-      <c r="D62" s="54"/>
-      <c r="E62" s="55"/>
-      <c r="F62" s="54"/>
-      <c r="G62" s="55"/>
-      <c r="H62" s="56"/>
-      <c r="I62" s="57"/>
-      <c r="J62" s="58"/>
+      <c r="C62" s="52"/>
+      <c r="D62" s="53"/>
+      <c r="E62" s="54"/>
+      <c r="F62" s="53"/>
+      <c r="G62" s="54"/>
+      <c r="H62" s="55"/>
+      <c r="I62" s="56"/>
+      <c r="J62" s="57"/>
       <c r="K62" s="13"/>
       <c r="L62" s="13"/>
       <c r="M62" s="13"/>
     </row>
     <row r="63" spans="1:13" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A63" s="13"/>
-      <c r="B63" s="52" t="s">
+      <c r="B63" s="51" t="s">
         <v>62</v>
       </c>
-      <c r="C63" s="53"/>
-      <c r="D63" s="54"/>
-      <c r="E63" s="55"/>
-      <c r="F63" s="54"/>
-      <c r="G63" s="55"/>
-      <c r="H63" s="56"/>
-      <c r="I63" s="57"/>
-      <c r="J63" s="58"/>
+      <c r="C63" s="52"/>
+      <c r="D63" s="53"/>
+      <c r="E63" s="54"/>
+      <c r="F63" s="53"/>
+      <c r="G63" s="54"/>
+      <c r="H63" s="55"/>
+      <c r="I63" s="56"/>
+      <c r="J63" s="57"/>
       <c r="K63" s="13"/>
       <c r="L63" s="13"/>
       <c r="M63" s="13"/>
     </row>
     <row r="64" spans="1:13" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A64" s="13"/>
-      <c r="B64" s="52" t="s">
+      <c r="B64" s="51" t="s">
         <v>63</v>
       </c>
-      <c r="C64" s="53"/>
-      <c r="D64" s="54"/>
-      <c r="E64" s="55"/>
-      <c r="F64" s="54"/>
-      <c r="G64" s="55"/>
-      <c r="H64" s="56"/>
-      <c r="I64" s="57"/>
-      <c r="J64" s="58"/>
+      <c r="C64" s="52"/>
+      <c r="D64" s="53"/>
+      <c r="E64" s="54"/>
+      <c r="F64" s="53"/>
+      <c r="G64" s="54"/>
+      <c r="H64" s="55"/>
+      <c r="I64" s="56"/>
+      <c r="J64" s="57"/>
       <c r="K64" s="13"/>
       <c r="L64" s="13"/>
       <c r="M64" s="13"/>
@@ -3034,51 +3038,51 @@
     </row>
     <row r="66" spans="1:13" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A66" s="13"/>
-      <c r="B66" s="44" t="s">
+      <c r="B66" s="43" t="s">
         <v>67</v>
       </c>
-      <c r="C66" s="45"/>
-      <c r="D66" s="45"/>
-      <c r="E66" s="45"/>
-      <c r="F66" s="45"/>
-      <c r="G66" s="45"/>
-      <c r="H66" s="45"/>
-      <c r="I66" s="45"/>
-      <c r="J66" s="46"/>
+      <c r="C66" s="44"/>
+      <c r="D66" s="44"/>
+      <c r="E66" s="44"/>
+      <c r="F66" s="44"/>
+      <c r="G66" s="44"/>
+      <c r="H66" s="44"/>
+      <c r="I66" s="44"/>
+      <c r="J66" s="45"/>
       <c r="K66" s="13"/>
       <c r="L66" s="13"/>
       <c r="M66" s="13"/>
     </row>
     <row r="67" spans="1:13" ht="72" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A67" s="13"/>
-      <c r="B67" s="47" t="s">
+      <c r="B67" s="46" t="s">
         <v>68</v>
       </c>
-      <c r="C67" s="48"/>
-      <c r="D67" s="49"/>
-      <c r="E67" s="50"/>
-      <c r="F67" s="50"/>
-      <c r="G67" s="50"/>
-      <c r="H67" s="50"/>
-      <c r="I67" s="50"/>
-      <c r="J67" s="51"/>
+      <c r="C67" s="47"/>
+      <c r="D67" s="48"/>
+      <c r="E67" s="49"/>
+      <c r="F67" s="49"/>
+      <c r="G67" s="49"/>
+      <c r="H67" s="49"/>
+      <c r="I67" s="49"/>
+      <c r="J67" s="50"/>
       <c r="K67" s="13"/>
       <c r="L67" s="13"/>
       <c r="M67" s="13"/>
     </row>
     <row r="68" spans="1:13" ht="72" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A68" s="13"/>
-      <c r="B68" s="47" t="s">
+      <c r="B68" s="46" t="s">
         <v>69</v>
       </c>
-      <c r="C68" s="48"/>
-      <c r="D68" s="49"/>
-      <c r="E68" s="50"/>
-      <c r="F68" s="50"/>
-      <c r="G68" s="50"/>
-      <c r="H68" s="50"/>
-      <c r="I68" s="50"/>
-      <c r="J68" s="51"/>
+      <c r="C68" s="47"/>
+      <c r="D68" s="48"/>
+      <c r="E68" s="49"/>
+      <c r="F68" s="49"/>
+      <c r="G68" s="49"/>
+      <c r="H68" s="49"/>
+      <c r="I68" s="49"/>
+      <c r="J68" s="50"/>
       <c r="K68" s="13"/>
       <c r="L68" s="13"/>
       <c r="M68" s="13"/>
@@ -3100,51 +3104,51 @@
     </row>
     <row r="70" spans="1:13" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A70" s="13"/>
-      <c r="B70" s="44" t="s">
+      <c r="B70" s="43" t="s">
         <v>70</v>
       </c>
-      <c r="C70" s="45"/>
-      <c r="D70" s="45"/>
-      <c r="E70" s="45"/>
-      <c r="F70" s="45"/>
-      <c r="G70" s="45"/>
-      <c r="H70" s="45"/>
-      <c r="I70" s="45"/>
-      <c r="J70" s="46"/>
+      <c r="C70" s="44"/>
+      <c r="D70" s="44"/>
+      <c r="E70" s="44"/>
+      <c r="F70" s="44"/>
+      <c r="G70" s="44"/>
+      <c r="H70" s="44"/>
+      <c r="I70" s="44"/>
+      <c r="J70" s="45"/>
       <c r="K70" s="13"/>
       <c r="L70" s="13"/>
       <c r="M70" s="13"/>
     </row>
     <row r="71" spans="1:13" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A71" s="13"/>
-      <c r="B71" s="47" t="s">
+      <c r="B71" s="46" t="s">
         <v>68</v>
       </c>
-      <c r="C71" s="48"/>
-      <c r="D71" s="49"/>
-      <c r="E71" s="50"/>
-      <c r="F71" s="50"/>
-      <c r="G71" s="50"/>
-      <c r="H71" s="50"/>
-      <c r="I71" s="50"/>
-      <c r="J71" s="51"/>
+      <c r="C71" s="47"/>
+      <c r="D71" s="48"/>
+      <c r="E71" s="49"/>
+      <c r="F71" s="49"/>
+      <c r="G71" s="49"/>
+      <c r="H71" s="49"/>
+      <c r="I71" s="49"/>
+      <c r="J71" s="50"/>
       <c r="K71" s="13"/>
       <c r="L71" s="13"/>
       <c r="M71" s="13"/>
     </row>
     <row r="72" spans="1:13" ht="72" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A72" s="13"/>
-      <c r="B72" s="47" t="s">
+      <c r="B72" s="46" t="s">
         <v>69</v>
       </c>
-      <c r="C72" s="48"/>
-      <c r="D72" s="49"/>
-      <c r="E72" s="50"/>
-      <c r="F72" s="50"/>
-      <c r="G72" s="50"/>
-      <c r="H72" s="50"/>
-      <c r="I72" s="50"/>
-      <c r="J72" s="51"/>
+      <c r="C72" s="47"/>
+      <c r="D72" s="48"/>
+      <c r="E72" s="49"/>
+      <c r="F72" s="49"/>
+      <c r="G72" s="49"/>
+      <c r="H72" s="49"/>
+      <c r="I72" s="49"/>
+      <c r="J72" s="50"/>
       <c r="K72" s="13"/>
       <c r="L72" s="13"/>
       <c r="M72" s="13"/>
@@ -3166,51 +3170,51 @@
     </row>
     <row r="74" spans="1:13" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A74" s="13"/>
-      <c r="B74" s="44" t="s">
+      <c r="B74" s="43" t="s">
         <v>71</v>
       </c>
-      <c r="C74" s="45"/>
-      <c r="D74" s="45"/>
-      <c r="E74" s="45"/>
-      <c r="F74" s="45"/>
-      <c r="G74" s="45"/>
-      <c r="H74" s="45"/>
-      <c r="I74" s="45"/>
-      <c r="J74" s="46"/>
+      <c r="C74" s="44"/>
+      <c r="D74" s="44"/>
+      <c r="E74" s="44"/>
+      <c r="F74" s="44"/>
+      <c r="G74" s="44"/>
+      <c r="H74" s="44"/>
+      <c r="I74" s="44"/>
+      <c r="J74" s="45"/>
       <c r="K74" s="13"/>
       <c r="L74" s="13"/>
       <c r="M74" s="13"/>
     </row>
     <row r="75" spans="1:13" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A75" s="13"/>
-      <c r="B75" s="47" t="s">
+      <c r="B75" s="46" t="s">
         <v>68</v>
       </c>
-      <c r="C75" s="48"/>
-      <c r="D75" s="49"/>
-      <c r="E75" s="50"/>
-      <c r="F75" s="50"/>
-      <c r="G75" s="50"/>
-      <c r="H75" s="50"/>
-      <c r="I75" s="50"/>
-      <c r="J75" s="51"/>
+      <c r="C75" s="47"/>
+      <c r="D75" s="48"/>
+      <c r="E75" s="49"/>
+      <c r="F75" s="49"/>
+      <c r="G75" s="49"/>
+      <c r="H75" s="49"/>
+      <c r="I75" s="49"/>
+      <c r="J75" s="50"/>
       <c r="K75" s="13"/>
       <c r="L75" s="13"/>
       <c r="M75" s="13"/>
     </row>
     <row r="76" spans="1:13" ht="71.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A76" s="13"/>
-      <c r="B76" s="47" t="s">
+      <c r="B76" s="46" t="s">
         <v>69</v>
       </c>
-      <c r="C76" s="48"/>
-      <c r="D76" s="49"/>
-      <c r="E76" s="50"/>
-      <c r="F76" s="50"/>
-      <c r="G76" s="50"/>
-      <c r="H76" s="50"/>
-      <c r="I76" s="50"/>
-      <c r="J76" s="51"/>
+      <c r="C76" s="47"/>
+      <c r="D76" s="48"/>
+      <c r="E76" s="49"/>
+      <c r="F76" s="49"/>
+      <c r="G76" s="49"/>
+      <c r="H76" s="49"/>
+      <c r="I76" s="49"/>
+      <c r="J76" s="50"/>
       <c r="K76" s="13"/>
       <c r="L76" s="13"/>
       <c r="M76" s="13"/>
@@ -3233,19 +3237,19 @@
     <row r="78" spans="1:13" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="11"/>
       <c r="B78" s="12"/>
-      <c r="C78" s="165" t="s">
+      <c r="C78" s="161" t="s">
         <v>99</v>
       </c>
-      <c r="D78" s="166"/>
-      <c r="E78" s="166"/>
-      <c r="F78" s="166"/>
-      <c r="G78" s="28" t="s">
+      <c r="D78" s="162"/>
+      <c r="E78" s="162"/>
+      <c r="F78" s="162"/>
+      <c r="G78" s="26" t="s">
         <v>98</v>
       </c>
-      <c r="H78" s="167" t="s">
+      <c r="H78" s="29" t="s">
         <v>100</v>
       </c>
-      <c r="I78" s="28" t="s">
+      <c r="I78" s="26" t="s">
         <v>97</v>
       </c>
       <c r="J78" s="12"/>
@@ -3254,96 +3258,96 @@
       <c r="M78" s="11"/>
     </row>
     <row r="79" spans="1:13" ht="48.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="150"/>
-      <c r="B79" s="150"/>
-      <c r="C79" s="150"/>
-      <c r="D79" s="150"/>
-      <c r="E79" s="148"/>
-      <c r="F79" s="148"/>
-      <c r="G79" s="150"/>
-      <c r="H79" s="150"/>
-      <c r="I79" s="148"/>
-      <c r="J79" s="148"/>
-      <c r="K79" s="150"/>
-      <c r="L79" s="150"/>
-      <c r="M79" s="150"/>
+      <c r="A79" s="146"/>
+      <c r="B79" s="146"/>
+      <c r="C79" s="146"/>
+      <c r="D79" s="146"/>
+      <c r="E79" s="144"/>
+      <c r="F79" s="144"/>
+      <c r="G79" s="146"/>
+      <c r="H79" s="146"/>
+      <c r="I79" s="144"/>
+      <c r="J79" s="144"/>
+      <c r="K79" s="146"/>
+      <c r="L79" s="146"/>
+      <c r="M79" s="146"/>
     </row>
     <row r="80" spans="1:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="150"/>
-      <c r="B80" s="150"/>
-      <c r="C80" s="150"/>
-      <c r="D80" s="150"/>
-      <c r="E80" s="148"/>
-      <c r="F80" s="148"/>
-      <c r="G80" s="150"/>
-      <c r="H80" s="150"/>
-      <c r="I80" s="148"/>
-      <c r="J80" s="148"/>
-      <c r="K80" s="150"/>
-      <c r="L80" s="150"/>
-      <c r="M80" s="150"/>
+      <c r="A80" s="146"/>
+      <c r="B80" s="146"/>
+      <c r="C80" s="146"/>
+      <c r="D80" s="146"/>
+      <c r="E80" s="144"/>
+      <c r="F80" s="144"/>
+      <c r="G80" s="146"/>
+      <c r="H80" s="146"/>
+      <c r="I80" s="144"/>
+      <c r="J80" s="144"/>
+      <c r="K80" s="146"/>
+      <c r="L80" s="146"/>
+      <c r="M80" s="146"/>
     </row>
     <row r="81" spans="1:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="150"/>
-      <c r="B81" s="150"/>
-      <c r="C81" s="150"/>
-      <c r="D81" s="150"/>
-      <c r="E81" s="148"/>
-      <c r="F81" s="148"/>
-      <c r="G81" s="150"/>
-      <c r="H81" s="150"/>
-      <c r="I81" s="148"/>
-      <c r="J81" s="148"/>
-      <c r="K81" s="150"/>
-      <c r="L81" s="150"/>
-      <c r="M81" s="150"/>
+      <c r="A81" s="146"/>
+      <c r="B81" s="146"/>
+      <c r="C81" s="146"/>
+      <c r="D81" s="146"/>
+      <c r="E81" s="144"/>
+      <c r="F81" s="144"/>
+      <c r="G81" s="146"/>
+      <c r="H81" s="146"/>
+      <c r="I81" s="144"/>
+      <c r="J81" s="144"/>
+      <c r="K81" s="146"/>
+      <c r="L81" s="146"/>
+      <c r="M81" s="146"/>
     </row>
     <row r="82" spans="1:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="150"/>
-      <c r="B82" s="150"/>
-      <c r="C82" s="150"/>
-      <c r="D82" s="150"/>
-      <c r="E82" s="148"/>
-      <c r="F82" s="148"/>
-      <c r="G82" s="150"/>
-      <c r="H82" s="150"/>
-      <c r="I82" s="148"/>
-      <c r="J82" s="148"/>
-      <c r="K82" s="150"/>
-      <c r="L82" s="150"/>
-      <c r="M82" s="150"/>
+      <c r="A82" s="146"/>
+      <c r="B82" s="146"/>
+      <c r="C82" s="146"/>
+      <c r="D82" s="146"/>
+      <c r="E82" s="144"/>
+      <c r="F82" s="144"/>
+      <c r="G82" s="146"/>
+      <c r="H82" s="146"/>
+      <c r="I82" s="144"/>
+      <c r="J82" s="144"/>
+      <c r="K82" s="146"/>
+      <c r="L82" s="146"/>
+      <c r="M82" s="146"/>
     </row>
     <row r="83" spans="1:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="151"/>
-      <c r="B83" s="151"/>
-      <c r="C83" s="151"/>
-      <c r="D83" s="151"/>
-      <c r="E83" s="148"/>
-      <c r="F83" s="148"/>
-      <c r="G83" s="151"/>
-      <c r="H83" s="151"/>
-      <c r="I83" s="148"/>
-      <c r="J83" s="148"/>
-      <c r="K83" s="151"/>
-      <c r="L83" s="151"/>
-      <c r="M83" s="151"/>
+      <c r="A83" s="147"/>
+      <c r="B83" s="147"/>
+      <c r="C83" s="147"/>
+      <c r="D83" s="147"/>
+      <c r="E83" s="144"/>
+      <c r="F83" s="144"/>
+      <c r="G83" s="147"/>
+      <c r="H83" s="147"/>
+      <c r="I83" s="144"/>
+      <c r="J83" s="144"/>
+      <c r="K83" s="147"/>
+      <c r="L83" s="147"/>
+      <c r="M83" s="147"/>
     </row>
     <row r="84" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="147"/>
-      <c r="B84" s="147"/>
-      <c r="C84" s="147"/>
-      <c r="D84" s="147"/>
-      <c r="E84" s="148"/>
-      <c r="F84" s="148"/>
-      <c r="G84" s="149" t="s">
+      <c r="A84" s="143"/>
+      <c r="B84" s="143"/>
+      <c r="C84" s="143"/>
+      <c r="D84" s="143"/>
+      <c r="E84" s="144"/>
+      <c r="F84" s="144"/>
+      <c r="G84" s="145" t="s">
         <v>27</v>
       </c>
-      <c r="H84" s="149"/>
-      <c r="I84" s="148"/>
-      <c r="J84" s="148"/>
-      <c r="K84" s="147"/>
-      <c r="L84" s="147"/>
-      <c r="M84" s="147"/>
+      <c r="H84" s="145"/>
+      <c r="I84" s="144"/>
+      <c r="J84" s="144"/>
+      <c r="K84" s="143"/>
+      <c r="L84" s="143"/>
+      <c r="M84" s="143"/>
     </row>
     <row r="85" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A85" s="12"/>
@@ -3361,25 +3365,25 @@
       <c r="M85" s="12"/>
     </row>
     <row r="86" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A86" s="22"/>
-      <c r="B86" s="43"/>
-      <c r="C86" s="43"/>
-      <c r="D86" s="43"/>
-      <c r="E86" s="43"/>
-      <c r="F86" s="43"/>
-      <c r="G86" s="43"/>
-      <c r="H86" s="43"/>
-      <c r="I86" s="43"/>
-      <c r="J86" s="43"/>
-      <c r="K86" s="22"/>
-      <c r="L86" s="22"/>
-      <c r="M86" s="22"/>
+      <c r="A86" s="20"/>
+      <c r="B86" s="42"/>
+      <c r="C86" s="42"/>
+      <c r="D86" s="42"/>
+      <c r="E86" s="42"/>
+      <c r="F86" s="42"/>
+      <c r="G86" s="42"/>
+      <c r="H86" s="42"/>
+      <c r="I86" s="42"/>
+      <c r="J86" s="42"/>
+      <c r="K86" s="20"/>
+      <c r="L86" s="20"/>
+      <c r="M86" s="20"/>
     </row>
     <row r="87" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="F87" s="35" t="s">
+      <c r="F87" s="34" t="s">
         <v>44</v>
       </c>
-      <c r="G87" s="35"/>
+      <c r="G87" s="34"/>
     </row>
     <row r="88" spans="1:13" x14ac:dyDescent="0.25"/>
   </sheetData>
@@ -3666,7 +3670,7 @@
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="SIEMPRE DEBE HABER OBSERVACIONES" prompt="SIEMPRE DEBE HABER OBSERVACIONES, COMO FUE EL PROCESO, Si hay factores por mejorar favor escribir las observaciones o los compromisos de mejora" sqref="H60:J60" xr:uid="{32775E1C-D08B-4F67-8718-8BE41F674436}"/>
   </dataValidations>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="5" scale="68" fitToHeight="0" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="5" scale="43" fitToWidth="0" orientation="portrait" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xWindow="756" yWindow="874" count="2">
@@ -3698,64 +3702,64 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="22" t="s">
         <v>85</v>
       </c>
-      <c r="B1" s="25" t="s">
+      <c r="B1" s="23" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="90" x14ac:dyDescent="0.25">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="21" t="s">
         <v>88</v>
       </c>
-      <c r="B2" s="27" t="s">
+      <c r="B2" s="25" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="90" x14ac:dyDescent="0.25">
-      <c r="A3" s="23" t="s">
+      <c r="A3" s="21" t="s">
         <v>87</v>
       </c>
-      <c r="B3" s="26" t="s">
+      <c r="B3" s="24" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="90" x14ac:dyDescent="0.25">
-      <c r="A4" s="23" t="s">
+      <c r="A4" s="21" t="s">
         <v>91</v>
       </c>
-      <c r="B4" s="26" t="s">
+      <c r="B4" s="24" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="75" x14ac:dyDescent="0.25">
-      <c r="A5" s="23" t="s">
+      <c r="A5" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="B5" s="26" t="s">
+      <c r="B5" s="24" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="75" x14ac:dyDescent="0.25">
-      <c r="A6" s="23" t="s">
+      <c r="A6" s="21" t="s">
         <v>90</v>
       </c>
-      <c r="B6" s="26" t="s">
+      <c r="B6" s="24" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="23"/>
+      <c r="A7" s="21"/>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="23"/>
+      <c r="A8" s="21"/>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="23"/>
+      <c r="A9" s="21"/>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="23"/>
+      <c r="A10" s="21"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
